--- a/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I223"/>
+  <dimension ref="A1:I226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4756,8 +4756,10 @@
           <t>м</t>
         </is>
       </c>
-      <c r="G144" s="1" t="n">
-        <v>3</v>
+      <c r="G144" s="1" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
       </c>
       <c r="H144" s="1" t="inlineStr"/>
       <c r="I144" s="1" t="inlineStr">
@@ -4810,13 +4812,15 @@
           <t>м</t>
         </is>
       </c>
-      <c r="G146" s="1" t="n">
-        <v>18</v>
+      <c r="G146" s="1" t="inlineStr">
+        <is>
+          <t>24,8</t>
+        </is>
       </c>
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr">
         <is>
-          <t>П1</t>
+          <t>П1 — 18 м; ВЗ (кухонный зонт) — 6,8 м</t>
         </is>
       </c>
     </row>
@@ -4911,10 +4915,14 @@
         </is>
       </c>
       <c r="G150" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H150" s="1" t="inlineStr"/>
-      <c r="I150" s="1" t="inlineStr"/>
+      <c r="I150" s="1" t="inlineStr">
+        <is>
+          <t>ВЗ (кухонный зонт)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -4957,10 +4965,14 @@
         </is>
       </c>
       <c r="G152" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H152" s="1" t="inlineStr"/>
-      <c r="I152" s="1" t="inlineStr"/>
+      <c r="I152" s="1" t="inlineStr">
+        <is>
+          <t>в т. ч. ВЗ (кухонный зонт) — 1</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -5244,7 +5256,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø200/Ø160</t>
+          <t>Переход круглый оцинкованный Ø200/Ø150</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr"/>
@@ -5256,10 +5268,14 @@
         </is>
       </c>
       <c r="G165" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H165" s="1" t="inlineStr"/>
-      <c r="I165" s="1" t="inlineStr"/>
+      <c r="I165" s="1" t="inlineStr">
+        <is>
+          <t>ВЗ (кухонный зонт)</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -5267,7 +5283,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø250/Ø160</t>
+          <t>Переход круглый оцинкованный Ø200/Ø160</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr"/>
@@ -5279,7 +5295,7 @@
         </is>
       </c>
       <c r="G166" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H166" s="1" t="inlineStr"/>
       <c r="I166" s="1" t="inlineStr"/>
@@ -5290,7 +5306,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø250/Ø200</t>
+          <t>Переход круглый оцинкованный Ø250/Ø160</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr"/>
@@ -5313,14 +5329,10 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Регулятор расхода воздуха (ирисовый клапан) Ø100</t>
-        </is>
-      </c>
-      <c r="C168" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Переход круглый оцинкованный Ø250/Ø200</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="inlineStr"/>
       <c r="D168" s="1" t="inlineStr"/>
       <c r="E168" s="1" t="inlineStr"/>
       <c r="F168" s="1" t="inlineStr">
@@ -5329,14 +5341,10 @@
         </is>
       </c>
       <c r="G168" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H168" s="1" t="inlineStr"/>
-      <c r="I168" s="1" t="inlineStr">
-        <is>
-          <t>РР, на ответвлениях</t>
-        </is>
-      </c>
+      <c r="I168" s="1" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -5344,7 +5352,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Регулятор расхода воздуха (ирисовый клапан) Ø125</t>
+          <t>Регулятор расхода воздуха (ирисовый клапан) Ø100</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -5360,7 +5368,7 @@
         </is>
       </c>
       <c r="G169" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H169" s="1" t="inlineStr"/>
       <c r="I169" s="1" t="inlineStr">
@@ -5375,7 +5383,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Регулятор расхода воздуха (ирисовый клапан) Ø160</t>
+          <t>Регулятор расхода воздуха (ирисовый клапан) Ø125</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -5391,7 +5399,7 @@
         </is>
       </c>
       <c r="G170" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H170" s="1" t="inlineStr"/>
       <c r="I170" s="1" t="inlineStr">
@@ -5406,7 +5414,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Диффузор щелевой (линейный) приточный в торце подшивки, L=600 мм, с камерой статического давления, присоединение Ø125, расход 70 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Регулятор расхода воздуха (ирисовый клапан) Ø160</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -5422,12 +5430,12 @@
         </is>
       </c>
       <c r="G171" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H171" s="1" t="inlineStr"/>
       <c r="I171" s="1" t="inlineStr">
         <is>
-          <t>1.10 — 3 шт.</t>
+          <t>РР, на ответвлениях</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5445,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Диффузор потолочный приточный с камерой статического давления, присоединение Ø100, расход 30/60 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Диффузор щелевой (линейный) приточный в торце подшивки, L=600 мм, с камерой статического давления, присоединение Ø125, расход 70 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -5458,7 +5466,7 @@
       <c r="H172" s="1" t="inlineStr"/>
       <c r="I172" s="1" t="inlineStr">
         <is>
-          <t>1.11 — 2 шт., 2.2</t>
+          <t>1.10 — 3 шт.</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5476,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Решётка приточная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Диффузор потолочный приточный с камерой статического давления, присоединение Ø100, расход 30/60 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -5484,12 +5492,12 @@
         </is>
       </c>
       <c r="G173" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H173" s="1" t="inlineStr"/>
       <c r="I173" s="1" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.11 — 2 шт., 2.2</t>
         </is>
       </c>
     </row>
@@ -5499,7 +5507,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø100, расход 40/50/60 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка приточная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -5515,12 +5523,12 @@
         </is>
       </c>
       <c r="G174" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H174" s="1" t="inlineStr"/>
       <c r="I174" s="1" t="inlineStr">
         <is>
-          <t>1.4, 1.3, 2.6</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -5530,7 +5538,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø125, расход 75/90 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø100, расход 40/50/60 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -5551,7 +5559,7 @@
       <c r="H175" s="1" t="inlineStr"/>
       <c r="I175" s="1" t="inlineStr">
         <is>
-          <t>2.9, 2.8, 2.1</t>
+          <t>1.4, 1.3, 2.6</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5569,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø125, расход 75/90 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -5577,12 +5585,12 @@
         </is>
       </c>
       <c r="G176" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H176" s="1" t="inlineStr"/>
       <c r="I176" s="1" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.9, 2.8, 2.1</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5600,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø125, расход 90 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -5613,7 +5621,7 @@
       <c r="H177" s="1" t="inlineStr"/>
       <c r="I177" s="1" t="inlineStr">
         <is>
-          <t>1.10 (кухня)</t>
+          <t>1.8</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5631,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø160, расход 120 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø125, расход 90 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -5644,7 +5652,7 @@
       <c r="H178" s="1" t="inlineStr"/>
       <c r="I178" s="1" t="inlineStr">
         <is>
-          <t>1.10 (верх 2-го света)</t>
+          <t>1.10 (кухня)</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5662,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Решётка наружная воздухозаборная 500×400, низ +2,600</t>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø160, расход 120 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -5675,7 +5683,7 @@
       <c r="H179" s="1" t="inlineStr"/>
       <c r="I179" s="1" t="inlineStr">
         <is>
-          <t>Н1, восточная стена топочной</t>
+          <t>1.10 (верх 2-го света)</t>
         </is>
       </c>
     </row>
@@ -5685,7 +5693,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Оголовок (зонт) воздуховода Ø250 выше кровли</t>
+          <t>Решётка наружная воздухозаборная 500×400, низ +2,600</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -5701,12 +5709,12 @@
         </is>
       </c>
       <c r="G180" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H180" s="1" t="inlineStr"/>
       <c r="I180" s="1" t="inlineStr">
         <is>
-          <t>выброс П1, В2 (Ш-2)</t>
+          <t>Н1, восточная стена топочной</t>
         </is>
       </c>
     </row>
@@ -5716,7 +5724,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная под воздуховод Ø250 (вытяжка топочной, естественная)</t>
+          <t>Оголовок (зонт) воздуховода Ø250 выше кровли</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -5732,12 +5740,12 @@
         </is>
       </c>
       <c r="G181" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H181" s="1" t="inlineStr"/>
       <c r="I181" s="1" t="inlineStr">
         <is>
-          <t>В2, 188 м³/ч</t>
+          <t>выброс П1, В2 (Ш-2)</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5755,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Решётка переточная в низу наружной двери топочной, живое сечение не менее 0,08 м²</t>
+          <t>Оголовок (зонт) воздуховода Ø200 выше кровли</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -5768,7 +5776,7 @@
       <c r="H182" s="1" t="inlineStr"/>
       <c r="I182" s="1" t="inlineStr">
         <is>
-          <t>ПН, 282 м³/ч</t>
+          <t>ВЗ (кухонный зонт), шахта над мангалом 1.12</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5786,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Решётка вентиляционная наружная 400×200</t>
+          <t>Решётка вытяжная настенная под воздуховод Ø250 (вытяжка топочной, естественная)</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -5794,12 +5802,12 @@
         </is>
       </c>
       <c r="G183" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H183" s="1" t="inlineStr"/>
       <c r="I183" s="1" t="inlineStr">
         <is>
-          <t>гараж 1.5: приток внизу, вытяжка вверху</t>
+          <t>В2, 188 м³/ч</t>
         </is>
       </c>
     </row>
@@ -5809,10 +5817,14 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Зонт кухонный над плитой 500–600 м³/ч</t>
-        </is>
-      </c>
-      <c r="C184" s="1" t="inlineStr"/>
+          <t>Решётка переточная в низу наружной двери топочной, живое сечение не менее 0,08 м²</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D184" s="1" t="inlineStr"/>
       <c r="E184" s="1" t="inlineStr"/>
       <c r="F184" s="1" t="inlineStr">
@@ -5826,7 +5838,7 @@
       <c r="H184" s="1" t="inlineStr"/>
       <c r="I184" s="1" t="inlineStr">
         <is>
-          <t>ВЗ, поставка Заказчика</t>
+          <t>ПН, 282 м³/ч</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5848,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ø150 (выброс ВЗ)</t>
+          <t>Решётка вентиляционная наружная 400×200</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -5852,12 +5864,12 @@
         </is>
       </c>
       <c r="G185" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H185" s="1" t="inlineStr"/>
       <c r="I185" s="1" t="inlineStr">
         <is>
-          <t>ВЗ</t>
+          <t>гараж 1.5: приток внизу, вытяжка вверху</t>
         </is>
       </c>
     </row>
@@ -5867,14 +5879,10 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Решётка наружная выброса ВЗ под воздуховод Ø150</t>
-        </is>
-      </c>
-      <c r="C186" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Зонт кухонный над плитой 500–600 м³/ч, располагаемое давление не менее 200 Па при 600 м³/ч</t>
+        </is>
+      </c>
+      <c r="C186" s="1" t="inlineStr"/>
       <c r="D186" s="1" t="inlineStr"/>
       <c r="E186" s="1" t="inlineStr"/>
       <c r="F186" s="1" t="inlineStr">
@@ -5888,7 +5896,7 @@
       <c r="H186" s="1" t="inlineStr"/>
       <c r="I186" s="1" t="inlineStr">
         <is>
-          <t>ВЗ, место — с АР</t>
+          <t>ВЗ, поставка Заказчика</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5906,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Клапан компенсации Ø200 с электроприводом, сблокирован с ВЗ, в наружной стене с решёткой</t>
+          <t>Клапан обратный Ø150</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -5910,7 +5918,7 @@
       <c r="E187" s="1" t="inlineStr"/>
       <c r="F187" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G187" s="1" t="n">
@@ -5919,7 +5927,7 @@
       <c r="H187" s="1" t="inlineStr"/>
       <c r="I187" s="1" t="inlineStr">
         <is>
-          <t>КК</t>
+          <t>ВЗ, на патрубке зонта</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5937,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Теплоизоляция воздуховодов рулонная толщиной 25 мм с паробарьером (фольга), класс горючести — по СП 60</t>
+          <t>Гильза для прохода воздуховода Ø200 в изоляции через наружную стену (под отверстие Ø320)</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -5941,16 +5949,16 @@
       <c r="E188" s="1" t="inlineStr"/>
       <c r="F188" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G188" s="1" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H188" s="1" t="inlineStr"/>
       <c r="I188" s="1" t="inlineStr">
         <is>
-          <t>Н и выброс П1 Ø250</t>
+          <t>ВЗ, сквозь стену на +3,400</t>
         </is>
       </c>
     </row>
@@ -5960,10 +5968,14 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Крепления воздуховодов: подвесы, хомуты с уплотнителем, шпильки, профиль</t>
-        </is>
-      </c>
-      <c r="C189" s="1" t="inlineStr"/>
+          <t>Клапан компенсации Ø200 с электроприводом, сблокирован с ВЗ, в наружной стене с решёткой</t>
+        </is>
+      </c>
+      <c r="C189" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D189" s="1" t="inlineStr"/>
       <c r="E189" s="1" t="inlineStr"/>
       <c r="F189" s="1" t="inlineStr">
@@ -5977,74 +5989,84 @@
       <c r="H189" s="1" t="inlineStr"/>
       <c r="I189" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>КК</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="inlineStr"/>
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>6. Кондиционирование (листы 9–11, 14)</t>
-        </is>
-      </c>
-      <c r="C190" s="1" t="n"/>
-      <c r="D190" s="1" t="n"/>
-      <c r="E190" s="1" t="n"/>
-      <c r="F190" s="1" t="n"/>
-      <c r="G190" s="1" t="n"/>
-      <c r="H190" s="1" t="n"/>
-      <c r="I190" s="1" t="n"/>
+      <c r="A190" s="1" t="n">
+        <v>183</v>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>Теплоизоляция воздуховодов рулонная толщиной 25 мм с паробарьером (фольга), класс горючести — по СП 60</t>
+        </is>
+      </c>
+      <c r="C190" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D190" s="1" t="inlineStr"/>
+      <c r="E190" s="1" t="inlineStr"/>
+      <c r="F190" s="1" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="G190" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="H190" s="1" t="inlineStr"/>
+      <c r="I190" s="1" t="inlineStr">
+        <is>
+          <t>Н и выброс П1 Ø250</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Наружный блок мини-VRV, тепловой насос, Qх = 22,4 кВт, ночной малошумный режим</t>
+          <t>Теплоизоляция воздуховода Ø200 из минеральной ваты, негорючая (НГ), толщина 50 мм, кашированная фольгой</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии VRV-S, модель — по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D191" s="1" t="inlineStr"/>
-      <c r="E191" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E191" s="1" t="inlineStr"/>
       <c r="F191" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G191" s="1" t="n">
-        <v>1</v>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G191" s="1" t="inlineStr">
+        <is>
+          <t>6,8</t>
+        </is>
       </c>
       <c r="H191" s="1" t="inlineStr"/>
       <c r="I191" s="1" t="inlineStr">
         <is>
-          <t>НБ-1, площадка у восточной стены топочной</t>
+          <t>ВЗ: холодная шахта, рядом дымоход мангала — только НГ</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Рама опорная наружного блока высотой 0,3–0,5 м</t>
-        </is>
-      </c>
-      <c r="C192" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Крепления воздуховодов: подвесы, хомуты с уплотнителем, шпильки, профиль</t>
+        </is>
+      </c>
+      <c r="C192" s="1" t="inlineStr"/>
       <c r="D192" s="1" t="inlineStr"/>
       <c r="E192" s="1" t="inlineStr"/>
       <c r="F192" s="1" t="inlineStr">
@@ -6058,44 +6080,24 @@
       <c r="H192" s="1" t="inlineStr"/>
       <c r="I192" s="1" t="inlineStr">
         <is>
-          <t>НБ-1, лист 14</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
-        <v>185</v>
-      </c>
-      <c r="B193" s="2" t="inlineStr">
-        <is>
-          <t>Внутренний блок канальный тонкий, Qх = 5,6 кВт, ≈900 м³/ч</t>
-        </is>
-      </c>
-      <c r="C193" s="1" t="inlineStr">
-        <is>
-          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
-        </is>
-      </c>
-      <c r="D193" s="1" t="inlineStr"/>
-      <c r="E193" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
-      <c r="F193" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G193" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H193" s="1" t="inlineStr"/>
-      <c r="I193" s="1" t="inlineStr">
-        <is>
-          <t>К-1 (1.10), К-2 (1.10)</t>
-        </is>
-      </c>
+      <c r="A193" s="1" t="inlineStr"/>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>6. Кондиционирование (листы 9–11, 14)</t>
+        </is>
+      </c>
+      <c r="C193" s="1" t="n"/>
+      <c r="D193" s="1" t="n"/>
+      <c r="E193" s="1" t="n"/>
+      <c r="F193" s="1" t="n"/>
+      <c r="G193" s="1" t="n"/>
+      <c r="H193" s="1" t="n"/>
+      <c r="I193" s="1" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -6103,12 +6105,12 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок канальный тонкий, Qх = 3,6 кВт, ≈600 м³/ч</t>
+          <t>Наружный блок мини-VRV, тепловой насос, Qх = 22,4 кВт, ночной малошумный режим</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+          <t>Daikin серии VRV-S, модель — по каталогу Daikin</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr"/>
@@ -6128,7 +6130,7 @@
       <c r="H194" s="1" t="inlineStr"/>
       <c r="I194" s="1" t="inlineStr">
         <is>
-          <t>К-3 (1.11)</t>
+          <t>НБ-1, площадка у восточной стены топочной</t>
         </is>
       </c>
     </row>
@@ -6138,32 +6140,28 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок канальный тонкий, Qх = 2,8 кВт, ≈480 м³/ч</t>
+          <t>Рама опорная наружного блока высотой 0,3–0,5 м</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr"/>
-      <c r="E195" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E195" s="1" t="inlineStr"/>
       <c r="F195" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G195" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H195" s="1" t="inlineStr"/>
       <c r="I195" s="1" t="inlineStr">
         <is>
-          <t>К-4 (2.3), К-5 (2.4), К-6 (2.5), К-7 (2.7)</t>
+          <t>НБ-1, лист 14</t>
         </is>
       </c>
     </row>
@@ -6173,12 +6171,12 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Пульт управления внутренним блоком</t>
+          <t>Внутренний блок канальный тонкий, Qх = 5,6 кВт, ≈900 м³/ч</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t>по каталогу Daikin</t>
+          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr"/>
@@ -6193,12 +6191,12 @@
         </is>
       </c>
       <c r="G196" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H196" s="1" t="inlineStr"/>
       <c r="I196" s="1" t="inlineStr">
         <is>
-          <t>тип — по решению Заказчика</t>
+          <t>К-1 (1.10), К-2 (1.10)</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6206,12 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Разветвитель фреоновый REFNET</t>
+          <t>Внутренний блок канальный тонкий, Qх = 3,6 кВт, ≈600 м³/ч</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>по каталогу Daikin</t>
+          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr"/>
@@ -6228,12 +6226,12 @@
         </is>
       </c>
       <c r="G197" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H197" s="1" t="inlineStr"/>
       <c r="I197" s="1" t="inlineStr">
         <is>
-          <t>Р1…Р6</t>
+          <t>К-3 (1.11)</t>
         </is>
       </c>
     </row>
@@ -6243,28 +6241,32 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø6,35 мм</t>
+          <t>Внутренний блок канальный тонкий, Qх = 2,8 кВт, ≈480 м³/ч</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr"/>
-      <c r="E198" s="1" t="inlineStr"/>
+      <c r="E198" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F198" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G198" s="1" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H198" s="1" t="inlineStr"/>
       <c r="I198" s="1" t="inlineStr">
         <is>
-          <t>жидкость</t>
+          <t>К-4 (2.3), К-5 (2.4), К-6 (2.5), К-7 (2.7)</t>
         </is>
       </c>
     </row>
@@ -6274,28 +6276,32 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø9,52 мм</t>
+          <t>Пульт управления внутренним блоком</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по каталогу Daikin</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr"/>
-      <c r="E199" s="1" t="inlineStr"/>
+      <c r="E199" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F199" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G199" s="1" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="H199" s="1" t="inlineStr"/>
       <c r="I199" s="1" t="inlineStr">
         <is>
-          <t>жидкость</t>
+          <t>тип — по решению Заказчика</t>
         </is>
       </c>
     </row>
@@ -6305,28 +6311,32 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø12,70 мм</t>
+          <t>Разветвитель фреоновый REFNET</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по каталогу Daikin</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr"/>
-      <c r="E200" s="1" t="inlineStr"/>
+      <c r="E200" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F200" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G200" s="1" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H200" s="1" t="inlineStr"/>
       <c r="I200" s="1" t="inlineStr">
         <is>
-          <t>газ</t>
+          <t>Р1…Р6</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6346,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø15,88 мм</t>
+          <t>Труба медная отожжённая для холодильной техники Ø6,35 мм</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
@@ -6352,12 +6362,12 @@
         </is>
       </c>
       <c r="G201" s="1" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H201" s="1" t="inlineStr"/>
       <c r="I201" s="1" t="inlineStr">
         <is>
-          <t>газ</t>
+          <t>жидкость</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6377,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø19,05 мм</t>
+          <t>Труба медная отожжённая для холодильной техники Ø9,52 мм</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
@@ -6383,12 +6393,12 @@
         </is>
       </c>
       <c r="G202" s="1" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H202" s="1" t="inlineStr"/>
       <c r="I202" s="1" t="inlineStr">
         <is>
-          <t>газ</t>
+          <t>жидкость</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6408,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø6,35, толщина — по паспорту Daikin</t>
+          <t>Труба медная отожжённая для холодильной техники Ø12,70 мм</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
@@ -6417,7 +6427,11 @@
         <v>19</v>
       </c>
       <c r="H203" s="1" t="inlineStr"/>
-      <c r="I203" s="1" t="inlineStr"/>
+      <c r="I203" s="1" t="inlineStr">
+        <is>
+          <t>газ</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -6425,7 +6439,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø9,52, толщина — по паспорту Daikin</t>
+          <t>Труба медная отожжённая для холодильной техники Ø15,88 мм</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
@@ -6441,10 +6455,14 @@
         </is>
       </c>
       <c r="G204" s="1" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H204" s="1" t="inlineStr"/>
-      <c r="I204" s="1" t="inlineStr"/>
+      <c r="I204" s="1" t="inlineStr">
+        <is>
+          <t>газ</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -6452,7 +6470,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø12,70, толщина — по паспорту Daikin</t>
+          <t>Труба медная отожжённая для холодильной техники Ø19,05 мм</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
@@ -6468,10 +6486,14 @@
         </is>
       </c>
       <c r="G205" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H205" s="1" t="inlineStr"/>
-      <c r="I205" s="1" t="inlineStr"/>
+      <c r="I205" s="1" t="inlineStr">
+        <is>
+          <t>газ</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -6479,7 +6501,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø15,88, толщина — по паспорту Daikin</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø6,35, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
@@ -6495,7 +6517,7 @@
         </is>
       </c>
       <c r="G206" s="1" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H206" s="1" t="inlineStr"/>
       <c r="I206" s="1" t="inlineStr"/>
@@ -6506,7 +6528,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø19,05, толщина — по паспорту Daikin</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø9,52, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
@@ -6522,7 +6544,7 @@
         </is>
       </c>
       <c r="G207" s="1" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H207" s="1" t="inlineStr"/>
       <c r="I207" s="1" t="inlineStr"/>
@@ -6533,32 +6555,26 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Хладагент для дозаправки (тип — по паспорту НБ-1)</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø12,70, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
         <is>
-          <t>по паспорту НБ-1</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D208" s="1" t="inlineStr"/>
       <c r="E208" s="1" t="inlineStr"/>
       <c r="F208" s="1" t="inlineStr">
         <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="G208" s="1" t="inlineStr">
-        <is>
-          <t>2,17</t>
-        </is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G208" s="1" t="n">
+        <v>19</v>
       </c>
       <c r="H208" s="1" t="inlineStr"/>
-      <c r="I208" s="1" t="inlineStr">
-        <is>
-          <t>по расчёту, уточнить при пуске</t>
-        </is>
-      </c>
+      <c r="I208" s="1" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
@@ -6566,26 +6582,26 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода фреонопроводов и дренажа через наружную стену и перекрытие</t>
-        </is>
-      </c>
-      <c r="C209" s="1" t="inlineStr"/>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø15,88, толщина — по паспорту Daikin</t>
+        </is>
+      </c>
+      <c r="C209" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D209" s="1" t="inlineStr"/>
       <c r="E209" s="1" t="inlineStr"/>
       <c r="F209" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G209" s="1" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H209" s="1" t="inlineStr"/>
-      <c r="I209" s="1" t="inlineStr">
-        <is>
-          <t>стена топочной, Ш-1</t>
-        </is>
-      </c>
+      <c r="I209" s="1" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
@@ -6593,7 +6609,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Диффузор щелевой блока К в торце подшивки, L=1000 мм</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø19,05, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
@@ -6605,18 +6621,14 @@
       <c r="E210" s="1" t="inlineStr"/>
       <c r="F210" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G210" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H210" s="1" t="inlineStr"/>
-      <c r="I210" s="1" t="inlineStr">
-        <is>
-          <t>К-1, К-2</t>
-        </is>
-      </c>
+      <c r="I210" s="1" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
@@ -6624,28 +6636,30 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Диффузор щелевой блока К в торце подшивки, L=1100 мм</t>
+          <t>Хладагент для дозаправки (тип — по паспорту НБ-1)</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по паспорту НБ-1</t>
         </is>
       </c>
       <c r="D211" s="1" t="inlineStr"/>
       <c r="E211" s="1" t="inlineStr"/>
       <c r="F211" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G211" s="1" t="n">
-        <v>1</v>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="G211" s="1" t="inlineStr">
+        <is>
+          <t>2,17</t>
+        </is>
       </c>
       <c r="H211" s="1" t="inlineStr"/>
       <c r="I211" s="1" t="inlineStr">
         <is>
-          <t>К-3</t>
+          <t>по расчёту, уточнить при пуске</t>
         </is>
       </c>
     </row>
@@ -6655,14 +6669,10 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Камера (плёнум) блока К с присоединением к щелевому диффузору</t>
-        </is>
-      </c>
-      <c r="C212" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Гильза стальная для прохода фреонопроводов и дренажа через наружную стену и перекрытие</t>
+        </is>
+      </c>
+      <c r="C212" s="1" t="inlineStr"/>
       <c r="D212" s="1" t="inlineStr"/>
       <c r="E212" s="1" t="inlineStr"/>
       <c r="F212" s="1" t="inlineStr">
@@ -6671,12 +6681,12 @@
         </is>
       </c>
       <c r="G212" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H212" s="1" t="inlineStr"/>
       <c r="I212" s="1" t="inlineStr">
         <is>
-          <t>К-1…К-3, по месту</t>
+          <t>стена топочной, Ш-1</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6696,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Решётка рециркуляции потолочная ≈300×300 под блоком К</t>
+          <t>Диффузор щелевой блока К в торце подшивки, L=1000 мм</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
@@ -6702,12 +6712,12 @@
         </is>
       </c>
       <c r="G213" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H213" s="1" t="inlineStr"/>
       <c r="I213" s="1" t="inlineStr">
         <is>
-          <t>К-1…К-3</t>
+          <t>К-1, К-2</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6727,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Решётка щелевая настенная 800×150 с регулированием, с напорной камерой (подача К и свежего воздуха П1)</t>
+          <t>Диффузор щелевой блока К в торце подшивки, L=1100 мм</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
@@ -6733,12 +6743,12 @@
         </is>
       </c>
       <c r="G214" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H214" s="1" t="inlineStr"/>
       <c r="I214" s="1" t="inlineStr">
         <is>
-          <t>ЩП, спальни 2.3–2.5, 2.7</t>
+          <t>К-3</t>
         </is>
       </c>
     </row>
@@ -6748,7 +6758,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Решётка щелевая настенная 800×150 с регулированием (возврат)</t>
+          <t>Камера (плёнум) блока К с присоединением к щелевому диффузору</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
@@ -6764,12 +6774,12 @@
         </is>
       </c>
       <c r="G215" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H215" s="1" t="inlineStr"/>
       <c r="I215" s="1" t="inlineStr">
         <is>
-          <t>ЩВ, спальни 2.3–2.5, 2.7</t>
+          <t>К-1…К-3, по месту</t>
         </is>
       </c>
     </row>
@@ -6779,24 +6789,28 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод прямоугольный из оцинкованной стали 250×150</t>
-        </is>
-      </c>
-      <c r="C216" s="1" t="inlineStr"/>
+          <t>Решётка рециркуляции потолочная ≈300×300 под блоком К</t>
+        </is>
+      </c>
+      <c r="C216" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D216" s="1" t="inlineStr"/>
       <c r="E216" s="1" t="inlineStr"/>
       <c r="F216" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G216" s="1" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H216" s="1" t="inlineStr"/>
       <c r="I216" s="1" t="inlineStr">
         <is>
-          <t>блоки К-4…К-7</t>
+          <t>К-1…К-3</t>
         </is>
       </c>
     </row>
@@ -6806,10 +6820,14 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° прямоугольный оцинкованный 250×150</t>
-        </is>
-      </c>
-      <c r="C217" s="1" t="inlineStr"/>
+          <t>Решётка щелевая настенная 800×150 с регулированием, с напорной камерой (подача К и свежего воздуха П1)</t>
+        </is>
+      </c>
+      <c r="C217" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D217" s="1" t="inlineStr"/>
       <c r="E217" s="1" t="inlineStr"/>
       <c r="F217" s="1" t="inlineStr">
@@ -6818,12 +6836,12 @@
         </is>
       </c>
       <c r="G217" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H217" s="1" t="inlineStr"/>
       <c r="I217" s="1" t="inlineStr">
         <is>
-          <t>блоки К-4…К-7</t>
+          <t>ЩП, спальни 2.3–2.5, 2.7</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6851,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
+          <t>Решётка щелевая настенная 800×150 с регулированием (возврат)</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
@@ -6845,16 +6863,16 @@
       <c r="E218" s="1" t="inlineStr"/>
       <c r="F218" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G218" s="1" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H218" s="1" t="inlineStr"/>
       <c r="I218" s="1" t="inlineStr">
         <is>
-          <t>дренаж конденсата К-1…К-7</t>
+          <t>ЩВ, спальни 2.3–2.5, 2.7</t>
         </is>
       </c>
     </row>
@@ -6864,28 +6882,24 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП Ø32 (45°/90°)</t>
-        </is>
-      </c>
-      <c r="C219" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод прямоугольный из оцинкованной стали 250×150</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="inlineStr"/>
       <c r="D219" s="1" t="inlineStr"/>
       <c r="E219" s="1" t="inlineStr"/>
       <c r="F219" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G219" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H219" s="1" t="inlineStr"/>
       <c r="I219" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>блоки К-4…К-7</t>
         </is>
       </c>
     </row>
@@ -6895,14 +6909,10 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП Ø32</t>
-        </is>
-      </c>
-      <c r="C220" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 90° прямоугольный оцинкованный 250×150</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="inlineStr"/>
       <c r="D220" s="1" t="inlineStr"/>
       <c r="E220" s="1" t="inlineStr"/>
       <c r="F220" s="1" t="inlineStr">
@@ -6914,7 +6924,11 @@
         <v>5</v>
       </c>
       <c r="H220" s="1" t="inlineStr"/>
-      <c r="I220" s="1" t="inlineStr"/>
+      <c r="I220" s="1" t="inlineStr">
+        <is>
+          <t>блоки К-4…К-7</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -6922,30 +6936,119 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
-        </is>
-      </c>
-      <c r="C221" s="1" t="inlineStr"/>
+          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
+        </is>
+      </c>
+      <c r="C221" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D221" s="1" t="inlineStr"/>
       <c r="E221" s="1" t="inlineStr"/>
       <c r="F221" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G221" s="1" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H221" s="1" t="inlineStr"/>
       <c r="I221" s="1" t="inlineStr">
         <is>
+          <t>дренаж конденсата К-1…К-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Отвод ПП Ø32 (45°/90°)</t>
+        </is>
+      </c>
+      <c r="C222" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D222" s="1" t="inlineStr"/>
+      <c r="E222" s="1" t="inlineStr"/>
+      <c r="F222" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G222" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H222" s="1" t="inlineStr"/>
+      <c r="I222" s="1" t="inlineStr">
+        <is>
           <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr"/>
-      <c r="B223" t="inlineStr">
+      <c r="A223" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Тройник ПП Ø32</t>
+        </is>
+      </c>
+      <c r="C223" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D223" s="1" t="inlineStr"/>
+      <c r="E223" s="1" t="inlineStr"/>
+      <c r="F223" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G223" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H223" s="1" t="inlineStr"/>
+      <c r="I223" s="1" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
+        </is>
+      </c>
+      <c r="C224" s="1" t="inlineStr"/>
+      <c r="D224" s="1" t="inlineStr"/>
+      <c r="E224" s="1" t="inlineStr"/>
+      <c r="F224" s="1" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G224" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H224" s="1" t="inlineStr"/>
+      <c r="I224" s="1" t="inlineStr">
+        <is>
+          <t>по месту</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I226"/>
+  <dimension ref="A1:I229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Гидравлический разделитель Ду 32, расход до 3,4 м³/ч, с автоматическим воздухоотводчиком и спускным краном</t>
+          <t>Гидравлический разделитель Ду 32, расход до 3,3 м³/ч, с автоматическим воздухоотводчиком и спускным краном</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная прямая Ду 32 в сборе: насос циркуляционный с электронным управлением класса 25-60 (G=1,69 м³/ч, H=2,92 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Группа насосная прямая Ду 32 в сборе: насос циркуляционный с электронным управлением класса 25-60 (G=1,64 м³/ч, H=2,84 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -2202,12 +2202,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 12 В, L=1950 мм, тепловая мощность при 70/55 °С не менее 1953 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 1953 Вт</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>КЗТО, модель — по каталогу</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr"/>
@@ -2237,12 +2237,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 12 В, L=1650 мм, тепловая мощность при 70/55 °С не менее 1653 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1650 мм, тепловая мощность при 70/55 °С не менее 1653 Вт</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>КЗТО, модель — по каталогу</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr"/>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 12 В, L=900 мм, тепловая мощность при 70/55 °С не менее 902 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=900 мм, тепловая мощность при 70/55 °С не менее 902 Вт</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>КЗТО, модель — по каталогу</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr"/>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 12 В, L=1950 мм, тепловая мощность при 70/55 °С не менее 880 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 880 Вт</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>КЗТО, модель — по каталогу</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr"/>
@@ -2342,12 +2342,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 12 В, L=2200 мм, тепловая мощность при 70/55 °С не менее 2355 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2200 мм, тепловая мощность при 70/55 °С не менее 2355 Вт</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>КЗТО, модель — по каталогу</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>КЗТО, модель — по каталогу</t>
+          <t>КЗТО «Бриз» (естественная конвекция), модель — по каталогу</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
@@ -2412,12 +2412,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 12 В, L=900 мм, глубина не более 150 мм, тепловая мощность при 70/55 °С не менее 613 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=900 мм, глубина не более 150 мм, тепловая мощность при 70/55 °С не менее 613 Вт</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>КЗТО, модель — по каталогу</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Коллектор прямой из нержавеющей стали 1" на 7 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+          <t>Коллектор прямой из нержавеющей стали 1" на 6 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -3674,7 +3674,7 @@
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 12 В, L=2150 мм, тепловая мощность при 70/55 °С не менее 1108 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2150 мм, тепловая мощность при 70/55 °С не менее 1108 Вт</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>КЗТО, модель — по каталогу</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr"/>
@@ -3786,20 +3786,16 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 12 В, L=2200 мм, тепловая мощность при 70/55 °С не менее 2614 Вт</t>
+          <t>Полотенцесушитель водяной, мощность не менее 590 Вт при 75/65/20 °С</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>КЗТО, модель — по каталогу; исполнение для влажных помещений — уточнить по каталогу КЗТО</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D111" s="1" t="inlineStr"/>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E111" s="1" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -3811,7 +3807,7 @@
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>Кв-б3 (б7)</t>
+          <t>Пс-б2 (б4)</t>
         </is>
       </c>
     </row>
@@ -3821,16 +3817,20 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Полотенцесушитель водяной, мощность не менее 1260 Вт при 75/65/20 °С</t>
+          <t>Конвектор внутрипольный из нержавеющей стали для влажных помещений, с вентилятором 24 В пост. тока, 260×140 мм, L=2200 мм, тепловая мощность при 70/55 °С не менее 2614 Вт</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>КЗТО «Бриз В TURBO Нерж»</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr"/>
-      <c r="E112" s="1" t="inlineStr"/>
+      <c r="E112" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -3842,7 +3842,7 @@
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>Пс-б1 (б3)</t>
+          <t>Кв-б3 (б7, у джакузи); в нише плиты, ≈2030 Вт/м при Δt50</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Полотенцесушитель водяной, мощность не менее 590 Вт при 75/65/20 °С</t>
+          <t>Узел нижнего подключения радиатора запорный, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -3868,12 +3868,12 @@
         </is>
       </c>
       <c r="G113" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>Пс-б2 (б4)</t>
+          <t>Р-б1, Р-б2</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Узел нижнего подключения радиатора запорный, присоединение евроконус G¾"</t>
+          <t>Клапан запорный G½" для подключения конвектора</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -3899,12 +3899,12 @@
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>Р-б1, Р-б2</t>
+          <t>Кв-б1…Кв-б3</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Клапан запорный G½" для подключения конвектора</t>
+          <t>Комплект запорных клапанов для полотенцесушителя G½"</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -3926,16 +3926,16 @@
       <c r="E115" s="1" t="inlineStr"/>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G115" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>Кв-б1…Кв-б3</t>
+          <t>Пс-б2</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Комплект запорных клапанов для полотенцесушителя G½"</t>
+          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — петли тёплого пола</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -3957,16 +3957,16 @@
       <c r="E116" s="1" t="inlineStr"/>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G116" s="1" t="n">
-        <v>2</v>
+        <v>272</v>
       </c>
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>Пс-б1, Пс-б2</t>
+          <t>петли — 7 шт., лист 12</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — петли тёплого пола</t>
+          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — подводки к приборам</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -3992,12 +3992,12 @@
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>272</v>
+        <v>125</v>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>петли — 7 шт., лист 12</t>
+          <t>лист 12</t>
         </is>
       </c>
     </row>
@@ -4007,7 +4007,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — подводки к приборам</t>
+          <t>Труба PE-Xa 32×4,4 с антидиффузионным слоем (EVOH) — линии ТО-Д и Б2</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
@@ -4023,12 +4023,12 @@
         </is>
       </c>
       <c r="G118" s="1" t="n">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>лист 12</t>
+          <t>от ввода КШ-Б1</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 32×4,4 с антидиффузионным слоем (EVOH) — линии ТО-Д и Б2</t>
+          <t>Фитинг компрессионный (евроконус) для трубы PE-Xa 16×2,0 на G¾"</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -4050,16 +4050,16 @@
       <c r="E119" s="1" t="inlineStr"/>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G119" s="1" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>от ввода КШ-Б1</t>
+          <t>коллекторы, радиаторы</t>
         </is>
       </c>
     </row>
@@ -4069,7 +4069,7 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Фитинг компрессионный (евроконус) для трубы PE-Xa 16×2,0 на G¾"</t>
+          <t>Фитинг компрессионный для трубы PE-Xa 16×2,0 на наружную резьбу G½"</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
@@ -4085,12 +4085,12 @@
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H120" s="1" t="inlineStr"/>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>коллекторы, радиаторы</t>
+          <t>конвекторы, полотенцесушители</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Фитинг компрессионный для трубы PE-Xa 16×2,0 на наружную резьбу G½"</t>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×4,4 на резьбу G1"</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
@@ -4116,12 +4116,12 @@
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>конвекторы, полотенцесушители</t>
+          <t>ТО-Д, Б2</t>
         </is>
       </c>
     </row>
@@ -4131,23 +4131,19 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×4,4 на резьбу G1"</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø32</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="inlineStr"/>
       <c r="D122" s="1" t="inlineStr"/>
       <c r="E122" s="1" t="inlineStr"/>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
@@ -4162,7 +4158,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø32</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена, толщина 6 мм, для трубы Ø16</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr"/>
@@ -4174,12 +4170,12 @@
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>43</v>
+        <v>261</v>
       </c>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>ТО-Д, Б2</t>
+          <t>подводки вне своих петель</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4185,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена, толщина 6 мм, для трубы Ø16</t>
+          <t>Труба гофрированная защитная (гофра) для трубы Ø16</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr"/>
@@ -4201,7 +4197,7 @@
         </is>
       </c>
       <c r="G124" s="1" t="n">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="H124" s="1" t="inlineStr"/>
       <c r="I124" s="1" t="inlineStr">
@@ -4216,7 +4212,7 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная (гофра) для трубы Ø16</t>
+          <t>Фиксатор поворота трубы Ø16 на 90° (выход из пола у коллектора)</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr"/>
@@ -4224,18 +4220,14 @@
       <c r="E125" s="1" t="inlineStr"/>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G125" s="1" t="n">
-        <v>271</v>
+        <v>14</v>
       </c>
       <c r="H125" s="1" t="inlineStr"/>
-      <c r="I125" s="1" t="inlineStr">
-        <is>
-          <t>подводки вне своих петель</t>
-        </is>
-      </c>
+      <c r="I125" s="1" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -4243,7 +4235,7 @@
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота трубы Ø16 на 90° (выход из пола у коллектора)</t>
+          <t>Пленка (мат) с разметкой для укладки труб тёплого пола</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr"/>
@@ -4251,14 +4243,18 @@
       <c r="E126" s="1" t="inlineStr"/>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G126" s="1" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H126" s="1" t="inlineStr"/>
-      <c r="I126" s="1" t="inlineStr"/>
+      <c r="I126" s="1" t="inlineStr">
+        <is>
+          <t>лист 12</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -4266,7 +4262,7 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Пленка (мат) с разметкой для укладки труб тёплого пола</t>
+          <t>Лента демпферная 10×150 мм</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr"/>
@@ -4274,16 +4270,16 @@
       <c r="E127" s="1" t="inlineStr"/>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G127" s="1" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>лист 12</t>
+          <t>по периметру зон и по границам петель</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4289,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Лента демпферная 10×150 мм</t>
+          <t>Скоба якорная для крепления трубы Ø16 к основанию, шаг 0,5 м</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr"/>
@@ -4301,60 +4297,68 @@
       <c r="E128" s="1" t="inlineStr"/>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G128" s="1" t="n">
-        <v>60</v>
+        <v>600</v>
       </c>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>по периметру зон и по границам петель</t>
+          <t>лист 12</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="1" t="inlineStr"/>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>4. Теплотрасса дом – баня (листы 13, 14)</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="n"/>
+      <c r="D129" s="1" t="n"/>
+      <c r="E129" s="1" t="n"/>
+      <c r="F129" s="1" t="n"/>
+      <c r="G129" s="1" t="n"/>
+      <c r="H129" s="1" t="n"/>
+      <c r="I129" s="1" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
         <v>124</v>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>Скоба якорная для крепления трубы Ø16 к основанию, шаг 0,5 м</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr"/>
-      <c r="D129" s="1" t="inlineStr"/>
-      <c r="E129" s="1" t="inlineStr"/>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G129" s="1" t="n">
-        <v>600</v>
-      </c>
-      <c r="H129" s="1" t="inlineStr"/>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>лист 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="1" t="inlineStr"/>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>4. Теплотрасса дом – баня (листы 13, 14)</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="n"/>
-      <c r="D130" s="1" t="n"/>
-      <c r="E130" s="1" t="n"/>
-      <c r="F130" s="1" t="n"/>
-      <c r="G130" s="1" t="n"/>
-      <c r="H130" s="1" t="n"/>
-      <c r="I130" s="1" t="n"/>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Труба предизолированная гибкая: две трубы PE-Xa 32×2,9 отопления и две санитарные трубы (по разделу ВК) в общей оболочке</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>Uponor Ecoflex Quattro, типоразмер — по каталогу</t>
+        </is>
+      </c>
+      <c r="D130" s="1" t="inlineStr"/>
+      <c r="E130" s="1" t="inlineStr">
+        <is>
+          <t>Uponor</t>
+        </is>
+      </c>
+      <c r="F130" s="1" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G130" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="H130" s="1" t="inlineStr"/>
+      <c r="I130" s="1" t="inlineStr">
+        <is>
+          <t>≈16,4 м по трассе с подъёмами + 10 %; лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -4362,12 +4366,12 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Труба предизолированная гибкая: две трубы PE-Xa 32×2,9 отопления и две санитарные трубы (по разделу ВК) в общей оболочке</t>
+          <t>Манжета концевая для трубы Ecoflex Quattro</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>Uponor Ecoflex Quattro, типоразмер — по каталогу</t>
+          <t>по каталогу производителя трубы</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr"/>
@@ -4378,16 +4382,16 @@
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G131" s="1" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="H131" s="1" t="inlineStr"/>
       <c r="I131" s="1" t="inlineStr">
         <is>
-          <t>≈15,3 м по трассе с подъёмами + 10 %; лист 14</t>
+          <t>вводы в дом и баню</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4401,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Манжета концевая для трубы Ecoflex Quattro</t>
+          <t>Гильза ввода с уплотнительным кольцом через фундамент (комплект ввода производителя)</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
@@ -4413,7 +4417,7 @@
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G132" s="1" t="n">
@@ -4422,7 +4426,7 @@
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>вводы в дом и баню</t>
+          <t>узлы 1, 2, лист 13</t>
         </is>
       </c>
     </row>
@@ -4432,23 +4436,15 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Гильза ввода с уплотнительным кольцом через фундамент (комплект ввода производителя)</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>по каталогу производителя трубы</t>
-        </is>
-      </c>
+          <t>Гильза в плите пола для трубы Ecoflex Quattro</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="inlineStr"/>
       <c r="D133" s="1" t="inlineStr"/>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t>Uponor</t>
-        </is>
-      </c>
+      <c r="E133" s="1" t="inlineStr"/>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G133" s="1" t="n">
@@ -4467,10 +4463,14 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Гильза в плите пола для трубы Ecoflex Quattro</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr"/>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×2,9 на резьбу G1"</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t>по каталогу производителя трубы</t>
+        </is>
+      </c>
       <c r="D134" s="1" t="inlineStr"/>
       <c r="E134" s="1" t="inlineStr"/>
       <c r="F134" s="1" t="inlineStr">
@@ -4479,12 +4479,12 @@
         </is>
       </c>
       <c r="G134" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr">
         <is>
-          <t>узлы 1, 2, лист 13</t>
+          <t>концы Т1, Т2</t>
         </is>
       </c>
     </row>
@@ -4494,72 +4494,72 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×2,9 на резьбу G1"</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>по каталогу производителя трубы</t>
-        </is>
-      </c>
+          <t>Лента сигнальная «Осторожно, теплотрасса»</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="inlineStr"/>
       <c r="D135" s="1" t="inlineStr"/>
       <c r="E135" s="1" t="inlineStr"/>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G135" s="1" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>концы Т1, Т2</t>
+          <t>300 мм над трубой</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="1" t="inlineStr"/>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>5. Вентиляция (листы 9–12)</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="n"/>
+      <c r="D136" s="1" t="n"/>
+      <c r="E136" s="1" t="n"/>
+      <c r="F136" s="1" t="n"/>
+      <c r="G136" s="1" t="n"/>
+      <c r="H136" s="1" t="n"/>
+      <c r="I136" s="1" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
         <v>130</v>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>Лента сигнальная «Осторожно, теплотрасса»</t>
-        </is>
-      </c>
-      <c r="C136" s="1" t="inlineStr"/>
-      <c r="D136" s="1" t="inlineStr"/>
-      <c r="E136" s="1" t="inlineStr"/>
-      <c r="F136" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G136" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="H136" s="1" t="inlineStr"/>
-      <c r="I136" s="1" t="inlineStr">
-        <is>
-          <t>300 мм над трубой</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="1" t="inlineStr"/>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>5. Вентиляция (листы 9–11)</t>
-        </is>
-      </c>
-      <c r="C137" s="1" t="n"/>
-      <c r="D137" s="1" t="n"/>
-      <c r="E137" s="1" t="n"/>
-      <c r="F137" s="1" t="n"/>
-      <c r="G137" s="1" t="n"/>
-      <c r="H137" s="1" t="n"/>
-      <c r="I137" s="1" t="n"/>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Установка приточно-вытяжная с роторным рекуператором (КПД не менее 80 %), 700 м³/ч, свободный напор не менее 200 Па (по расчёту 159 Па), водяной калорифер ≈2,6 кВт (70/50 °С), фильтры ePM1 50 % / ePM10 50 %, автоматика с защитой калорифера от замерзания</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t>марка — по выбору Заказчика</t>
+        </is>
+      </c>
+      <c r="D137" s="1" t="inlineStr"/>
+      <c r="E137" s="1" t="inlineStr"/>
+      <c r="F137" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G137" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" s="1" t="inlineStr"/>
+      <c r="I137" s="1" t="inlineStr">
+        <is>
+          <t>П1, под потолком топочной, низ +2,900</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Установка приточно-вытяжная с роторным рекуператором (КПД не менее 80 %), 700 м³/ч, свободный напор не менее 200 Па (по расчёту 159 Па), водяной калорифер ≈2,6 кВт (70/50 °С), фильтры ePM1 50 % / ePM10 50 %, автоматика с защитой калорифера от замерзания</t>
+          <t>Кран шаровой G¾" (обвязка калорифера П1, подача и обратка)</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>марка — по выбору Заказчика</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr"/>
@@ -4583,12 +4583,12 @@
         </is>
       </c>
       <c r="G138" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>П1, под потолком топочной, низ +2,900</t>
+          <t>П1</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой G¾" (обвязка калорифера П1, подача и обратка)</t>
+          <t>Фильтр сетчатый G¾" (обвязка калорифера П1)</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
@@ -4614,7 +4614,7 @@
         </is>
       </c>
       <c r="G139" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Фильтр сетчатый G¾" (обвязка калорифера П1)</t>
+          <t>Шумоглушитель круглый Ø250, L=1000 мм</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
@@ -4645,12 +4645,12 @@
         </is>
       </c>
       <c r="G140" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr">
         <is>
-          <t>П1</t>
+          <t>ШГ, на П и В у П1</t>
         </is>
       </c>
     </row>
@@ -4660,28 +4660,24 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Шумоглушитель круглый Ø250, L=1000 мм</t>
-        </is>
-      </c>
-      <c r="C141" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø100, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="inlineStr"/>
       <c r="D141" s="1" t="inlineStr"/>
       <c r="E141" s="1" t="inlineStr"/>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G141" s="1" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>ШГ, на П и В у П1</t>
+          <t>П1 — 29 м; баня ВВ-б1, ВВ-б2 — 3 м</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4687,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø100, толщина стали — по СП 60.13330</t>
+          <t>Воздуховод круглый из оцинкованной стали Ø125, толщина стали — по СП 60.13330</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr"/>
@@ -4703,7 +4699,7 @@
         </is>
       </c>
       <c r="G142" s="1" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr">
@@ -4718,7 +4714,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø125, толщина стали — по СП 60.13330</t>
+          <t>Воздуховод круглый из оцинкованной стали Ø150, толщина стали — по СП 60.13330</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr"/>
@@ -4729,13 +4725,15 @@
           <t>м</t>
         </is>
       </c>
-      <c r="G143" s="1" t="n">
-        <v>26</v>
+      <c r="G143" s="1" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
       </c>
       <c r="H143" s="1" t="inlineStr"/>
       <c r="I143" s="1" t="inlineStr">
         <is>
-          <t>П1</t>
+          <t>ВЗ (кухонный зонт)</t>
         </is>
       </c>
     </row>
@@ -4745,7 +4743,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø150, толщина стали — по СП 60.13330</t>
+          <t>Воздуховод круглый из оцинкованной стали Ø160, толщина стали — по СП 60.13330</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr"/>
@@ -4756,15 +4754,13 @@
           <t>м</t>
         </is>
       </c>
-      <c r="G144" s="1" t="inlineStr">
-        <is>
-          <t>2,7</t>
-        </is>
+      <c r="G144" s="1" t="n">
+        <v>18</v>
       </c>
       <c r="H144" s="1" t="inlineStr"/>
       <c r="I144" s="1" t="inlineStr">
         <is>
-          <t>ВЗ (кухонный зонт)</t>
+          <t>П1</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4770,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø160, толщина стали — по СП 60.13330</t>
+          <t>Воздуховод круглый из оцинкованной стали Ø200, толщина стали — по СП 60.13330</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr"/>
@@ -4785,13 +4781,15 @@
           <t>м</t>
         </is>
       </c>
-      <c r="G145" s="1" t="n">
-        <v>18</v>
+      <c r="G145" s="1" t="inlineStr">
+        <is>
+          <t>24,8</t>
+        </is>
       </c>
       <c r="H145" s="1" t="inlineStr"/>
       <c r="I145" s="1" t="inlineStr">
         <is>
-          <t>П1</t>
+          <t>П1 — 18 м; ВЗ (кухонный зонт) — 6,8 м</t>
         </is>
       </c>
     </row>
@@ -4801,7 +4799,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø200, толщина стали — по СП 60.13330</t>
+          <t>Воздуховод круглый из оцинкованной стали Ø250, толщина стали — по СП 60.13330</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr"/>
@@ -4812,15 +4810,13 @@
           <t>м</t>
         </is>
       </c>
-      <c r="G146" s="1" t="inlineStr">
-        <is>
-          <t>24,8</t>
-        </is>
+      <c r="G146" s="1" t="n">
+        <v>38</v>
       </c>
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr">
         <is>
-          <t>П1 — 18 м; ВЗ (кухонный зонт) — 6,8 м</t>
+          <t>П1: магистрали, Н, выброс в Ш-2; В2 в Ш-2</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4826,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø250, толщина стали — по СП 60.13330</t>
+          <t>Отвод 90° круглый оцинкованный Ø100</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr"/>
@@ -4838,16 +4834,16 @@
       <c r="E147" s="1" t="inlineStr"/>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G147" s="1" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="H147" s="1" t="inlineStr"/>
       <c r="I147" s="1" t="inlineStr">
         <is>
-          <t>П1: магистрали, Н, выброс в Ш-2; В2 в Ш-2</t>
+          <t>в т. ч. баня ВВ-б1, ВВ-б2 — 2</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4853,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø100</t>
+          <t>Отвод 90° круглый оцинкованный Ø125</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr"/>
@@ -4869,7 +4865,7 @@
         </is>
       </c>
       <c r="G148" s="1" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H148" s="1" t="inlineStr"/>
       <c r="I148" s="1" t="inlineStr"/>
@@ -4880,7 +4876,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø125</t>
+          <t>Отвод 90° круглый оцинкованный Ø150</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr"/>
@@ -4892,10 +4888,14 @@
         </is>
       </c>
       <c r="G149" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H149" s="1" t="inlineStr"/>
-      <c r="I149" s="1" t="inlineStr"/>
+      <c r="I149" s="1" t="inlineStr">
+        <is>
+          <t>ВЗ (кухонный зонт)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø150</t>
+          <t>Отвод 90° круглый оцинкованный Ø160</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr"/>
@@ -4915,14 +4915,10 @@
         </is>
       </c>
       <c r="G150" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H150" s="1" t="inlineStr"/>
-      <c r="I150" s="1" t="inlineStr">
-        <is>
-          <t>ВЗ (кухонный зонт)</t>
-        </is>
-      </c>
+      <c r="I150" s="1" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -4930,7 +4926,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø160</t>
+          <t>Отвод 90° круглый оцинкованный Ø200</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr"/>
@@ -4942,10 +4938,14 @@
         </is>
       </c>
       <c r="G151" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H151" s="1" t="inlineStr"/>
-      <c r="I151" s="1" t="inlineStr"/>
+      <c r="I151" s="1" t="inlineStr">
+        <is>
+          <t>в т. ч. ВЗ (кухонный зонт) — 1</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø200</t>
+          <t>Отвод 90° круглый оцинкованный Ø250</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr"/>
@@ -4965,14 +4965,10 @@
         </is>
       </c>
       <c r="G152" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H152" s="1" t="inlineStr"/>
-      <c r="I152" s="1" t="inlineStr">
-        <is>
-          <t>в т. ч. ВЗ (кухонный зонт) — 1</t>
-        </is>
-      </c>
+      <c r="I152" s="1" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -4980,7 +4976,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø250</t>
+          <t>Тройник круглый оцинкованный Ø125/Ø100</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr"/>
@@ -4992,7 +4988,7 @@
         </is>
       </c>
       <c r="G153" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H153" s="1" t="inlineStr"/>
       <c r="I153" s="1" t="inlineStr"/>
@@ -5003,7 +4999,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø125/Ø100</t>
+          <t>Тройник круглый оцинкованный Ø160/Ø100</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr"/>
@@ -5015,7 +5011,7 @@
         </is>
       </c>
       <c r="G154" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H154" s="1" t="inlineStr"/>
       <c r="I154" s="1" t="inlineStr"/>
@@ -5026,7 +5022,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø160/Ø100</t>
+          <t>Тройник круглый оцинкованный Ø160/Ø125</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr"/>
@@ -5038,7 +5034,7 @@
         </is>
       </c>
       <c r="G155" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H155" s="1" t="inlineStr"/>
       <c r="I155" s="1" t="inlineStr"/>
@@ -5049,7 +5045,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø160/Ø125</t>
+          <t>Тройник круглый оцинкованный Ø200/Ø125</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr"/>
@@ -5061,7 +5057,7 @@
         </is>
       </c>
       <c r="G156" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H156" s="1" t="inlineStr"/>
       <c r="I156" s="1" t="inlineStr"/>
@@ -5072,7 +5068,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø200/Ø125</t>
+          <t>Тройник круглый оцинкованный Ø200/Ø160</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr"/>
@@ -5084,7 +5080,7 @@
         </is>
       </c>
       <c r="G157" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H157" s="1" t="inlineStr"/>
       <c r="I157" s="1" t="inlineStr"/>
@@ -5095,7 +5091,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø200/Ø160</t>
+          <t>Тройник круглый оцинкованный Ø200/Ø200</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr"/>
@@ -5118,7 +5114,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø200/Ø200</t>
+          <t>Тройник круглый оцинкованный Ø250/Ø100</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr"/>
@@ -5130,7 +5126,7 @@
         </is>
       </c>
       <c r="G159" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H159" s="1" t="inlineStr"/>
       <c r="I159" s="1" t="inlineStr"/>
@@ -5141,7 +5137,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø250/Ø100</t>
+          <t>Тройник круглый оцинкованный Ø250/Ø200</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr"/>
@@ -5164,7 +5160,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø250/Ø200</t>
+          <t>Переход круглый оцинкованный Ø125/Ø100</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr"/>
@@ -5176,7 +5172,7 @@
         </is>
       </c>
       <c r="G161" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H161" s="1" t="inlineStr"/>
       <c r="I161" s="1" t="inlineStr"/>
@@ -5187,7 +5183,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø125/Ø100</t>
+          <t>Переход круглый оцинкованный Ø160/Ø125</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr"/>
@@ -5199,7 +5195,7 @@
         </is>
       </c>
       <c r="G162" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H162" s="1" t="inlineStr"/>
       <c r="I162" s="1" t="inlineStr"/>
@@ -5210,7 +5206,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø160/Ø125</t>
+          <t>Переход круглый оцинкованный Ø200/Ø100</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr"/>
@@ -5222,7 +5218,7 @@
         </is>
       </c>
       <c r="G163" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H163" s="1" t="inlineStr"/>
       <c r="I163" s="1" t="inlineStr"/>
@@ -5233,7 +5229,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø200/Ø100</t>
+          <t>Переход круглый оцинкованный Ø200/Ø150</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr"/>
@@ -5248,7 +5244,11 @@
         <v>1</v>
       </c>
       <c r="H164" s="1" t="inlineStr"/>
-      <c r="I164" s="1" t="inlineStr"/>
+      <c r="I164" s="1" t="inlineStr">
+        <is>
+          <t>ВЗ (кухонный зонт)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø200/Ø150</t>
+          <t>Переход круглый оцинкованный Ø200/Ø160</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr"/>
@@ -5268,14 +5268,10 @@
         </is>
       </c>
       <c r="G165" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H165" s="1" t="inlineStr"/>
-      <c r="I165" s="1" t="inlineStr">
-        <is>
-          <t>ВЗ (кухонный зонт)</t>
-        </is>
-      </c>
+      <c r="I165" s="1" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -5283,7 +5279,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø200/Ø160</t>
+          <t>Переход круглый оцинкованный Ø250/Ø160</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr"/>
@@ -5295,7 +5291,7 @@
         </is>
       </c>
       <c r="G166" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H166" s="1" t="inlineStr"/>
       <c r="I166" s="1" t="inlineStr"/>
@@ -5306,7 +5302,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø250/Ø160</t>
+          <t>Переход круглый оцинкованный Ø250/Ø200</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr"/>
@@ -5329,10 +5325,14 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø250/Ø200</t>
-        </is>
-      </c>
-      <c r="C168" s="1" t="inlineStr"/>
+          <t>Регулятор расхода воздуха (ирисовый клапан) Ø100</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D168" s="1" t="inlineStr"/>
       <c r="E168" s="1" t="inlineStr"/>
       <c r="F168" s="1" t="inlineStr">
@@ -5341,10 +5341,14 @@
         </is>
       </c>
       <c r="G168" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H168" s="1" t="inlineStr"/>
-      <c r="I168" s="1" t="inlineStr"/>
+      <c r="I168" s="1" t="inlineStr">
+        <is>
+          <t>РР, на ответвлениях</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -5352,7 +5356,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Регулятор расхода воздуха (ирисовый клапан) Ø100</t>
+          <t>Регулятор расхода воздуха (ирисовый клапан) Ø125</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -5368,7 +5372,7 @@
         </is>
       </c>
       <c r="G169" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H169" s="1" t="inlineStr"/>
       <c r="I169" s="1" t="inlineStr">
@@ -5383,7 +5387,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Регулятор расхода воздуха (ирисовый клапан) Ø125</t>
+          <t>Регулятор расхода воздуха (ирисовый клапан) Ø160</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -5399,7 +5403,7 @@
         </is>
       </c>
       <c r="G170" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H170" s="1" t="inlineStr"/>
       <c r="I170" s="1" t="inlineStr">
@@ -5414,7 +5418,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Регулятор расхода воздуха (ирисовый клапан) Ø160</t>
+          <t>Диффузор щелевой (линейный) приточный в торце подшивки, L=600 мм, с камерой статического давления, присоединение Ø125, расход 70 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -5430,12 +5434,12 @@
         </is>
       </c>
       <c r="G171" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H171" s="1" t="inlineStr"/>
       <c r="I171" s="1" t="inlineStr">
         <is>
-          <t>РР, на ответвлениях</t>
+          <t>1.10 — 3 шт.</t>
         </is>
       </c>
     </row>
@@ -5445,7 +5449,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Диффузор щелевой (линейный) приточный в торце подшивки, L=600 мм, с камерой статического давления, присоединение Ø125, расход 70 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Диффузор потолочный приточный с камерой статического давления, присоединение Ø100, расход 30/60 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -5466,7 +5470,7 @@
       <c r="H172" s="1" t="inlineStr"/>
       <c r="I172" s="1" t="inlineStr">
         <is>
-          <t>1.10 — 3 шт.</t>
+          <t>1.11 — 2 шт., 2.2</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5480,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Диффузор потолочный приточный с камерой статического давления, присоединение Ø100, расход 30/60 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка приточная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -5492,12 +5496,12 @@
         </is>
       </c>
       <c r="G173" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H173" s="1" t="inlineStr"/>
       <c r="I173" s="1" t="inlineStr">
         <is>
-          <t>1.11 — 2 шт., 2.2</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5511,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Решётка приточная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø100, расход 40/50/60 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -5523,12 +5527,12 @@
         </is>
       </c>
       <c r="G174" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H174" s="1" t="inlineStr"/>
       <c r="I174" s="1" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.4, 1.3, 2.6</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5542,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø100, расход 40/50/60 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø125, расход 75/90 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -5559,7 +5563,7 @@
       <c r="H175" s="1" t="inlineStr"/>
       <c r="I175" s="1" t="inlineStr">
         <is>
-          <t>1.4, 1.3, 2.6</t>
+          <t>2.9, 2.8, 2.1</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5573,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø125, расход 75/90 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -5585,12 +5589,12 @@
         </is>
       </c>
       <c r="G176" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H176" s="1" t="inlineStr"/>
       <c r="I176" s="1" t="inlineStr">
         <is>
-          <t>2.9, 2.8, 2.1</t>
+          <t>1.8</t>
         </is>
       </c>
     </row>
@@ -5600,7 +5604,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø125, расход 90 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -5621,7 +5625,7 @@
       <c r="H177" s="1" t="inlineStr"/>
       <c r="I177" s="1" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.10 (кухня)</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5635,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø125, расход 90 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø160, расход 120 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -5652,7 +5656,7 @@
       <c r="H178" s="1" t="inlineStr"/>
       <c r="I178" s="1" t="inlineStr">
         <is>
-          <t>1.10 (кухня)</t>
+          <t>1.10 (верх 2-го света)</t>
         </is>
       </c>
     </row>
@@ -5662,7 +5666,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø160, расход 120 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка наружная воздухозаборная 500×400, низ +2,600</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -5683,7 +5687,7 @@
       <c r="H179" s="1" t="inlineStr"/>
       <c r="I179" s="1" t="inlineStr">
         <is>
-          <t>1.10 (верх 2-го света)</t>
+          <t>Н1, восточная стена топочной</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5697,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Решётка наружная воздухозаборная 500×400, низ +2,600</t>
+          <t>Оголовок (зонт) воздуховода Ø250 выше кровли</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -5709,12 +5713,12 @@
         </is>
       </c>
       <c r="G180" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H180" s="1" t="inlineStr"/>
       <c r="I180" s="1" t="inlineStr">
         <is>
-          <t>Н1, восточная стена топочной</t>
+          <t>выброс П1, В2 (Ш-2)</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5728,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Оголовок (зонт) воздуховода Ø250 выше кровли</t>
+          <t>Оголовок (зонт) воздуховода Ø200 выше кровли</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -5740,12 +5744,12 @@
         </is>
       </c>
       <c r="G181" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H181" s="1" t="inlineStr"/>
       <c r="I181" s="1" t="inlineStr">
         <is>
-          <t>выброс П1, В2 (Ш-2)</t>
+          <t>ВЗ (кухонный зонт), шахта над мангалом 1.12</t>
         </is>
       </c>
     </row>
@@ -5755,7 +5759,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Оголовок (зонт) воздуховода Ø200 выше кровли</t>
+          <t>Решётка вытяжная настенная под воздуховод Ø250 (вытяжка топочной, естественная)</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -5776,7 +5780,7 @@
       <c r="H182" s="1" t="inlineStr"/>
       <c r="I182" s="1" t="inlineStr">
         <is>
-          <t>ВЗ (кухонный зонт), шахта над мангалом 1.12</t>
+          <t>В2, 188 м³/ч</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5790,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная под воздуховод Ø250 (вытяжка топочной, естественная)</t>
+          <t>Решётка переточная в низу наружной двери топочной, живое сечение не менее 0,08 м²</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -5807,7 +5811,7 @@
       <c r="H183" s="1" t="inlineStr"/>
       <c r="I183" s="1" t="inlineStr">
         <is>
-          <t>В2, 188 м³/ч</t>
+          <t>ПН, 282 м³/ч</t>
         </is>
       </c>
     </row>
@@ -5817,7 +5821,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Решётка переточная в низу наружной двери топочной, живое сечение не менее 0,08 м²</t>
+          <t>Решётка вентиляционная наружная 400×200</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -5833,12 +5837,12 @@
         </is>
       </c>
       <c r="G184" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H184" s="1" t="inlineStr"/>
       <c r="I184" s="1" t="inlineStr">
         <is>
-          <t>ПН, 282 м³/ч</t>
+          <t>гараж 1.5: приток внизу, вытяжка вверху</t>
         </is>
       </c>
     </row>
@@ -5848,14 +5852,10 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Решётка вентиляционная наружная 400×200</t>
-        </is>
-      </c>
-      <c r="C185" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Зонт кухонный над плитой 500–600 м³/ч, располагаемое давление не менее 200 Па при 600 м³/ч</t>
+        </is>
+      </c>
+      <c r="C185" s="1" t="inlineStr"/>
       <c r="D185" s="1" t="inlineStr"/>
       <c r="E185" s="1" t="inlineStr"/>
       <c r="F185" s="1" t="inlineStr">
@@ -5864,12 +5864,12 @@
         </is>
       </c>
       <c r="G185" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H185" s="1" t="inlineStr"/>
       <c r="I185" s="1" t="inlineStr">
         <is>
-          <t>гараж 1.5: приток внизу, вытяжка вверху</t>
+          <t>ВЗ, поставка Заказчика</t>
         </is>
       </c>
     </row>
@@ -5879,10 +5879,14 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Зонт кухонный над плитой 500–600 м³/ч, располагаемое давление не менее 200 Па при 600 м³/ч</t>
-        </is>
-      </c>
-      <c r="C186" s="1" t="inlineStr"/>
+          <t>Клапан обратный Ø150</t>
+        </is>
+      </c>
+      <c r="C186" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D186" s="1" t="inlineStr"/>
       <c r="E186" s="1" t="inlineStr"/>
       <c r="F186" s="1" t="inlineStr">
@@ -5896,7 +5900,7 @@
       <c r="H186" s="1" t="inlineStr"/>
       <c r="I186" s="1" t="inlineStr">
         <is>
-          <t>ВЗ, поставка Заказчика</t>
+          <t>ВЗ, на патрубке зонта</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5910,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ø150</t>
+          <t>Гильза для прохода воздуховода Ø200 в изоляции через наружную стену (под отверстие Ø320)</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -5927,7 +5931,7 @@
       <c r="H187" s="1" t="inlineStr"/>
       <c r="I187" s="1" t="inlineStr">
         <is>
-          <t>ВЗ, на патрубке зонта</t>
+          <t>ВЗ, сквозь стену на +3,400</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5941,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Гильза для прохода воздуховода Ø200 в изоляции через наружную стену (под отверстие Ø320)</t>
+          <t>Клапан компенсации Ø200 с электроприводом, сблокирован с ВЗ, в наружной стене с решёткой</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -5949,7 +5953,7 @@
       <c r="E188" s="1" t="inlineStr"/>
       <c r="F188" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G188" s="1" t="n">
@@ -5958,7 +5962,7 @@
       <c r="H188" s="1" t="inlineStr"/>
       <c r="I188" s="1" t="inlineStr">
         <is>
-          <t>ВЗ, сквозь стену на +3,400</t>
+          <t>КК</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5972,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Клапан компенсации Ø200 с электроприводом, сблокирован с ВЗ, в наружной стене с решёткой</t>
+          <t>Теплоизоляция воздуховодов рулонная толщиной 25 мм с паробарьером (фольга), класс горючести — по СП 60</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -5980,16 +5984,16 @@
       <c r="E189" s="1" t="inlineStr"/>
       <c r="F189" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G189" s="1" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H189" s="1" t="inlineStr"/>
       <c r="I189" s="1" t="inlineStr">
         <is>
-          <t>КК</t>
+          <t>Н и выброс П1 Ø250</t>
         </is>
       </c>
     </row>
@@ -5999,7 +6003,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Теплоизоляция воздуховодов рулонная толщиной 25 мм с паробарьером (фольга), класс горючести — по СП 60</t>
+          <t>Теплоизоляция воздуховода Ø200 из минеральной ваты, негорючая (НГ), толщина 50 мм, кашированная фольгой</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -6011,16 +6015,18 @@
       <c r="E190" s="1" t="inlineStr"/>
       <c r="F190" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="G190" s="1" t="n">
-        <v>16</v>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G190" s="1" t="inlineStr">
+        <is>
+          <t>6,8</t>
+        </is>
       </c>
       <c r="H190" s="1" t="inlineStr"/>
       <c r="I190" s="1" t="inlineStr">
         <is>
-          <t>Н и выброс П1 Ø250</t>
+          <t>ВЗ: холодная шахта, рядом дымоход мангала — только НГ</t>
         </is>
       </c>
     </row>
@@ -6030,30 +6036,24 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Теплоизоляция воздуховода Ø200 из минеральной ваты, негорючая (НГ), толщина 50 мм, кашированная фольгой</t>
-        </is>
-      </c>
-      <c r="C191" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Крепления воздуховодов: подвесы, хомуты с уплотнителем, шпильки, профиль</t>
+        </is>
+      </c>
+      <c r="C191" s="1" t="inlineStr"/>
       <c r="D191" s="1" t="inlineStr"/>
       <c r="E191" s="1" t="inlineStr"/>
       <c r="F191" s="1" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G191" s="1" t="inlineStr">
-        <is>
-          <t>6,8</t>
-        </is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G191" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="H191" s="1" t="inlineStr"/>
       <c r="I191" s="1" t="inlineStr">
         <is>
-          <t>ВЗ: холодная шахта, рядом дымоход мангала — только НГ</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
@@ -6063,84 +6063,100 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Крепления воздуховодов: подвесы, хомуты с уплотнителем, шпильки, профиль</t>
-        </is>
-      </c>
-      <c r="C192" s="1" t="inlineStr"/>
+          <t>Вентилятор канальный малошумный Ø100, 2 скорости, датчик влажности и таймер, IPX4, с обратным клапаном</t>
+        </is>
+      </c>
+      <c r="C192" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D192" s="1" t="inlineStr"/>
       <c r="E192" s="1" t="inlineStr"/>
       <c r="F192" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G192" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H192" s="1" t="inlineStr"/>
       <c r="I192" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>ВВ-б1 (с/у б3) — 25/50 м³/ч; ВВ-б2 (помывочная б7) — 60/100 м³/ч; лист 12</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="inlineStr"/>
-      <c r="B193" s="3" t="inlineStr">
-        <is>
-          <t>6. Кондиционирование (листы 9–11, 14)</t>
-        </is>
-      </c>
-      <c r="C193" s="1" t="n"/>
-      <c r="D193" s="1" t="n"/>
-      <c r="E193" s="1" t="n"/>
-      <c r="F193" s="1" t="n"/>
-      <c r="G193" s="1" t="n"/>
-      <c r="H193" s="1" t="n"/>
-      <c r="I193" s="1" t="n"/>
+      <c r="A193" s="1" t="n">
+        <v>186</v>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>Решётка вытяжная потолочная под воздуховод Ø100</t>
+        </is>
+      </c>
+      <c r="C193" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D193" s="1" t="inlineStr"/>
+      <c r="E193" s="1" t="inlineStr"/>
+      <c r="F193" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G193" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H193" s="1" t="inlineStr"/>
+      <c r="I193" s="1" t="inlineStr">
+        <is>
+          <t>ВВ-б1, ВВ-б2</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Наружный блок мини-VRV, тепловой насос, Qх = 22,4 кВт, ночной малошумный режим</t>
+          <t>Решётка наружная с гравитационными жалюзи Ø100</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии VRV-S, модель — по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr"/>
-      <c r="E194" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E194" s="1" t="inlineStr"/>
       <c r="F194" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G194" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H194" s="1" t="inlineStr"/>
       <c r="I194" s="1" t="inlineStr">
         <is>
-          <t>НБ-1, площадка у восточной стены топочной</t>
+          <t>ВВ-б1, ВВ-б2</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Рама опорная наружного блока высотой 0,3–0,5 м</t>
+          <t>Гильза Ø110 для прохода воздуховода Ø100 через наружную стену</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
@@ -6152,53 +6168,33 @@
       <c r="E195" s="1" t="inlineStr"/>
       <c r="F195" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G195" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H195" s="1" t="inlineStr"/>
       <c r="I195" s="1" t="inlineStr">
         <is>
-          <t>НБ-1, лист 14</t>
+          <t>ВВ-б1, ВВ-б2, ось +2,20</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
-        <v>188</v>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>Внутренний блок канальный тонкий, Qх = 5,6 кВт, ≈900 м³/ч</t>
-        </is>
-      </c>
-      <c r="C196" s="1" t="inlineStr">
-        <is>
-          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
-        </is>
-      </c>
-      <c r="D196" s="1" t="inlineStr"/>
-      <c r="E196" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
-      <c r="F196" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G196" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H196" s="1" t="inlineStr"/>
-      <c r="I196" s="1" t="inlineStr">
-        <is>
-          <t>К-1 (1.10), К-2 (1.10)</t>
-        </is>
-      </c>
+      <c r="A196" s="1" t="inlineStr"/>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>6. Кондиционирование (листы 9–11, 14)</t>
+        </is>
+      </c>
+      <c r="C196" s="1" t="n"/>
+      <c r="D196" s="1" t="n"/>
+      <c r="E196" s="1" t="n"/>
+      <c r="F196" s="1" t="n"/>
+      <c r="G196" s="1" t="n"/>
+      <c r="H196" s="1" t="n"/>
+      <c r="I196" s="1" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -6206,12 +6202,12 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок канальный тонкий, Qх = 3,6 кВт, ≈600 м³/ч</t>
+          <t>Наружный блок мини-VRV, тепловой насос, Qх = 22,4 кВт, ночной малошумный режим</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+          <t>Daikin серии VRV-S, модель — по каталогу Daikin</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr"/>
@@ -6231,7 +6227,7 @@
       <c r="H197" s="1" t="inlineStr"/>
       <c r="I197" s="1" t="inlineStr">
         <is>
-          <t>К-3 (1.11)</t>
+          <t>НБ-1, площадка у восточной стены топочной</t>
         </is>
       </c>
     </row>
@@ -6241,32 +6237,28 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок канальный тонкий, Qх = 2,8 кВт, ≈480 м³/ч</t>
+          <t>Рама опорная наружного блока высотой 0,3–0,5 м</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr"/>
-      <c r="E198" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E198" s="1" t="inlineStr"/>
       <c r="F198" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G198" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H198" s="1" t="inlineStr"/>
       <c r="I198" s="1" t="inlineStr">
         <is>
-          <t>К-4 (2.3), К-5 (2.4), К-6 (2.5), К-7 (2.7)</t>
+          <t>НБ-1, лист 14</t>
         </is>
       </c>
     </row>
@@ -6276,12 +6268,12 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Пульт управления внутренним блоком</t>
+          <t>Внутренний блок канальный тонкий, Qх = 5,6 кВт, ≈900 м³/ч</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>по каталогу Daikin</t>
+          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr"/>
@@ -6296,12 +6288,12 @@
         </is>
       </c>
       <c r="G199" s="1" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H199" s="1" t="inlineStr"/>
       <c r="I199" s="1" t="inlineStr">
         <is>
-          <t>тип — по решению Заказчика</t>
+          <t>К-1 (1.10), К-2 (1.10)</t>
         </is>
       </c>
     </row>
@@ -6311,12 +6303,12 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Разветвитель фреоновый REFNET</t>
+          <t>Внутренний блок канальный тонкий, Qх = 3,6 кВт, ≈600 м³/ч</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>по каталогу Daikin</t>
+          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr"/>
@@ -6331,12 +6323,12 @@
         </is>
       </c>
       <c r="G200" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H200" s="1" t="inlineStr"/>
       <c r="I200" s="1" t="inlineStr">
         <is>
-          <t>Р1…Р6</t>
+          <t>К-3 (1.11)</t>
         </is>
       </c>
     </row>
@@ -6346,28 +6338,32 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø6,35 мм</t>
+          <t>Внутренний блок канальный тонкий, Qх = 2,8 кВт, ≈480 м³/ч</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr"/>
-      <c r="E201" s="1" t="inlineStr"/>
+      <c r="E201" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F201" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G201" s="1" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H201" s="1" t="inlineStr"/>
       <c r="I201" s="1" t="inlineStr">
         <is>
-          <t>жидкость</t>
+          <t>К-4 (2.3), К-5 (2.4), К-6 (2.5), К-7 (2.7)</t>
         </is>
       </c>
     </row>
@@ -6377,28 +6373,32 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø9,52 мм</t>
+          <t>Пульт управления внутренним блоком</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по каталогу Daikin</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr"/>
-      <c r="E202" s="1" t="inlineStr"/>
+      <c r="E202" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F202" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G202" s="1" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="H202" s="1" t="inlineStr"/>
       <c r="I202" s="1" t="inlineStr">
         <is>
-          <t>жидкость</t>
+          <t>тип — по решению Заказчика</t>
         </is>
       </c>
     </row>
@@ -6408,28 +6408,32 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø12,70 мм</t>
+          <t>Разветвитель фреоновый REFNET</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по каталогу Daikin</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr"/>
-      <c r="E203" s="1" t="inlineStr"/>
+      <c r="E203" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F203" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G203" s="1" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="H203" s="1" t="inlineStr"/>
       <c r="I203" s="1" t="inlineStr">
         <is>
-          <t>газ</t>
+          <t>Р1…Р6</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6443,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø15,88 мм</t>
+          <t>Труба медная отожжённая для холодильной техники Ø6,35 мм</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
@@ -6455,12 +6459,12 @@
         </is>
       </c>
       <c r="G204" s="1" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H204" s="1" t="inlineStr"/>
       <c r="I204" s="1" t="inlineStr">
         <is>
-          <t>газ</t>
+          <t>жидкость</t>
         </is>
       </c>
     </row>
@@ -6470,7 +6474,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø19,05 мм</t>
+          <t>Труба медная отожжённая для холодильной техники Ø9,52 мм</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
@@ -6486,12 +6490,12 @@
         </is>
       </c>
       <c r="G205" s="1" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H205" s="1" t="inlineStr"/>
       <c r="I205" s="1" t="inlineStr">
         <is>
-          <t>газ</t>
+          <t>жидкость</t>
         </is>
       </c>
     </row>
@@ -6501,7 +6505,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø6,35, толщина — по паспорту Daikin</t>
+          <t>Труба медная отожжённая для холодильной техники Ø12,70 мм</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
@@ -6520,7 +6524,11 @@
         <v>19</v>
       </c>
       <c r="H206" s="1" t="inlineStr"/>
-      <c r="I206" s="1" t="inlineStr"/>
+      <c r="I206" s="1" t="inlineStr">
+        <is>
+          <t>газ</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -6528,7 +6536,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø9,52, толщина — по паспорту Daikin</t>
+          <t>Труба медная отожжённая для холодильной техники Ø15,88 мм</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
@@ -6544,10 +6552,14 @@
         </is>
       </c>
       <c r="G207" s="1" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="H207" s="1" t="inlineStr"/>
-      <c r="I207" s="1" t="inlineStr"/>
+      <c r="I207" s="1" t="inlineStr">
+        <is>
+          <t>газ</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
@@ -6555,7 +6567,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø12,70, толщина — по паспорту Daikin</t>
+          <t>Труба медная отожжённая для холодильной техники Ø19,05 мм</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
@@ -6571,10 +6583,14 @@
         </is>
       </c>
       <c r="G208" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H208" s="1" t="inlineStr"/>
-      <c r="I208" s="1" t="inlineStr"/>
+      <c r="I208" s="1" t="inlineStr">
+        <is>
+          <t>газ</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
@@ -6582,7 +6598,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø15,88, толщина — по паспорту Daikin</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø6,35, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
@@ -6598,7 +6614,7 @@
         </is>
       </c>
       <c r="G209" s="1" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H209" s="1" t="inlineStr"/>
       <c r="I209" s="1" t="inlineStr"/>
@@ -6609,7 +6625,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø19,05, толщина — по паспорту Daikin</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø9,52, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
@@ -6625,7 +6641,7 @@
         </is>
       </c>
       <c r="G210" s="1" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H210" s="1" t="inlineStr"/>
       <c r="I210" s="1" t="inlineStr"/>
@@ -6636,32 +6652,26 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Хладагент для дозаправки (тип — по паспорту НБ-1)</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø12,70, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
         <is>
-          <t>по паспорту НБ-1</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D211" s="1" t="inlineStr"/>
       <c r="E211" s="1" t="inlineStr"/>
       <c r="F211" s="1" t="inlineStr">
         <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="G211" s="1" t="inlineStr">
-        <is>
-          <t>2,17</t>
-        </is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G211" s="1" t="n">
+        <v>19</v>
       </c>
       <c r="H211" s="1" t="inlineStr"/>
-      <c r="I211" s="1" t="inlineStr">
-        <is>
-          <t>по расчёту, уточнить при пуске</t>
-        </is>
-      </c>
+      <c r="I211" s="1" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
@@ -6669,26 +6679,26 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода фреонопроводов и дренажа через наружную стену и перекрытие</t>
-        </is>
-      </c>
-      <c r="C212" s="1" t="inlineStr"/>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø15,88, толщина — по паспорту Daikin</t>
+        </is>
+      </c>
+      <c r="C212" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D212" s="1" t="inlineStr"/>
       <c r="E212" s="1" t="inlineStr"/>
       <c r="F212" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G212" s="1" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H212" s="1" t="inlineStr"/>
-      <c r="I212" s="1" t="inlineStr">
-        <is>
-          <t>стена топочной, Ш-1</t>
-        </is>
-      </c>
+      <c r="I212" s="1" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -6696,7 +6706,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Диффузор щелевой блока К в торце подшивки, L=1000 мм</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø19,05, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
@@ -6708,18 +6718,14 @@
       <c r="E213" s="1" t="inlineStr"/>
       <c r="F213" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G213" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H213" s="1" t="inlineStr"/>
-      <c r="I213" s="1" t="inlineStr">
-        <is>
-          <t>К-1, К-2</t>
-        </is>
-      </c>
+      <c r="I213" s="1" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -6727,28 +6733,30 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Диффузор щелевой блока К в торце подшивки, L=1100 мм</t>
+          <t>Хладагент для дозаправки (тип — по паспорту НБ-1)</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по паспорту НБ-1</t>
         </is>
       </c>
       <c r="D214" s="1" t="inlineStr"/>
       <c r="E214" s="1" t="inlineStr"/>
       <c r="F214" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G214" s="1" t="n">
-        <v>1</v>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="G214" s="1" t="inlineStr">
+        <is>
+          <t>2,17</t>
+        </is>
       </c>
       <c r="H214" s="1" t="inlineStr"/>
       <c r="I214" s="1" t="inlineStr">
         <is>
-          <t>К-3</t>
+          <t>по расчёту, уточнить при пуске</t>
         </is>
       </c>
     </row>
@@ -6758,14 +6766,10 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Камера (плёнум) блока К с присоединением к щелевому диффузору</t>
-        </is>
-      </c>
-      <c r="C215" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Гильза стальная для прохода фреонопроводов и дренажа через наружную стену и перекрытие</t>
+        </is>
+      </c>
+      <c r="C215" s="1" t="inlineStr"/>
       <c r="D215" s="1" t="inlineStr"/>
       <c r="E215" s="1" t="inlineStr"/>
       <c r="F215" s="1" t="inlineStr">
@@ -6774,12 +6778,12 @@
         </is>
       </c>
       <c r="G215" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H215" s="1" t="inlineStr"/>
       <c r="I215" s="1" t="inlineStr">
         <is>
-          <t>К-1…К-3, по месту</t>
+          <t>стена топочной, Ш-1</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6793,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Решётка рециркуляции потолочная ≈300×300 под блоком К</t>
+          <t>Диффузор щелевой блока К в торце подшивки, L=1000 мм</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
@@ -6805,12 +6809,12 @@
         </is>
       </c>
       <c r="G216" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H216" s="1" t="inlineStr"/>
       <c r="I216" s="1" t="inlineStr">
         <is>
-          <t>К-1…К-3</t>
+          <t>К-1, К-2</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6824,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Решётка щелевая настенная 800×150 с регулированием, с напорной камерой (подача К и свежего воздуха П1)</t>
+          <t>Диффузор щелевой блока К в торце подшивки, L=1100 мм</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
@@ -6836,12 +6840,12 @@
         </is>
       </c>
       <c r="G217" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H217" s="1" t="inlineStr"/>
       <c r="I217" s="1" t="inlineStr">
         <is>
-          <t>ЩП, спальни 2.3–2.5, 2.7</t>
+          <t>К-3</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6855,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Решётка щелевая настенная 800×150 с регулированием (возврат)</t>
+          <t>Камера (плёнум) блока К с присоединением к щелевому диффузору</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
@@ -6867,12 +6871,12 @@
         </is>
       </c>
       <c r="G218" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H218" s="1" t="inlineStr"/>
       <c r="I218" s="1" t="inlineStr">
         <is>
-          <t>ЩВ, спальни 2.3–2.5, 2.7</t>
+          <t>К-1…К-3, по месту</t>
         </is>
       </c>
     </row>
@@ -6882,24 +6886,28 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод прямоугольный из оцинкованной стали 250×150</t>
-        </is>
-      </c>
-      <c r="C219" s="1" t="inlineStr"/>
+          <t>Решётка рециркуляции потолочная ≈300×300 под блоком К</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D219" s="1" t="inlineStr"/>
       <c r="E219" s="1" t="inlineStr"/>
       <c r="F219" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G219" s="1" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H219" s="1" t="inlineStr"/>
       <c r="I219" s="1" t="inlineStr">
         <is>
-          <t>блоки К-4…К-7</t>
+          <t>К-1…К-3</t>
         </is>
       </c>
     </row>
@@ -6909,10 +6917,14 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° прямоугольный оцинкованный 250×150</t>
-        </is>
-      </c>
-      <c r="C220" s="1" t="inlineStr"/>
+          <t>Решётка щелевая настенная 800×150 с регулированием, с напорной камерой (подача К и свежего воздуха П1)</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D220" s="1" t="inlineStr"/>
       <c r="E220" s="1" t="inlineStr"/>
       <c r="F220" s="1" t="inlineStr">
@@ -6921,12 +6933,12 @@
         </is>
       </c>
       <c r="G220" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H220" s="1" t="inlineStr"/>
       <c r="I220" s="1" t="inlineStr">
         <is>
-          <t>блоки К-4…К-7</t>
+          <t>ЩП, спальни 2.3–2.5, 2.7</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6948,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
+          <t>Решётка щелевая настенная 800×150 с регулированием (возврат)</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
@@ -6948,16 +6960,16 @@
       <c r="E221" s="1" t="inlineStr"/>
       <c r="F221" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G221" s="1" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="H221" s="1" t="inlineStr"/>
       <c r="I221" s="1" t="inlineStr">
         <is>
-          <t>дренаж конденсата К-1…К-7</t>
+          <t>ЩВ, спальни 2.3–2.5, 2.7</t>
         </is>
       </c>
     </row>
@@ -6967,28 +6979,24 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП Ø32 (45°/90°)</t>
-        </is>
-      </c>
-      <c r="C222" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод прямоугольный из оцинкованной стали 250×150</t>
+        </is>
+      </c>
+      <c r="C222" s="1" t="inlineStr"/>
       <c r="D222" s="1" t="inlineStr"/>
       <c r="E222" s="1" t="inlineStr"/>
       <c r="F222" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G222" s="1" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H222" s="1" t="inlineStr"/>
       <c r="I222" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>блоки К-4…К-7</t>
         </is>
       </c>
     </row>
@@ -6998,14 +7006,10 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП Ø32</t>
-        </is>
-      </c>
-      <c r="C223" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 90° прямоугольный оцинкованный 250×150</t>
+        </is>
+      </c>
+      <c r="C223" s="1" t="inlineStr"/>
       <c r="D223" s="1" t="inlineStr"/>
       <c r="E223" s="1" t="inlineStr"/>
       <c r="F223" s="1" t="inlineStr">
@@ -7017,7 +7021,11 @@
         <v>5</v>
       </c>
       <c r="H223" s="1" t="inlineStr"/>
-      <c r="I223" s="1" t="inlineStr"/>
+      <c r="I223" s="1" t="inlineStr">
+        <is>
+          <t>блоки К-4…К-7</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -7025,30 +7033,119 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
-        </is>
-      </c>
-      <c r="C224" s="1" t="inlineStr"/>
+          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
+        </is>
+      </c>
+      <c r="C224" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D224" s="1" t="inlineStr"/>
       <c r="E224" s="1" t="inlineStr"/>
       <c r="F224" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G224" s="1" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H224" s="1" t="inlineStr"/>
       <c r="I224" s="1" t="inlineStr">
         <is>
+          <t>дренаж конденсата К-1…К-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Отвод ПП Ø32 (45°/90°)</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="inlineStr"/>
+      <c r="E225" s="1" t="inlineStr"/>
+      <c r="F225" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G225" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H225" s="1" t="inlineStr"/>
+      <c r="I225" s="1" t="inlineStr">
+        <is>
           <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr"/>
-      <c r="B226" t="inlineStr">
+      <c r="A226" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Тройник ПП Ø32</t>
+        </is>
+      </c>
+      <c r="C226" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D226" s="1" t="inlineStr"/>
+      <c r="E226" s="1" t="inlineStr"/>
+      <c r="F226" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G226" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H226" s="1" t="inlineStr"/>
+      <c r="I226" s="1" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
+        </is>
+      </c>
+      <c r="C227" s="1" t="inlineStr"/>
+      <c r="D227" s="1" t="inlineStr"/>
+      <c r="E227" s="1" t="inlineStr"/>
+      <c r="F227" s="1" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G227" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H227" s="1" t="inlineStr"/>
+      <c r="I227" s="1" t="inlineStr">
+        <is>
+          <t>по месту</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I229"/>
+  <dimension ref="A1:I225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,49 м³/ч, H=1,58 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,44 м³/ч, H=1,46 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,80 м³/ч, H=1,22 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,85 м³/ч, H=1,22 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная смесительная Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,89 м³/ч, H=1,83 м), трёхходовой смесительный клапан с электроприводом, краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Группа насосная смесительная Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-60 (G=0,86 м³/ч, H=3,54 м), трёхходовой смесительный клапан с электроприводом, краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная смесительная Ду 20 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,11 м³/ч, H=1,29 м), трёхходовой смесительный клапан с электроприводом, краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Отвод от РК к нагревателю П1 Ду 20 без насоса (G=0,11 м³/ч): краны шаровые — 2, фильтр сетчатый — 1, клапан балансировочный — 1, термометры — 2, манометры с кранами — 2</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -1010,7 +1010,7 @@
       <c r="E19" s="1" t="inlineStr"/>
       <c r="F19" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G19" s="1" t="n">
@@ -1019,7 +1019,7 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>Н5 → калорифер П1</t>
+          <t>Н5 → П1; насос и 3-ходовой клапан — в комплекте П1 (Turkov)</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная прямая Ду 32 в сборе: насос циркуляционный с электронным управлением класса 25-60 (G=1,64 м³/ч, H=2,84 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Группа насосная прямая Ду 32 в сборе: насос циркуляционный с электронным управлением класса 25-60 (G=1,62 м³/ч, H=2,81 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Шкаф управления котельной: каскадный погодозависимый контроллер (штатный Viessmann), управление ПК, насосами и клапанами групп, датчики температуры (наружный, ГС, Б1, обратка ПК, ТП, П1), удалённый доступ</t>
+          <t>Шкаф управления котельной: каскадный погодозависимый контроллер (штатный Viessmann), управление ПК, насосами и клапанами групп, датчики температуры (наружный, ГС, Б1, обратка ПК, ТП), удалённый доступ</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>ШУ; состав — по проекту автоматизации</t>
+          <t>ШУ; П1 — своя автоматика Turkov; состав — по проекту автоматизации</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 36,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,43 м³/ч, H=0,87 м), байпас, защитный термостат-ограничитель 45 °С</t>
+          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 36,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,44 м³/ч, H=0,97 м), байпас, защитный термостат-ограничитель 45 °С</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Коллектор прямой из нержавеющей стали 1" на 9 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"; выход В6 — резерв, с заглушками</t>
+          <t>Коллектор прямой из нержавеющей стали 1" на 7 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"; выход В6 — резерв, с заглушками</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 42,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,11 м³/ч, H=0,80 м), байпас, защитный термостат-ограничитель 55 °С</t>
+          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 42,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,07 м³/ч, H=0,58 м), байпас, защитный термостат-ограничитель 55 °С</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 22/500, L=1100 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1411 Вт</t>
+          <t>Радиатор стальной панельный 22/500, L=1700 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 2271 Вт</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 880 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 894 Вт</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2200 мм, тепловая мощность при 70/55 °С не менее 2355 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2200 мм, тепловая мощность при 70/55 °С не менее 2345 Вт</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Полотенцесушитель водяной, мощность не менее 599 Вт при 75/65/20 °С</t>
+          <t>Узел нижнего подключения радиатора запорный, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2463,12 +2463,12 @@
         </is>
       </c>
       <c r="G66" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>Пс-1 (2.8)</t>
+          <t>Р-1, Р-2, Р-3, Р-5</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Полотенцесушитель водяной, мощность не менее 239 Вт при 75/65/20 °С</t>
+          <t>Клапан термостатический G½" с термостатической головкой</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G67" s="1" t="n">
@@ -2499,7 +2499,7 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>Пс-2 (2.9)</t>
+          <t>Р-т</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Узел нижнего подключения радиатора запорный, присоединение евроконус G¾"</t>
+          <t>Клапан запорно-балансировочный G½"</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2525,12 +2525,12 @@
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>Р-1, Р-2, Р-3, Р-5</t>
+          <t>Р-т</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Клапан термостатический G½" с термостатической головкой</t>
+          <t>Клапан запорный G½" для подключения конвектора</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2552,16 +2552,16 @@
       <c r="E69" s="1" t="inlineStr"/>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>Р-т</t>
+          <t>Кв-1…Кв-8, Кн-1, Кн-3</t>
         </is>
       </c>
     </row>
@@ -2571,12 +2571,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Клапан запорно-балансировочный G½"</t>
+          <t>Тройник стальной переходной Ду 25×15 (отвод на Р-т от группы Н3)</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>ГОСТ 8949-75</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr"/>
@@ -2587,12 +2587,12 @@
         </is>
       </c>
       <c r="G70" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>Р-т</t>
+          <t>у РК</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Клапан запорный G½" для подключения конвектора</t>
+          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH), для отопления, t до 95 °С — петли тёплого пола</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -2614,16 +2614,16 @@
       <c r="E71" s="1" t="inlineStr"/>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G71" s="1" t="n">
-        <v>20</v>
+        <v>1335</v>
       </c>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>Кв-1…Кв-8, Кн-1, Кн-3</t>
+          <t>петли — 22 шт., листы 4, 5</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Комплект запорных клапанов для полотенцесушителя G½"</t>
+          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — подводки к приборам</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -2645,16 +2645,16 @@
       <c r="E72" s="1" t="inlineStr"/>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G72" s="1" t="n">
-        <v>2</v>
+        <v>532</v>
       </c>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>Пс-1, Пс-2</t>
+          <t>листы 3, 5</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Тройник стальной переходной Ду 25×15 (отвод на Р-т от группы Н3)</t>
+          <t>Фитинг компрессионный (евроконус) для трубы PE-Xa 16×2,0 на G¾"</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8949-75</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr"/>
@@ -2680,12 +2680,12 @@
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>у РК</t>
+          <t>коллекторы, радиаторы</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH), для отопления, t до 95 °С — петли тёплого пола</t>
+          <t>Фитинг компрессионный для трубы PE-Xa 16×2,0 на наружную резьбу G½"</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2707,16 +2707,16 @@
       <c r="E74" s="1" t="inlineStr"/>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G74" s="1" t="n">
-        <v>1512</v>
+        <v>24</v>
       </c>
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>петли — 22 шт., листы 4, 5</t>
+          <t>конвекторы, Р-т</t>
         </is>
       </c>
     </row>
@@ -2726,14 +2726,10 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — подводки к приборам</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена, толщина 6 мм, для трубы Ø16</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr"/>
       <c r="D75" s="1" t="inlineStr"/>
       <c r="E75" s="1" t="inlineStr"/>
       <c r="F75" s="1" t="inlineStr">
@@ -2742,12 +2738,12 @@
         </is>
       </c>
       <c r="G75" s="1" t="n">
-        <v>564</v>
+        <v>313</v>
       </c>
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>листы 3, 5</t>
+          <t>подводки 1 этажа</t>
         </is>
       </c>
     </row>
@@ -2757,14 +2753,10 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 20×2,8 с антидиффузионным слоем (EVOH) — магистрали</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Труба гофрированная защитная (гофра) для трубы Ø16</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr"/>
       <c r="D76" s="1" t="inlineStr"/>
       <c r="E76" s="1" t="inlineStr"/>
       <c r="F76" s="1" t="inlineStr">
@@ -2773,12 +2765,12 @@
         </is>
       </c>
       <c r="G76" s="1" t="n">
-        <v>38</v>
+        <v>532</v>
       </c>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>Н4 → КШ-1, Н5 → калорифер П1</t>
+          <t>подводки к приборам</t>
         </is>
       </c>
     </row>
@@ -2788,14 +2780,10 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 25×3,5 с антидиффузионным слоем (EVOH) — магистраль</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Труба гофрированная защитная (гофра) для трубы Ø16 на выходах петель из стяжки, по 1 м на конец</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr"/>
       <c r="D77" s="1" t="inlineStr"/>
       <c r="E77" s="1" t="inlineStr"/>
       <c r="F77" s="1" t="inlineStr">
@@ -2804,12 +2792,12 @@
         </is>
       </c>
       <c r="G77" s="1" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>Н2 → КШ-4, стояки в 1.7</t>
+          <t>у коллекторов</t>
         </is>
       </c>
     </row>
@@ -2819,30 +2807,22 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 32×4,4 с антидиффузионным слоем (EVOH) — магистрали</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Фиксатор поворота трубы Ø16 на 90° (выход из пола у коллектора)</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr"/>
       <c r="D78" s="1" t="inlineStr"/>
       <c r="E78" s="1" t="inlineStr"/>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G78" s="1" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="H78" s="1" t="inlineStr"/>
-      <c r="I78" s="1" t="inlineStr">
-        <is>
-          <t>Н3 → КШ-2, Н4 → КШ-3</t>
-        </is>
-      </c>
+      <c r="I78" s="1" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -2850,7 +2830,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Фитинг компрессионный (евроконус) для трубы PE-Xa 16×2,0 на G¾"</t>
+          <t>Труба PE-Xa 20×2,8 с антидиффузионным слоем (EVOH) — магистрали</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2862,16 +2842,16 @@
       <c r="E79" s="1" t="inlineStr"/>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G79" s="1" t="n">
-        <v>84</v>
+        <v>14</v>
       </c>
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>коллекторы, радиаторы</t>
+          <t>Н5 → нагреватель П1</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2861,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Фитинг компрессионный для трубы PE-Xa 16×2,0 на наружную резьбу G½"</t>
+          <t>Труба PE-Xa 25×3,5 с антидиффузионным слоем (EVOH) — магистрали</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -2893,16 +2873,16 @@
       <c r="E80" s="1" t="inlineStr"/>
       <c r="F80" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G80" s="1" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>конвекторы, полотенцесушители, Р-т</t>
+          <t>Н2 → КШ-4, стояки в 1.7, Н4 → КШ-1, Н4 → КШ-3</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2892,7 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 20×2,8 на резьбу G¾"</t>
+          <t>Труба PE-Xa 32×4,4 с антидиффузионным слоем (EVOH) — магистрали</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -2924,16 +2904,16 @@
       <c r="E81" s="1" t="inlineStr"/>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G81" s="1" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>концы магистралей</t>
+          <t>Н3 → КШ-2</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2923,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 25×3,5 на резьбу G1"</t>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 20×2,8 на резьбу G¾"</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -2964,7 +2944,7 @@
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>концы магистрали</t>
+          <t>концы магистралей</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2954,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×4,4 на резьбу G1"</t>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 25×3,5 на резьбу G1"</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -2990,7 +2970,7 @@
         </is>
       </c>
       <c r="G83" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
@@ -3005,24 +2985,28 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø20</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr"/>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×4,4 на резьбу G1"</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D84" s="1" t="inlineStr"/>
       <c r="E84" s="1" t="inlineStr"/>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G84" s="1" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>магистрали</t>
+          <t>концы магистралей</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3016,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø25</t>
+          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø20</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr"/>
@@ -3044,12 +3028,12 @@
         </is>
       </c>
       <c r="G85" s="1" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>магистраль</t>
+          <t>магистрали</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3043,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø32</t>
+          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø25</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr"/>
@@ -3071,7 +3055,7 @@
         </is>
       </c>
       <c r="G86" s="1" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H86" s="1" t="inlineStr"/>
       <c r="I86" s="1" t="inlineStr">
@@ -3086,7 +3070,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена, толщина 6 мм, для трубы Ø16</t>
+          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø32</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr"/>
@@ -3098,12 +3082,12 @@
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>313</v>
+        <v>22</v>
       </c>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>подводки 1 этажа</t>
+          <t>магистрали</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3097,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная (гофра) для трубы Ø16</t>
+          <t>Пленка (мат) с разметкой для укладки труб тёплого пола</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr"/>
@@ -3121,16 +3105,16 @@
       <c r="E88" s="1" t="inlineStr"/>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>564</v>
+        <v>178</v>
       </c>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>подводки к приборам</t>
+          <t>листы 4, 5</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3124,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная (гофра) для трубы Ø16 на выходах петель из стяжки, по 1 м на конец</t>
+          <t>Лента демпферная 10×150 мм</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr"/>
@@ -3152,12 +3136,12 @@
         </is>
       </c>
       <c r="G89" s="1" t="n">
-        <v>49</v>
+        <v>264</v>
       </c>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>у коллекторов</t>
+          <t>по периметру зон и по границам петель</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3151,7 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота трубы Ø16 на 90° (выход из пола у коллектора)</t>
+          <t>Скоба якорная для крепления трубы Ø16 к основанию, шаг 0,5 м</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr"/>
@@ -3179,106 +3163,122 @@
         </is>
       </c>
       <c r="G90" s="1" t="n">
-        <v>44</v>
+        <v>2700</v>
       </c>
       <c r="H90" s="1" t="inlineStr"/>
-      <c r="I90" s="1" t="inlineStr"/>
+      <c r="I90" s="1" t="inlineStr">
+        <is>
+          <t>листы 4, 5</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>Пленка (мат) с разметкой для укладки труб тёплого пола</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr"/>
-      <c r="D91" s="1" t="inlineStr"/>
-      <c r="E91" s="1" t="inlineStr"/>
-      <c r="F91" s="1" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="G91" s="1" t="n">
-        <v>206</v>
-      </c>
-      <c r="H91" s="1" t="inlineStr"/>
-      <c r="I91" s="1" t="inlineStr">
-        <is>
-          <t>листы 4, 5</t>
-        </is>
-      </c>
+      <c r="A91" s="1" t="inlineStr"/>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>3. Отопление бани (листы 12, 13)</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="n"/>
+      <c r="D91" s="1" t="n"/>
+      <c r="E91" s="1" t="n"/>
+      <c r="F91" s="1" t="n"/>
+      <c r="G91" s="1" t="n"/>
+      <c r="H91" s="1" t="n"/>
+      <c r="I91" s="1" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Лента демпферная 10×150 мм</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr"/>
+          <t>Шкаф коллекторный встроенный ШРВ-3 (ширина ≈750 мм), высота ≈650 мм</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D92" s="1" t="inlineStr"/>
       <c r="E92" s="1" t="inlineStr"/>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G92" s="1" t="n">
-        <v>264</v>
+        <v>1</v>
       </c>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>по периметру зон и по границам петель</t>
+          <t>КШ-Б1 (с/у б3)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Скоба якорная для крепления трубы Ø16 к основанию, шаг 0,5 м</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr"/>
+          <t>Коллектор прямой из нержавеющей стали 1" на 5 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D93" s="1" t="inlineStr"/>
       <c r="E93" s="1" t="inlineStr"/>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G93" s="1" t="n">
-        <v>3100</v>
+        <v>1</v>
       </c>
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>листы 4, 5</t>
+          <t>КШ-Б1 (с/у б3)</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr"/>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>3. Отопление бани (листы 12, 13)</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="n"/>
-      <c r="D94" s="1" t="n"/>
-      <c r="E94" s="1" t="n"/>
-      <c r="F94" s="1" t="n"/>
-      <c r="G94" s="1" t="n"/>
-      <c r="H94" s="1" t="n"/>
-      <c r="I94" s="1" t="n"/>
+      <c r="A94" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Шкаф коллекторный встроенный ШРВ-3 (ширина ≈750 мм), двухъярусный, высота ≈1250 мм</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="inlineStr"/>
+      <c r="E94" s="1" t="inlineStr"/>
+      <c r="F94" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G94" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H94" s="1" t="inlineStr"/>
+      <c r="I94" s="1" t="inlineStr">
+        <is>
+          <t>КШ-Б2 (с/у б3)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встроенный ШРВ-3 (ширина ≈750 мм), высота ≈650 мм</t>
+          <t>Коллектор тёплого пола из нержавеющей стали 1" на 7 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -3298,7 +3298,7 @@
       <c r="E95" s="1" t="inlineStr"/>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G95" s="1" t="n">
@@ -3307,7 +3307,7 @@
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>КШ-Б1 (с/у б3)</t>
+          <t>КШ-Б2 (с/у б3)</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Коллектор прямой из нержавеющей стали 1" на 6 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 44,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,17 м³/ч, H=0,96 м), байпас, защитный термостат-ограничитель 55 °С</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -3338,7 +3338,7 @@
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>КШ-Б1 (с/у б3)</t>
+          <t>КШ-Б2 (с/у б3)</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встроенный ШРВ-3 (ширина ≈750 мм), двухъярусный, высота ≈1250 мм</t>
+          <t>Кран шаровой полнопроходной G1" (ввод Ecoflex, подача и обратка)</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -3364,12 +3364,12 @@
         </is>
       </c>
       <c r="G97" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>КШ-Б2 (с/у б3)</t>
+          <t>ввод КШ-Б1</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Коллектор тёплого пола из нержавеющей стали 1" на 7 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+          <t>Фильтр сетчатый G1" (ввод, подача)</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -3391,7 +3391,7 @@
       <c r="E98" s="1" t="inlineStr"/>
       <c r="F98" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G98" s="1" t="n">
@@ -3400,7 +3400,7 @@
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>КШ-Б2 (с/у б3)</t>
+          <t>ФС</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 44,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,17 м³/ч, H=0,95 м), байпас, защитный термостат-ограничитель 55 °С</t>
+          <t>Клапан трёхходовой переключающий с электроприводом Ду 25, расход 1146 кг/ч; приоритет загрузки Б2 по датчику бойлера</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -3422,7 +3422,7 @@
       <c r="E99" s="1" t="inlineStr"/>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G99" s="1" t="n">
@@ -3431,7 +3431,7 @@
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>КШ-Б2 (с/у б3)</t>
+          <t>УК1</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой полнопроходной G1" (ввод Ecoflex, подача и обратка)</t>
+          <t>Клапан зональный двухходовой с электроприводом Ду 25 (линия ТО-Д, по таймеру СПА)</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -3457,12 +3457,12 @@
         </is>
       </c>
       <c r="G100" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>ввод КШ-Б1</t>
+          <t>УК2</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Фильтр сетчатый G1" (ввод, подача)</t>
+          <t>Клапан балансировочный Ду 25 (линия ТО-Д)</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -3493,7 +3493,7 @@
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>ФС</t>
+          <t>ТО-Д</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Клапан трёхходовой переключающий с электроприводом Ду 25, расход 1146 кг/ч; приоритет загрузки Б2 по датчику бойлера</t>
+          <t>Теплообменник пластинчатый 20 кВт, 70/50 → 38/28 °С, расход греющей воды 860 кг/ч</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -3524,7 +3524,7 @@
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>УК1</t>
+          <t>ТО-Д; вторичный контур — СПА (ВК)</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Клапан зональный двухходовой с электроприводом Ду 25 (линия ТО-Д, по таймеру СПА)</t>
+          <t>Бойлер косвенного нагрева 200 л, узкий Ø520 мм, змеевик 20 кВт (расход 1146 кг/ч)</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -3555,7 +3555,7 @@
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>УК2</t>
+          <t>Б2; обвязка ГВС — раздел ВК</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Клапан балансировочный Ду 25 (линия ТО-Д)</t>
+          <t>Сервопривод термоэлектрический 230 В, нормально закрытый, на термостатический клапан коллектора</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -3581,12 +3581,12 @@
         </is>
       </c>
       <c r="G104" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>ТО-Д</t>
+          <t>управление — автоматика «Люкс»</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Теплообменник пластинчатый 20 кВт, 70/50 → 38/28 °С, расход греющей воды 860 кг/ч</t>
+          <t>Радиатор стальной панельный 33/500, L=1100 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1528 Вт</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -3617,7 +3617,7 @@
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>ТО-Д; вторичный контур — СПА (ВК)</t>
+          <t>Р-б1 (б5)</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Бойлер косвенного нагрева 200 л, узкий Ø520 мм, змеевик 20 кВт (расход 1146 кг/ч)</t>
+          <t>Радиатор стальной панельный 33/500, L=500 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 632 Вт</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -3648,7 +3648,7 @@
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>Б2; обвязка ГВС — раздел ВК</t>
+          <t>Р-б2 (б2)</t>
         </is>
       </c>
     </row>
@@ -3658,28 +3658,32 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Сервопривод термоэлектрический 230 В, нормально закрытый, на термостатический клапан коллектора</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2150 мм, тепловая мощность при 70/55 °С не менее 1108 Вт</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr"/>
-      <c r="E107" s="1" t="inlineStr"/>
+      <c r="E107" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>управление — автоматика «Люкс»</t>
+          <t>Кв-б1 (б6), Кв-б2 (б6)</t>
         </is>
       </c>
     </row>
@@ -3689,16 +3693,20 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 33/500, L=1100 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1528 Вт</t>
+          <t>Конвектор внутрипольный из нержавеющей стали для влажных помещений, с вентилятором 24 В пост. тока, 260×140 мм, L=2200 мм, тепловая мощность при 70/55 °С не менее 2614 Вт</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>КЗТО «Бриз В TURBO Нерж»</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr"/>
-      <c r="E108" s="1" t="inlineStr"/>
+      <c r="E108" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -3710,7 +3718,7 @@
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>Р-б1 (б5)</t>
+          <t>Кв-б3 (б7, у джакузи); в нише плиты, ≈2030 Вт/м при Δt50</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3728,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 33/500, L=500 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 632 Вт</t>
+          <t>Узел нижнего подключения радиатора запорный, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -3736,12 +3744,12 @@
         </is>
       </c>
       <c r="G109" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>Р-б2 (б2)</t>
+          <t>Р-б1, Р-б2</t>
         </is>
       </c>
     </row>
@@ -3751,32 +3759,28 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2150 мм, тепловая мощность при 70/55 °С не менее 1108 Вт</t>
+          <t>Клапан запорный G½" для подключения конвектора</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
         <is>
-          <t>КЗТО «Бриз В», модель — по каталогу</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D110" s="1" t="inlineStr"/>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E110" s="1" t="inlineStr"/>
       <c r="F110" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G110" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>Кв-б1 (б6), Кв-б2 (б6)</t>
+          <t>Кв-б1…Кв-б3</t>
         </is>
       </c>
     </row>
@@ -3786,7 +3790,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Полотенцесушитель водяной, мощность не менее 590 Вт при 75/65/20 °С</t>
+          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — петли тёплого пола</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -3798,16 +3802,16 @@
       <c r="E111" s="1" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>1</v>
+        <v>271</v>
       </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>Пс-б2 (б4)</t>
+          <t>петли — 7 шт., лист 12</t>
         </is>
       </c>
     </row>
@@ -3817,32 +3821,28 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный из нержавеющей стали для влажных помещений, с вентилятором 24 В пост. тока, 260×140 мм, L=2200 мм, тепловая мощность при 70/55 °С не менее 2614 Вт</t>
+          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — подводки к приборам</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>КЗТО «Бриз В TURBO Нерж»</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr"/>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E112" s="1" t="inlineStr"/>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G112" s="1" t="n">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>Кв-б3 (б7, у джакузи); в нише плиты, ≈2030 Вт/м при Δt50</t>
+          <t>лист 12</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Узел нижнего подключения радиатора запорный, присоединение евроконус G¾"</t>
+          <t>Труба PE-Xa 32×4,4 с антидиффузионным слоем (EVOH) — линии ТО-Д и Б2</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -3864,16 +3864,16 @@
       <c r="E113" s="1" t="inlineStr"/>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G113" s="1" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>Р-б1, Р-б2</t>
+          <t>от ввода КШ-Б1</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3883,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Клапан запорный G½" для подключения конвектора</t>
+          <t>Фитинг компрессионный (евроконус) для трубы PE-Xa 16×2,0 на G¾"</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -3899,12 +3899,12 @@
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>Кв-б1…Кв-б3</t>
+          <t>коллекторы, радиаторы</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3914,7 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Комплект запорных клапанов для полотенцесушителя G½"</t>
+          <t>Фитинг компрессионный для трубы PE-Xa 16×2,0 на наружную резьбу G½"</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -3926,16 +3926,16 @@
       <c r="E115" s="1" t="inlineStr"/>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G115" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>Пс-б2</t>
+          <t>конвекторы</t>
         </is>
       </c>
     </row>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — петли тёплого пола</t>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×4,4 на резьбу G1"</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
@@ -3957,16 +3957,16 @@
       <c r="E116" s="1" t="inlineStr"/>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G116" s="1" t="n">
-        <v>272</v>
+        <v>8</v>
       </c>
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>петли — 7 шт., лист 12</t>
+          <t>ТО-Д, Б2</t>
         </is>
       </c>
     </row>
@@ -3976,14 +3976,10 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — подводки к приборам</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø32</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="inlineStr"/>
       <c r="D117" s="1" t="inlineStr"/>
       <c r="E117" s="1" t="inlineStr"/>
       <c r="F117" s="1" t="inlineStr">
@@ -3992,12 +3988,12 @@
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>лист 12</t>
+          <t>ТО-Д, Б2</t>
         </is>
       </c>
     </row>
@@ -4007,14 +4003,10 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 32×4,4 с антидиффузионным слоем (EVOH) — линии ТО-Д и Б2</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена, толщина 6 мм, для трубы Ø16</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="inlineStr"/>
       <c r="D118" s="1" t="inlineStr"/>
       <c r="E118" s="1" t="inlineStr"/>
       <c r="F118" s="1" t="inlineStr">
@@ -4023,12 +4015,12 @@
         </is>
       </c>
       <c r="G118" s="1" t="n">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>от ввода КШ-Б1</t>
+          <t>подводки вне своих петель</t>
         </is>
       </c>
     </row>
@@ -4038,28 +4030,24 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Фитинг компрессионный (евроконус) для трубы PE-Xa 16×2,0 на G¾"</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Труба гофрированная защитная (гофра) для трубы Ø16</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="inlineStr"/>
       <c r="D119" s="1" t="inlineStr"/>
       <c r="E119" s="1" t="inlineStr"/>
       <c r="F119" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G119" s="1" t="n">
-        <v>30</v>
+        <v>252</v>
       </c>
       <c r="H119" s="1" t="inlineStr"/>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>коллекторы, радиаторы</t>
+          <t>подводки вне своих петель</t>
         </is>
       </c>
     </row>
@@ -4069,14 +4057,10 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Фитинг компрессионный для трубы PE-Xa 16×2,0 на наружную резьбу G½"</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Фиксатор поворота трубы Ø16 на 90° (выход из пола у коллектора)</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr"/>
       <c r="D120" s="1" t="inlineStr"/>
       <c r="E120" s="1" t="inlineStr"/>
       <c r="F120" s="1" t="inlineStr">
@@ -4085,14 +4069,10 @@
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H120" s="1" t="inlineStr"/>
-      <c r="I120" s="1" t="inlineStr">
-        <is>
-          <t>конвекторы, полотенцесушители</t>
-        </is>
-      </c>
+      <c r="I120" s="1" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -4100,28 +4080,24 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×4,4 на резьбу G1"</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Пленка (мат) с разметкой для укладки труб тёплого пола</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr"/>
       <c r="D121" s="1" t="inlineStr"/>
       <c r="E121" s="1" t="inlineStr"/>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>ТО-Д, Б2</t>
+          <t>лист 12</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4107,7 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø32</t>
+          <t>Лента демпферная 10×150 мм</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr"/>
@@ -4143,12 +4119,12 @@
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>ТО-Д, Б2</t>
+          <t>по периметру зон и по границам петель</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4134,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена, толщина 6 мм, для трубы Ø16</t>
+          <t>Скоба якорная для крепления трубы Ø16 к основанию, шаг 0,5 м</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr"/>
@@ -4166,130 +4142,146 @@
       <c r="E123" s="1" t="inlineStr"/>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>261</v>
+        <v>600</v>
       </c>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>подводки вне своих петель</t>
+          <t>лист 12</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
-        <v>119</v>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>Труба гофрированная защитная (гофра) для трубы Ø16</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr"/>
-      <c r="D124" s="1" t="inlineStr"/>
-      <c r="E124" s="1" t="inlineStr"/>
-      <c r="F124" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G124" s="1" t="n">
-        <v>261</v>
-      </c>
-      <c r="H124" s="1" t="inlineStr"/>
-      <c r="I124" s="1" t="inlineStr">
-        <is>
-          <t>подводки вне своих петель</t>
-        </is>
-      </c>
+      <c r="A124" s="1" t="inlineStr"/>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>4. Теплотрасса дом – баня (листы 13, 14)</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="n"/>
+      <c r="D124" s="1" t="n"/>
+      <c r="E124" s="1" t="n"/>
+      <c r="F124" s="1" t="n"/>
+      <c r="G124" s="1" t="n"/>
+      <c r="H124" s="1" t="n"/>
+      <c r="I124" s="1" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота трубы Ø16 на 90° (выход из пола у коллектора)</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr"/>
+          <t>Труба предизолированная гибкая: две трубы PE-Xa 32×2,9 отопления и две санитарные трубы (по разделу ВК) в общей оболочке</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>Uponor Ecoflex Quattro, типоразмер — по каталогу</t>
+        </is>
+      </c>
       <c r="D125" s="1" t="inlineStr"/>
-      <c r="E125" s="1" t="inlineStr"/>
+      <c r="E125" s="1" t="inlineStr">
+        <is>
+          <t>Uponor</t>
+        </is>
+      </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G125" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H125" s="1" t="inlineStr"/>
-      <c r="I125" s="1" t="inlineStr"/>
+      <c r="I125" s="1" t="inlineStr">
+        <is>
+          <t>≈16,4 м по трассе с подъёмами + 10 %; лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Пленка (мат) с разметкой для укладки труб тёплого пола</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr"/>
+          <t>Манжета концевая для трубы Ecoflex Quattro</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>по каталогу производителя трубы</t>
+        </is>
+      </c>
       <c r="D126" s="1" t="inlineStr"/>
-      <c r="E126" s="1" t="inlineStr"/>
+      <c r="E126" s="1" t="inlineStr">
+        <is>
+          <t>Uponor</t>
+        </is>
+      </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G126" s="1" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="H126" s="1" t="inlineStr"/>
       <c r="I126" s="1" t="inlineStr">
         <is>
-          <t>лист 12</t>
+          <t>вводы в дом и баню</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Лента демпферная 10×150 мм</t>
-        </is>
-      </c>
-      <c r="C127" s="1" t="inlineStr"/>
+          <t>Гильза ввода с уплотнительным кольцом через фундамент (комплект ввода производителя)</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>по каталогу производителя трубы</t>
+        </is>
+      </c>
       <c r="D127" s="1" t="inlineStr"/>
-      <c r="E127" s="1" t="inlineStr"/>
+      <c r="E127" s="1" t="inlineStr">
+        <is>
+          <t>Uponor</t>
+        </is>
+      </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G127" s="1" t="n">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>по периметру зон и по границам петель</t>
+          <t>узлы 1, 2, лист 13</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Скоба якорная для крепления трубы Ø16 к основанию, шаг 0,5 м</t>
+          <t>Гильза в плите пола для трубы Ecoflex Quattro</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr"/>
@@ -4301,29 +4293,45 @@
         </is>
       </c>
       <c r="G128" s="1" t="n">
-        <v>600</v>
+        <v>2</v>
       </c>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>лист 12</t>
+          <t>узлы 1, 2, лист 13</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="inlineStr"/>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>4. Теплотрасса дом – баня (листы 13, 14)</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="n"/>
-      <c r="D129" s="1" t="n"/>
-      <c r="E129" s="1" t="n"/>
-      <c r="F129" s="1" t="n"/>
-      <c r="G129" s="1" t="n"/>
-      <c r="H129" s="1" t="n"/>
-      <c r="I129" s="1" t="n"/>
+      <c r="A129" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×2,9 на резьбу G1"</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>по каталогу производителя трубы</t>
+        </is>
+      </c>
+      <c r="D129" s="1" t="inlineStr"/>
+      <c r="E129" s="1" t="inlineStr"/>
+      <c r="F129" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G129" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H129" s="1" t="inlineStr"/>
+      <c r="I129" s="1" t="inlineStr">
+        <is>
+          <t>концы Т1, Т2</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -4331,115 +4339,91 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Труба предизолированная гибкая: две трубы PE-Xa 32×2,9 отопления и две санитарные трубы (по разделу ВК) в общей оболочке</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>Uponor Ecoflex Quattro, типоразмер — по каталогу</t>
-        </is>
-      </c>
+          <t>Лента сигнальная «Осторожно, теплотрасса»</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="inlineStr"/>
       <c r="D130" s="1" t="inlineStr"/>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t>Uponor</t>
-        </is>
-      </c>
+      <c r="E130" s="1" t="inlineStr"/>
       <c r="F130" s="1" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
       <c r="G130" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr">
         <is>
-          <t>≈16,4 м по трассе с подъёмами + 10 %; лист 14</t>
+          <t>300 мм над трубой</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
-        <v>125</v>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>Манжета концевая для трубы Ecoflex Quattro</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>по каталогу производителя трубы</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr"/>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>Uponor</t>
-        </is>
-      </c>
-      <c r="F131" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G131" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H131" s="1" t="inlineStr"/>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t>вводы в дом и баню</t>
-        </is>
-      </c>
+      <c r="A131" s="1" t="inlineStr"/>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>5. Вентиляция (листы 9–12)</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="n"/>
+      <c r="D131" s="1" t="n"/>
+      <c r="E131" s="1" t="n"/>
+      <c r="F131" s="1" t="n"/>
+      <c r="G131" s="1" t="n"/>
+      <c r="H131" s="1" t="n"/>
+      <c r="I131" s="1" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Гильза ввода с уплотнительным кольцом через фундамент (комплект ввода производителя)</t>
+          <t>Приточно-вытяжная установка с рекуперацией тепла и влаги (пластинчатый энтальпийный рекуператор), 750 м³/ч, свободный напор ≈180 Па при 750 м³/ч (по расчёту сети 159 Па при 700 м³/ч), водяной нагреватель (≈2,6 кВт, 70/50 °С) со смесительным узлом и автоматикой в комплекте, патрубки Ø250, ≈1500×1080×610 мм, ≈145 кг, 220 В, ≈0,8 кВт</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>по каталогу производителя трубы</t>
+          <t>Turkov Zenit 750 Heco W (или аналог)</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr"/>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>Uponor</t>
+          <t>Turkov</t>
         </is>
       </c>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G132" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>узлы 1, 2, лист 13</t>
+          <t>П1, под потолком топочной (лист 9)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Гильза в плите пола для трубы Ecoflex Quattro</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr"/>
+          <t>Кран шаровой G¾" (подключение нагревателя П1 к смесительному узлу, подача и обратка)</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D133" s="1" t="inlineStr"/>
       <c r="E133" s="1" t="inlineStr"/>
       <c r="F133" s="1" t="inlineStr">
@@ -4453,29 +4437,29 @@
       <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr">
         <is>
-          <t>узлы 1, 2, лист 13</t>
+          <t>П1; фильтр — на отводе Н5 у РК</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×2,9 на резьбу G1"</t>
+          <t>Труба полипропиленовая канализационная Ø32 — дренаж конденсата П1 к трапу топочной (сифон с сухим затвором — раздел ВК)</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>по каталогу производителя трубы</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr"/>
       <c r="E134" s="1" t="inlineStr"/>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G134" s="1" t="n">
@@ -4484,51 +4468,71 @@
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr">
         <is>
-          <t>концы Т1, Т2</t>
+          <t>П1: опуск с +2,450 к трапу (листы 7, 9)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Лента сигнальная «Осторожно, теплотрасса»</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr"/>
+          <t>Клапан воздушный круглый Ø250 с электроприводом 230 В с возвратной пружиной (нормально закрыт), на наружном воздухе П1; не ставится, если встроен в установку Turkov</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D135" s="1" t="inlineStr"/>
       <c r="E135" s="1" t="inlineStr"/>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G135" s="1" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>300 мм над трубой</t>
+          <t>КВ-Н; защита нагревателя П1 от разморозки при отключении питания</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="inlineStr"/>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>5. Вентиляция (листы 9–12)</t>
-        </is>
-      </c>
-      <c r="C136" s="1" t="n"/>
-      <c r="D136" s="1" t="n"/>
-      <c r="E136" s="1" t="n"/>
-      <c r="F136" s="1" t="n"/>
-      <c r="G136" s="1" t="n"/>
-      <c r="H136" s="1" t="n"/>
-      <c r="I136" s="1" t="n"/>
+      <c r="A136" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Шумоглушитель круглый Ø250, L=600 мм</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D136" s="1" t="inlineStr"/>
+      <c r="E136" s="1" t="inlineStr"/>
+      <c r="F136" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G136" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H136" s="1" t="inlineStr"/>
+      <c r="I136" s="1" t="inlineStr">
+        <is>
+          <t>ШГ, на П и В у П1, между опуском и западной стеной топочной</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -4536,28 +4540,24 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Установка приточно-вытяжная с роторным рекуператором (КПД не менее 80 %), 700 м³/ч, свободный напор не менее 200 Па (по расчёту 159 Па), водяной калорифер ≈2,6 кВт (70/50 °С), фильтры ePM1 50 % / ePM10 50 %, автоматика с защитой калорифера от замерзания</t>
-        </is>
-      </c>
-      <c r="C137" s="1" t="inlineStr">
-        <is>
-          <t>марка — по выбору Заказчика</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø100, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="inlineStr"/>
       <c r="D137" s="1" t="inlineStr"/>
       <c r="E137" s="1" t="inlineStr"/>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G137" s="1" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr">
         <is>
-          <t>П1, под потолком топочной, низ +2,900</t>
+          <t>П1 — 29 м; баня ВВ-б1, ВВ-б2 — 3 м</t>
         </is>
       </c>
     </row>
@@ -4567,23 +4567,19 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой G¾" (обвязка калорифера П1, подача и обратка)</t>
-        </is>
-      </c>
-      <c r="C138" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø125, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="inlineStr"/>
       <c r="D138" s="1" t="inlineStr"/>
       <c r="E138" s="1" t="inlineStr"/>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G138" s="1" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
@@ -4598,28 +4594,26 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Фильтр сетчатый G¾" (обвязка калорифера П1)</t>
-        </is>
-      </c>
-      <c r="C139" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø150, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="inlineStr"/>
       <c r="D139" s="1" t="inlineStr"/>
       <c r="E139" s="1" t="inlineStr"/>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G139" s="1" t="n">
-        <v>1</v>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G139" s="1" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
       </c>
       <c r="H139" s="1" t="inlineStr"/>
       <c r="I139" s="1" t="inlineStr">
         <is>
-          <t>П1</t>
+          <t>ВЗ (кухонный зонт)</t>
         </is>
       </c>
     </row>
@@ -4629,28 +4623,24 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Шумоглушитель круглый Ø250, L=1000 мм</t>
-        </is>
-      </c>
-      <c r="C140" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø160, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="inlineStr"/>
       <c r="D140" s="1" t="inlineStr"/>
       <c r="E140" s="1" t="inlineStr"/>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G140" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr">
         <is>
-          <t>ШГ, на П и В у П1</t>
+          <t>П1</t>
         </is>
       </c>
     </row>
@@ -4660,7 +4650,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø100, толщина стали — по СП 60.13330</t>
+          <t>Воздуховод круглый из оцинкованной стали Ø200, толщина стали — по СП 60.13330</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr"/>
@@ -4671,13 +4661,15 @@
           <t>м</t>
         </is>
       </c>
-      <c r="G141" s="1" t="n">
-        <v>32</v>
+      <c r="G141" s="1" t="inlineStr">
+        <is>
+          <t>24,8</t>
+        </is>
       </c>
       <c r="H141" s="1" t="inlineStr"/>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>П1 — 29 м; баня ВВ-б1, ВВ-б2 — 3 м</t>
+          <t>П1 — 18 м; ВЗ (кухонный зонт) — 6,8 м</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4679,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø125, толщина стали — по СП 60.13330</t>
+          <t>Воздуховод круглый из оцинкованной стали Ø250, толщина стали — по СП 60.13330</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr"/>
@@ -4699,12 +4691,12 @@
         </is>
       </c>
       <c r="G142" s="1" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr">
         <is>
-          <t>П1</t>
+          <t>П1: магистрали, Н, выброс в Ш-2; В2 в Ш-2</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4706,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø150, толщина стали — по СП 60.13330</t>
+          <t>Отвод 90° круглый оцинкованный Ø100</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr"/>
@@ -4722,18 +4714,16 @@
       <c r="E143" s="1" t="inlineStr"/>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G143" s="1" t="inlineStr">
-        <is>
-          <t>2,7</t>
-        </is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G143" s="1" t="n">
+        <v>11</v>
       </c>
       <c r="H143" s="1" t="inlineStr"/>
       <c r="I143" s="1" t="inlineStr">
         <is>
-          <t>ВЗ (кухонный зонт)</t>
+          <t>в т. ч. баня ВВ-б1, ВВ-б2 — 2</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4733,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø160, толщина стали — по СП 60.13330</t>
+          <t>Отвод 90° круглый оцинкованный Ø125</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr"/>
@@ -4751,18 +4741,14 @@
       <c r="E144" s="1" t="inlineStr"/>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G144" s="1" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="H144" s="1" t="inlineStr"/>
-      <c r="I144" s="1" t="inlineStr">
-        <is>
-          <t>П1</t>
-        </is>
-      </c>
+      <c r="I144" s="1" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -4770,7 +4756,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø200, толщина стали — по СП 60.13330</t>
+          <t>Отвод 90° круглый оцинкованный Ø150</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr"/>
@@ -4778,18 +4764,16 @@
       <c r="E145" s="1" t="inlineStr"/>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G145" s="1" t="inlineStr">
-        <is>
-          <t>24,8</t>
-        </is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G145" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="H145" s="1" t="inlineStr"/>
       <c r="I145" s="1" t="inlineStr">
         <is>
-          <t>П1 — 18 м; ВЗ (кухонный зонт) — 6,8 м</t>
+          <t>ВЗ (кухонный зонт)</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4783,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø250, толщина стали — по СП 60.13330</t>
+          <t>Отвод 90° круглый оцинкованный Ø160</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr"/>
@@ -4807,18 +4791,14 @@
       <c r="E146" s="1" t="inlineStr"/>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G146" s="1" t="n">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="H146" s="1" t="inlineStr"/>
-      <c r="I146" s="1" t="inlineStr">
-        <is>
-          <t>П1: магистрали, Н, выброс в Ш-2; В2 в Ш-2</t>
-        </is>
-      </c>
+      <c r="I146" s="1" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -4826,7 +4806,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø100</t>
+          <t>Отвод 90° круглый оцинкованный Ø200</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr"/>
@@ -4838,12 +4818,12 @@
         </is>
       </c>
       <c r="G147" s="1" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="H147" s="1" t="inlineStr"/>
       <c r="I147" s="1" t="inlineStr">
         <is>
-          <t>в т. ч. баня ВВ-б1, ВВ-б2 — 2</t>
+          <t>в т. ч. ВЗ (кухонный зонт) — 1</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4833,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø125</t>
+          <t>Отвод 90° круглый оцинкованный Ø250</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr"/>
@@ -4865,7 +4845,7 @@
         </is>
       </c>
       <c r="G148" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H148" s="1" t="inlineStr"/>
       <c r="I148" s="1" t="inlineStr"/>
@@ -4876,7 +4856,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø150</t>
+          <t>Тройник круглый оцинкованный Ø125/Ø100</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr"/>
@@ -4891,11 +4871,7 @@
         <v>3</v>
       </c>
       <c r="H149" s="1" t="inlineStr"/>
-      <c r="I149" s="1" t="inlineStr">
-        <is>
-          <t>ВЗ (кухонный зонт)</t>
-        </is>
-      </c>
+      <c r="I149" s="1" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -4903,7 +4879,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø160</t>
+          <t>Тройник круглый оцинкованный Ø160/Ø100</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr"/>
@@ -4915,7 +4891,7 @@
         </is>
       </c>
       <c r="G150" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H150" s="1" t="inlineStr"/>
       <c r="I150" s="1" t="inlineStr"/>
@@ -4926,7 +4902,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø200</t>
+          <t>Тройник круглый оцинкованный Ø160/Ø125</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr"/>
@@ -4941,11 +4917,7 @@
         <v>4</v>
       </c>
       <c r="H151" s="1" t="inlineStr"/>
-      <c r="I151" s="1" t="inlineStr">
-        <is>
-          <t>в т. ч. ВЗ (кухонный зонт) — 1</t>
-        </is>
-      </c>
+      <c r="I151" s="1" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -4953,7 +4925,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø250</t>
+          <t>Тройник круглый оцинкованный Ø200/Ø125</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr"/>
@@ -4965,7 +4937,7 @@
         </is>
       </c>
       <c r="G152" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H152" s="1" t="inlineStr"/>
       <c r="I152" s="1" t="inlineStr"/>
@@ -4976,7 +4948,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø125/Ø100</t>
+          <t>Тройник круглый оцинкованный Ø200/Ø160</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr"/>
@@ -4988,7 +4960,7 @@
         </is>
       </c>
       <c r="G153" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H153" s="1" t="inlineStr"/>
       <c r="I153" s="1" t="inlineStr"/>
@@ -4999,7 +4971,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø160/Ø100</t>
+          <t>Тройник круглый оцинкованный Ø200/Ø200</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr"/>
@@ -5011,7 +4983,7 @@
         </is>
       </c>
       <c r="G154" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H154" s="1" t="inlineStr"/>
       <c r="I154" s="1" t="inlineStr"/>
@@ -5022,7 +4994,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø160/Ø125</t>
+          <t>Тройник круглый оцинкованный Ø250/Ø100</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr"/>
@@ -5034,7 +5006,7 @@
         </is>
       </c>
       <c r="G155" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H155" s="1" t="inlineStr"/>
       <c r="I155" s="1" t="inlineStr"/>
@@ -5045,7 +5017,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø200/Ø125</t>
+          <t>Тройник круглый оцинкованный Ø250/Ø200</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr"/>
@@ -5068,7 +5040,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø200/Ø160</t>
+          <t>Переход круглый оцинкованный Ø125/Ø100</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr"/>
@@ -5080,7 +5052,7 @@
         </is>
       </c>
       <c r="G157" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H157" s="1" t="inlineStr"/>
       <c r="I157" s="1" t="inlineStr"/>
@@ -5091,7 +5063,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø200/Ø200</t>
+          <t>Переход круглый оцинкованный Ø160/Ø125</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr"/>
@@ -5103,7 +5075,7 @@
         </is>
       </c>
       <c r="G158" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H158" s="1" t="inlineStr"/>
       <c r="I158" s="1" t="inlineStr"/>
@@ -5114,7 +5086,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø250/Ø100</t>
+          <t>Переход круглый оцинкованный Ø200/Ø100</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr"/>
@@ -5126,7 +5098,7 @@
         </is>
       </c>
       <c r="G159" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H159" s="1" t="inlineStr"/>
       <c r="I159" s="1" t="inlineStr"/>
@@ -5137,7 +5109,7 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø250/Ø200</t>
+          <t>Переход круглый оцинкованный Ø200/Ø150</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr"/>
@@ -5149,10 +5121,14 @@
         </is>
       </c>
       <c r="G160" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H160" s="1" t="inlineStr"/>
-      <c r="I160" s="1" t="inlineStr"/>
+      <c r="I160" s="1" t="inlineStr">
+        <is>
+          <t>ВЗ (кухонный зонт)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -5160,7 +5136,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø125/Ø100</t>
+          <t>Переход круглый оцинкованный Ø200/Ø160</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr"/>
@@ -5183,7 +5159,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø160/Ø125</t>
+          <t>Переход круглый оцинкованный Ø250/Ø160</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr"/>
@@ -5195,7 +5171,7 @@
         </is>
       </c>
       <c r="G162" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H162" s="1" t="inlineStr"/>
       <c r="I162" s="1" t="inlineStr"/>
@@ -5206,7 +5182,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø200/Ø100</t>
+          <t>Переход круглый оцинкованный Ø250/Ø200</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr"/>
@@ -5229,10 +5205,14 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø200/Ø150</t>
-        </is>
-      </c>
-      <c r="C164" s="1" t="inlineStr"/>
+          <t>Регулятор расхода воздуха (ирисовый клапан) Ø100</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D164" s="1" t="inlineStr"/>
       <c r="E164" s="1" t="inlineStr"/>
       <c r="F164" s="1" t="inlineStr">
@@ -5241,12 +5221,12 @@
         </is>
       </c>
       <c r="G164" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H164" s="1" t="inlineStr"/>
       <c r="I164" s="1" t="inlineStr">
         <is>
-          <t>ВЗ (кухонный зонт)</t>
+          <t>РР, на ответвлениях</t>
         </is>
       </c>
     </row>
@@ -5256,10 +5236,14 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø200/Ø160</t>
-        </is>
-      </c>
-      <c r="C165" s="1" t="inlineStr"/>
+          <t>Регулятор расхода воздуха (ирисовый клапан) Ø125</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D165" s="1" t="inlineStr"/>
       <c r="E165" s="1" t="inlineStr"/>
       <c r="F165" s="1" t="inlineStr">
@@ -5268,10 +5252,14 @@
         </is>
       </c>
       <c r="G165" s="1" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H165" s="1" t="inlineStr"/>
-      <c r="I165" s="1" t="inlineStr"/>
+      <c r="I165" s="1" t="inlineStr">
+        <is>
+          <t>РР, на ответвлениях</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -5279,10 +5267,14 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø250/Ø160</t>
-        </is>
-      </c>
-      <c r="C166" s="1" t="inlineStr"/>
+          <t>Регулятор расхода воздуха (ирисовый клапан) Ø160</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D166" s="1" t="inlineStr"/>
       <c r="E166" s="1" t="inlineStr"/>
       <c r="F166" s="1" t="inlineStr">
@@ -5294,7 +5286,11 @@
         <v>1</v>
       </c>
       <c r="H166" s="1" t="inlineStr"/>
-      <c r="I166" s="1" t="inlineStr"/>
+      <c r="I166" s="1" t="inlineStr">
+        <is>
+          <t>РР, на ответвлениях</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -5302,10 +5298,14 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø250/Ø200</t>
-        </is>
-      </c>
-      <c r="C167" s="1" t="inlineStr"/>
+          <t>Диффузор щелевой (линейный) приточный в торце подшивки, L=600 мм, с камерой статического давления, присоединение Ø125, расход 70 м³/ч; типоразмер — по расходу, по каталогу</t>
+        </is>
+      </c>
+      <c r="C167" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D167" s="1" t="inlineStr"/>
       <c r="E167" s="1" t="inlineStr"/>
       <c r="F167" s="1" t="inlineStr">
@@ -5314,10 +5314,14 @@
         </is>
       </c>
       <c r="G167" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H167" s="1" t="inlineStr"/>
-      <c r="I167" s="1" t="inlineStr"/>
+      <c r="I167" s="1" t="inlineStr">
+        <is>
+          <t>1.10 — 3 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -5325,7 +5329,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Регулятор расхода воздуха (ирисовый клапан) Ø100</t>
+          <t>Диффузор потолочный приточный с камерой статического давления, присоединение Ø100, расход 30/60 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -5341,12 +5345,12 @@
         </is>
       </c>
       <c r="G168" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H168" s="1" t="inlineStr"/>
       <c r="I168" s="1" t="inlineStr">
         <is>
-          <t>РР, на ответвлениях</t>
+          <t>1.11 — 2 шт., 2.2</t>
         </is>
       </c>
     </row>
@@ -5356,7 +5360,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Регулятор расхода воздуха (ирисовый клапан) Ø125</t>
+          <t>Решётка приточная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -5372,12 +5376,12 @@
         </is>
       </c>
       <c r="G169" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H169" s="1" t="inlineStr"/>
       <c r="I169" s="1" t="inlineStr">
         <is>
-          <t>РР, на ответвлениях</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -5387,7 +5391,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Регулятор расхода воздуха (ирисовый клапан) Ø160</t>
+          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø100, расход 40/50/60 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -5403,12 +5407,12 @@
         </is>
       </c>
       <c r="G170" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H170" s="1" t="inlineStr"/>
       <c r="I170" s="1" t="inlineStr">
         <is>
-          <t>РР, на ответвлениях</t>
+          <t>1.4, 1.3, 2.6</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5422,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Диффузор щелевой (линейный) приточный в торце подшивки, L=600 мм, с камерой статического давления, присоединение Ø125, расход 70 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø125, расход 75/90 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -5439,7 +5443,7 @@
       <c r="H171" s="1" t="inlineStr"/>
       <c r="I171" s="1" t="inlineStr">
         <is>
-          <t>1.10 — 3 шт.</t>
+          <t>2.9, 2.8, 2.1</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5453,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Диффузор потолочный приточный с камерой статического давления, присоединение Ø100, расход 30/60 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -5465,12 +5469,12 @@
         </is>
       </c>
       <c r="G172" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H172" s="1" t="inlineStr"/>
       <c r="I172" s="1" t="inlineStr">
         <is>
-          <t>1.11 — 2 шт., 2.2</t>
+          <t>1.8</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5484,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Решётка приточная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø125, расход 90 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -5501,7 +5505,7 @@
       <c r="H173" s="1" t="inlineStr"/>
       <c r="I173" s="1" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.10 (кухня)</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5515,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø100, расход 40/50/60 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø160, расход 120 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -5527,12 +5531,12 @@
         </is>
       </c>
       <c r="G174" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H174" s="1" t="inlineStr"/>
       <c r="I174" s="1" t="inlineStr">
         <is>
-          <t>1.4, 1.3, 2.6</t>
+          <t>1.10 (верх 2-го света)</t>
         </is>
       </c>
     </row>
@@ -5542,7 +5546,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø125, расход 75/90 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка наружная воздухозаборная 500×400, низ +2,600</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -5558,12 +5562,12 @@
         </is>
       </c>
       <c r="G175" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H175" s="1" t="inlineStr"/>
       <c r="I175" s="1" t="inlineStr">
         <is>
-          <t>2.9, 2.8, 2.1</t>
+          <t>Н1, восточная стена топочной</t>
         </is>
       </c>
     </row>
@@ -5573,7 +5577,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Оголовок (зонт) воздуховода Ø250 выше кровли</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
@@ -5589,12 +5593,12 @@
         </is>
       </c>
       <c r="G176" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H176" s="1" t="inlineStr"/>
       <c r="I176" s="1" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>выброс П1, В2 (Ш-2)</t>
         </is>
       </c>
     </row>
@@ -5604,7 +5608,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø125, расход 90 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Оголовок (зонт) воздуховода Ø200 выше кровли</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -5625,7 +5629,7 @@
       <c r="H177" s="1" t="inlineStr"/>
       <c r="I177" s="1" t="inlineStr">
         <is>
-          <t>1.10 (кухня)</t>
+          <t>ВЗ (кухонный зонт), шахта над мангалом 1.12</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5639,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø160, расход 120 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная под воздуховод Ø250 (вытяжка топочной, естественная)</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -5656,7 +5660,7 @@
       <c r="H178" s="1" t="inlineStr"/>
       <c r="I178" s="1" t="inlineStr">
         <is>
-          <t>1.10 (верх 2-го света)</t>
+          <t>В2, 188 м³/ч</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5670,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Решётка наружная воздухозаборная 500×400, низ +2,600</t>
+          <t>Решётка переточная в низу наружной двери топочной, живое сечение не менее 0,08 м²</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -5687,7 +5691,7 @@
       <c r="H179" s="1" t="inlineStr"/>
       <c r="I179" s="1" t="inlineStr">
         <is>
-          <t>Н1, восточная стена топочной</t>
+          <t>ПН, 282 м³/ч</t>
         </is>
       </c>
     </row>
@@ -5697,7 +5701,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Оголовок (зонт) воздуховода Ø250 выше кровли</t>
+          <t>Решётка вентиляционная наружная 400×200</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -5718,7 +5722,7 @@
       <c r="H180" s="1" t="inlineStr"/>
       <c r="I180" s="1" t="inlineStr">
         <is>
-          <t>выброс П1, В2 (Ш-2)</t>
+          <t>гараж 1.5: приток внизу, вытяжка вверху</t>
         </is>
       </c>
     </row>
@@ -5728,14 +5732,10 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Оголовок (зонт) воздуховода Ø200 выше кровли</t>
-        </is>
-      </c>
-      <c r="C181" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Зонт кухонный над плитой 500–600 м³/ч, располагаемое давление не менее 200 Па при 600 м³/ч</t>
+        </is>
+      </c>
+      <c r="C181" s="1" t="inlineStr"/>
       <c r="D181" s="1" t="inlineStr"/>
       <c r="E181" s="1" t="inlineStr"/>
       <c r="F181" s="1" t="inlineStr">
@@ -5749,7 +5749,7 @@
       <c r="H181" s="1" t="inlineStr"/>
       <c r="I181" s="1" t="inlineStr">
         <is>
-          <t>ВЗ (кухонный зонт), шахта над мангалом 1.12</t>
+          <t>ВЗ, поставка Заказчика</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная под воздуховод Ø250 (вытяжка топочной, естественная)</t>
+          <t>Клапан обратный Ø150</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -5780,7 +5780,7 @@
       <c r="H182" s="1" t="inlineStr"/>
       <c r="I182" s="1" t="inlineStr">
         <is>
-          <t>В2, 188 м³/ч</t>
+          <t>ВЗ, на патрубке зонта</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Решётка переточная в низу наружной двери топочной, живое сечение не менее 0,08 м²</t>
+          <t>Гильза для прохода воздуховода Ø200 в изоляции через наружную стену (под отверстие Ø320)</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -5811,7 +5811,7 @@
       <c r="H183" s="1" t="inlineStr"/>
       <c r="I183" s="1" t="inlineStr">
         <is>
-          <t>ПН, 282 м³/ч</t>
+          <t>ВЗ, сквозь стену на +3,400</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Решётка вентиляционная наружная 400×200</t>
+          <t>Клапан компенсации Ø200 с электроприводом, сблокирован с ВЗ, в наружной стене с решёткой</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -5833,16 +5833,16 @@
       <c r="E184" s="1" t="inlineStr"/>
       <c r="F184" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G184" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H184" s="1" t="inlineStr"/>
       <c r="I184" s="1" t="inlineStr">
         <is>
-          <t>гараж 1.5: приток внизу, вытяжка вверху</t>
+          <t>КК</t>
         </is>
       </c>
     </row>
@@ -5852,24 +5852,28 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Зонт кухонный над плитой 500–600 м³/ч, располагаемое давление не менее 200 Па при 600 м³/ч</t>
-        </is>
-      </c>
-      <c r="C185" s="1" t="inlineStr"/>
+          <t>Теплоизоляция воздуховодов рулонная толщиной 25 мм с паробарьером (фольга), класс горючести — по СП 60</t>
+        </is>
+      </c>
+      <c r="C185" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D185" s="1" t="inlineStr"/>
       <c r="E185" s="1" t="inlineStr"/>
       <c r="F185" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G185" s="1" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H185" s="1" t="inlineStr"/>
       <c r="I185" s="1" t="inlineStr">
         <is>
-          <t>ВЗ, поставка Заказчика</t>
+          <t>Н и выброс П1 Ø250</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5883,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ø150</t>
+          <t>Теплоизоляция воздуховода Ø200 из минеральной ваты, негорючая (НГ), толщина 50 мм, кашированная фольгой</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -5891,16 +5895,18 @@
       <c r="E186" s="1" t="inlineStr"/>
       <c r="F186" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G186" s="1" t="n">
-        <v>1</v>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G186" s="1" t="inlineStr">
+        <is>
+          <t>6,8</t>
+        </is>
       </c>
       <c r="H186" s="1" t="inlineStr"/>
       <c r="I186" s="1" t="inlineStr">
         <is>
-          <t>ВЗ, на патрубке зонта</t>
+          <t>ВЗ: холодная шахта, рядом дымоход мангала — только НГ</t>
         </is>
       </c>
     </row>
@@ -5910,19 +5916,15 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Гильза для прохода воздуховода Ø200 в изоляции через наружную стену (под отверстие Ø320)</t>
-        </is>
-      </c>
-      <c r="C187" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Крепления воздуховодов: подвесы, хомуты с уплотнителем, шпильки, профиль</t>
+        </is>
+      </c>
+      <c r="C187" s="1" t="inlineStr"/>
       <c r="D187" s="1" t="inlineStr"/>
       <c r="E187" s="1" t="inlineStr"/>
       <c r="F187" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G187" s="1" t="n">
@@ -5931,7 +5933,7 @@
       <c r="H187" s="1" t="inlineStr"/>
       <c r="I187" s="1" t="inlineStr">
         <is>
-          <t>ВЗ, сквозь стену на +3,400</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5943,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Клапан компенсации Ø200 с электроприводом, сблокирован с ВЗ, в наружной стене с решёткой</t>
+          <t>Вентилятор канальный малошумный Ø100, 2 скорости, датчик влажности и таймер, IPX4, с обратным клапаном</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -5953,16 +5955,16 @@
       <c r="E188" s="1" t="inlineStr"/>
       <c r="F188" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G188" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H188" s="1" t="inlineStr"/>
       <c r="I188" s="1" t="inlineStr">
         <is>
-          <t>КК</t>
+          <t>ВВ-б1 (с/у б3) — 25/50 м³/ч; ВВ-б2 (помывочная б7) — 60/100 м³/ч; лист 12</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5974,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Теплоизоляция воздуховодов рулонная толщиной 25 мм с паробарьером (фольга), класс горючести — по СП 60</t>
+          <t>Решётка вытяжная потолочная под воздуховод Ø100</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -5984,16 +5986,16 @@
       <c r="E189" s="1" t="inlineStr"/>
       <c r="F189" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G189" s="1" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H189" s="1" t="inlineStr"/>
       <c r="I189" s="1" t="inlineStr">
         <is>
-          <t>Н и выброс П1 Ø250</t>
+          <t>ВВ-б1, ВВ-б2</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6005,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Теплоизоляция воздуховода Ø200 из минеральной ваты, негорючая (НГ), толщина 50 мм, кашированная фольгой</t>
+          <t>Решётка наружная с гравитационными жалюзи Ø100</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -6015,18 +6017,16 @@
       <c r="E190" s="1" t="inlineStr"/>
       <c r="F190" s="1" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G190" s="1" t="inlineStr">
-        <is>
-          <t>6,8</t>
-        </is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G190" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="H190" s="1" t="inlineStr"/>
       <c r="I190" s="1" t="inlineStr">
         <is>
-          <t>ВЗ: холодная шахта, рядом дымоход мангала — только НГ</t>
+          <t>ВВ-б1, ВВ-б2</t>
         </is>
       </c>
     </row>
@@ -6036,96 +6036,88 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Крепления воздуховодов: подвесы, хомуты с уплотнителем, шпильки, профиль</t>
-        </is>
-      </c>
-      <c r="C191" s="1" t="inlineStr"/>
+          <t>Гильза Ø110 для прохода воздуховода Ø100 через наружную стену</t>
+        </is>
+      </c>
+      <c r="C191" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D191" s="1" t="inlineStr"/>
       <c r="E191" s="1" t="inlineStr"/>
       <c r="F191" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G191" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H191" s="1" t="inlineStr"/>
       <c r="I191" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>ВВ-б1, ВВ-б2, ось +2,20</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
-        <v>185</v>
-      </c>
-      <c r="B192" s="2" t="inlineStr">
-        <is>
-          <t>Вентилятор канальный малошумный Ø100, 2 скорости, датчик влажности и таймер, IPX4, с обратным клапаном</t>
-        </is>
-      </c>
-      <c r="C192" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D192" s="1" t="inlineStr"/>
-      <c r="E192" s="1" t="inlineStr"/>
-      <c r="F192" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G192" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H192" s="1" t="inlineStr"/>
-      <c r="I192" s="1" t="inlineStr">
-        <is>
-          <t>ВВ-б1 (с/у б3) — 25/50 м³/ч; ВВ-б2 (помывочная б7) — 60/100 м³/ч; лист 12</t>
-        </is>
-      </c>
+      <c r="A192" s="1" t="inlineStr"/>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>6. Кондиционирование (листы 9–11, 14)</t>
+        </is>
+      </c>
+      <c r="C192" s="1" t="n"/>
+      <c r="D192" s="1" t="n"/>
+      <c r="E192" s="1" t="n"/>
+      <c r="F192" s="1" t="n"/>
+      <c r="G192" s="1" t="n"/>
+      <c r="H192" s="1" t="n"/>
+      <c r="I192" s="1" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная потолочная под воздуховод Ø100</t>
+          <t>Наружный блок мини-VRV, тепловой насос, Qх = 22,4 кВт, ночной малошумный режим</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Daikin серии VRV-S, модель — по каталогу Daikin</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr"/>
-      <c r="E193" s="1" t="inlineStr"/>
+      <c r="E193" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F193" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G193" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H193" s="1" t="inlineStr"/>
       <c r="I193" s="1" t="inlineStr">
         <is>
-          <t>ВВ-б1, ВВ-б2</t>
+          <t>НБ-1, площадка у восточной стены топочной</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Решётка наружная с гравитационными жалюзи Ø100</t>
+          <t>Рама опорная наружного блока высотой 0,3–0,5 м</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -6137,35 +6129,39 @@
       <c r="E194" s="1" t="inlineStr"/>
       <c r="F194" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G194" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H194" s="1" t="inlineStr"/>
       <c r="I194" s="1" t="inlineStr">
         <is>
-          <t>ВВ-б1, ВВ-б2</t>
+          <t>НБ-1, лист 14</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Гильза Ø110 для прохода воздуховода Ø100 через наружную стену</t>
+          <t>Внутренний блок канальный тонкий, Qх = 5,6 кВт, ≈900 м³/ч</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr"/>
-      <c r="E195" s="1" t="inlineStr"/>
+      <c r="E195" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F195" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -6177,24 +6173,44 @@
       <c r="H195" s="1" t="inlineStr"/>
       <c r="I195" s="1" t="inlineStr">
         <is>
-          <t>ВВ-б1, ВВ-б2, ось +2,20</t>
+          <t>К-1 (1.10), К-2 (1.10)</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="inlineStr"/>
-      <c r="B196" s="3" t="inlineStr">
-        <is>
-          <t>6. Кондиционирование (листы 9–11, 14)</t>
-        </is>
-      </c>
-      <c r="C196" s="1" t="n"/>
-      <c r="D196" s="1" t="n"/>
-      <c r="E196" s="1" t="n"/>
-      <c r="F196" s="1" t="n"/>
-      <c r="G196" s="1" t="n"/>
-      <c r="H196" s="1" t="n"/>
-      <c r="I196" s="1" t="n"/>
+      <c r="A196" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Внутренний блок канальный тонкий, Qх = 3,6 кВт, ≈600 м³/ч</t>
+        </is>
+      </c>
+      <c r="C196" s="1" t="inlineStr">
+        <is>
+          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+        </is>
+      </c>
+      <c r="D196" s="1" t="inlineStr"/>
+      <c r="E196" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
+      <c r="F196" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G196" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" s="1" t="inlineStr"/>
+      <c r="I196" s="1" t="inlineStr">
+        <is>
+          <t>К-3 (1.11)</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -6202,12 +6218,12 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Наружный блок мини-VRV, тепловой насос, Qх = 22,4 кВт, ночной малошумный режим</t>
+          <t>Внутренний блок канальный тонкий, Qх = 2,8 кВт, ≈480 м³/ч</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии VRV-S, модель — по каталогу Daikin</t>
+          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr"/>
@@ -6222,12 +6238,12 @@
         </is>
       </c>
       <c r="G197" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H197" s="1" t="inlineStr"/>
       <c r="I197" s="1" t="inlineStr">
         <is>
-          <t>НБ-1, площадка у восточной стены топочной</t>
+          <t>К-4 (2.3), К-5 (2.4), К-6 (2.5), К-7 (2.7)</t>
         </is>
       </c>
     </row>
@@ -6237,28 +6253,32 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Рама опорная наружного блока высотой 0,3–0,5 м</t>
+          <t>Пульт управления внутренним блоком</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по каталогу Daikin</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr"/>
-      <c r="E198" s="1" t="inlineStr"/>
+      <c r="E198" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F198" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G198" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H198" s="1" t="inlineStr"/>
       <c r="I198" s="1" t="inlineStr">
         <is>
-          <t>НБ-1, лист 14</t>
+          <t>тип — по решению Заказчика</t>
         </is>
       </c>
     </row>
@@ -6268,12 +6288,12 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок канальный тонкий, Qх = 5,6 кВт, ≈900 м³/ч</t>
+          <t>Разветвитель фреоновый REFNET</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+          <t>по каталогу Daikin</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr"/>
@@ -6288,12 +6308,12 @@
         </is>
       </c>
       <c r="G199" s="1" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H199" s="1" t="inlineStr"/>
       <c r="I199" s="1" t="inlineStr">
         <is>
-          <t>К-1 (1.10), К-2 (1.10)</t>
+          <t>Р1…Р6</t>
         </is>
       </c>
     </row>
@@ -6303,32 +6323,28 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок канальный тонкий, Qх = 3,6 кВт, ≈600 м³/ч</t>
+          <t>Труба медная отожжённая для холодильной техники Ø6,35 мм</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr"/>
-      <c r="E200" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E200" s="1" t="inlineStr"/>
       <c r="F200" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G200" s="1" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H200" s="1" t="inlineStr"/>
       <c r="I200" s="1" t="inlineStr">
         <is>
-          <t>К-3 (1.11)</t>
+          <t>жидкость</t>
         </is>
       </c>
     </row>
@@ -6338,32 +6354,28 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок канальный тонкий, Qх = 2,8 кВт, ≈480 м³/ч</t>
+          <t>Труба медная отожжённая для холодильной техники Ø9,52 мм</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr"/>
-      <c r="E201" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E201" s="1" t="inlineStr"/>
       <c r="F201" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G201" s="1" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="H201" s="1" t="inlineStr"/>
       <c r="I201" s="1" t="inlineStr">
         <is>
-          <t>К-4 (2.3), К-5 (2.4), К-6 (2.5), К-7 (2.7)</t>
+          <t>жидкость</t>
         </is>
       </c>
     </row>
@@ -6373,32 +6385,28 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Пульт управления внутренним блоком</t>
+          <t>Труба медная отожжённая для холодильной техники Ø12,70 мм</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr"/>
-      <c r="E202" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E202" s="1" t="inlineStr"/>
       <c r="F202" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G202" s="1" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H202" s="1" t="inlineStr"/>
       <c r="I202" s="1" t="inlineStr">
         <is>
-          <t>тип — по решению Заказчика</t>
+          <t>газ</t>
         </is>
       </c>
     </row>
@@ -6408,32 +6416,28 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Разветвитель фреоновый REFNET</t>
+          <t>Труба медная отожжённая для холодильной техники Ø15,88 мм</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr"/>
-      <c r="E203" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E203" s="1" t="inlineStr"/>
       <c r="F203" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G203" s="1" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="H203" s="1" t="inlineStr"/>
       <c r="I203" s="1" t="inlineStr">
         <is>
-          <t>Р1…Р6</t>
+          <t>газ</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6447,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø6,35 мм</t>
+          <t>Труба медная отожжённая для холодильной техники Ø19,05 мм</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
@@ -6459,12 +6463,12 @@
         </is>
       </c>
       <c r="G204" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H204" s="1" t="inlineStr"/>
       <c r="I204" s="1" t="inlineStr">
         <is>
-          <t>жидкость</t>
+          <t>газ</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6478,7 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø9,52 мм</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø6,35, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
@@ -6490,14 +6494,10 @@
         </is>
       </c>
       <c r="G205" s="1" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="H205" s="1" t="inlineStr"/>
-      <c r="I205" s="1" t="inlineStr">
-        <is>
-          <t>жидкость</t>
-        </is>
-      </c>
+      <c r="I205" s="1" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -6505,7 +6505,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø12,70 мм</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø9,52, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
@@ -6521,14 +6521,10 @@
         </is>
       </c>
       <c r="G206" s="1" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="H206" s="1" t="inlineStr"/>
-      <c r="I206" s="1" t="inlineStr">
-        <is>
-          <t>газ</t>
-        </is>
-      </c>
+      <c r="I206" s="1" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -6536,7 +6532,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø15,88 мм</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø12,70, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
@@ -6552,14 +6548,10 @@
         </is>
       </c>
       <c r="G207" s="1" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H207" s="1" t="inlineStr"/>
-      <c r="I207" s="1" t="inlineStr">
-        <is>
-          <t>газ</t>
-        </is>
-      </c>
+      <c r="I207" s="1" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
@@ -6567,7 +6559,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø19,05 мм</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø15,88, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
@@ -6583,14 +6575,10 @@
         </is>
       </c>
       <c r="G208" s="1" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H208" s="1" t="inlineStr"/>
-      <c r="I208" s="1" t="inlineStr">
-        <is>
-          <t>газ</t>
-        </is>
-      </c>
+      <c r="I208" s="1" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
@@ -6598,7 +6586,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø6,35, толщина — по паспорту Daikin</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø19,05, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
@@ -6614,7 +6602,7 @@
         </is>
       </c>
       <c r="G209" s="1" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H209" s="1" t="inlineStr"/>
       <c r="I209" s="1" t="inlineStr"/>
@@ -6625,26 +6613,32 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø9,52, толщина — по паспорту Daikin</t>
+          <t>Хладагент для дозаправки (тип — по паспорту НБ-1)</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по паспорту НБ-1</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr"/>
       <c r="E210" s="1" t="inlineStr"/>
       <c r="F210" s="1" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G210" s="1" t="n">
-        <v>37</v>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="G210" s="1" t="inlineStr">
+        <is>
+          <t>2,17</t>
+        </is>
       </c>
       <c r="H210" s="1" t="inlineStr"/>
-      <c r="I210" s="1" t="inlineStr"/>
+      <c r="I210" s="1" t="inlineStr">
+        <is>
+          <t>по расчёту, уточнить при пуске</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
@@ -6652,26 +6646,26 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø12,70, толщина — по паспорту Daikin</t>
-        </is>
-      </c>
-      <c r="C211" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Гильза стальная для прохода фреонопроводов и дренажа через наружную стену и перекрытие</t>
+        </is>
+      </c>
+      <c r="C211" s="1" t="inlineStr"/>
       <c r="D211" s="1" t="inlineStr"/>
       <c r="E211" s="1" t="inlineStr"/>
       <c r="F211" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G211" s="1" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H211" s="1" t="inlineStr"/>
-      <c r="I211" s="1" t="inlineStr"/>
+      <c r="I211" s="1" t="inlineStr">
+        <is>
+          <t>стена топочной, Ш-1</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
@@ -6679,7 +6673,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø15,88, толщина — по паспорту Daikin</t>
+          <t>Диффузор щелевой блока К в торце подшивки, L=1000 мм</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
@@ -6691,14 +6685,18 @@
       <c r="E212" s="1" t="inlineStr"/>
       <c r="F212" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G212" s="1" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="H212" s="1" t="inlineStr"/>
-      <c r="I212" s="1" t="inlineStr"/>
+      <c r="I212" s="1" t="inlineStr">
+        <is>
+          <t>К-1, К-2</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -6706,7 +6704,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø19,05, толщина — по паспорту Daikin</t>
+          <t>Диффузор щелевой блока К в торце подшивки, L=1100 мм</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
@@ -6718,14 +6716,18 @@
       <c r="E213" s="1" t="inlineStr"/>
       <c r="F213" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G213" s="1" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H213" s="1" t="inlineStr"/>
-      <c r="I213" s="1" t="inlineStr"/>
+      <c r="I213" s="1" t="inlineStr">
+        <is>
+          <t>К-3</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -6733,30 +6735,28 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Хладагент для дозаправки (тип — по паспорту НБ-1)</t>
+          <t>Камера (плёнум) блока К с присоединением к щелевому диффузору</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
         <is>
-          <t>по паспорту НБ-1</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D214" s="1" t="inlineStr"/>
       <c r="E214" s="1" t="inlineStr"/>
       <c r="F214" s="1" t="inlineStr">
         <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="G214" s="1" t="inlineStr">
-        <is>
-          <t>2,17</t>
-        </is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G214" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="H214" s="1" t="inlineStr"/>
       <c r="I214" s="1" t="inlineStr">
         <is>
-          <t>по расчёту, уточнить при пуске</t>
+          <t>К-1…К-3, по месту</t>
         </is>
       </c>
     </row>
@@ -6766,10 +6766,14 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода фреонопроводов и дренажа через наружную стену и перекрытие</t>
-        </is>
-      </c>
-      <c r="C215" s="1" t="inlineStr"/>
+          <t>Решётка рециркуляции потолочная ≈300×300 под блоком К</t>
+        </is>
+      </c>
+      <c r="C215" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D215" s="1" t="inlineStr"/>
       <c r="E215" s="1" t="inlineStr"/>
       <c r="F215" s="1" t="inlineStr">
@@ -6778,12 +6782,12 @@
         </is>
       </c>
       <c r="G215" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H215" s="1" t="inlineStr"/>
       <c r="I215" s="1" t="inlineStr">
         <is>
-          <t>стена топочной, Ш-1</t>
+          <t>К-1…К-3</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6797,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Диффузор щелевой блока К в торце подшивки, L=1000 мм</t>
+          <t>Решётка щелевая настенная 800×150 с регулированием, с напорной камерой (подача К и свежего воздуха П1)</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
@@ -6809,12 +6813,12 @@
         </is>
       </c>
       <c r="G216" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H216" s="1" t="inlineStr"/>
       <c r="I216" s="1" t="inlineStr">
         <is>
-          <t>К-1, К-2</t>
+          <t>ЩП, спальни 2.3–2.5, 2.7</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6828,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Диффузор щелевой блока К в торце подшивки, L=1100 мм</t>
+          <t>Решётка щелевая настенная 800×150 с регулированием (возврат)</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
@@ -6840,12 +6844,12 @@
         </is>
       </c>
       <c r="G217" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H217" s="1" t="inlineStr"/>
       <c r="I217" s="1" t="inlineStr">
         <is>
-          <t>К-3</t>
+          <t>ЩВ, спальни 2.3–2.5, 2.7</t>
         </is>
       </c>
     </row>
@@ -6855,28 +6859,24 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Камера (плёнум) блока К с присоединением к щелевому диффузору</t>
-        </is>
-      </c>
-      <c r="C218" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод прямоугольный из оцинкованной стали 250×150</t>
+        </is>
+      </c>
+      <c r="C218" s="1" t="inlineStr"/>
       <c r="D218" s="1" t="inlineStr"/>
       <c r="E218" s="1" t="inlineStr"/>
       <c r="F218" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G218" s="1" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="H218" s="1" t="inlineStr"/>
       <c r="I218" s="1" t="inlineStr">
         <is>
-          <t>К-1…К-3, по месту</t>
+          <t>блоки К-4…К-7</t>
         </is>
       </c>
     </row>
@@ -6886,14 +6886,10 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Решётка рециркуляции потолочная ≈300×300 под блоком К</t>
-        </is>
-      </c>
-      <c r="C219" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 90° прямоугольный оцинкованный 250×150</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="inlineStr"/>
       <c r="D219" s="1" t="inlineStr"/>
       <c r="E219" s="1" t="inlineStr"/>
       <c r="F219" s="1" t="inlineStr">
@@ -6902,12 +6898,12 @@
         </is>
       </c>
       <c r="G219" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H219" s="1" t="inlineStr"/>
       <c r="I219" s="1" t="inlineStr">
         <is>
-          <t>К-1…К-3</t>
+          <t>блоки К-4…К-7</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6913,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Решётка щелевая настенная 800×150 с регулированием, с напорной камерой (подача К и свежего воздуха П1)</t>
+          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
         </is>
       </c>
       <c r="C220" s="1" t="inlineStr">
@@ -6929,16 +6925,16 @@
       <c r="E220" s="1" t="inlineStr"/>
       <c r="F220" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G220" s="1" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="H220" s="1" t="inlineStr"/>
       <c r="I220" s="1" t="inlineStr">
         <is>
-          <t>ЩП, спальни 2.3–2.5, 2.7</t>
+          <t>дренаж конденсата К-1…К-7</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6944,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Решётка щелевая настенная 800×150 с регулированием (возврат)</t>
+          <t>Отвод ПП Ø32 (45°/90°)</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
@@ -6964,12 +6960,12 @@
         </is>
       </c>
       <c r="G221" s="1" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H221" s="1" t="inlineStr"/>
       <c r="I221" s="1" t="inlineStr">
         <is>
-          <t>ЩВ, спальни 2.3–2.5, 2.7</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
@@ -6979,26 +6975,26 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод прямоугольный из оцинкованной стали 250×150</t>
-        </is>
-      </c>
-      <c r="C222" s="1" t="inlineStr"/>
+          <t>Тройник ПП Ø32</t>
+        </is>
+      </c>
+      <c r="C222" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D222" s="1" t="inlineStr"/>
       <c r="E222" s="1" t="inlineStr"/>
       <c r="F222" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G222" s="1" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H222" s="1" t="inlineStr"/>
-      <c r="I222" s="1" t="inlineStr">
-        <is>
-          <t>блоки К-4…К-7</t>
-        </is>
-      </c>
+      <c r="I222" s="1" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -7006,7 +7002,7 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° прямоугольный оцинкованный 250×150</t>
+          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
         </is>
       </c>
       <c r="C223" s="1" t="inlineStr"/>
@@ -7014,138 +7010,22 @@
       <c r="E223" s="1" t="inlineStr"/>
       <c r="F223" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G223" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H223" s="1" t="inlineStr"/>
       <c r="I223" s="1" t="inlineStr">
         <is>
-          <t>блоки К-4…К-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="1" t="n">
-        <v>216</v>
-      </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
-        </is>
-      </c>
-      <c r="C224" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D224" s="1" t="inlineStr"/>
-      <c r="E224" s="1" t="inlineStr"/>
-      <c r="F224" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G224" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="H224" s="1" t="inlineStr"/>
-      <c r="I224" s="1" t="inlineStr">
-        <is>
-          <t>дренаж конденсата К-1…К-7</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
-        <v>217</v>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>Отвод ПП Ø32 (45°/90°)</t>
-        </is>
-      </c>
-      <c r="C225" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D225" s="1" t="inlineStr"/>
-      <c r="E225" s="1" t="inlineStr"/>
-      <c r="F225" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G225" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="H225" s="1" t="inlineStr"/>
-      <c r="I225" s="1" t="inlineStr">
-        <is>
-          <t>по месту</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>Тройник ПП Ø32</t>
-        </is>
-      </c>
-      <c r="C226" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D226" s="1" t="inlineStr"/>
-      <c r="E226" s="1" t="inlineStr"/>
-      <c r="F226" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G226" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H226" s="1" t="inlineStr"/>
-      <c r="I226" s="1" t="inlineStr"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="1" t="n">
-        <v>219</v>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
-        </is>
-      </c>
-      <c r="C227" s="1" t="inlineStr"/>
-      <c r="D227" s="1" t="inlineStr"/>
-      <c r="E227" s="1" t="inlineStr"/>
-      <c r="F227" s="1" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G227" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H227" s="1" t="inlineStr"/>
-      <c r="I227" s="1" t="inlineStr">
-        <is>
-          <t>по месту</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr"/>
-      <c r="B229" t="inlineStr">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I225"/>
+  <dimension ref="A1:I228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,44 м³/ч, H=1,46 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,45 м³/ч, H=1,49 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,85 м³/ч, H=1,22 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,85 м³/ч, H=1,20 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная смесительная Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-60 (G=0,86 м³/ч, H=3,54 м), трёхходовой смесительный клапан с электроприводом, краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Группа насосная смесительная Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-60 (G=0,86 м³/ч, H=3,44 м), трёхходовой смесительный клапан с электроприводом, краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -1706,7 +1706,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Коллектор тёплого пола из нержавеющей стали 1" на 9 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+          <t>Коллектор тёплого пола из нержавеющей стали 1" на 10 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 36,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,44 м³/ч, H=0,97 м), байпас, защитный термостат-ограничитель 45 °С</t>
+          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 36,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,60 м³/ч, H=1,41 м), байпас, защитный термостат-ограничитель 45 °С</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 42,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,07 м³/ч, H=0,58 м), байпас, защитный термостат-ограничитель 55 °С</t>
+          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 42,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,11 м³/ч, H=0,70 м), байпас, защитный термостат-ограничитель 55 °С</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -2032,7 +2032,7 @@
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 1953 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 1908 Вт</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1650 мм, тепловая мощность при 70/55 °С не менее 1653 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1650 мм, тепловая мощность при 70/55 °С не менее 1614 Вт</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=900 мм, тепловая мощность при 70/55 °С не менее 902 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=900 мм, тепловая мощность при 70/55 °С не менее 881 Вт</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 894 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 898 Вт</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -2618,12 +2618,12 @@
         </is>
       </c>
       <c r="G71" s="1" t="n">
-        <v>1335</v>
+        <v>1450</v>
       </c>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>петли — 22 шт., листы 4, 5</t>
+          <t>петли — 23 шт., листы 4, 5</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H73" s="1" t="inlineStr"/>
       <c r="I73" s="1" t="inlineStr">
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="G77" s="1" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
@@ -2819,7 +2819,7 @@
         </is>
       </c>
       <c r="G78" s="1" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
@@ -3136,7 +3136,7 @@
         </is>
       </c>
       <c r="G89" s="1" t="n">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="G90" s="1" t="n">
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="G143" s="1" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H143" s="1" t="inlineStr"/>
       <c r="I143" s="1" t="inlineStr">
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="G200" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H200" s="1" t="inlineStr"/>
       <c r="I200" s="1" t="inlineStr">
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="G202" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H202" s="1" t="inlineStr"/>
       <c r="I202" s="1" t="inlineStr">
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="G203" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H203" s="1" t="inlineStr"/>
       <c r="I203" s="1" t="inlineStr">
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="G205" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H205" s="1" t="inlineStr"/>
       <c r="I205" s="1" t="inlineStr"/>
@@ -6548,7 +6548,7 @@
         </is>
       </c>
       <c r="G207" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H207" s="1" t="inlineStr"/>
       <c r="I207" s="1" t="inlineStr"/>
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="G208" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H208" s="1" t="inlineStr"/>
       <c r="I208" s="1" t="inlineStr"/>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G210" s="1" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="H210" s="1" t="inlineStr"/>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Камера (плёнум) блока К с присоединением к щелевому диффузору</t>
+          <t>Камера статического давления (КСД) щелевого диффузора блока К, переходная от фланца блока, с выравнивающей перфорированной решёткой, в теплоизоляции 10 мм</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
@@ -6756,7 +6756,7 @@
       <c r="H214" s="1" t="inlineStr"/>
       <c r="I214" s="1" t="inlineStr">
         <is>
-          <t>К-1…К-3, по месту</t>
+          <t>К-1 — L=1000, глуб. 240, К-2 — L=1000, глуб. 240, К-3 — L=1100, глуб. 350</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Решётка рециркуляции потолочная ≈300×300 под блоком К</t>
+          <t>Решётка-люк рециркуляции потолочная съёмная 600×600 под блоком К (забор воздуха снизу)</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
@@ -6787,7 +6787,7 @@
       <c r="H215" s="1" t="inlineStr"/>
       <c r="I215" s="1" t="inlineStr">
         <is>
-          <t>К-1…К-3</t>
+          <t>К-1…К-3, вместо люка 600×600</t>
         </is>
       </c>
     </row>
@@ -6797,7 +6797,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Решётка щелевая настенная 800×150 с регулированием, с напорной камерой (подача К и свежего воздуха П1)</t>
+          <t>Решётка щелевая настенная 800×150 с регулированием (подача К и свежего воздуха П1)</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Решётка щелевая настенная 800×150 с регулированием (возврат)</t>
+          <t>Камера статического давления (КСД) для решётки 800×150, подача, с выравнивающей перфорированной решёткой, в теплоизоляции 10 мм; присоединение — фланец блока (К-4…К-6) или 250×150 (К-7), боковой патрубок Ø100 свежего воздуха П1</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
@@ -6849,7 +6849,7 @@
       <c r="H217" s="1" t="inlineStr"/>
       <c r="I217" s="1" t="inlineStr">
         <is>
-          <t>ЩВ, спальни 2.3–2.5, 2.7</t>
+          <t>КСД у ЩП</t>
         </is>
       </c>
     </row>
@@ -6859,24 +6859,28 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод прямоугольный из оцинкованной стали 250×150</t>
-        </is>
-      </c>
-      <c r="C218" s="1" t="inlineStr"/>
+          <t>Решётка щелевая настенная 800×150 с регулированием (возврат)</t>
+        </is>
+      </c>
+      <c r="C218" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D218" s="1" t="inlineStr"/>
       <c r="E218" s="1" t="inlineStr"/>
       <c r="F218" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G218" s="1" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H218" s="1" t="inlineStr"/>
       <c r="I218" s="1" t="inlineStr">
         <is>
-          <t>блоки К-4…К-7</t>
+          <t>ЩВ, спальни 2.3–2.5, 2.7</t>
         </is>
       </c>
     </row>
@@ -6886,10 +6890,14 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° прямоугольный оцинкованный 250×150</t>
-        </is>
-      </c>
-      <c r="C219" s="1" t="inlineStr"/>
+          <t>Камера статического давления (КСД) для решётки 800×150, возврат, глубиной 220 мм, патрубок 250×150</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D219" s="1" t="inlineStr"/>
       <c r="E219" s="1" t="inlineStr"/>
       <c r="F219" s="1" t="inlineStr">
@@ -6898,12 +6906,12 @@
         </is>
       </c>
       <c r="G219" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H219" s="1" t="inlineStr"/>
       <c r="I219" s="1" t="inlineStr">
         <is>
-          <t>блоки К-4…К-7</t>
+          <t>КСД у ЩВ</t>
         </is>
       </c>
     </row>
@@ -6913,14 +6921,10 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
-        </is>
-      </c>
-      <c r="C220" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод прямоугольный из оцинкованной стали 250×150</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="inlineStr"/>
       <c r="D220" s="1" t="inlineStr"/>
       <c r="E220" s="1" t="inlineStr"/>
       <c r="F220" s="1" t="inlineStr">
@@ -6929,12 +6933,12 @@
         </is>
       </c>
       <c r="G220" s="1" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="H220" s="1" t="inlineStr"/>
       <c r="I220" s="1" t="inlineStr">
         <is>
-          <t>дренаж конденсата К-1…К-7</t>
+          <t>блоки К-4…К-7</t>
         </is>
       </c>
     </row>
@@ -6944,14 +6948,10 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП Ø32 (45°/90°)</t>
-        </is>
-      </c>
-      <c r="C221" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 90° прямоугольный оцинкованный 250×150</t>
+        </is>
+      </c>
+      <c r="C221" s="1" t="inlineStr"/>
       <c r="D221" s="1" t="inlineStr"/>
       <c r="E221" s="1" t="inlineStr"/>
       <c r="F221" s="1" t="inlineStr">
@@ -6960,12 +6960,12 @@
         </is>
       </c>
       <c r="G221" s="1" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H221" s="1" t="inlineStr"/>
       <c r="I221" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>блоки К-4…К-7</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП Ø32</t>
+          <t>Теплоизоляция из вспененного каучука 10 мм, самоклеящаяся, для КСД и воздуховодов подачи блоков К</t>
         </is>
       </c>
       <c r="C222" s="1" t="inlineStr">
@@ -6987,14 +6987,18 @@
       <c r="E222" s="1" t="inlineStr"/>
       <c r="F222" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G222" s="1" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H222" s="1" t="inlineStr"/>
-      <c r="I222" s="1" t="inlineStr"/>
+      <c r="I222" s="1" t="inlineStr">
+        <is>
+          <t>КСД К-1…К-3 и ЩП, подача К-7</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -7002,30 +7006,119 @@
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
-        </is>
-      </c>
-      <c r="C223" s="1" t="inlineStr"/>
+          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
+        </is>
+      </c>
+      <c r="C223" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D223" s="1" t="inlineStr"/>
       <c r="E223" s="1" t="inlineStr"/>
       <c r="F223" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G223" s="1" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H223" s="1" t="inlineStr"/>
       <c r="I223" s="1" t="inlineStr">
         <is>
+          <t>дренаж конденсата К-1…К-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Отвод ПП Ø32 (45°/90°)</t>
+        </is>
+      </c>
+      <c r="C224" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D224" s="1" t="inlineStr"/>
+      <c r="E224" s="1" t="inlineStr"/>
+      <c r="F224" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G224" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H224" s="1" t="inlineStr"/>
+      <c r="I224" s="1" t="inlineStr">
+        <is>
           <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr"/>
-      <c r="B225" t="inlineStr">
+      <c r="A225" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Тройник ПП Ø32</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="inlineStr"/>
+      <c r="E225" s="1" t="inlineStr"/>
+      <c r="F225" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G225" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H225" s="1" t="inlineStr"/>
+      <c r="I225" s="1" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
+        </is>
+      </c>
+      <c r="C226" s="1" t="inlineStr"/>
+      <c r="D226" s="1" t="inlineStr"/>
+      <c r="E226" s="1" t="inlineStr"/>
+      <c r="F226" s="1" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G226" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H226" s="1" t="inlineStr"/>
+      <c r="I226" s="1" t="inlineStr">
+        <is>
+          <t>по месту</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I228"/>
+  <dimension ref="A1:I223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Гидравлический разделитель Ду 32, расход до 3,3 м³/ч, с автоматическим воздухоотводчиком и спускным краном</t>
+          <t>Гидравлический разделитель Ду 32, расход до 3,2 м³/ч, с автоматическим воздухоотводчиком и спускным краном</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,45 м³/ч, H=1,49 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,46 м³/ч, H=1,51 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,85 м³/ч, H=1,20 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,72 м³/ч, H=1,20 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -957,7 +957,7 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>Н3 → КШ-2, Р-т</t>
+          <t>Н3 → КШ-2</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная смесительная Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-60 (G=0,86 м³/ч, H=3,44 м), трёхходовой смесительный клапан с электроприводом, краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Группа насосная смесительная Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-60 (G=0,86 м³/ч, H=3,45 м), трёхходовой смесительный клапан с электроприводом, краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -1481,100 +1481,112 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ду 32 (Ø42,3)</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr"/>
-      <c r="D35" s="1" t="inlineStr"/>
-      <c r="E35" s="1" t="inlineStr"/>
-      <c r="F35" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G35" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="H35" s="1" t="inlineStr"/>
-      <c r="I35" s="1" t="inlineStr">
-        <is>
-          <t>трубы котельной</t>
-        </is>
-      </c>
+      <c r="A35" s="1" t="inlineStr"/>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>2. Отопление дома (листы 3–6)</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n"/>
+      <c r="D35" s="1" t="n"/>
+      <c r="E35" s="1" t="n"/>
+      <c r="F35" s="1" t="n"/>
+      <c r="G35" s="1" t="n"/>
+      <c r="H35" s="1" t="n"/>
+      <c r="I35" s="1" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ду 25 (Ø33,5)</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr"/>
+          <t>Шкаф коллекторный встроенный ≈850×1300×150 мм (как КШ-2, КШ-5)</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D36" s="1" t="inlineStr"/>
       <c r="E36" s="1" t="inlineStr"/>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G36" s="1" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>трубы котельной</t>
+          <t>КШ-1 (тамбур 1.7)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ду 20 (Ø26,8)</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr"/>
+          <t>Коллектор тёплого пола из нержавеющей стали 1" на 6 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D37" s="1" t="inlineStr"/>
       <c r="E37" s="1" t="inlineStr"/>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G37" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>трубы котельной</t>
+          <t>КШ-1 (тамбур 1.7)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr"/>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>2. Отопление дома (листы 3–6)</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="n"/>
-      <c r="D38" s="1" t="n"/>
-      <c r="E38" s="1" t="n"/>
-      <c r="F38" s="1" t="n"/>
-      <c r="G38" s="1" t="n"/>
-      <c r="H38" s="1" t="n"/>
-      <c r="I38" s="1" t="n"/>
+      <c r="A38" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Шкаф коллекторный встроенный двухъярусный ≈850×1300×150 мм</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr"/>
+      <c r="E38" s="1" t="inlineStr"/>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="1" t="inlineStr"/>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>КШ-2 (тамбур 1.7); узел — на КШ-2 и КШ-5</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -1582,7 +1594,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встроенный ≈600×650×120 мм</t>
+          <t>Коллектор прямой из нержавеющей стали 1" на 8 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -1594,7 +1606,7 @@
       <c r="E39" s="1" t="inlineStr"/>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G39" s="1" t="n">
@@ -1603,7 +1615,7 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>КШ-1 (тамбур 1.7)</t>
+          <t>КШ-2 (тамбур 1.7); узел — на КШ-2 и КШ-5</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1625,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Коллектор тёплого пола из нержавеющей стали 1" на 6 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+          <t>Коллектор тёплого пола из нержавеющей стали 1" на 5 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"; проходной — из торцов транзит на КШ-5</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -1634,7 +1646,7 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>КШ-1 (тамбур 1.7)</t>
+          <t>КШ-2 (тамбур 1.7); узел — на КШ-2 и КШ-5</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1656,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный двухъярусный ≈900×1300×150 мм</t>
+          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 36,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,66 м³/ч, H=1,47 м), байпас, защитный термостат-ограничитель 45 °С</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -1656,7 +1668,7 @@
       <c r="E41" s="1" t="inlineStr"/>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G41" s="1" t="n">
@@ -1665,7 +1677,7 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>КШ-2 (тамбур 1.7)</t>
+          <t>КШ-2 (тамбур 1.7); узел — на КШ-2 и КШ-5</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1687,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Коллектор прямой из нержавеющей стали 1" на 8 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+          <t>Шкаф коллекторный встроенный ≈850×1300×150 мм (как КШ-1, КШ-2)</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1687,7 +1699,7 @@
       <c r="E42" s="1" t="inlineStr"/>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G42" s="1" t="n">
@@ -1696,7 +1708,7 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>КШ-2 (тамбур 1.7)</t>
+          <t>КШ-5 (тамбур 1.7), от смесительного узла КШ-2</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1718,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Коллектор тёплого пола из нержавеющей стали 1" на 10 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+          <t>Коллектор тёплого пола из нержавеющей стали 1" на 5 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1727,7 +1739,7 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>КШ-2 (тамбур 1.7)</t>
+          <t>КШ-5 (тамбур 1.7), от смесительного узла КШ-2</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1749,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 36,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,60 м³/ч, H=1,41 м), байпас, защитный термостат-ограничитель 45 °С</t>
+          <t>Шкаф коллекторный встроенный ≈550×650×120 мм</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1749,7 +1761,7 @@
       <c r="E44" s="1" t="inlineStr"/>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G44" s="1" t="n">
@@ -1758,7 +1770,7 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>КШ-2 (тамбур 1.7)</t>
+          <t>КШ-3 (топочная 1.6)</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1780,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встроенный ≈550×650×120 мм</t>
+          <t>Коллектор тёплого пола из нержавеющей стали 1" на 5 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1780,7 +1792,7 @@
       <c r="E45" s="1" t="inlineStr"/>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G45" s="1" t="n">
@@ -1799,7 +1811,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Коллектор тёплого пола из нержавеющей стали 1" на 5 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+          <t>Шкаф коллекторный встроенный двухъярусный ≈750×1250×150 мм</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1811,7 +1823,7 @@
       <c r="E46" s="1" t="inlineStr"/>
       <c r="F46" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G46" s="1" t="n">
@@ -1820,7 +1832,7 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>КШ-3 (топочная 1.6)</t>
+          <t>КШ-4 (2.6)</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1842,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встроенный двухъярусный ≈750×1250×150 мм</t>
+          <t>Коллектор прямой из нержавеющей стали 1" на 7 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"; выход В6 — резерв, с заглушками</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1842,7 +1854,7 @@
       <c r="E47" s="1" t="inlineStr"/>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G47" s="1" t="n">
@@ -1861,7 +1873,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Коллектор прямой из нержавеющей стали 1" на 7 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"; выход В6 — резерв, с заглушками</t>
+          <t>Коллектор тёплого пола из нержавеющей стали 1" на 2 выхода: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1892,7 +1904,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Коллектор тёплого пола из нержавеющей стали 1" на 2 выхода: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 42,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,13 м³/ч, H=0,97 м), байпас, защитный термостат-ограничитель 55 °С</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1923,7 +1935,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 42,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,11 м³/ч, H=0,70 м), байпас, защитный термостат-ограничитель 55 °С</t>
+          <t>Кран шаровой полнопроходной G1" (вход коллекторного шкафа, подача и обратка)</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -1935,16 +1947,16 @@
       <c r="E50" s="1" t="inlineStr"/>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G50" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>КШ-4 (2.6)</t>
+          <t>КШ-1…КШ-5</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1966,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой полнопроходной G1" (вход коллекторного шкафа, подача и обратка)</t>
+          <t>Фильтр сетчатый G1" (вход коллекторного шкафа, подача)</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -1970,7 +1982,7 @@
         </is>
       </c>
       <c r="G51" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr">
@@ -1985,7 +1997,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Фильтр сетчатый G1" (вход коллекторного шкафа, подача)</t>
+          <t>Сервопривод термоэлектрический 230 В, нормально закрытый, на термостатический клапан коллектора</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
@@ -2001,12 +2013,12 @@
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>КШ-1…КШ-4</t>
+          <t>управление — автоматика «Люкс»</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2028,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Сервопривод термоэлектрический 230 В, нормально закрытый, на термостатический клапан коллектора</t>
+          <t>Радиатор стальной панельный 33/300, L=1700 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1571 Вт</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
@@ -2032,12 +2044,12 @@
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>управление — автоматика «Люкс»</t>
+          <t>Р-1 (2.3)</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2059,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 33/300, L=1700 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1571 Вт</t>
+          <t>Радиатор стальной панельный 33/300, L=1300 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1169 Вт</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -2068,7 +2080,7 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>Р-1 (2.3)</t>
+          <t>Р-2 (2.4)</t>
         </is>
       </c>
     </row>
@@ -2078,7 +2090,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 33/300, L=1300 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1169 Вт</t>
+          <t>Радиатор стальной панельный 33/300, L=1700 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1611 Вт</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -2099,7 +2111,7 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>Р-2 (2.4)</t>
+          <t>Р-3 (2.5)</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2121,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 33/300, L=1700 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1611 Вт</t>
+          <t>Радиатор стальной панельный 22/500, L=600 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 614 Вт</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -2130,7 +2142,7 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>Р-3 (2.5)</t>
+          <t>Р-5 (2.6)</t>
         </is>
       </c>
     </row>
@@ -2140,28 +2152,32 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 22/500, L=600 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 614 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 1908 Вт</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr"/>
-      <c r="E57" s="1" t="inlineStr"/>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F57" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G57" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>Р-5 (2.6)</t>
+          <t>Кв-1 (1.10), Кв-2 (1.10)</t>
         </is>
       </c>
     </row>
@@ -2171,16 +2187,20 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 22/500, L=1700 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 2271 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1650 мм, тепловая мощность при 70/55 °С не менее 1614 Вт</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr"/>
-      <c r="E58" s="1" t="inlineStr"/>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F58" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -2192,7 +2212,7 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>Р-т (1.6)</t>
+          <t>Кв-3 (1.10)</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2222,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 1908 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=900 мм, тепловая мощность при 70/55 °С не менее 881 Вт</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -2227,7 +2247,7 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>Кв-1 (1.10), Кв-2 (1.10)</t>
+          <t>Кв-4 (1.10), Кв-5 (1.10)</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2257,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1650 мм, тепловая мощность при 70/55 °С не менее 1614 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 894 Вт</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -2257,12 +2277,12 @@
         </is>
       </c>
       <c r="G60" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>Кв-3 (1.10)</t>
+          <t>Кв-6 (1.11), Кв-7 (1.11)</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2292,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=900 мм, тепловая мощность при 70/55 °С не менее 881 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2200 мм, тепловая мощность при 70/55 °С не менее 2345 Вт</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -2292,12 +2312,12 @@
         </is>
       </c>
       <c r="G61" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>Кв-4 (1.10), Кв-5 (1.10)</t>
+          <t>Кв-8 (1.9)</t>
         </is>
       </c>
     </row>
@@ -2307,12 +2327,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 898 Вт</t>
+          <t>Конвектор внутрипольный без вентилятора (естественная конвекция), L=2750 мм, глубина не более 150 мм, тепловая мощность при 70/55 °С не менее 1701 Вт</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>КЗТО «Бриз В», модель — по каталогу</t>
+          <t>КЗТО «Бриз» (естественная конвекция), модель — по каталогу</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr"/>
@@ -2327,12 +2347,12 @@
         </is>
       </c>
       <c r="G62" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>Кв-6 (1.11), Кв-7 (1.11)</t>
+          <t>Кн-1 (2.7)</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2362,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2200 мм, тепловая мощность при 70/55 °С не менее 2345 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=900 мм, глубина не более 150 мм, тепловая мощность при 70/55 °С не менее 613 Вт</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -2367,7 +2387,7 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>Кв-8 (1.9)</t>
+          <t>Кн-3 (2.2)</t>
         </is>
       </c>
     </row>
@@ -2377,32 +2397,28 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный без вентилятора (естественная конвекция), L=2750 мм, глубина не более 150 мм, тепловая мощность при 70/55 °С не менее 1701 Вт</t>
+          <t>Узел нижнего подключения радиатора запорный, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>КЗТО «Бриз» (естественная конвекция), модель — по каталогу</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr"/>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E64" s="1" t="inlineStr"/>
       <c r="F64" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G64" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr">
         <is>
-          <t>Кн-1 (2.7)</t>
+          <t>Р-1, Р-2, Р-3, Р-5</t>
         </is>
       </c>
     </row>
@@ -2412,32 +2428,28 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=900 мм, глубина не более 150 мм, тепловая мощность при 70/55 °С не менее 613 Вт</t>
+          <t>Клапан запорный G½" для подключения конвектора</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>КЗТО «Бриз В», модель — по каталогу</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr"/>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E65" s="1" t="inlineStr"/>
       <c r="F65" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G65" s="1" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr">
         <is>
-          <t>Кн-3 (2.2)</t>
+          <t>Кв-1…Кв-8, Кн-1, Кн-3</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2459,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Узел нижнего подключения радиатора запорный, присоединение евроконус G¾"</t>
+          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH), для отопления, t до 95 °С — петли тёплого пола</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2459,16 +2471,16 @@
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G66" s="1" t="n">
-        <v>4</v>
+        <v>1448</v>
       </c>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>Р-1, Р-2, Р-3, Р-5</t>
+          <t>петли — 23 шт., листы 4, 5</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2490,7 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Клапан термостатический G½" с термостатической головкой</t>
+          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — подводки к приборам</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2490,16 +2502,16 @@
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>1</v>
+        <v>518</v>
       </c>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>Р-т</t>
+          <t>листы 3, 5</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2521,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Клапан запорно-балансировочный G½"</t>
+          <t>Фитинг компрессионный (евроконус) для трубы PE-Xa 16×2,0 на G¾"</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2525,12 +2537,12 @@
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>Р-т</t>
+          <t>коллекторы, радиаторы</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2552,7 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Клапан запорный G½" для подключения конвектора</t>
+          <t>Фитинг компрессионный для трубы PE-Xa 16×2,0 на наружную резьбу G½"</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2561,7 +2573,7 @@
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>Кв-1…Кв-8, Кн-1, Кн-3</t>
+          <t>конвекторы</t>
         </is>
       </c>
     </row>
@@ -2571,28 +2583,24 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Тройник стальной переходной Ду 25×15 (отвод на Р-т от группы Н3)</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>ГОСТ 8949-75</t>
-        </is>
-      </c>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена, толщина 6 мм, для трубы Ø16</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr"/>
       <c r="D70" s="1" t="inlineStr"/>
       <c r="E70" s="1" t="inlineStr"/>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G70" s="1" t="n">
-        <v>2</v>
+        <v>300</v>
       </c>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>у РК</t>
+          <t>подводки 1 этажа</t>
         </is>
       </c>
     </row>
@@ -2602,14 +2610,10 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH), для отопления, t до 95 °С — петли тёплого пола</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Труба гофрированная защитная (гофра) для трубы Ø16</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr"/>
       <c r="D71" s="1" t="inlineStr"/>
       <c r="E71" s="1" t="inlineStr"/>
       <c r="F71" s="1" t="inlineStr">
@@ -2618,12 +2622,12 @@
         </is>
       </c>
       <c r="G71" s="1" t="n">
-        <v>1450</v>
+        <v>518</v>
       </c>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>петли — 23 шт., листы 4, 5</t>
+          <t>подводки к приборам</t>
         </is>
       </c>
     </row>
@@ -2633,14 +2637,10 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — подводки к приборам</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Труба гофрированная защитная (гофра) для трубы Ø16 на выходах петель из стяжки, по 1 м на конец</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr"/>
       <c r="D72" s="1" t="inlineStr"/>
       <c r="E72" s="1" t="inlineStr"/>
       <c r="F72" s="1" t="inlineStr">
@@ -2649,12 +2649,12 @@
         </is>
       </c>
       <c r="G72" s="1" t="n">
-        <v>532</v>
+        <v>51</v>
       </c>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>листы 3, 5</t>
+          <t>у коллекторов</t>
         </is>
       </c>
     </row>
@@ -2664,14 +2664,10 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Фитинг компрессионный (евроконус) для трубы PE-Xa 16×2,0 на G¾"</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Фиксатор поворота трубы Ø16 на 90° (выход из пола у коллектора)</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr"/>
       <c r="D73" s="1" t="inlineStr"/>
       <c r="E73" s="1" t="inlineStr"/>
       <c r="F73" s="1" t="inlineStr">
@@ -2680,14 +2676,10 @@
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="H73" s="1" t="inlineStr"/>
-      <c r="I73" s="1" t="inlineStr">
-        <is>
-          <t>коллекторы, радиаторы</t>
-        </is>
-      </c>
+      <c r="I73" s="1" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -2695,7 +2687,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Фитинг компрессионный для трубы PE-Xa 16×2,0 на наружную резьбу G½"</t>
+          <t>Труба PE-Xa 20×2,8 с антидиффузионным слоем (EVOH) — магистрали</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2707,16 +2699,16 @@
       <c r="E74" s="1" t="inlineStr"/>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G74" s="1" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>конвекторы, Р-т</t>
+          <t>Н5 → нагреватель П1</t>
         </is>
       </c>
     </row>
@@ -2726,10 +2718,14 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена, толщина 6 мм, для трубы Ø16</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr"/>
+          <t>Труба PE-Xa 25×3,5 с антидиффузионным слоем (EVOH) — магистрали</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D75" s="1" t="inlineStr"/>
       <c r="E75" s="1" t="inlineStr"/>
       <c r="F75" s="1" t="inlineStr">
@@ -2738,12 +2734,12 @@
         </is>
       </c>
       <c r="G75" s="1" t="n">
-        <v>313</v>
+        <v>73</v>
       </c>
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>подводки 1 этажа</t>
+          <t>Н2 → КШ-4, стояки в 1.7, Н4 → КШ-1, Н4 → КШ-3, транзит КШ-2 → КШ-5 (36 °С, в полу 1.7)</t>
         </is>
       </c>
     </row>
@@ -2753,10 +2749,14 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная (гофра) для трубы Ø16</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr"/>
+          <t>Труба PE-Xa 32×4,4 с антидиффузионным слоем (EVOH) — магистрали</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D76" s="1" t="inlineStr"/>
       <c r="E76" s="1" t="inlineStr"/>
       <c r="F76" s="1" t="inlineStr">
@@ -2765,12 +2765,12 @@
         </is>
       </c>
       <c r="G76" s="1" t="n">
-        <v>532</v>
+        <v>22</v>
       </c>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>подводки к приборам</t>
+          <t>Н3 → КШ-2</t>
         </is>
       </c>
     </row>
@@ -2780,24 +2780,28 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная (гофра) для трубы Ø16 на выходах петель из стяжки, по 1 м на конец</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr"/>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 20×2,8 на резьбу G¾"</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D77" s="1" t="inlineStr"/>
       <c r="E77" s="1" t="inlineStr"/>
       <c r="F77" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G77" s="1" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>у коллекторов</t>
+          <t>концы магистралей</t>
         </is>
       </c>
     </row>
@@ -2807,10 +2811,14 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота трубы Ø16 на 90° (выход из пола у коллектора)</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr"/>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 25×3,5 на резьбу G1"</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D78" s="1" t="inlineStr"/>
       <c r="E78" s="1" t="inlineStr"/>
       <c r="F78" s="1" t="inlineStr">
@@ -2819,10 +2827,14 @@
         </is>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="H78" s="1" t="inlineStr"/>
-      <c r="I78" s="1" t="inlineStr"/>
+      <c r="I78" s="1" t="inlineStr">
+        <is>
+          <t>концы магистралей</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -2830,7 +2842,7 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 20×2,8 с антидиффузионным слоем (EVOH) — магистрали</t>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×4,4 на резьбу G1"</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2842,16 +2854,16 @@
       <c r="E79" s="1" t="inlineStr"/>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G79" s="1" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>Н5 → нагреватель П1</t>
+          <t>концы магистралей</t>
         </is>
       </c>
     </row>
@@ -2861,14 +2873,10 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 25×3,5 с антидиффузионным слоем (EVOH) — магистрали</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø20</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr"/>
       <c r="D80" s="1" t="inlineStr"/>
       <c r="E80" s="1" t="inlineStr"/>
       <c r="F80" s="1" t="inlineStr">
@@ -2877,12 +2885,12 @@
         </is>
       </c>
       <c r="G80" s="1" t="n">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>Н2 → КШ-4, стояки в 1.7, Н4 → КШ-1, Н4 → КШ-3</t>
+          <t>магистрали</t>
         </is>
       </c>
     </row>
@@ -2892,14 +2900,10 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 32×4,4 с антидиффузионным слоем (EVOH) — магистрали</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø25</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr"/>
       <c r="D81" s="1" t="inlineStr"/>
       <c r="E81" s="1" t="inlineStr"/>
       <c r="F81" s="1" t="inlineStr">
@@ -2908,12 +2912,12 @@
         </is>
       </c>
       <c r="G81" s="1" t="n">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>Н3 → КШ-2</t>
+          <t>магистрали</t>
         </is>
       </c>
     </row>
@@ -2923,28 +2927,24 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 20×2,8 на резьбу G¾"</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø32</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr"/>
       <c r="D82" s="1" t="inlineStr"/>
       <c r="E82" s="1" t="inlineStr"/>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G82" s="1" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="H82" s="1" t="inlineStr"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>концы магистралей</t>
+          <t>магистрали</t>
         </is>
       </c>
     </row>
@@ -2954,28 +2954,24 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 25×3,5 на резьбу G1"</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Пленка (мат) с разметкой для укладки труб тёплого пола</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr"/>
       <c r="D83" s="1" t="inlineStr"/>
       <c r="E83" s="1" t="inlineStr"/>
       <c r="F83" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G83" s="1" t="n">
-        <v>12</v>
+        <v>190</v>
       </c>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>концы магистралей</t>
+          <t>листы 4, 5</t>
         </is>
       </c>
     </row>
@@ -2985,28 +2981,24 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×4,4 на резьбу G1"</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Лента демпферная 10×150 мм</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr"/>
       <c r="D84" s="1" t="inlineStr"/>
       <c r="E84" s="1" t="inlineStr"/>
       <c r="F84" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G84" s="1" t="n">
-        <v>4</v>
+        <v>283</v>
       </c>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>концы магистралей</t>
+          <t>по периметру зон и по границам петель</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3008,7 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø20</t>
+          <t>Скоба якорная для крепления трубы Ø16 к основанию, шаг 0,5 м</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr"/>
@@ -3024,168 +3016,188 @@
       <c r="E85" s="1" t="inlineStr"/>
       <c r="F85" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G85" s="1" t="n">
-        <v>14</v>
+        <v>2900</v>
       </c>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>магистрали</t>
+          <t>листы 4, 5</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>82</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø25</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr"/>
-      <c r="D86" s="1" t="inlineStr"/>
-      <c r="E86" s="1" t="inlineStr"/>
-      <c r="F86" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G86" s="1" t="n">
-        <v>67</v>
-      </c>
-      <c r="H86" s="1" t="inlineStr"/>
-      <c r="I86" s="1" t="inlineStr">
-        <is>
-          <t>магистрали</t>
-        </is>
-      </c>
+      <c r="A86" s="1" t="inlineStr"/>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>3. Отопление бани (листы 12, 13)</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="n"/>
+      <c r="D86" s="1" t="n"/>
+      <c r="E86" s="1" t="n"/>
+      <c r="F86" s="1" t="n"/>
+      <c r="G86" s="1" t="n"/>
+      <c r="H86" s="1" t="n"/>
+      <c r="I86" s="1" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø32</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="inlineStr"/>
+          <t>Шкаф коллекторный встроенный ШРВ-3 (ширина ≈750 мм), высота ≈650 мм</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D87" s="1" t="inlineStr"/>
       <c r="E87" s="1" t="inlineStr"/>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>магистрали</t>
+          <t>КШ-Б1 (с/у б3)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Пленка (мат) с разметкой для укладки труб тёплого пола</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr"/>
+          <t>Коллектор прямой из нержавеющей стали 1" на 5 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D88" s="1" t="inlineStr"/>
       <c r="E88" s="1" t="inlineStr"/>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>187</v>
+        <v>1</v>
       </c>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>листы 4, 5</t>
+          <t>КШ-Б1 (с/у б3)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Лента демпферная 10×150 мм</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr"/>
+          <t>Шкаф коллекторный встроенный ШРВ-3 (ширина ≈750 мм), двухъярусный, высота ≈1250 мм</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D89" s="1" t="inlineStr"/>
       <c r="E89" s="1" t="inlineStr"/>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G89" s="1" t="n">
-        <v>280</v>
+        <v>1</v>
       </c>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>по периметру зон и по границам петель</t>
+          <t>КШ-Б2 (с/у б3)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Скоба якорная для крепления трубы Ø16 к основанию, шаг 0,5 м</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr"/>
+          <t>Коллектор тёплого пола из нержавеющей стали 1" на 7 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D90" s="1" t="inlineStr"/>
       <c r="E90" s="1" t="inlineStr"/>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G90" s="1" t="n">
-        <v>2900</v>
+        <v>1</v>
       </c>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>листы 4, 5</t>
+          <t>КШ-Б2 (с/у б3)</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="inlineStr"/>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>3. Отопление бани (листы 12, 13)</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="n"/>
-      <c r="D91" s="1" t="n"/>
-      <c r="E91" s="1" t="n"/>
-      <c r="F91" s="1" t="n"/>
-      <c r="G91" s="1" t="n"/>
-      <c r="H91" s="1" t="n"/>
-      <c r="I91" s="1" t="n"/>
+      <c r="A91" s="1" t="n">
+        <v>86</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 44,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,17 м³/ч, H=0,96 м), байпас, защитный термостат-ограничитель 55 °С</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="inlineStr"/>
+      <c r="E91" s="1" t="inlineStr"/>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G91" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="1" t="inlineStr"/>
+      <c r="I91" s="1" t="inlineStr">
+        <is>
+          <t>КШ-Б2 (с/у б3)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -3193,7 +3205,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встроенный ШРВ-3 (ширина ≈750 мм), высота ≈650 мм</t>
+          <t>Кран шаровой полнопроходной G1" (ввод Ecoflex, подача и обратка)</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -3209,12 +3221,12 @@
         </is>
       </c>
       <c r="G92" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>КШ-Б1 (с/у б3)</t>
+          <t>ввод КШ-Б1</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3236,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Коллектор прямой из нержавеющей стали 1" на 5 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+          <t>Фильтр сетчатый G1" (ввод, подача)</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
@@ -3236,7 +3248,7 @@
       <c r="E93" s="1" t="inlineStr"/>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G93" s="1" t="n">
@@ -3245,7 +3257,7 @@
       <c r="H93" s="1" t="inlineStr"/>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>КШ-Б1 (с/у б3)</t>
+          <t>ФС</t>
         </is>
       </c>
     </row>
@@ -3255,7 +3267,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встроенный ШРВ-3 (ширина ≈750 мм), двухъярусный, высота ≈1250 мм</t>
+          <t>Клапан трёхходовой переключающий с электроприводом Ду 25, расход 1146 кг/ч; приоритет загрузки Б2 по датчику бойлера</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -3276,7 +3288,7 @@
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr">
         <is>
-          <t>КШ-Б2 (с/у б3)</t>
+          <t>УК1</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3298,7 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Коллектор тёплого пола из нержавеющей стали 1" на 7 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+          <t>Клапан зональный двухходовой с электроприводом Ду 25 (линия ТО-Д, по таймеру СПА)</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -3298,7 +3310,7 @@
       <c r="E95" s="1" t="inlineStr"/>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G95" s="1" t="n">
@@ -3307,7 +3319,7 @@
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>КШ-Б2 (с/у б3)</t>
+          <t>УК2</t>
         </is>
       </c>
     </row>
@@ -3317,7 +3329,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 44,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,17 м³/ч, H=0,96 м), байпас, защитный термостат-ограничитель 55 °С</t>
+          <t>Клапан балансировочный Ду 25 (линия ТО-Д)</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -3329,7 +3341,7 @@
       <c r="E96" s="1" t="inlineStr"/>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G96" s="1" t="n">
@@ -3338,7 +3350,7 @@
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>КШ-Б2 (с/у б3)</t>
+          <t>ТО-Д</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3360,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой полнопроходной G1" (ввод Ecoflex, подача и обратка)</t>
+          <t>Теплообменник пластинчатый 20 кВт, 70/50 → 38/28 °С, расход греющей воды 860 кг/ч</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -3364,12 +3376,12 @@
         </is>
       </c>
       <c r="G97" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>ввод КШ-Б1</t>
+          <t>ТО-Д; вторичный контур — СПА (ВК)</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3391,7 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Фильтр сетчатый G1" (ввод, подача)</t>
+          <t>Бойлер косвенного нагрева 200 л, узкий Ø520 мм, змеевик 20 кВт (расход 1146 кг/ч)</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -3400,7 +3412,7 @@
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>ФС</t>
+          <t>Б2; обвязка ГВС — раздел ВК</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3422,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Клапан трёхходовой переключающий с электроприводом Ду 25, расход 1146 кг/ч; приоритет загрузки Б2 по датчику бойлера</t>
+          <t>Сервопривод термоэлектрический 230 В, нормально закрытый, на термостатический клапан коллектора</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -3426,12 +3438,12 @@
         </is>
       </c>
       <c r="G99" s="1" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>УК1</t>
+          <t>управление — автоматика «Люкс»</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3453,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Клапан зональный двухходовой с электроприводом Ду 25 (линия ТО-Д, по таймеру СПА)</t>
+          <t>Радиатор стальной панельный 33/500, L=1100 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1528 Вт</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -3462,7 +3474,7 @@
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>УК2</t>
+          <t>Р-б1 (б5)</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3484,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Клапан балансировочный Ду 25 (линия ТО-Д)</t>
+          <t>Радиатор стальной панельный 33/500, L=500 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 632 Вт</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -3493,7 +3505,7 @@
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>ТО-Д</t>
+          <t>Р-б2 (б2)</t>
         </is>
       </c>
     </row>
@@ -3503,28 +3515,32 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Теплообменник пластинчатый 20 кВт, 70/50 → 38/28 °С, расход греющей воды 860 кг/ч</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2150 мм, тепловая мощность при 70/55 °С не менее 1108 Вт</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr"/>
-      <c r="E102" s="1" t="inlineStr"/>
+      <c r="E102" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G102" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>ТО-Д; вторичный контур — СПА (ВК)</t>
+          <t>Кв-б1 (б6), Кв-б2 (б6)</t>
         </is>
       </c>
     </row>
@@ -3534,16 +3550,20 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Бойлер косвенного нагрева 200 л, узкий Ø520 мм, змеевик 20 кВт (расход 1146 кг/ч)</t>
+          <t>Конвектор внутрипольный из нержавеющей стали для влажных помещений, с вентилятором 24 В пост. тока, 260×140 мм, L=2200 мм, тепловая мощность при 70/55 °С не менее 2614 Вт</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>КЗТО «Бриз В TURBO Нерж»</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr"/>
-      <c r="E103" s="1" t="inlineStr"/>
+      <c r="E103" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -3555,7 +3575,7 @@
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>Б2; обвязка ГВС — раздел ВК</t>
+          <t>Кв-б3 (б7, у джакузи); в нише плиты, ≈2030 Вт/м при Δt50</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3585,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Сервопривод термоэлектрический 230 В, нормально закрытый, на термостатический клапан коллектора</t>
+          <t>Узел нижнего подключения радиатора запорный, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -3581,12 +3601,12 @@
         </is>
       </c>
       <c r="G104" s="1" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>управление — автоматика «Люкс»</t>
+          <t>Р-б1, Р-б2</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3616,7 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 33/500, L=1100 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1528 Вт</t>
+          <t>Клапан запорный G½" для подключения конвектора</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -3612,12 +3632,12 @@
         </is>
       </c>
       <c r="G105" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>Р-б1 (б5)</t>
+          <t>Кв-б1…Кв-б3</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3647,7 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 33/500, L=500 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 632 Вт</t>
+          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — петли тёплого пола</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -3639,16 +3659,16 @@
       <c r="E106" s="1" t="inlineStr"/>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G106" s="1" t="n">
-        <v>1</v>
+        <v>271</v>
       </c>
       <c r="H106" s="1" t="inlineStr"/>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>Р-б2 (б2)</t>
+          <t>петли — 7 шт., лист 12</t>
         </is>
       </c>
     </row>
@@ -3658,32 +3678,28 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2150 мм, тепловая мощность при 70/55 °С не менее 1108 Вт</t>
+          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — подводки к приборам</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t>КЗТО «Бриз В», модель — по каталогу</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr"/>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E107" s="1" t="inlineStr"/>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>Кв-б1 (б6), Кв-б2 (б6)</t>
+          <t>лист 12</t>
         </is>
       </c>
     </row>
@@ -3693,32 +3709,28 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный из нержавеющей стали для влажных помещений, с вентилятором 24 В пост. тока, 260×140 мм, L=2200 мм, тепловая мощность при 70/55 °С не менее 2614 Вт</t>
+          <t>Труба PE-Xa 32×4,4 с антидиффузионным слоем (EVOH) — линии ТО-Д и Б2</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>КЗТО «Бриз В TURBO Нерж»</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D108" s="1" t="inlineStr"/>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E108" s="1" t="inlineStr"/>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G108" s="1" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="H108" s="1" t="inlineStr"/>
       <c r="I108" s="1" t="inlineStr">
         <is>
-          <t>Кв-б3 (б7, у джакузи); в нише плиты, ≈2030 Вт/м при Δt50</t>
+          <t>от ввода КШ-Б1</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3740,7 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Узел нижнего подключения радиатора запорный, присоединение евроконус G¾"</t>
+          <t>Фитинг компрессионный (евроконус) для трубы PE-Xa 16×2,0 на G¾"</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
@@ -3744,12 +3756,12 @@
         </is>
       </c>
       <c r="G109" s="1" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>Р-б1, Р-б2</t>
+          <t>коллекторы, радиаторы</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3771,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Клапан запорный G½" для подключения конвектора</t>
+          <t>Фитинг компрессионный для трубы PE-Xa 16×2,0 на наружную резьбу G½"</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -3780,7 +3792,7 @@
       <c r="H110" s="1" t="inlineStr"/>
       <c r="I110" s="1" t="inlineStr">
         <is>
-          <t>Кв-б1…Кв-б3</t>
+          <t>конвекторы</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3802,7 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — петли тёплого пола</t>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×4,4 на резьбу G1"</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
@@ -3802,16 +3814,16 @@
       <c r="E111" s="1" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>271</v>
+        <v>8</v>
       </c>
       <c r="H111" s="1" t="inlineStr"/>
       <c r="I111" s="1" t="inlineStr">
         <is>
-          <t>петли — 7 шт., лист 12</t>
+          <t>ТО-Д, Б2</t>
         </is>
       </c>
     </row>
@@ -3821,14 +3833,10 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — подводки к приборам</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø32</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="inlineStr"/>
       <c r="D112" s="1" t="inlineStr"/>
       <c r="E112" s="1" t="inlineStr"/>
       <c r="F112" s="1" t="inlineStr">
@@ -3837,12 +3845,12 @@
         </is>
       </c>
       <c r="G112" s="1" t="n">
-        <v>116</v>
+        <v>43</v>
       </c>
       <c r="H112" s="1" t="inlineStr"/>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>лист 12</t>
+          <t>ТО-Д, Б2</t>
         </is>
       </c>
     </row>
@@ -3852,14 +3860,10 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 32×4,4 с антидиффузионным слоем (EVOH) — линии ТО-Д и Б2</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена, толщина 6 мм, для трубы Ø16</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="inlineStr"/>
       <c r="D113" s="1" t="inlineStr"/>
       <c r="E113" s="1" t="inlineStr"/>
       <c r="F113" s="1" t="inlineStr">
@@ -3868,12 +3872,12 @@
         </is>
       </c>
       <c r="G113" s="1" t="n">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
         <is>
-          <t>от ввода КШ-Б1</t>
+          <t>подводки вне своих петель</t>
         </is>
       </c>
     </row>
@@ -3883,28 +3887,24 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Фитинг компрессионный (евроконус) для трубы PE-Xa 16×2,0 на G¾"</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Труба гофрированная защитная (гофра) для трубы Ø16</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="inlineStr"/>
       <c r="D114" s="1" t="inlineStr"/>
       <c r="E114" s="1" t="inlineStr"/>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>28</v>
+        <v>252</v>
       </c>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">
         <is>
-          <t>коллекторы, радиаторы</t>
+          <t>подводки вне своих петель</t>
         </is>
       </c>
     </row>
@@ -3914,14 +3914,10 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Фитинг компрессионный для трубы PE-Xa 16×2,0 на наружную резьбу G½"</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Фиксатор поворота трубы Ø16 на 90° (выход из пола у коллектора)</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="inlineStr"/>
       <c r="D115" s="1" t="inlineStr"/>
       <c r="E115" s="1" t="inlineStr"/>
       <c r="F115" s="1" t="inlineStr">
@@ -3930,14 +3926,10 @@
         </is>
       </c>
       <c r="G115" s="1" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H115" s="1" t="inlineStr"/>
-      <c r="I115" s="1" t="inlineStr">
-        <is>
-          <t>конвекторы</t>
-        </is>
-      </c>
+      <c r="I115" s="1" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -3945,28 +3937,24 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×4,4 на резьбу G1"</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Пленка (мат) с разметкой для укладки труб тёплого пола</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="inlineStr"/>
       <c r="D116" s="1" t="inlineStr"/>
       <c r="E116" s="1" t="inlineStr"/>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G116" s="1" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="H116" s="1" t="inlineStr"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>ТО-Д, Б2</t>
+          <t>лист 12</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3964,7 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø32</t>
+          <t>Лента демпферная 10×150 мм</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr"/>
@@ -3988,12 +3976,12 @@
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
       <c r="I117" s="1" t="inlineStr">
         <is>
-          <t>ТО-Д, Б2</t>
+          <t>по периметру зон и по границам петель</t>
         </is>
       </c>
     </row>
@@ -4003,7 +3991,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена, толщина 6 мм, для трубы Ø16</t>
+          <t>Скоба якорная для крепления трубы Ø16 к основанию, шаг 0,5 м</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr"/>
@@ -4011,130 +3999,146 @@
       <c r="E118" s="1" t="inlineStr"/>
       <c r="F118" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G118" s="1" t="n">
-        <v>252</v>
+        <v>600</v>
       </c>
       <c r="H118" s="1" t="inlineStr"/>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>подводки вне своих петель</t>
+          <t>лист 12</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
-        <v>114</v>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>Труба гофрированная защитная (гофра) для трубы Ø16</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr"/>
-      <c r="D119" s="1" t="inlineStr"/>
-      <c r="E119" s="1" t="inlineStr"/>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G119" s="1" t="n">
-        <v>252</v>
-      </c>
-      <c r="H119" s="1" t="inlineStr"/>
-      <c r="I119" s="1" t="inlineStr">
-        <is>
-          <t>подводки вне своих петель</t>
-        </is>
-      </c>
+      <c r="A119" s="1" t="inlineStr"/>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>4. Теплотрасса дом – баня (листы 13, 14)</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="n"/>
+      <c r="D119" s="1" t="n"/>
+      <c r="E119" s="1" t="n"/>
+      <c r="F119" s="1" t="n"/>
+      <c r="G119" s="1" t="n"/>
+      <c r="H119" s="1" t="n"/>
+      <c r="I119" s="1" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота трубы Ø16 на 90° (выход из пола у коллектора)</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr"/>
+          <t>Труба предизолированная гибкая: две трубы PE-Xa 32×2,9 отопления и две санитарные трубы (по разделу ВК) в общей оболочке</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>Uponor Ecoflex Quattro, типоразмер — по каталогу</t>
+        </is>
+      </c>
       <c r="D120" s="1" t="inlineStr"/>
-      <c r="E120" s="1" t="inlineStr"/>
+      <c r="E120" s="1" t="inlineStr">
+        <is>
+          <t>Uponor</t>
+        </is>
+      </c>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H120" s="1" t="inlineStr"/>
-      <c r="I120" s="1" t="inlineStr"/>
+      <c r="I120" s="1" t="inlineStr">
+        <is>
+          <t>≈16,4 м по трассе с подъёмами + 10 %; лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Пленка (мат) с разметкой для укладки труб тёплого пола</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr"/>
+          <t>Манжета концевая для трубы Ecoflex Quattro</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>по каталогу производителя трубы</t>
+        </is>
+      </c>
       <c r="D121" s="1" t="inlineStr"/>
-      <c r="E121" s="1" t="inlineStr"/>
+      <c r="E121" s="1" t="inlineStr">
+        <is>
+          <t>Uponor</t>
+        </is>
+      </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>лист 12</t>
+          <t>вводы в дом и баню</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Лента демпферная 10×150 мм</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr"/>
+          <t>Гильза ввода с уплотнительным кольцом через фундамент (комплект ввода производителя)</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>по каталогу производителя трубы</t>
+        </is>
+      </c>
       <c r="D122" s="1" t="inlineStr"/>
-      <c r="E122" s="1" t="inlineStr"/>
+      <c r="E122" s="1" t="inlineStr">
+        <is>
+          <t>Uponor</t>
+        </is>
+      </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>по периметру зон и по границам петель</t>
+          <t>узлы 1, 2, лист 13</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Скоба якорная для крепления трубы Ø16 к основанию, шаг 0,5 м</t>
+          <t>Гильза в плите пола для трубы Ecoflex Quattro</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr"/>
@@ -4146,29 +4150,45 @@
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>600</v>
+        <v>2</v>
       </c>
       <c r="H123" s="1" t="inlineStr"/>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>лист 12</t>
+          <t>узлы 1, 2, лист 13</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="inlineStr"/>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>4. Теплотрасса дом – баня (листы 13, 14)</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="n"/>
-      <c r="D124" s="1" t="n"/>
-      <c r="E124" s="1" t="n"/>
-      <c r="F124" s="1" t="n"/>
-      <c r="G124" s="1" t="n"/>
-      <c r="H124" s="1" t="n"/>
-      <c r="I124" s="1" t="n"/>
+      <c r="A124" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×2,9 на резьбу G1"</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>по каталогу производителя трубы</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="inlineStr"/>
+      <c r="E124" s="1" t="inlineStr"/>
+      <c r="F124" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G124" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H124" s="1" t="inlineStr"/>
+      <c r="I124" s="1" t="inlineStr">
+        <is>
+          <t>концы Т1, Т2</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -4176,115 +4196,91 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Труба предизолированная гибкая: две трубы PE-Xa 32×2,9 отопления и две санитарные трубы (по разделу ВК) в общей оболочке</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>Uponor Ecoflex Quattro, типоразмер — по каталогу</t>
-        </is>
-      </c>
+          <t>Лента сигнальная «Осторожно, теплотрасса»</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="inlineStr"/>
       <c r="D125" s="1" t="inlineStr"/>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>Uponor</t>
-        </is>
-      </c>
+      <c r="E125" s="1" t="inlineStr"/>
       <c r="F125" s="1" t="inlineStr">
         <is>
           <t>м</t>
         </is>
       </c>
       <c r="G125" s="1" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H125" s="1" t="inlineStr"/>
       <c r="I125" s="1" t="inlineStr">
         <is>
-          <t>≈16,4 м по трассе с подъёмами + 10 %; лист 14</t>
+          <t>300 мм над трубой</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
-        <v>120</v>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>Манжета концевая для трубы Ecoflex Quattro</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>по каталогу производителя трубы</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr"/>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>Uponor</t>
-        </is>
-      </c>
-      <c r="F126" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G126" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H126" s="1" t="inlineStr"/>
-      <c r="I126" s="1" t="inlineStr">
-        <is>
-          <t>вводы в дом и баню</t>
-        </is>
-      </c>
+      <c r="A126" s="1" t="inlineStr"/>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>5. Вентиляция (листы 9–12)</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="n"/>
+      <c r="D126" s="1" t="n"/>
+      <c r="E126" s="1" t="n"/>
+      <c r="F126" s="1" t="n"/>
+      <c r="G126" s="1" t="n"/>
+      <c r="H126" s="1" t="n"/>
+      <c r="I126" s="1" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Гильза ввода с уплотнительным кольцом через фундамент (комплект ввода производителя)</t>
+          <t>Приточно-вытяжная установка с рекуперацией тепла и влаги (пластинчатый энтальпийный рекуператор), 750 м³/ч, свободный напор ≈180 Па при 750 м³/ч (по расчёту сети 159 Па при 700 м³/ч), водяной нагреватель (≈2,6 кВт, 70/50 °С) со смесительным узлом и автоматикой в комплекте, патрубки Ø250, ≈1500×1080×610 мм, ≈145 кг, 220 В, ≈0,8 кВт</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>по каталогу производителя трубы</t>
+          <t>Turkov Zenit 750 Heco W (или аналог)</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr"/>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t>Uponor</t>
+          <t>Turkov</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G127" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>узлы 1, 2, лист 13</t>
+          <t>П1, под потолком топочной (лист 9)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Гильза в плите пола для трубы Ecoflex Quattro</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr"/>
+          <t>Кран шаровой G¾" (подключение нагревателя П1 к смесительному узлу, подача и обратка)</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D128" s="1" t="inlineStr"/>
       <c r="E128" s="1" t="inlineStr"/>
       <c r="F128" s="1" t="inlineStr">
@@ -4298,29 +4294,29 @@
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>узлы 1, 2, лист 13</t>
+          <t>П1; фильтр — на отводе Н5 у РК</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×2,9 на резьбу G1"</t>
+          <t>Труба полипропиленовая канализационная Ø32 — дренаж конденсата П1 к трапу топочной (сифон с сухим затвором — раздел ВК)</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>по каталогу производителя трубы</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr"/>
       <c r="E129" s="1" t="inlineStr"/>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G129" s="1" t="n">
@@ -4329,51 +4325,71 @@
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>концы Т1, Т2</t>
+          <t>П1: опуск с +2,450 к трапу (листы 7, 9)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Лента сигнальная «Осторожно, теплотрасса»</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr"/>
+          <t>Клапан воздушный круглый Ø250 с электроприводом 230 В с возвратной пружиной (нормально закрыт), на наружном воздухе П1; не ставится, если встроен в установку Turkov</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D130" s="1" t="inlineStr"/>
       <c r="E130" s="1" t="inlineStr"/>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G130" s="1" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr">
         <is>
-          <t>300 мм над трубой</t>
+          <t>КВ-Н; защита нагревателя П1 от разморозки при отключении питания</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="inlineStr"/>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>5. Вентиляция (листы 9–12)</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="n"/>
-      <c r="D131" s="1" t="n"/>
-      <c r="E131" s="1" t="n"/>
-      <c r="F131" s="1" t="n"/>
-      <c r="G131" s="1" t="n"/>
-      <c r="H131" s="1" t="n"/>
-      <c r="I131" s="1" t="n"/>
+      <c r="A131" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Шумоглушитель круглый Ø250, L=600 мм</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr"/>
+      <c r="E131" s="1" t="inlineStr"/>
+      <c r="F131" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G131" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H131" s="1" t="inlineStr"/>
+      <c r="I131" s="1" t="inlineStr">
+        <is>
+          <t>ШГ, на П и В у П1, между опуском и западной стеной топочной</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -4381,32 +4397,24 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Приточно-вытяжная установка с рекуперацией тепла и влаги (пластинчатый энтальпийный рекуператор), 750 м³/ч, свободный напор ≈180 Па при 750 м³/ч (по расчёту сети 159 Па при 700 м³/ч), водяной нагреватель (≈2,6 кВт, 70/50 °С) со смесительным узлом и автоматикой в комплекте, патрубки Ø250, ≈1500×1080×610 мм, ≈145 кг, 220 В, ≈0,8 кВт</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>Turkov Zenit 750 Heco W (или аналог)</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø100, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr"/>
       <c r="D132" s="1" t="inlineStr"/>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>Turkov</t>
-        </is>
-      </c>
+      <c r="E132" s="1" t="inlineStr"/>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G132" s="1" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>П1, под потолком топочной (лист 9)</t>
+          <t>П1 — 29 м; баня ВВ-б1, ВВ-б2 — 3 м</t>
         </is>
       </c>
     </row>
@@ -4416,28 +4424,24 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой G¾" (подключение нагревателя П1 к смесительному узлу, подача и обратка)</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø125, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="inlineStr"/>
       <c r="D133" s="1" t="inlineStr"/>
       <c r="E133" s="1" t="inlineStr"/>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G133" s="1" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr">
         <is>
-          <t>П1; фильтр — на отводе Н5 у РК</t>
+          <t>П1</t>
         </is>
       </c>
     </row>
@@ -4447,14 +4451,10 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø32 — дренаж конденсата П1 к трапу топочной (сифон с сухим затвором — раздел ВК)</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø150, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="inlineStr"/>
       <c r="D134" s="1" t="inlineStr"/>
       <c r="E134" s="1" t="inlineStr"/>
       <c r="F134" s="1" t="inlineStr">
@@ -4462,13 +4462,15 @@
           <t>м</t>
         </is>
       </c>
-      <c r="G134" s="1" t="n">
-        <v>4</v>
+      <c r="G134" s="1" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
       </c>
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr">
         <is>
-          <t>П1: опуск с +2,450 к трапу (листы 7, 9)</t>
+          <t>ВЗ (кухонный зонт)</t>
         </is>
       </c>
     </row>
@@ -4478,28 +4480,24 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Клапан воздушный круглый Ø250 с электроприводом 230 В с возвратной пружиной (нормально закрыт), на наружном воздухе П1; не ставится, если встроен в установку Turkov</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø160, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="inlineStr"/>
       <c r="D135" s="1" t="inlineStr"/>
       <c r="E135" s="1" t="inlineStr"/>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G135" s="1" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>КВ-Н; защита нагревателя П1 от разморозки при отключении питания</t>
+          <t>П1</t>
         </is>
       </c>
     </row>
@@ -4509,28 +4507,26 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Шумоглушитель круглый Ø250, L=600 мм</t>
-        </is>
-      </c>
-      <c r="C136" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø200, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="inlineStr"/>
       <c r="D136" s="1" t="inlineStr"/>
       <c r="E136" s="1" t="inlineStr"/>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G136" s="1" t="n">
-        <v>2</v>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G136" s="1" t="inlineStr">
+        <is>
+          <t>24,8</t>
+        </is>
       </c>
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr">
         <is>
-          <t>ШГ, на П и В у П1, между опуском и западной стеной топочной</t>
+          <t>П1 — 18 м; ВЗ (кухонный зонт) — 6,8 м</t>
         </is>
       </c>
     </row>
@@ -4540,7 +4536,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø100, толщина стали — по СП 60.13330</t>
+          <t>Воздуховод круглый из оцинкованной стали Ø250, толщина стали — по СП 60.13330</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr"/>
@@ -4552,12 +4548,12 @@
         </is>
       </c>
       <c r="G137" s="1" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr">
         <is>
-          <t>П1 — 29 м; баня ВВ-б1, ВВ-б2 — 3 м</t>
+          <t>П1: магистрали, Н, выброс в Ш-2; В2 в Ш-2</t>
         </is>
       </c>
     </row>
@@ -4567,7 +4563,7 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø125, толщина стали — по СП 60.13330</t>
+          <t>Отвод 90° круглый оцинкованный Ø100</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr"/>
@@ -4575,16 +4571,16 @@
       <c r="E138" s="1" t="inlineStr"/>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G138" s="1" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>П1</t>
+          <t>в т. ч. баня ВВ-б1, ВВ-б2 — 2</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4590,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø150, толщина стали — по СП 60.13330</t>
+          <t>Отвод 90° круглый оцинкованный Ø125</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr"/>
@@ -4602,20 +4598,14 @@
       <c r="E139" s="1" t="inlineStr"/>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G139" s="1" t="inlineStr">
-        <is>
-          <t>2,7</t>
-        </is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G139" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="H139" s="1" t="inlineStr"/>
-      <c r="I139" s="1" t="inlineStr">
-        <is>
-          <t>ВЗ (кухонный зонт)</t>
-        </is>
-      </c>
+      <c r="I139" s="1" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -4623,7 +4613,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø160, толщина стали — по СП 60.13330</t>
+          <t>Отвод 90° круглый оцинкованный Ø150</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr"/>
@@ -4631,16 +4621,16 @@
       <c r="E140" s="1" t="inlineStr"/>
       <c r="F140" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G140" s="1" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr">
         <is>
-          <t>П1</t>
+          <t>ВЗ (кухонный зонт)</t>
         </is>
       </c>
     </row>
@@ -4650,7 +4640,7 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø200, толщина стали — по СП 60.13330</t>
+          <t>Отвод 90° круглый оцинкованный Ø160</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr"/>
@@ -4658,20 +4648,14 @@
       <c r="E141" s="1" t="inlineStr"/>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G141" s="1" t="inlineStr">
-        <is>
-          <t>24,8</t>
-        </is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G141" s="1" t="n">
+        <v>6</v>
       </c>
       <c r="H141" s="1" t="inlineStr"/>
-      <c r="I141" s="1" t="inlineStr">
-        <is>
-          <t>П1 — 18 м; ВЗ (кухонный зонт) — 6,8 м</t>
-        </is>
-      </c>
+      <c r="I141" s="1" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -4679,7 +4663,7 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø250, толщина стали — по СП 60.13330</t>
+          <t>Отвод 90° круглый оцинкованный Ø200</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr"/>
@@ -4687,16 +4671,16 @@
       <c r="E142" s="1" t="inlineStr"/>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G142" s="1" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr">
         <is>
-          <t>П1: магистрали, Н, выброс в Ш-2; В2 в Ш-2</t>
+          <t>в т. ч. ВЗ (кухонный зонт) — 1</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4690,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø100</t>
+          <t>Отвод 90° круглый оцинкованный Ø250</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr"/>
@@ -4718,14 +4702,10 @@
         </is>
       </c>
       <c r="G143" s="1" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H143" s="1" t="inlineStr"/>
-      <c r="I143" s="1" t="inlineStr">
-        <is>
-          <t>в т. ч. баня ВВ-б1, ВВ-б2 — 2</t>
-        </is>
-      </c>
+      <c r="I143" s="1" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -4733,7 +4713,7 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø125</t>
+          <t>Тройник круглый оцинкованный Ø125/Ø100</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr"/>
@@ -4745,7 +4725,7 @@
         </is>
       </c>
       <c r="G144" s="1" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H144" s="1" t="inlineStr"/>
       <c r="I144" s="1" t="inlineStr"/>
@@ -4756,7 +4736,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø150</t>
+          <t>Тройник круглый оцинкованный Ø160/Ø100</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr"/>
@@ -4768,14 +4748,10 @@
         </is>
       </c>
       <c r="G145" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H145" s="1" t="inlineStr"/>
-      <c r="I145" s="1" t="inlineStr">
-        <is>
-          <t>ВЗ (кухонный зонт)</t>
-        </is>
-      </c>
+      <c r="I145" s="1" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -4783,7 +4759,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø160</t>
+          <t>Тройник круглый оцинкованный Ø160/Ø125</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr"/>
@@ -4795,7 +4771,7 @@
         </is>
       </c>
       <c r="G146" s="1" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H146" s="1" t="inlineStr"/>
       <c r="I146" s="1" t="inlineStr"/>
@@ -4806,7 +4782,7 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø200</t>
+          <t>Тройник круглый оцинкованный Ø200/Ø125</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr"/>
@@ -4818,14 +4794,10 @@
         </is>
       </c>
       <c r="G147" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H147" s="1" t="inlineStr"/>
-      <c r="I147" s="1" t="inlineStr">
-        <is>
-          <t>в т. ч. ВЗ (кухонный зонт) — 1</t>
-        </is>
-      </c>
+      <c r="I147" s="1" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -4833,7 +4805,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø250</t>
+          <t>Тройник круглый оцинкованный Ø200/Ø160</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr"/>
@@ -4845,7 +4817,7 @@
         </is>
       </c>
       <c r="G148" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H148" s="1" t="inlineStr"/>
       <c r="I148" s="1" t="inlineStr"/>
@@ -4856,7 +4828,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø125/Ø100</t>
+          <t>Тройник круглый оцинкованный Ø200/Ø200</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr"/>
@@ -4868,7 +4840,7 @@
         </is>
       </c>
       <c r="G149" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H149" s="1" t="inlineStr"/>
       <c r="I149" s="1" t="inlineStr"/>
@@ -4879,7 +4851,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø160/Ø100</t>
+          <t>Тройник круглый оцинкованный Ø250/Ø100</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr"/>
@@ -4902,7 +4874,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø160/Ø125</t>
+          <t>Тройник круглый оцинкованный Ø250/Ø200</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr"/>
@@ -4914,7 +4886,7 @@
         </is>
       </c>
       <c r="G151" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H151" s="1" t="inlineStr"/>
       <c r="I151" s="1" t="inlineStr"/>
@@ -4925,7 +4897,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø200/Ø125</t>
+          <t>Переход круглый оцинкованный Ø125/Ø100</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr"/>
@@ -4937,7 +4909,7 @@
         </is>
       </c>
       <c r="G152" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H152" s="1" t="inlineStr"/>
       <c r="I152" s="1" t="inlineStr"/>
@@ -4948,7 +4920,7 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø200/Ø160</t>
+          <t>Переход круглый оцинкованный Ø160/Ø125</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr"/>
@@ -4960,7 +4932,7 @@
         </is>
       </c>
       <c r="G153" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H153" s="1" t="inlineStr"/>
       <c r="I153" s="1" t="inlineStr"/>
@@ -4971,7 +4943,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø200/Ø200</t>
+          <t>Переход круглый оцинкованный Ø200/Ø100</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr"/>
@@ -4994,7 +4966,7 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø250/Ø100</t>
+          <t>Переход круглый оцинкованный Ø200/Ø150</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr"/>
@@ -5006,10 +4978,14 @@
         </is>
       </c>
       <c r="G155" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H155" s="1" t="inlineStr"/>
-      <c r="I155" s="1" t="inlineStr"/>
+      <c r="I155" s="1" t="inlineStr">
+        <is>
+          <t>ВЗ (кухонный зонт)</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -5017,7 +4993,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø250/Ø200</t>
+          <t>Переход круглый оцинкованный Ø200/Ø160</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr"/>
@@ -5029,7 +5005,7 @@
         </is>
       </c>
       <c r="G156" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H156" s="1" t="inlineStr"/>
       <c r="I156" s="1" t="inlineStr"/>
@@ -5040,7 +5016,7 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø125/Ø100</t>
+          <t>Переход круглый оцинкованный Ø250/Ø160</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr"/>
@@ -5052,7 +5028,7 @@
         </is>
       </c>
       <c r="G157" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H157" s="1" t="inlineStr"/>
       <c r="I157" s="1" t="inlineStr"/>
@@ -5063,7 +5039,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø160/Ø125</t>
+          <t>Переход круглый оцинкованный Ø250/Ø200</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr"/>
@@ -5075,7 +5051,7 @@
         </is>
       </c>
       <c r="G158" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H158" s="1" t="inlineStr"/>
       <c r="I158" s="1" t="inlineStr"/>
@@ -5086,10 +5062,14 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø200/Ø100</t>
-        </is>
-      </c>
-      <c r="C159" s="1" t="inlineStr"/>
+          <t>Регулятор расхода воздуха (ирисовый клапан) Ø100</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D159" s="1" t="inlineStr"/>
       <c r="E159" s="1" t="inlineStr"/>
       <c r="F159" s="1" t="inlineStr">
@@ -5098,10 +5078,14 @@
         </is>
       </c>
       <c r="G159" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H159" s="1" t="inlineStr"/>
-      <c r="I159" s="1" t="inlineStr"/>
+      <c r="I159" s="1" t="inlineStr">
+        <is>
+          <t>РР, на ответвлениях</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -5109,10 +5093,14 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø200/Ø150</t>
-        </is>
-      </c>
-      <c r="C160" s="1" t="inlineStr"/>
+          <t>Регулятор расхода воздуха (ирисовый клапан) Ø125</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D160" s="1" t="inlineStr"/>
       <c r="E160" s="1" t="inlineStr"/>
       <c r="F160" s="1" t="inlineStr">
@@ -5121,12 +5109,12 @@
         </is>
       </c>
       <c r="G160" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H160" s="1" t="inlineStr"/>
       <c r="I160" s="1" t="inlineStr">
         <is>
-          <t>ВЗ (кухонный зонт)</t>
+          <t>РР, на ответвлениях</t>
         </is>
       </c>
     </row>
@@ -5136,10 +5124,14 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø200/Ø160</t>
-        </is>
-      </c>
-      <c r="C161" s="1" t="inlineStr"/>
+          <t>Регулятор расхода воздуха (ирисовый клапан) Ø160</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D161" s="1" t="inlineStr"/>
       <c r="E161" s="1" t="inlineStr"/>
       <c r="F161" s="1" t="inlineStr">
@@ -5148,10 +5140,14 @@
         </is>
       </c>
       <c r="G161" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H161" s="1" t="inlineStr"/>
-      <c r="I161" s="1" t="inlineStr"/>
+      <c r="I161" s="1" t="inlineStr">
+        <is>
+          <t>РР, на ответвлениях</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -5159,10 +5155,14 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø250/Ø160</t>
-        </is>
-      </c>
-      <c r="C162" s="1" t="inlineStr"/>
+          <t>Диффузор щелевой (линейный) приточный в торце подшивки, L=600 мм, с камерой статического давления, присоединение Ø125, расход 70 м³/ч; типоразмер — по расходу, по каталогу</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D162" s="1" t="inlineStr"/>
       <c r="E162" s="1" t="inlineStr"/>
       <c r="F162" s="1" t="inlineStr">
@@ -5171,10 +5171,14 @@
         </is>
       </c>
       <c r="G162" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H162" s="1" t="inlineStr"/>
-      <c r="I162" s="1" t="inlineStr"/>
+      <c r="I162" s="1" t="inlineStr">
+        <is>
+          <t>1.10 — 3 шт.</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -5182,10 +5186,14 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø250/Ø200</t>
-        </is>
-      </c>
-      <c r="C163" s="1" t="inlineStr"/>
+          <t>Диффузор потолочный приточный с камерой статического давления, присоединение Ø100, расход 30/60 м³/ч; типоразмер — по расходу, по каталогу</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D163" s="1" t="inlineStr"/>
       <c r="E163" s="1" t="inlineStr"/>
       <c r="F163" s="1" t="inlineStr">
@@ -5194,10 +5202,14 @@
         </is>
       </c>
       <c r="G163" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H163" s="1" t="inlineStr"/>
-      <c r="I163" s="1" t="inlineStr"/>
+      <c r="I163" s="1" t="inlineStr">
+        <is>
+          <t>1.11 — 2 шт., 2.2</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -5205,7 +5217,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Регулятор расхода воздуха (ирисовый клапан) Ø100</t>
+          <t>Решётка приточная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -5221,12 +5233,12 @@
         </is>
       </c>
       <c r="G164" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H164" s="1" t="inlineStr"/>
       <c r="I164" s="1" t="inlineStr">
         <is>
-          <t>РР, на ответвлениях</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5248,7 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Регулятор расхода воздуха (ирисовый клапан) Ø125</t>
+          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø100, расход 40/50/60 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -5252,12 +5264,12 @@
         </is>
       </c>
       <c r="G165" s="1" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H165" s="1" t="inlineStr"/>
       <c r="I165" s="1" t="inlineStr">
         <is>
-          <t>РР, на ответвлениях</t>
+          <t>1.4, 1.3, 2.6</t>
         </is>
       </c>
     </row>
@@ -5267,7 +5279,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Регулятор расхода воздуха (ирисовый клапан) Ø160</t>
+          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø125, расход 75/90 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -5283,12 +5295,12 @@
         </is>
       </c>
       <c r="G166" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H166" s="1" t="inlineStr"/>
       <c r="I166" s="1" t="inlineStr">
         <is>
-          <t>РР, на ответвлениях</t>
+          <t>2.9, 2.8, 2.1</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5310,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Диффузор щелевой (линейный) приточный в торце подшивки, L=600 мм, с камерой статического давления, присоединение Ø125, расход 70 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -5314,12 +5326,12 @@
         </is>
       </c>
       <c r="G167" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H167" s="1" t="inlineStr"/>
       <c r="I167" s="1" t="inlineStr">
         <is>
-          <t>1.10 — 3 шт.</t>
+          <t>1.8</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5341,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Диффузор потолочный приточный с камерой статического давления, присоединение Ø100, расход 30/60 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø125, расход 90 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -5345,12 +5357,12 @@
         </is>
       </c>
       <c r="G168" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H168" s="1" t="inlineStr"/>
       <c r="I168" s="1" t="inlineStr">
         <is>
-          <t>1.11 — 2 шт., 2.2</t>
+          <t>1.10 (кухня)</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5372,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Решётка приточная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø160, расход 120 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -5381,7 +5393,7 @@
       <c r="H169" s="1" t="inlineStr"/>
       <c r="I169" s="1" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.10 (верх 2-го света)</t>
         </is>
       </c>
     </row>
@@ -5391,7 +5403,7 @@
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø100, расход 40/50/60 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка наружная воздухозаборная 500×400, низ +2,600</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -5407,12 +5419,12 @@
         </is>
       </c>
       <c r="G170" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H170" s="1" t="inlineStr"/>
       <c r="I170" s="1" t="inlineStr">
         <is>
-          <t>1.4, 1.3, 2.6</t>
+          <t>Н1, восточная стена топочной</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5434,7 @@
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø125, расход 75/90 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Оголовок (зонт) воздуховода Ø250 выше кровли</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -5438,12 +5450,12 @@
         </is>
       </c>
       <c r="G171" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H171" s="1" t="inlineStr"/>
       <c r="I171" s="1" t="inlineStr">
         <is>
-          <t>2.9, 2.8, 2.1</t>
+          <t>выброс П1, В2 (Ш-2)</t>
         </is>
       </c>
     </row>
@@ -5453,7 +5465,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Оголовок (зонт) воздуховода Ø200 выше кровли</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -5474,7 +5486,7 @@
       <c r="H172" s="1" t="inlineStr"/>
       <c r="I172" s="1" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>ВЗ (кухонный зонт), шахта над мангалом 1.12</t>
         </is>
       </c>
     </row>
@@ -5484,7 +5496,7 @@
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø125, расход 90 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная под воздуховод Ø250 (вытяжка топочной, естественная)</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -5505,7 +5517,7 @@
       <c r="H173" s="1" t="inlineStr"/>
       <c r="I173" s="1" t="inlineStr">
         <is>
-          <t>1.10 (кухня)</t>
+          <t>В2, 188 м³/ч</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5527,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø160, расход 120 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка переточная в низу наружной двери топочной, живое сечение не менее 0,08 м²</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -5536,7 +5548,7 @@
       <c r="H174" s="1" t="inlineStr"/>
       <c r="I174" s="1" t="inlineStr">
         <is>
-          <t>1.10 (верх 2-го света)</t>
+          <t>ПН, 282 м³/ч</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5558,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Решётка наружная воздухозаборная 500×400, низ +2,600</t>
+          <t>Решётка вентиляционная наружная 400×200</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -5562,12 +5574,12 @@
         </is>
       </c>
       <c r="G175" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H175" s="1" t="inlineStr"/>
       <c r="I175" s="1" t="inlineStr">
         <is>
-          <t>Н1, восточная стена топочной</t>
+          <t>гараж 1.5: приток внизу, вытяжка вверху</t>
         </is>
       </c>
     </row>
@@ -5577,14 +5589,10 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Оголовок (зонт) воздуховода Ø250 выше кровли</t>
-        </is>
-      </c>
-      <c r="C176" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Зонт кухонный над плитой 500–600 м³/ч, располагаемое давление не менее 200 Па при 600 м³/ч</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="inlineStr"/>
       <c r="D176" s="1" t="inlineStr"/>
       <c r="E176" s="1" t="inlineStr"/>
       <c r="F176" s="1" t="inlineStr">
@@ -5593,12 +5601,12 @@
         </is>
       </c>
       <c r="G176" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H176" s="1" t="inlineStr"/>
       <c r="I176" s="1" t="inlineStr">
         <is>
-          <t>выброс П1, В2 (Ш-2)</t>
+          <t>ВЗ, поставка Заказчика</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5616,7 @@
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Оголовок (зонт) воздуховода Ø200 выше кровли</t>
+          <t>Клапан обратный Ø150</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -5629,7 +5637,7 @@
       <c r="H177" s="1" t="inlineStr"/>
       <c r="I177" s="1" t="inlineStr">
         <is>
-          <t>ВЗ (кухонный зонт), шахта над мангалом 1.12</t>
+          <t>ВЗ, на патрубке зонта</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5647,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная под воздуховод Ø250 (вытяжка топочной, естественная)</t>
+          <t>Гильза для прохода воздуховода Ø200 в изоляции через наружную стену (под отверстие Ø320)</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -5660,7 +5668,7 @@
       <c r="H178" s="1" t="inlineStr"/>
       <c r="I178" s="1" t="inlineStr">
         <is>
-          <t>В2, 188 м³/ч</t>
+          <t>ВЗ, сквозь стену на +3,400</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5678,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Решётка переточная в низу наружной двери топочной, живое сечение не менее 0,08 м²</t>
+          <t>Клапан компенсации Ø200 с электроприводом, сблокирован с ВЗ, в наружной стене с решёткой</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -5682,7 +5690,7 @@
       <c r="E179" s="1" t="inlineStr"/>
       <c r="F179" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G179" s="1" t="n">
@@ -5691,7 +5699,7 @@
       <c r="H179" s="1" t="inlineStr"/>
       <c r="I179" s="1" t="inlineStr">
         <is>
-          <t>ПН, 282 м³/ч</t>
+          <t>КК</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5709,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Решётка вентиляционная наружная 400×200</t>
+          <t>Теплоизоляция воздуховодов рулонная толщиной 25 мм с паробарьером (фольга), класс горючести — по СП 60</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -5713,16 +5721,16 @@
       <c r="E180" s="1" t="inlineStr"/>
       <c r="F180" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G180" s="1" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H180" s="1" t="inlineStr"/>
       <c r="I180" s="1" t="inlineStr">
         <is>
-          <t>гараж 1.5: приток внизу, вытяжка вверху</t>
+          <t>Н и выброс П1 Ø250</t>
         </is>
       </c>
     </row>
@@ -5732,24 +5740,30 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Зонт кухонный над плитой 500–600 м³/ч, располагаемое давление не менее 200 Па при 600 м³/ч</t>
-        </is>
-      </c>
-      <c r="C181" s="1" t="inlineStr"/>
+          <t>Теплоизоляция воздуховода Ø200 из минеральной ваты, негорючая (НГ), толщина 50 мм, кашированная фольгой</t>
+        </is>
+      </c>
+      <c r="C181" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D181" s="1" t="inlineStr"/>
       <c r="E181" s="1" t="inlineStr"/>
       <c r="F181" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G181" s="1" t="n">
-        <v>1</v>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G181" s="1" t="inlineStr">
+        <is>
+          <t>6,8</t>
+        </is>
       </c>
       <c r="H181" s="1" t="inlineStr"/>
       <c r="I181" s="1" t="inlineStr">
         <is>
-          <t>ВЗ, поставка Заказчика</t>
+          <t>ВЗ: холодная шахта, рядом дымоход мангала — только НГ</t>
         </is>
       </c>
     </row>
@@ -5759,19 +5773,15 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ø150</t>
-        </is>
-      </c>
-      <c r="C182" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Крепления воздуховодов: подвесы, хомуты с уплотнителем, шпильки, профиль</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="inlineStr"/>
       <c r="D182" s="1" t="inlineStr"/>
       <c r="E182" s="1" t="inlineStr"/>
       <c r="F182" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G182" s="1" t="n">
@@ -5780,7 +5790,7 @@
       <c r="H182" s="1" t="inlineStr"/>
       <c r="I182" s="1" t="inlineStr">
         <is>
-          <t>ВЗ, на патрубке зонта</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
@@ -5790,7 +5800,7 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Гильза для прохода воздуховода Ø200 в изоляции через наружную стену (под отверстие Ø320)</t>
+          <t>Вентилятор канальный малошумный Ø100, 2 скорости, датчик влажности и таймер, IPX4, с обратным клапаном</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -5806,12 +5816,12 @@
         </is>
       </c>
       <c r="G183" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H183" s="1" t="inlineStr"/>
       <c r="I183" s="1" t="inlineStr">
         <is>
-          <t>ВЗ, сквозь стену на +3,400</t>
+          <t>ВВ-б1 (с/у б3) — 25/50 м³/ч; ВВ-б2 (помывочная б7) — 60/100 м³/ч; лист 12</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5831,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Клапан компенсации Ø200 с электроприводом, сблокирован с ВЗ, в наружной стене с решёткой</t>
+          <t>Решётка вытяжная потолочная под воздуховод Ø100</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -5833,16 +5843,16 @@
       <c r="E184" s="1" t="inlineStr"/>
       <c r="F184" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G184" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H184" s="1" t="inlineStr"/>
       <c r="I184" s="1" t="inlineStr">
         <is>
-          <t>КК</t>
+          <t>ВВ-б1, ВВ-б2</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5862,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Теплоизоляция воздуховодов рулонная толщиной 25 мм с паробарьером (фольга), класс горючести — по СП 60</t>
+          <t>Решётка наружная с гравитационными жалюзи Ø100</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -5864,16 +5874,16 @@
       <c r="E185" s="1" t="inlineStr"/>
       <c r="F185" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G185" s="1" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="H185" s="1" t="inlineStr"/>
       <c r="I185" s="1" t="inlineStr">
         <is>
-          <t>Н и выброс П1 Ø250</t>
+          <t>ВВ-б1, ВВ-б2</t>
         </is>
       </c>
     </row>
@@ -5883,7 +5893,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Теплоизоляция воздуховода Ø200 из минеральной ваты, негорючая (НГ), толщина 50 мм, кашированная фольгой</t>
+          <t>Гильза Ø110 для прохода воздуховода Ø100 через наружную стену</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -5895,86 +5905,76 @@
       <c r="E186" s="1" t="inlineStr"/>
       <c r="F186" s="1" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G186" s="1" t="inlineStr">
-        <is>
-          <t>6,8</t>
-        </is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G186" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="H186" s="1" t="inlineStr"/>
       <c r="I186" s="1" t="inlineStr">
         <is>
-          <t>ВЗ: холодная шахта, рядом дымоход мангала — только НГ</t>
+          <t>ВВ-б1, ВВ-б2, ось +2,20</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>Крепления воздуховодов: подвесы, хомуты с уплотнителем, шпильки, профиль</t>
-        </is>
-      </c>
-      <c r="C187" s="1" t="inlineStr"/>
-      <c r="D187" s="1" t="inlineStr"/>
-      <c r="E187" s="1" t="inlineStr"/>
-      <c r="F187" s="1" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G187" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H187" s="1" t="inlineStr"/>
-      <c r="I187" s="1" t="inlineStr">
-        <is>
-          <t>по месту</t>
-        </is>
-      </c>
+      <c r="A187" s="1" t="inlineStr"/>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>6. Кондиционирование (листы 9–11, 14)</t>
+        </is>
+      </c>
+      <c r="C187" s="1" t="n"/>
+      <c r="D187" s="1" t="n"/>
+      <c r="E187" s="1" t="n"/>
+      <c r="F187" s="1" t="n"/>
+      <c r="G187" s="1" t="n"/>
+      <c r="H187" s="1" t="n"/>
+      <c r="I187" s="1" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Вентилятор канальный малошумный Ø100, 2 скорости, датчик влажности и таймер, IPX4, с обратным клапаном</t>
+          <t>Наружный блок мини-VRV, тепловой насос, Qх = 22,4 кВт, ночной малошумный режим</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Daikin серии VRV-S, модель — по каталогу Daikin</t>
         </is>
       </c>
       <c r="D188" s="1" t="inlineStr"/>
-      <c r="E188" s="1" t="inlineStr"/>
+      <c r="E188" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F188" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G188" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H188" s="1" t="inlineStr"/>
       <c r="I188" s="1" t="inlineStr">
         <is>
-          <t>ВВ-б1 (с/у б3) — 25/50 м³/ч; ВВ-б2 (помывочная б7) — 60/100 м³/ч; лист 12</t>
+          <t>НБ-1, площадка у восточной стены топочной</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная потолочная под воздуховод Ø100</t>
+          <t>Рама опорная наружного блока высотой 0,3–0,5 м</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -5986,35 +5986,39 @@
       <c r="E189" s="1" t="inlineStr"/>
       <c r="F189" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G189" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H189" s="1" t="inlineStr"/>
       <c r="I189" s="1" t="inlineStr">
         <is>
-          <t>ВВ-б1, ВВ-б2</t>
+          <t>НБ-1, лист 14</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Решётка наружная с гравитационными жалюзи Ø100</t>
+          <t>Внутренний блок канальный тонкий, Qх = 5,6 кВт, ≈900 м³/ч</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
         </is>
       </c>
       <c r="D190" s="1" t="inlineStr"/>
-      <c r="E190" s="1" t="inlineStr"/>
+      <c r="E190" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F190" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -6026,55 +6030,79 @@
       <c r="H190" s="1" t="inlineStr"/>
       <c r="I190" s="1" t="inlineStr">
         <is>
-          <t>ВВ-б1, ВВ-б2</t>
+          <t>К-1 (1.10), К-2 (1.10)</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Гильза Ø110 для прохода воздуховода Ø100 через наружную стену</t>
+          <t>Внутренний блок канальный тонкий, Qх = 3,6 кВт, ≈600 м³/ч</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
         </is>
       </c>
       <c r="D191" s="1" t="inlineStr"/>
-      <c r="E191" s="1" t="inlineStr"/>
+      <c r="E191" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F191" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G191" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H191" s="1" t="inlineStr"/>
       <c r="I191" s="1" t="inlineStr">
         <is>
-          <t>ВВ-б1, ВВ-б2, ось +2,20</t>
+          <t>К-3 (1.11)</t>
         </is>
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="inlineStr"/>
-      <c r="B192" s="3" t="inlineStr">
-        <is>
-          <t>6. Кондиционирование (листы 9–11, 14)</t>
-        </is>
-      </c>
-      <c r="C192" s="1" t="n"/>
-      <c r="D192" s="1" t="n"/>
-      <c r="E192" s="1" t="n"/>
-      <c r="F192" s="1" t="n"/>
-      <c r="G192" s="1" t="n"/>
-      <c r="H192" s="1" t="n"/>
-      <c r="I192" s="1" t="n"/>
+      <c r="A192" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>Внутренний блок канальный тонкий, Qх = 2,8 кВт, ≈480 м³/ч</t>
+        </is>
+      </c>
+      <c r="C192" s="1" t="inlineStr">
+        <is>
+          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+        </is>
+      </c>
+      <c r="D192" s="1" t="inlineStr"/>
+      <c r="E192" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
+      <c r="F192" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G192" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H192" s="1" t="inlineStr"/>
+      <c r="I192" s="1" t="inlineStr">
+        <is>
+          <t>К-4 (2.3), К-5 (2.4), К-6 (2.5), К-7 (2.7)</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -6082,12 +6110,12 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Наружный блок мини-VRV, тепловой насос, Qх = 22,4 кВт, ночной малошумный режим</t>
+          <t>Пульт управления внутренним блоком</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии VRV-S, модель — по каталогу Daikin</t>
+          <t>по каталогу Daikin</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr"/>
@@ -6102,12 +6130,12 @@
         </is>
       </c>
       <c r="G193" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H193" s="1" t="inlineStr"/>
       <c r="I193" s="1" t="inlineStr">
         <is>
-          <t>НБ-1, площадка у восточной стены топочной</t>
+          <t>тип — по решению Заказчика</t>
         </is>
       </c>
     </row>
@@ -6117,28 +6145,32 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Рама опорная наружного блока высотой 0,3–0,5 м</t>
+          <t>Разветвитель фреоновый REFNET</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по каталогу Daikin</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr"/>
-      <c r="E194" s="1" t="inlineStr"/>
+      <c r="E194" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F194" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G194" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H194" s="1" t="inlineStr"/>
       <c r="I194" s="1" t="inlineStr">
         <is>
-          <t>НБ-1, лист 14</t>
+          <t>Р1…Р6</t>
         </is>
       </c>
     </row>
@@ -6148,32 +6180,28 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок канальный тонкий, Qх = 5,6 кВт, ≈900 м³/ч</t>
+          <t>Труба медная отожжённая для холодильной техники Ø6,35 мм</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr"/>
-      <c r="E195" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E195" s="1" t="inlineStr"/>
       <c r="F195" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G195" s="1" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H195" s="1" t="inlineStr"/>
       <c r="I195" s="1" t="inlineStr">
         <is>
-          <t>К-1 (1.10), К-2 (1.10)</t>
+          <t>жидкость</t>
         </is>
       </c>
     </row>
@@ -6183,32 +6211,28 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок канальный тонкий, Qх = 3,6 кВт, ≈600 м³/ч</t>
+          <t>Труба медная отожжённая для холодильной техники Ø9,52 мм</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr"/>
-      <c r="E196" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E196" s="1" t="inlineStr"/>
       <c r="F196" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G196" s="1" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="H196" s="1" t="inlineStr"/>
       <c r="I196" s="1" t="inlineStr">
         <is>
-          <t>К-3 (1.11)</t>
+          <t>жидкость</t>
         </is>
       </c>
     </row>
@@ -6218,32 +6242,28 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок канальный тонкий, Qх = 2,8 кВт, ≈480 м³/ч</t>
+          <t>Труба медная отожжённая для холодильной техники Ø12,70 мм</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr"/>
-      <c r="E197" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E197" s="1" t="inlineStr"/>
       <c r="F197" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G197" s="1" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H197" s="1" t="inlineStr"/>
       <c r="I197" s="1" t="inlineStr">
         <is>
-          <t>К-4 (2.3), К-5 (2.4), К-6 (2.5), К-7 (2.7)</t>
+          <t>газ</t>
         </is>
       </c>
     </row>
@@ -6253,32 +6273,28 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Пульт управления внутренним блоком</t>
+          <t>Труба медная отожжённая для холодильной техники Ø15,88 мм</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr"/>
-      <c r="E198" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E198" s="1" t="inlineStr"/>
       <c r="F198" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G198" s="1" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="H198" s="1" t="inlineStr"/>
       <c r="I198" s="1" t="inlineStr">
         <is>
-          <t>тип — по решению Заказчика</t>
+          <t>газ</t>
         </is>
       </c>
     </row>
@@ -6288,32 +6304,28 @@
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Разветвитель фреоновый REFNET</t>
+          <t>Труба медная отожжённая для холодильной техники Ø19,05 мм</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr"/>
-      <c r="E199" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E199" s="1" t="inlineStr"/>
       <c r="F199" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G199" s="1" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H199" s="1" t="inlineStr"/>
       <c r="I199" s="1" t="inlineStr">
         <is>
-          <t>Р1…Р6</t>
+          <t>газ</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6335,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø6,35 мм</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø6,35, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
@@ -6342,11 +6354,7 @@
         <v>20</v>
       </c>
       <c r="H200" s="1" t="inlineStr"/>
-      <c r="I200" s="1" t="inlineStr">
-        <is>
-          <t>жидкость</t>
-        </is>
-      </c>
+      <c r="I200" s="1" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -6354,7 +6362,7 @@
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø9,52 мм</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø9,52, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
@@ -6373,11 +6381,7 @@
         <v>37</v>
       </c>
       <c r="H201" s="1" t="inlineStr"/>
-      <c r="I201" s="1" t="inlineStr">
-        <is>
-          <t>жидкость</t>
-        </is>
-      </c>
+      <c r="I201" s="1" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -6385,7 +6389,7 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø12,70 мм</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø12,70, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
@@ -6404,11 +6408,7 @@
         <v>20</v>
       </c>
       <c r="H202" s="1" t="inlineStr"/>
-      <c r="I202" s="1" t="inlineStr">
-        <is>
-          <t>газ</t>
-        </is>
-      </c>
+      <c r="I202" s="1" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø15,88 мм</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø15,88, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
@@ -6435,11 +6435,7 @@
         <v>23</v>
       </c>
       <c r="H203" s="1" t="inlineStr"/>
-      <c r="I203" s="1" t="inlineStr">
-        <is>
-          <t>газ</t>
-        </is>
-      </c>
+      <c r="I203" s="1" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -6447,7 +6443,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø19,05 мм</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø19,05, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
@@ -6466,11 +6462,7 @@
         <v>14</v>
       </c>
       <c r="H204" s="1" t="inlineStr"/>
-      <c r="I204" s="1" t="inlineStr">
-        <is>
-          <t>газ</t>
-        </is>
-      </c>
+      <c r="I204" s="1" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -6478,26 +6470,32 @@
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø6,35, толщина — по паспорту Daikin</t>
+          <t>Хладагент для дозаправки (тип — по паспорту НБ-1)</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по паспорту НБ-1</t>
         </is>
       </c>
       <c r="D205" s="1" t="inlineStr"/>
       <c r="E205" s="1" t="inlineStr"/>
       <c r="F205" s="1" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G205" s="1" t="n">
-        <v>20</v>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="G205" s="1" t="inlineStr">
+        <is>
+          <t>2,15</t>
+        </is>
       </c>
       <c r="H205" s="1" t="inlineStr"/>
-      <c r="I205" s="1" t="inlineStr"/>
+      <c r="I205" s="1" t="inlineStr">
+        <is>
+          <t>по расчёту, уточнить при пуске</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -6505,26 +6503,26 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø9,52, толщина — по паспорту Daikin</t>
-        </is>
-      </c>
-      <c r="C206" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Гильза стальная для прохода фреонопроводов и дренажа через наружную стену и перекрытие</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="inlineStr"/>
       <c r="D206" s="1" t="inlineStr"/>
       <c r="E206" s="1" t="inlineStr"/>
       <c r="F206" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G206" s="1" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="H206" s="1" t="inlineStr"/>
-      <c r="I206" s="1" t="inlineStr"/>
+      <c r="I206" s="1" t="inlineStr">
+        <is>
+          <t>стена топочной, Ш-1</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -6532,7 +6530,7 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø12,70, толщина — по паспорту Daikin</t>
+          <t>Диффузор щелевой блока К в торце подшивки, L=1000 мм</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
@@ -6544,14 +6542,18 @@
       <c r="E207" s="1" t="inlineStr"/>
       <c r="F207" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G207" s="1" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H207" s="1" t="inlineStr"/>
-      <c r="I207" s="1" t="inlineStr"/>
+      <c r="I207" s="1" t="inlineStr">
+        <is>
+          <t>К-1, К-2</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
@@ -6559,7 +6561,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø15,88, толщина — по паспорту Daikin</t>
+          <t>Диффузор щелевой блока К в торце подшивки, L=1100 мм</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
@@ -6571,14 +6573,18 @@
       <c r="E208" s="1" t="inlineStr"/>
       <c r="F208" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G208" s="1" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H208" s="1" t="inlineStr"/>
-      <c r="I208" s="1" t="inlineStr"/>
+      <c r="I208" s="1" t="inlineStr">
+        <is>
+          <t>К-3</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
@@ -6586,7 +6592,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø19,05, толщина — по паспорту Daikin</t>
+          <t>Камера статического давления (КСД) щелевого диффузора блока К, переходная от фланца блока, с выравнивающей перфорированной решёткой, в теплоизоляции 10 мм</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
@@ -6598,14 +6604,18 @@
       <c r="E209" s="1" t="inlineStr"/>
       <c r="F209" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G209" s="1" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H209" s="1" t="inlineStr"/>
-      <c r="I209" s="1" t="inlineStr"/>
+      <c r="I209" s="1" t="inlineStr">
+        <is>
+          <t>К-1 — L=1000, глуб. 240, К-2 — L=1000, глуб. 240, К-3 — L=1100, глуб. 350</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
@@ -6613,30 +6623,28 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Хладагент для дозаправки (тип — по паспорту НБ-1)</t>
+          <t>Решётка-люк рециркуляции потолочная съёмная 600×600 под блоком К (забор воздуха снизу)</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>по паспорту НБ-1</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr"/>
       <c r="E210" s="1" t="inlineStr"/>
       <c r="F210" s="1" t="inlineStr">
         <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="G210" s="1" t="inlineStr">
-        <is>
-          <t>2,15</t>
-        </is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G210" s="1" t="n">
+        <v>3</v>
       </c>
       <c r="H210" s="1" t="inlineStr"/>
       <c r="I210" s="1" t="inlineStr">
         <is>
-          <t>по расчёту, уточнить при пуске</t>
+          <t>К-1…К-3, вместо люка 600×600</t>
         </is>
       </c>
     </row>
@@ -6646,10 +6654,14 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Гильза стальная для прохода фреонопроводов и дренажа через наружную стену и перекрытие</t>
-        </is>
-      </c>
-      <c r="C211" s="1" t="inlineStr"/>
+          <t>Решётка щелевая настенная 800×150 с регулированием (подача К и свежего воздуха П1)</t>
+        </is>
+      </c>
+      <c r="C211" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D211" s="1" t="inlineStr"/>
       <c r="E211" s="1" t="inlineStr"/>
       <c r="F211" s="1" t="inlineStr">
@@ -6658,12 +6670,12 @@
         </is>
       </c>
       <c r="G211" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H211" s="1" t="inlineStr"/>
       <c r="I211" s="1" t="inlineStr">
         <is>
-          <t>стена топочной, Ш-1</t>
+          <t>ЩП, спальни 2.3–2.5, 2.7</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6685,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Диффузор щелевой блока К в торце подшивки, L=1000 мм</t>
+          <t>Камера статического давления (КСД) для решётки 800×150, подача, с выравнивающей перфорированной решёткой, в теплоизоляции 10 мм; присоединение — фланец блока (К-4…К-6) или 250×150 (К-7), боковой патрубок Ø100 свежего воздуха П1</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
@@ -6689,12 +6701,12 @@
         </is>
       </c>
       <c r="G212" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H212" s="1" t="inlineStr"/>
       <c r="I212" s="1" t="inlineStr">
         <is>
-          <t>К-1, К-2</t>
+          <t>КСД у ЩП</t>
         </is>
       </c>
     </row>
@@ -6704,7 +6716,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Диффузор щелевой блока К в торце подшивки, L=1100 мм</t>
+          <t>Решётка щелевая настенная 800×150 с регулированием (возврат)</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
@@ -6720,12 +6732,12 @@
         </is>
       </c>
       <c r="G213" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H213" s="1" t="inlineStr"/>
       <c r="I213" s="1" t="inlineStr">
         <is>
-          <t>К-3</t>
+          <t>ЩВ, спальни 2.3–2.5, 2.7</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6747,7 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Камера статического давления (КСД) щелевого диффузора блока К, переходная от фланца блока, с выравнивающей перфорированной решёткой, в теплоизоляции 10 мм</t>
+          <t>Камера статического давления (КСД) для решётки 800×150, возврат, глубиной 220 мм, патрубок 250×150</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
@@ -6751,12 +6763,12 @@
         </is>
       </c>
       <c r="G214" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H214" s="1" t="inlineStr"/>
       <c r="I214" s="1" t="inlineStr">
         <is>
-          <t>К-1 — L=1000, глуб. 240, К-2 — L=1000, глуб. 240, К-3 — L=1100, глуб. 350</t>
+          <t>КСД у ЩВ</t>
         </is>
       </c>
     </row>
@@ -6766,28 +6778,24 @@
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Решётка-люк рециркуляции потолочная съёмная 600×600 под блоком К (забор воздуха снизу)</t>
-        </is>
-      </c>
-      <c r="C215" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод прямоугольный из оцинкованной стали 250×150</t>
+        </is>
+      </c>
+      <c r="C215" s="1" t="inlineStr"/>
       <c r="D215" s="1" t="inlineStr"/>
       <c r="E215" s="1" t="inlineStr"/>
       <c r="F215" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G215" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="H215" s="1" t="inlineStr"/>
       <c r="I215" s="1" t="inlineStr">
         <is>
-          <t>К-1…К-3, вместо люка 600×600</t>
+          <t>блоки К-4…К-7</t>
         </is>
       </c>
     </row>
@@ -6797,14 +6805,10 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Решётка щелевая настенная 800×150 с регулированием (подача К и свежего воздуха П1)</t>
-        </is>
-      </c>
-      <c r="C216" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 90° прямоугольный оцинкованный 250×150</t>
+        </is>
+      </c>
+      <c r="C216" s="1" t="inlineStr"/>
       <c r="D216" s="1" t="inlineStr"/>
       <c r="E216" s="1" t="inlineStr"/>
       <c r="F216" s="1" t="inlineStr">
@@ -6813,12 +6817,12 @@
         </is>
       </c>
       <c r="G216" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H216" s="1" t="inlineStr"/>
       <c r="I216" s="1" t="inlineStr">
         <is>
-          <t>ЩП, спальни 2.3–2.5, 2.7</t>
+          <t>блоки К-4…К-7</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6832,7 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Камера статического давления (КСД) для решётки 800×150, подача, с выравнивающей перфорированной решёткой, в теплоизоляции 10 мм; присоединение — фланец блока (К-4…К-6) или 250×150 (К-7), боковой патрубок Ø100 свежего воздуха П1</t>
+          <t>Теплоизоляция из вспененного каучука 10 мм, самоклеящаяся, для КСД и воздуховодов подачи блоков К</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
@@ -6840,16 +6844,16 @@
       <c r="E217" s="1" t="inlineStr"/>
       <c r="F217" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G217" s="1" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H217" s="1" t="inlineStr"/>
       <c r="I217" s="1" t="inlineStr">
         <is>
-          <t>КСД у ЩП</t>
+          <t>КСД К-1…К-3 и ЩП, подача К-7</t>
         </is>
       </c>
     </row>
@@ -6859,7 +6863,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Решётка щелевая настенная 800×150 с регулированием (возврат)</t>
+          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
@@ -6871,16 +6875,16 @@
       <c r="E218" s="1" t="inlineStr"/>
       <c r="F218" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G218" s="1" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="H218" s="1" t="inlineStr"/>
       <c r="I218" s="1" t="inlineStr">
         <is>
-          <t>ЩВ, спальни 2.3–2.5, 2.7</t>
+          <t>дренаж конденсата К-1…К-7</t>
         </is>
       </c>
     </row>
@@ -6890,7 +6894,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Камера статического давления (КСД) для решётки 800×150, возврат, глубиной 220 мм, патрубок 250×150</t>
+          <t>Отвод ПП Ø32 (45°/90°)</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
@@ -6906,12 +6910,12 @@
         </is>
       </c>
       <c r="G219" s="1" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H219" s="1" t="inlineStr"/>
       <c r="I219" s="1" t="inlineStr">
         <is>
-          <t>КСД у ЩВ</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
@@ -6921,26 +6925,26 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод прямоугольный из оцинкованной стали 250×150</t>
-        </is>
-      </c>
-      <c r="C220" s="1" t="inlineStr"/>
+          <t>Тройник ПП Ø32</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D220" s="1" t="inlineStr"/>
       <c r="E220" s="1" t="inlineStr"/>
       <c r="F220" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G220" s="1" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H220" s="1" t="inlineStr"/>
-      <c r="I220" s="1" t="inlineStr">
-        <is>
-          <t>блоки К-4…К-7</t>
-        </is>
-      </c>
+      <c r="I220" s="1" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -6948,7 +6952,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° прямоугольный оцинкованный 250×150</t>
+          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr"/>
@@ -6956,169 +6960,22 @@
       <c r="E221" s="1" t="inlineStr"/>
       <c r="F221" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G221" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H221" s="1" t="inlineStr"/>
       <c r="I221" s="1" t="inlineStr">
         <is>
-          <t>блоки К-4…К-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="1" t="n">
-        <v>214</v>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>Теплоизоляция из вспененного каучука 10 мм, самоклеящаяся, для КСД и воздуховодов подачи блоков К</t>
-        </is>
-      </c>
-      <c r="C222" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D222" s="1" t="inlineStr"/>
-      <c r="E222" s="1" t="inlineStr"/>
-      <c r="F222" s="1" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="G222" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="H222" s="1" t="inlineStr"/>
-      <c r="I222" s="1" t="inlineStr">
-        <is>
-          <t>КСД К-1…К-3 и ЩП, подача К-7</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
-        <v>215</v>
-      </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
-        </is>
-      </c>
-      <c r="C223" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D223" s="1" t="inlineStr"/>
-      <c r="E223" s="1" t="inlineStr"/>
-      <c r="F223" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G223" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="H223" s="1" t="inlineStr"/>
-      <c r="I223" s="1" t="inlineStr">
-        <is>
-          <t>дренаж конденсата К-1…К-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="1" t="n">
-        <v>216</v>
-      </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>Отвод ПП Ø32 (45°/90°)</t>
-        </is>
-      </c>
-      <c r="C224" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D224" s="1" t="inlineStr"/>
-      <c r="E224" s="1" t="inlineStr"/>
-      <c r="F224" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G224" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="H224" s="1" t="inlineStr"/>
-      <c r="I224" s="1" t="inlineStr">
-        <is>
-          <t>по месту</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="1" t="n">
-        <v>217</v>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>Тройник ПП Ø32</t>
-        </is>
-      </c>
-      <c r="C225" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D225" s="1" t="inlineStr"/>
-      <c r="E225" s="1" t="inlineStr"/>
-      <c r="F225" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G225" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H225" s="1" t="inlineStr"/>
-      <c r="I225" s="1" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
-        </is>
-      </c>
-      <c r="C226" s="1" t="inlineStr"/>
-      <c r="D226" s="1" t="inlineStr"/>
-      <c r="E226" s="1" t="inlineStr"/>
-      <c r="F226" s="1" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G226" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H226" s="1" t="inlineStr"/>
-      <c r="I226" s="1" t="inlineStr">
-        <is>
-          <t>по месту</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr"/>
-      <c r="B228" t="inlineStr">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -936,7 +936,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,72 м³/ч, H=1,20 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,71 м³/ч, H=1,19 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 36,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,66 м³/ч, H=1,47 м), байпас, защитный термостат-ограничитель 45 °С</t>
+          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 36,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,70 м³/ч, H=1,47 м), байпас, защитный термостат-ограничитель 45 °С</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2200 мм, тепловая мощность при 70/55 °С не менее 2345 Вт</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2200 мм, тепловая мощность при 70/55 °С не менее 2171 Вт</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -2475,7 +2475,7 @@
         </is>
       </c>
       <c r="G66" s="1" t="n">
-        <v>1448</v>
+        <v>1475</v>
       </c>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr">
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="G83" s="1" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
@@ -2993,7 +2993,7 @@
         </is>
       </c>
       <c r="G84" s="1" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
@@ -3020,7 +3020,7 @@
         </is>
       </c>
       <c r="G85" s="1" t="n">
-        <v>2900</v>
+        <v>3000</v>
       </c>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Решётка приточная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка приточная настенная с регулирующим клапаном, на камере статического давления (КСД) с круглым патрубком, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, на камере статического давления (КСД) с круглым патрубком, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø125, расход 90 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, на камере статического давления (КСД) с круглым патрубком, присоединение Ø125, расход 90 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, присоединение Ø160, расход 120 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, на камере статического давления (КСД) с круглым патрубком, присоединение Ø160, расход 120 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">

--- a/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I223"/>
+  <dimension ref="A1:I230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6832,28 +6832,24 @@
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Теплоизоляция из вспененного каучука 10 мм, самоклеящаяся, для КСД и воздуховодов подачи блоков К</t>
-        </is>
-      </c>
-      <c r="C217" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 45° круглый оцинкованный Ø250</t>
+        </is>
+      </c>
+      <c r="C217" s="1" t="inlineStr"/>
       <c r="D217" s="1" t="inlineStr"/>
       <c r="E217" s="1" t="inlineStr"/>
       <c r="F217" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G217" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H217" s="1" t="inlineStr"/>
       <c r="I217" s="1" t="inlineStr">
         <is>
-          <t>КСД К-1…К-3 и ЩП, подача К-7</t>
+          <t>обходы пересечений, лист 11</t>
         </is>
       </c>
     </row>
@@ -6863,28 +6859,24 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
-        </is>
-      </c>
-      <c r="C218" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 45° круглый оцинкованный Ø200</t>
+        </is>
+      </c>
+      <c r="C218" s="1" t="inlineStr"/>
       <c r="D218" s="1" t="inlineStr"/>
       <c r="E218" s="1" t="inlineStr"/>
       <c r="F218" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G218" s="1" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="H218" s="1" t="inlineStr"/>
       <c r="I218" s="1" t="inlineStr">
         <is>
-          <t>дренаж конденсата К-1…К-7</t>
+          <t>обходы пересечений, лист 11</t>
         </is>
       </c>
     </row>
@@ -6894,14 +6886,10 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП Ø32 (45°/90°)</t>
-        </is>
-      </c>
-      <c r="C219" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 45° круглый оцинкованный Ø160</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="inlineStr"/>
       <c r="D219" s="1" t="inlineStr"/>
       <c r="E219" s="1" t="inlineStr"/>
       <c r="F219" s="1" t="inlineStr">
@@ -6910,12 +6898,12 @@
         </is>
       </c>
       <c r="G219" s="1" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H219" s="1" t="inlineStr"/>
       <c r="I219" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>обходы пересечений, лист 11</t>
         </is>
       </c>
     </row>
@@ -6925,14 +6913,10 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП Ø32</t>
-        </is>
-      </c>
-      <c r="C220" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 45° круглый оцинкованный Ø125</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="inlineStr"/>
       <c r="D220" s="1" t="inlineStr"/>
       <c r="E220" s="1" t="inlineStr"/>
       <c r="F220" s="1" t="inlineStr">
@@ -6941,10 +6925,14 @@
         </is>
       </c>
       <c r="G220" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H220" s="1" t="inlineStr"/>
-      <c r="I220" s="1" t="inlineStr"/>
+      <c r="I220" s="1" t="inlineStr">
+        <is>
+          <t>обходы пересечений, лист 11</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -6952,7 +6940,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
+          <t>Отвод 45° круглый оцинкованный Ø100</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr"/>
@@ -6960,22 +6948,223 @@
       <c r="E221" s="1" t="inlineStr"/>
       <c r="F221" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G221" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H221" s="1" t="inlineStr"/>
       <c r="I221" s="1" t="inlineStr">
         <is>
+          <t>обходы пересечений, лист 11</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Воздуховод прямоугольный из оцинкованной стали 150×100</t>
+        </is>
+      </c>
+      <c r="C222" s="1" t="inlineStr"/>
+      <c r="D222" s="1" t="inlineStr"/>
+      <c r="E222" s="1" t="inlineStr"/>
+      <c r="F222" s="1" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G222" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H222" s="1" t="inlineStr"/>
+      <c r="I222" s="1" t="inlineStr">
+        <is>
+          <t>В Ø125 под П, П-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Переход оцинкованный Ø125 / 150×100</t>
+        </is>
+      </c>
+      <c r="C223" s="1" t="inlineStr"/>
+      <c r="D223" s="1" t="inlineStr"/>
+      <c r="E223" s="1" t="inlineStr"/>
+      <c r="F223" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G223" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H223" s="1" t="inlineStr"/>
+      <c r="I223" s="1" t="inlineStr">
+        <is>
+          <t>В Ø125 под П, П-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Теплоизоляция из вспененного каучука 10 мм, самоклеящаяся, для КСД и воздуховодов подачи блоков К</t>
+        </is>
+      </c>
+      <c r="C224" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D224" s="1" t="inlineStr"/>
+      <c r="E224" s="1" t="inlineStr"/>
+      <c r="F224" s="1" t="inlineStr">
+        <is>
+          <t>м²</t>
+        </is>
+      </c>
+      <c r="G224" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="H224" s="1" t="inlineStr"/>
+      <c r="I224" s="1" t="inlineStr">
+        <is>
+          <t>КСД К-1…К-3 и ЩП, подача К-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D225" s="1" t="inlineStr"/>
+      <c r="E225" s="1" t="inlineStr"/>
+      <c r="F225" s="1" t="inlineStr">
+        <is>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G225" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="H225" s="1" t="inlineStr"/>
+      <c r="I225" s="1" t="inlineStr">
+        <is>
+          <t>дренаж конденсата К-1…К-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Отвод ПП Ø32 (45°/90°)</t>
+        </is>
+      </c>
+      <c r="C226" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D226" s="1" t="inlineStr"/>
+      <c r="E226" s="1" t="inlineStr"/>
+      <c r="F226" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G226" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H226" s="1" t="inlineStr"/>
+      <c r="I226" s="1" t="inlineStr">
+        <is>
           <t>по месту</t>
         </is>
       </c>
     </row>
-    <row r="223">
-      <c r="A223" t="inlineStr"/>
-      <c r="B223" t="inlineStr">
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Тройник ПП Ø32</t>
+        </is>
+      </c>
+      <c r="C227" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D227" s="1" t="inlineStr"/>
+      <c r="E227" s="1" t="inlineStr"/>
+      <c r="F227" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G227" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H227" s="1" t="inlineStr"/>
+      <c r="I227" s="1" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
+        </is>
+      </c>
+      <c r="C228" s="1" t="inlineStr"/>
+      <c r="D228" s="1" t="inlineStr"/>
+      <c r="E228" s="1" t="inlineStr"/>
+      <c r="F228" s="1" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G228" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H228" s="1" t="inlineStr"/>
+      <c r="I228" s="1" t="inlineStr">
+        <is>
+          <t>по месту</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
@@ -3872,7 +3872,7 @@
         </is>
       </c>
       <c r="G113" s="1" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H113" s="1" t="inlineStr"/>
       <c r="I113" s="1" t="inlineStr">
@@ -3899,7 +3899,7 @@
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H114" s="1" t="inlineStr"/>
       <c r="I114" s="1" t="inlineStr">

--- a/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I230"/>
+  <dimension ref="A1:I197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       <c r="A3" s="1" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>1. Топочная (листы 7, 8)</t>
+          <t>1. Котельная (топочная 1.6)</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -521,93 +521,55 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Котёл газовый конденсационный настенный одноконтурный ≈24–25 кВт, с каскадным управлением</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Viessmann, серия с каскадным управлением (напр. Vitodens 200-W); типоразмер — по каталогу Viessmann</t>
-        </is>
-      </c>
+          <t>Оборудование, трубопроводы, арматура, насосные группы и дымоходы котельной — по спецификации И05.09.26-ТМ.СО</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr"/>
       <c r="D4" s="1" t="inlineStr"/>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>Viessmann</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>2</v>
-      </c>
+      <c r="E4" s="1" t="inlineStr"/>
+      <c r="F4" s="1" t="inlineStr"/>
+      <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr">
         <is>
-          <t>К1, К2; расход газа на два котла ≈5,43 м³/ч — уточняется по паспорту</t>
+          <t>раздел ТМ (решение Заказчицы 22.10.2026)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Комплект каскадного дымохода для двух котлов Ø125: каскадный коллектор с уклоном 3° к котлам, клапаны (заслонки) дымовых газов, отвод конденсата</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>штатный Viessmann, по каталогу</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr"/>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>Viessmann</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1" t="inlineStr"/>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>листы 7, 8</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2. Отопление дома (листы 3–6)</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+      <c r="E5" s="1" t="n"/>
+      <c r="F5" s="1" t="n"/>
+      <c r="G5" s="1" t="n"/>
+      <c r="H5" s="1" t="n"/>
+      <c r="I5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Дымоход Ø125 в канале шахты Ш-2 до оголовка выше кровли: трубы, ревизия, опоры, оголовок</t>
+          <t>Шкаф коллекторный встроенный ≈850×1300×150 мм (как КШ-2, КШ-5)</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>штатный Viessmann, по каталогу</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr"/>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>Viessmann</t>
-        </is>
-      </c>
+      <c r="E6" s="1" t="inlineStr"/>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G6" s="1" t="n">
@@ -616,17 +578,17 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>длина — по высоте Ш-2 (АР)</t>
+          <t>КШ-1 (тамбур 1.7)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Котёл пеллетный водогрейный ≈50 кВт с горелкой, автоподачей и автоматикой</t>
+          <t>Коллектор тёплого пола из нержавеющей стали 1" на 6 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -638,7 +600,7 @@
       <c r="E7" s="1" t="inlineStr"/>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G7" s="1" t="n">
@@ -647,22 +609,22 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr">
         <is>
-          <t>ПК, резерв на полную нагрузку</t>
+          <t>КШ-1 (тамбур 1.7)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Бункер пеллет 300–500 л со шнеком подачи</t>
+          <t>Шкаф коллекторный встроенный двухъярусный ≈850×1300×150 мм</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>комплект ПК</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr"/>
@@ -678,22 +640,22 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr">
         <is>
-          <t>БП</t>
+          <t>КШ-2 (тамбур 1.7); узел — на КШ-2 и КШ-5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Дымоход котла ПК Ø180 из нержавеющей стали от котла до канала Ø280: отвод, ревизия, конденсатосборник</t>
+          <t>Коллектор прямой из нержавеющей стали 1" на 8 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>по паспорту ПК</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr"/>
@@ -709,17 +671,17 @@
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>лист 7</t>
+          <t>КШ-2 (тамбур 1.7); узел — на КШ-2 и КШ-5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Дымоход пеллетного котла утеплённый (сэндвич) Ø200/280 из нержавеющей стали, снаружи здания, выше кровли</t>
+          <t>Коллектор тёплого пола из нержавеющей стали 1" на 5 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"; проходной — из торцов транзит на КШ-5</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -740,29 +702,29 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>длина — по АР</t>
+          <t>КШ-2 (тамбур 1.7); узел — на КШ-2 и КШ-5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Насос циркуляционный котлового контура ПК, G≈2,1 м³/ч</t>
+          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 36,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,70 м³/ч, H=1,47 м), байпас, защитный термостат-ограничитель 45 °С</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>по паспорту ПК</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
       <c r="E11" s="1" t="inlineStr"/>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G11" s="1" t="n">
@@ -771,17 +733,17 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr">
         <is>
-          <t>Н1</t>
+          <t>КШ-2 (тамбур 1.7); узел — на КШ-2 и КШ-5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Клапан термостатический трёхходовой подмеса 55 °С, Ду 32 (защита обратки ПК)</t>
+          <t>Шкаф коллекторный встроенный ≈850×1300×150 мм (как КШ-1, КШ-2)</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -802,17 +764,17 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr">
         <is>
-          <t>КТ</t>
+          <t>КШ-5 (тамбур 1.7), от смесительного узла КШ-2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Гидравлический разделитель Ду 32, расход до 3,2 м³/ч, с автоматическим воздухоотводчиком и спускным краном</t>
+          <t>Коллектор тёплого пола из нержавеющей стали 1" на 5 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
@@ -824,7 +786,7 @@
       <c r="E13" s="1" t="inlineStr"/>
       <c r="F13" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G13" s="1" t="n">
@@ -833,17 +795,17 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr">
         <is>
-          <t>ГС</t>
+          <t>КШ-5 (тамбур 1.7), от смесительного узла КШ-2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Шламоотделитель магнитный Ду 32 (на обратке перед ГС)</t>
+          <t>Шкаф коллекторный встроенный ≈550×650×120 мм</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -864,17 +826,17 @@
       <c r="H14" s="1" t="inlineStr"/>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>ШО</t>
+          <t>КШ-3 (топочная 1.6)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Коллектор распределительный двухкамерный Ду 32 на 6 насосных групп, с теплоизоляцией и кронштейнами</t>
+          <t>Коллектор тёплого пола из нержавеющей стали 1" на 5 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
@@ -886,7 +848,7 @@
       <c r="E15" s="1" t="inlineStr"/>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G15" s="1" t="n">
@@ -895,17 +857,17 @@
       <c r="H15" s="1" t="inlineStr"/>
       <c r="I15" s="1" t="inlineStr">
         <is>
-          <t>РК</t>
+          <t>КШ-3 (топочная 1.6)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,46 м³/ч, H=1,51 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Шкаф коллекторный встроенный двухъярусный ≈750×1250×150 мм</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -926,17 +888,17 @@
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr">
         <is>
-          <t>Н2 → КШ-4 (2 эт.)</t>
+          <t>КШ-4 (2.6)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=0,71 м³/ч, H=1,19 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Коллектор прямой из нержавеющей стали 1" на 7 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"; выход В6 — резерв, с заглушками</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -948,7 +910,7 @@
       <c r="E17" s="1" t="inlineStr"/>
       <c r="F17" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G17" s="1" t="n">
@@ -957,17 +919,17 @@
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr">
         <is>
-          <t>Н3 → КШ-2</t>
+          <t>КШ-4 (2.6)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная смесительная Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-60 (G=0,86 м³/ч, H=3,45 м), трёхходовой смесительный клапан с электроприводом, краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Коллектор тёплого пола из нержавеющей стали 1" на 2 выхода: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -979,7 +941,7 @@
       <c r="E18" s="1" t="inlineStr"/>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G18" s="1" t="n">
@@ -988,17 +950,17 @@
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr">
         <is>
-          <t>Н4 → ТП: КШ-1, КШ-3</t>
+          <t>КШ-4 (2.6)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Отвод от РК к нагревателю П1 Ду 20 без насоса (G=0,11 м³/ч): краны шаровые — 2, фильтр сетчатый — 1, клапан балансировочный — 1, термометры — 2, манометры с кранами — 2</t>
+          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 42,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,13 м³/ч, H=0,97 м), байпас, защитный термостат-ограничитель 55 °С</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -1019,17 +981,17 @@
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>Н5 → П1; насос и 3-ходовой клапан — в комплекте П1 (Turkov)</t>
+          <t>КШ-4 (2.6)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная прямая Ду 32 в сборе: насос циркуляционный с электронным управлением класса 25-60 (G=1,62 м³/ч, H=2,81 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Кран шаровой полнопроходной G1" (вход коллекторного шкафа, подача и обратка)</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
@@ -1045,22 +1007,22 @@
         </is>
       </c>
       <c r="G20" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr">
         <is>
-          <t>Н6 → баня: КШ-Б1, КШ-Б2</t>
+          <t>КШ-1…КШ-5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Группа насосная прямая Ду 25 в сборе: насос циркуляционный с электронным управлением класса 25-40 (G=1,20 м³/ч, H=1,35 м), краны шаровые с термометрами, обратный клапан, теплоизоляция</t>
+          <t>Фильтр сетчатый G1" (вход коллекторного шкафа, подача)</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -1076,22 +1038,22 @@
         </is>
       </c>
       <c r="G21" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>Н7 → Б1 (приоритет)</t>
+          <t>КШ-1…КШ-4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Бойлер косвенного нагрева 300 л, змеевик ≈28 кВт</t>
+          <t>Сервопривод термоэлектрический 230 В, нормально закрытый, на термостатический клапан коллектора</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -1107,22 +1069,22 @@
         </is>
       </c>
       <c r="G22" s="1" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>Б1, приоритет ГВС</t>
+          <t>управление — автоматика «Люкс»</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Бак расширительный мембранный для отопления 80 л, начальное давление 1,2 бар</t>
+          <t>Радиатор стальной панельный 33/300, L=1700 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1571 Вт</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -1143,17 +1105,17 @@
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>РБ</t>
+          <t>Р-1 (2.3)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Бак расширительный мембранный для ГВС (питьевая вода) 18 л</t>
+          <t>Радиатор стальной панельный 33/300, L=1300 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1169 Вт</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1174,17 +1136,17 @@
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>РБ-ГВС</t>
+          <t>Р-2 (2.4)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Группа безопасности котла: клапан предохранительный 3 бар, манометр, автоматический воздухоотводчик</t>
+          <t>Радиатор стальной панельный 33/300, L=1700 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1611 Вт</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1205,17 +1167,17 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>ГБ</t>
+          <t>Р-3 (2.5)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Группа безопасности бойлера 6 бар</t>
+          <t>Радиатор стальной панельный 22/500, L=600 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 614 Вт</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1236,56 +1198,68 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>ГБ-ГВС</t>
+          <t>Р-5 (2.6)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Узел подпитки Ду 15: краны шаровые, фильтр, редуктор давления 1,5 бар, обратный клапан</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 1908 Вт</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr"/>
-      <c r="E27" s="1" t="inlineStr"/>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F27" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G27" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr">
         <is>
-          <t>УП</t>
+          <t>Кв-1 (1.10), Кв-2 (1.10)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Шкаф управления котельной: каскадный погодозависимый контроллер (штатный Viessmann), управление ПК, насосами и клапанами групп, датчики температуры (наружный, ГС, Б1, обратка ПК, ТП), удалённый доступ</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr"/>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1650 мм, тепловая мощность при 70/55 °С не менее 1614 Вт</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
+        </is>
+      </c>
       <c r="D28" s="1" t="inlineStr"/>
-      <c r="E28" s="1" t="inlineStr"/>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F28" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G28" s="1" t="n">
@@ -1294,153 +1268,173 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>ШУ; П1 — своя автоматика Turkov; состав — по проекту автоматизации</t>
+          <t>Кв-3 (1.10)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная Ду 32×3,2</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=900 мм, тепловая мощность при 70/55 °С не менее 881 Вт</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 3262-75</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr"/>
-      <c r="E29" s="1" t="inlineStr"/>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F29" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G29" s="1" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>каскад К1, К2 → ГС, контур ПК, ГС → РК</t>
+          <t>Кв-4 (1.10), Кв-5 (1.10)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная Ду 25×3,2</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 894 Вт</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 3262-75</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr"/>
-      <c r="E30" s="1" t="inlineStr"/>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F30" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G30" s="1" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t>подключение К2, загрузка Б1</t>
+          <t>Кв-6 (1.11), Кв-7 (1.11)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная Ду 20×2,8</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2200 мм, тепловая мощность при 70/55 °С не менее 2171 Вт</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 3262-75</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr"/>
-      <c r="E31" s="1" t="inlineStr"/>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F31" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G31" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>подключение РБ</t>
+          <t>Кв-8 (1.9)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Труба стальная водогазопроводная Ду 15×2,8</t>
+          <t>Конвектор внутрипольный без вентилятора (естественная конвекция), L=2750 мм, глубина не более 150 мм, тепловая мощность при 70/55 °С не менее 1701 Вт</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 3262-75</t>
+          <t>КЗТО «Бриз» (естественная конвекция), модель — по каталогу</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr"/>
-      <c r="E32" s="1" t="inlineStr"/>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G32" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>подпитка</t>
+          <t>Кн-1 (2.7)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Фасонные части стальные к трубам Ду 15–32 (отводы, тройники, переходы, сгоны, муфты, контргайки)</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=900 мм, глубина не более 150 мм, тепловая мощность при 70/55 °С не менее 613 Вт</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>ГОСТ 8946-75, 8948-75, 8954-75, 8957-75, 8969-75</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr"/>
-      <c r="E33" s="1" t="inlineStr"/>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F33" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G33" s="1" t="n">
@@ -1449,51 +1443,71 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>Кн-3 (2.2)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Опоры и подвески трубопроводов котельной (хомуты с резиновым вкладышем, шпильки, профиль)</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr"/>
+          <t>Узел нижнего подключения радиатора запорный, присоединение евроконус G¾"</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D34" s="1" t="inlineStr"/>
       <c r="E34" s="1" t="inlineStr"/>
       <c r="F34" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G34" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>Р-1, Р-2, Р-3, Р-5</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr"/>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>2. Отопление дома (листы 3–6)</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="n"/>
-      <c r="D35" s="1" t="n"/>
-      <c r="E35" s="1" t="n"/>
-      <c r="F35" s="1" t="n"/>
-      <c r="G35" s="1" t="n"/>
-      <c r="H35" s="1" t="n"/>
-      <c r="I35" s="1" t="n"/>
+      <c r="A35" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Клапан запорный G½" для подключения конвектора</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr"/>
+      <c r="E35" s="1" t="inlineStr"/>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H35" s="1" t="inlineStr"/>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>Кв-1…Кв-8, Кн-1, Кн-3</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1501,7 +1515,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встроенный ≈850×1300×150 мм (как КШ-2, КШ-5)</t>
+          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH), для отопления, t до 95 °С — петли тёплого пола</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -1513,16 +1527,16 @@
       <c r="E36" s="1" t="inlineStr"/>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G36" s="1" t="n">
-        <v>1</v>
+        <v>1475</v>
       </c>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>КШ-1 (тамбур 1.7)</t>
+          <t>петли — 23 шт., листы 4, 5</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1546,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Коллектор тёплого пола из нержавеющей стали 1" на 6 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — подводки к приборам</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1544,16 +1558,16 @@
       <c r="E37" s="1" t="inlineStr"/>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G37" s="1" t="n">
-        <v>1</v>
+        <v>518</v>
       </c>
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>КШ-1 (тамбур 1.7)</t>
+          <t>листы 3, 5</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1577,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встроенный двухъярусный ≈850×1300×150 мм</t>
+          <t>Фитинг компрессионный (евроконус) для трубы PE-Xa 16×2,0 на G¾"</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -1579,12 +1593,12 @@
         </is>
       </c>
       <c r="G38" s="1" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>КШ-2 (тамбур 1.7); узел — на КШ-2 и КШ-5</t>
+          <t>коллекторы, радиаторы</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1608,7 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Коллектор прямой из нержавеющей стали 1" на 8 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+          <t>Фитинг компрессионный для трубы PE-Xa 16×2,0 на наружную резьбу G½"</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -1606,16 +1620,16 @@
       <c r="E39" s="1" t="inlineStr"/>
       <c r="F39" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G39" s="1" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>КШ-2 (тамбур 1.7); узел — на КШ-2 и КШ-5</t>
+          <t>конвекторы</t>
         </is>
       </c>
     </row>
@@ -1625,28 +1639,24 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Коллектор тёплого пола из нержавеющей стали 1" на 5 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"; проходной — из торцов транзит на КШ-5</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена, толщина 6 мм, для трубы Ø16</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr"/>
       <c r="D40" s="1" t="inlineStr"/>
       <c r="E40" s="1" t="inlineStr"/>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G40" s="1" t="n">
-        <v>1</v>
+        <v>300</v>
       </c>
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr">
         <is>
-          <t>КШ-2 (тамбур 1.7); узел — на КШ-2 и КШ-5</t>
+          <t>подводки 1 этажа</t>
         </is>
       </c>
     </row>
@@ -1656,28 +1666,24 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 36,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,70 м³/ч, H=1,47 м), байпас, защитный термостат-ограничитель 45 °С</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Труба гофрированная защитная (гофра) для трубы Ø16</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr"/>
       <c r="D41" s="1" t="inlineStr"/>
       <c r="E41" s="1" t="inlineStr"/>
       <c r="F41" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>1</v>
+        <v>518</v>
       </c>
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr">
         <is>
-          <t>КШ-2 (тамбур 1.7); узел — на КШ-2 и КШ-5</t>
+          <t>подводки к приборам</t>
         </is>
       </c>
     </row>
@@ -1687,28 +1693,24 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встроенный ≈850×1300×150 мм (как КШ-1, КШ-2)</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Труба гофрированная защитная (гофра) для трубы Ø16 на выходах петель из стяжки, по 1 м на конец</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr"/>
       <c r="D42" s="1" t="inlineStr"/>
       <c r="E42" s="1" t="inlineStr"/>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>КШ-5 (тамбур 1.7), от смесительного узла КШ-2</t>
+          <t>у коллекторов</t>
         </is>
       </c>
     </row>
@@ -1718,30 +1720,22 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Коллектор тёплого пола из нержавеющей стали 1" на 5 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Фиксатор поворота трубы Ø16 на 90° (выход из пола у коллектора)</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr"/>
       <c r="D43" s="1" t="inlineStr"/>
       <c r="E43" s="1" t="inlineStr"/>
       <c r="F43" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="H43" s="1" t="inlineStr"/>
-      <c r="I43" s="1" t="inlineStr">
-        <is>
-          <t>КШ-5 (тамбур 1.7), от смесительного узла КШ-2</t>
-        </is>
-      </c>
+      <c r="I43" s="1" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -1749,7 +1743,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встроенный ≈550×650×120 мм</t>
+          <t>Труба PE-Xa 25×3,5 с антидиффузионным слоем (EVOH) — магистрали от стены топочной</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1761,16 +1755,16 @@
       <c r="E44" s="1" t="inlineStr"/>
       <c r="F44" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G44" s="1" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr">
         <is>
-          <t>КШ-3 (топочная 1.6)</t>
+          <t>Н2 → КШ-4, стояки в 1.7, Н4 → КШ-1, транзит КШ-2 → КШ-5 (36 °С, в полу 1.7)</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1774,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Коллектор тёплого пола из нержавеющей стали 1" на 5 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+          <t>Труба PE-Xa 32×4,4 с антидиффузионным слоем (EVOH) — магистрали от стены топочной</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1792,16 +1786,16 @@
       <c r="E45" s="1" t="inlineStr"/>
       <c r="F45" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G45" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr">
         <is>
-          <t>КШ-3 (топочная 1.6)</t>
+          <t>Н3 → КШ-2</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1805,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встроенный двухъярусный ≈750×1250×150 мм</t>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 25×3,5 на резьбу G1"</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
@@ -1827,12 +1821,12 @@
         </is>
       </c>
       <c r="G46" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr">
         <is>
-          <t>КШ-4 (2.6)</t>
+          <t>концы магистралей</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1836,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Коллектор прямой из нержавеющей стали 1" на 7 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"; выход В6 — резерв, с заглушками</t>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×4,4 на резьбу G1"</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1854,16 +1848,16 @@
       <c r="E47" s="1" t="inlineStr"/>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G47" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr">
         <is>
-          <t>КШ-4 (2.6)</t>
+          <t>концы магистралей</t>
         </is>
       </c>
     </row>
@@ -1873,28 +1867,24 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Коллектор тёплого пола из нержавеющей стали 1" на 2 выхода: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø25</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr"/>
       <c r="D48" s="1" t="inlineStr"/>
       <c r="E48" s="1" t="inlineStr"/>
       <c r="F48" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G48" s="1" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr">
         <is>
-          <t>КШ-4 (2.6)</t>
+          <t>магистрали</t>
         </is>
       </c>
     </row>
@@ -1904,28 +1894,24 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 42,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,13 м³/ч, H=0,97 м), байпас, защитный термостат-ограничитель 55 °С</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø32</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr"/>
       <c r="D49" s="1" t="inlineStr"/>
       <c r="E49" s="1" t="inlineStr"/>
       <c r="F49" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G49" s="1" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>КШ-4 (2.6)</t>
+          <t>магистрали</t>
         </is>
       </c>
     </row>
@@ -1935,28 +1921,24 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой полнопроходной G1" (вход коллекторного шкафа, подача и обратка)</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Пленка (мат) с разметкой для укладки труб тёплого пола</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr"/>
       <c r="D50" s="1" t="inlineStr"/>
       <c r="E50" s="1" t="inlineStr"/>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G50" s="1" t="n">
-        <v>10</v>
+        <v>196</v>
       </c>
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>КШ-1…КШ-5</t>
+          <t>листы 4, 5</t>
         </is>
       </c>
     </row>
@@ -1966,28 +1948,24 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Фильтр сетчатый G1" (вход коллекторного шкафа, подача)</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Лента демпферная 10×150 мм</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr"/>
       <c r="D51" s="1" t="inlineStr"/>
       <c r="E51" s="1" t="inlineStr"/>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G51" s="1" t="n">
-        <v>4</v>
+        <v>286</v>
       </c>
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>КШ-1…КШ-4</t>
+          <t>по периметру зон и по границам петель</t>
         </is>
       </c>
     </row>
@@ -1997,14 +1975,10 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Сервопривод термоэлектрический 230 В, нормально закрытый, на термостатический клапан коллектора</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Скоба якорная для крепления трубы Ø16 к основанию, шаг 0,5 м</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr"/>
       <c r="D52" s="1" t="inlineStr"/>
       <c r="E52" s="1" t="inlineStr"/>
       <c r="F52" s="1" t="inlineStr">
@@ -2013,53 +1987,37 @@
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>37</v>
+        <v>3000</v>
       </c>
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>управление — автоматика «Люкс»</t>
+          <t>листы 4, 5</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Радиатор стальной панельный 33/300, L=1700 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1571 Вт</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr"/>
-      <c r="E53" s="1" t="inlineStr"/>
-      <c r="F53" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G53" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="1" t="inlineStr"/>
-      <c r="I53" s="1" t="inlineStr">
-        <is>
-          <t>Р-1 (2.3)</t>
-        </is>
-      </c>
+      <c r="A53" s="1" t="inlineStr"/>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>3. Отопление бани (листы 12, 13)</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="n"/>
+      <c r="D53" s="1" t="n"/>
+      <c r="E53" s="1" t="n"/>
+      <c r="F53" s="1" t="n"/>
+      <c r="G53" s="1" t="n"/>
+      <c r="H53" s="1" t="n"/>
+      <c r="I53" s="1" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 33/300, L=1300 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1169 Вт</t>
+          <t>Шкаф коллекторный встроенный ШРВ-3 (ширина ≈750 мм), высота ≈650 мм</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -2080,17 +2038,17 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr">
         <is>
-          <t>Р-2 (2.4)</t>
+          <t>КШ-Б1 (с/у б3)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 33/300, L=1700 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1611 Вт</t>
+          <t>Коллектор прямой из нержавеющей стали 1" на 5 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
@@ -2102,7 +2060,7 @@
       <c r="E55" s="1" t="inlineStr"/>
       <c r="F55" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G55" s="1" t="n">
@@ -2111,17 +2069,17 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr">
         <is>
-          <t>Р-3 (2.5)</t>
+          <t>КШ-Б1 (с/у б3)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 22/500, L=600 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 614 Вт</t>
+          <t>Шкаф коллекторный встроенный ШРВ-3 (ширина ≈750 мм), двухъярусный, высота ≈1250 мм</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -2142,68 +2100,60 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>Р-5 (2.6)</t>
+          <t>КШ-Б2 (с/у б3)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 1908 Вт</t>
+          <t>Коллектор тёплого пола из нержавеющей стали 1" на 7 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>КЗТО «Бриз В», модель — по каталогу</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr"/>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E57" s="1" t="inlineStr"/>
       <c r="F57" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G57" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr">
         <is>
-          <t>Кв-1 (1.10), Кв-2 (1.10)</t>
+          <t>КШ-Б2 (с/у б3)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1650 мм, тепловая мощность при 70/55 °С не менее 1614 Вт</t>
+          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 44,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,17 м³/ч, H=0,96 м), байпас, защитный термостат-ограничитель 55 °С</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>КЗТО «Бриз В», модель — по каталогу</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr"/>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E58" s="1" t="inlineStr"/>
       <c r="F58" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G58" s="1" t="n">
@@ -2212,30 +2162,26 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>Кв-3 (1.10)</t>
+          <t>КШ-Б2 (с/у б3)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=900 мм, тепловая мощность при 70/55 °С не менее 881 Вт</t>
+          <t>Кран шаровой полнопроходной G1" (ввод Ecoflex, подача и обратка)</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>КЗТО «Бриз В», модель — по каталогу</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr"/>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E59" s="1" t="inlineStr"/>
       <c r="F59" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -2247,65 +2193,57 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr">
         <is>
-          <t>Кв-4 (1.10), Кв-5 (1.10)</t>
+          <t>ввод КШ-Б1</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=1950 мм, тепловая мощность при 70/55 °С не менее 894 Вт</t>
+          <t>Фильтр сетчатый G1" (ввод, подача)</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>КЗТО «Бриз В», модель — по каталогу</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr"/>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E60" s="1" t="inlineStr"/>
       <c r="F60" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G60" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>Кв-6 (1.11), Кв-7 (1.11)</t>
+          <t>ФС</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2200 мм, тепловая мощность при 70/55 °С не менее 2171 Вт</t>
+          <t>Клапан трёхходовой переключающий с электроприводом Ду 25, расход 1146 кг/ч; приоритет загрузки Б2 по датчику бойлера</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>КЗТО «Бриз В», модель — по каталогу</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr"/>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E61" s="1" t="inlineStr"/>
       <c r="F61" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -2317,30 +2255,26 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr">
         <is>
-          <t>Кв-8 (1.9)</t>
+          <t>УК1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный без вентилятора (естественная конвекция), L=2750 мм, глубина не более 150 мм, тепловая мощность при 70/55 °С не менее 1701 Вт</t>
+          <t>Клапан зональный двухходовой с электроприводом Ду 25 (линия ТО-Д, по таймеру СПА)</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>КЗТО «Бриз» (естественная конвекция), модель — по каталогу</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr"/>
-      <c r="E62" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E62" s="1" t="inlineStr"/>
       <c r="F62" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -2352,30 +2286,26 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>Кн-1 (2.7)</t>
+          <t>УК2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=900 мм, глубина не более 150 мм, тепловая мощность при 70/55 °С не менее 613 Вт</t>
+          <t>Клапан балансировочный Ду 25 (линия ТО-Д)</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>КЗТО «Бриз В», модель — по каталогу</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr"/>
-      <c r="E63" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E63" s="1" t="inlineStr"/>
       <c r="F63" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -2387,17 +2317,17 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>Кн-3 (2.2)</t>
+          <t>ТО-Д</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Узел нижнего подключения радиатора запорный, присоединение евроконус G¾"</t>
+          <t>Теплообменник пластинчатый 20 кВт, 70/50 → 38/28 °С, расход греющей воды 860 кг/ч</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
@@ -2413,22 +2343,22 @@
         </is>
       </c>
       <c r="G64" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr">
         <is>
-          <t>Р-1, Р-2, Р-3, Р-5</t>
+          <t>ТО-Д; вторичный контур — СПА (ВК)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Клапан запорный G½" для подключения конвектора</t>
+          <t>Бойлер косвенного нагрева 200 л, узкий Ø520 мм, змеевик 20 кВт (расход 1146 кг/ч)</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
@@ -2444,22 +2374,22 @@
         </is>
       </c>
       <c r="G65" s="1" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr">
         <is>
-          <t>Кв-1…Кв-8, Кн-1, Кн-3</t>
+          <t>Б2; обвязка ГВС — раздел ВК</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH), для отопления, t до 95 °С — петли тёплого пола</t>
+          <t>Сервопривод термоэлектрический 230 В, нормально закрытый, на термостатический клапан коллектора</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
@@ -2471,26 +2401,26 @@
       <c r="E66" s="1" t="inlineStr"/>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G66" s="1" t="n">
-        <v>1475</v>
+        <v>12</v>
       </c>
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr">
         <is>
-          <t>петли — 23 шт., листы 4, 5</t>
+          <t>управление — автоматика «Люкс»</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — подводки к приборам</t>
+          <t>Радиатор стальной панельный 33/500, L=1100 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1528 Вт</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
@@ -2502,26 +2432,26 @@
       <c r="E67" s="1" t="inlineStr"/>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>518</v>
+        <v>1</v>
       </c>
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>листы 3, 5</t>
+          <t>Р-б1 (б5)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Фитинг компрессионный (евроконус) для трубы PE-Xa 16×2,0 на G¾"</t>
+          <t>Радиатор стальной панельный 33/500, L=500 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 632 Вт</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
@@ -2537,157 +2467,185 @@
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="H68" s="1" t="inlineStr"/>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>коллекторы, радиаторы</t>
+          <t>Р-б2 (б2)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Фитинг компрессионный для трубы PE-Xa 16×2,0 на наружную резьбу G½"</t>
+          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2150 мм, тепловая мощность при 70/55 °С не менее 1108 Вт</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>КЗТО «Бриз В», модель — по каталогу</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr"/>
-      <c r="E69" s="1" t="inlineStr"/>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H69" s="1" t="inlineStr"/>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>конвекторы</t>
+          <t>Кв-б1 (б6), Кв-б2 (б6)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена, толщина 6 мм, для трубы Ø16</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr"/>
+          <t>Конвектор внутрипольный из нержавеющей стали для влажных помещений, с вентилятором 24 В пост. тока, 260×140 мм, L=2200 мм, тепловая мощность при 70/55 °С не менее 2614 Вт</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО «Бриз В TURBO Нерж»</t>
+        </is>
+      </c>
       <c r="D70" s="1" t="inlineStr"/>
-      <c r="E70" s="1" t="inlineStr"/>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>КЗТО</t>
+        </is>
+      </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G70" s="1" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H70" s="1" t="inlineStr"/>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>подводки 1 этажа</t>
+          <t>Кв-б3 (б7, у джакузи); в нише плиты, ≈2030 Вт/м при Δt50</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная (гофра) для трубы Ø16</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr"/>
+          <t>Узел нижнего подключения радиатора запорный, присоединение евроконус G¾"</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D71" s="1" t="inlineStr"/>
       <c r="E71" s="1" t="inlineStr"/>
       <c r="F71" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G71" s="1" t="n">
-        <v>518</v>
+        <v>2</v>
       </c>
       <c r="H71" s="1" t="inlineStr"/>
       <c r="I71" s="1" t="inlineStr">
         <is>
-          <t>подводки к приборам</t>
+          <t>Р-б1, Р-б2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная (гофра) для трубы Ø16 на выходах петель из стяжки, по 1 м на конец</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr"/>
+          <t>Клапан запорный G½" для подключения конвектора</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D72" s="1" t="inlineStr"/>
       <c r="E72" s="1" t="inlineStr"/>
       <c r="F72" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G72" s="1" t="n">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="H72" s="1" t="inlineStr"/>
       <c r="I72" s="1" t="inlineStr">
         <is>
-          <t>у коллекторов</t>
+          <t>Кв-б1…Кв-б3</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота трубы Ø16 на 90° (выход из пола у коллектора)</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr"/>
+          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — петли тёплого пола</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D73" s="1" t="inlineStr"/>
       <c r="E73" s="1" t="inlineStr"/>
       <c r="F73" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46</v>
+        <v>271</v>
       </c>
       <c r="H73" s="1" t="inlineStr"/>
-      <c r="I73" s="1" t="inlineStr"/>
+      <c r="I73" s="1" t="inlineStr">
+        <is>
+          <t>петли — 7 шт., лист 12</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 20×2,8 с антидиффузионным слоем (EVOH) — магистрали</t>
+          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — подводки к приборам</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2703,22 +2661,22 @@
         </is>
       </c>
       <c r="G74" s="1" t="n">
-        <v>14</v>
+        <v>118</v>
       </c>
       <c r="H74" s="1" t="inlineStr"/>
       <c r="I74" s="1" t="inlineStr">
         <is>
-          <t>Н5 → нагреватель П1</t>
+          <t>лист 12</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 25×3,5 с антидиффузионным слоем (EVOH) — магистрали</t>
+          <t>Труба PE-Xa 32×4,4 с антидиффузионным слоем (EVOH) — линии ТО-Д и Б2</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -2734,22 +2692,22 @@
         </is>
       </c>
       <c r="G75" s="1" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>Н2 → КШ-4, стояки в 1.7, Н4 → КШ-1, Н4 → КШ-3, транзит КШ-2 → КШ-5 (36 °С, в полу 1.7)</t>
+          <t>от ввода КШ-Б1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 32×4,4 с антидиффузионным слоем (EVOH) — магистрали</t>
+          <t>Фитинг компрессионный (евроконус) для трубы PE-Xa 16×2,0 на G¾"</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2761,26 +2719,26 @@
       <c r="E76" s="1" t="inlineStr"/>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G76" s="1" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr">
         <is>
-          <t>Н3 → КШ-2</t>
+          <t>коллекторы, радиаторы</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 20×2,8 на резьбу G¾"</t>
+          <t>Фитинг компрессионный для трубы PE-Xa 16×2,0 на наружную резьбу G½"</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2796,22 +2754,22 @@
         </is>
       </c>
       <c r="G77" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>концы магистралей</t>
+          <t>конвекторы</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 25×3,5 на резьбу G1"</t>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×4,4 на резьбу G1"</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2827,53 +2785,49 @@
         </is>
       </c>
       <c r="G78" s="1" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>концы магистралей</t>
+          <t>ТО-Д, Б2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×4,4 на резьбу G1"</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø32</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr"/>
       <c r="D79" s="1" t="inlineStr"/>
       <c r="E79" s="1" t="inlineStr"/>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G79" s="1" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>концы магистралей</t>
+          <t>ТО-Д, Б2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø20</t>
+          <t>Трубка теплоизоляционная из вспененного полиэтилена, толщина 6 мм, для трубы Ø16</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr"/>
@@ -2885,22 +2839,22 @@
         </is>
       </c>
       <c r="G80" s="1" t="n">
-        <v>14</v>
+        <v>253</v>
       </c>
       <c r="H80" s="1" t="inlineStr"/>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>магистрали</t>
+          <t>подводки вне своих петель</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø25</t>
+          <t>Труба гофрированная защитная (гофра) для трубы Ø16</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr"/>
@@ -2912,22 +2866,22 @@
         </is>
       </c>
       <c r="G81" s="1" t="n">
-        <v>73</v>
+        <v>253</v>
       </c>
       <c r="H81" s="1" t="inlineStr"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>магистрали</t>
+          <t>подводки вне своих петель</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø32</t>
+          <t>Фиксатор поворота трубы Ø16 на 90° (выход из пола у коллектора)</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr"/>
@@ -2935,22 +2889,18 @@
       <c r="E82" s="1" t="inlineStr"/>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G82" s="1" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H82" s="1" t="inlineStr"/>
-      <c r="I82" s="1" t="inlineStr">
-        <is>
-          <t>магистрали</t>
-        </is>
-      </c>
+      <c r="I82" s="1" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
@@ -2966,18 +2916,18 @@
         </is>
       </c>
       <c r="G83" s="1" t="n">
-        <v>196</v>
+        <v>28</v>
       </c>
       <c r="H83" s="1" t="inlineStr"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>листы 4, 5</t>
+          <t>лист 12</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
@@ -2993,7 +2943,7 @@
         </is>
       </c>
       <c r="G84" s="1" t="n">
-        <v>286</v>
+        <v>79</v>
       </c>
       <c r="H84" s="1" t="inlineStr"/>
       <c r="I84" s="1" t="inlineStr">
@@ -3004,7 +2954,7 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
@@ -3020,12 +2970,12 @@
         </is>
       </c>
       <c r="G85" s="1" t="n">
-        <v>3000</v>
+        <v>600</v>
       </c>
       <c r="H85" s="1" t="inlineStr"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>листы 4, 5</t>
+          <t>лист 12</t>
         </is>
       </c>
     </row>
@@ -3033,7 +2983,7 @@
       <c r="A86" s="1" t="inlineStr"/>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>3. Отопление бани (листы 12, 13)</t>
+          <t>4. Теплотрасса дом – баня (листы 13, 14)</t>
         </is>
       </c>
       <c r="C86" s="1" t="n"/>
@@ -3046,237 +2996,229 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встроенный ШРВ-3 (ширина ≈750 мм), высота ≈650 мм</t>
+          <t>Труба предизолированная гибкая: две трубы PE-Xa 32×2,9 отопления и две санитарные трубы (по разделу ВК) в общей оболочке</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Uponor Ecoflex Quattro, типоразмер — по каталогу</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr"/>
-      <c r="E87" s="1" t="inlineStr"/>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>Uponor</t>
+        </is>
+      </c>
       <c r="F87" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>КШ-Б1 (с/у б3)</t>
+          <t>≈16,4 м по трассе с подъёмами + 10 %; лист 14</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Коллектор прямой из нержавеющей стали 1" на 5 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
+          <t>Манжета концевая для трубы Ecoflex Quattro</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по каталогу производителя трубы</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr"/>
-      <c r="E88" s="1" t="inlineStr"/>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>Uponor</t>
+        </is>
+      </c>
       <c r="F88" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H88" s="1" t="inlineStr"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>КШ-Б1 (с/у б3)</t>
+          <t>вводы в дом и баню</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Шкаф коллекторный встроенный ШРВ-3 (ширина ≈750 мм), двухъярусный, высота ≈1250 мм</t>
+          <t>Гильза ввода с уплотнительным кольцом через фундамент (комплект ввода производителя)</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по каталогу производителя трубы</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr"/>
-      <c r="E89" s="1" t="inlineStr"/>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>Uponor</t>
+        </is>
+      </c>
       <c r="F89" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G89" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H89" s="1" t="inlineStr"/>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>КШ-Б2 (с/у б3)</t>
+          <t>узлы 1, 2, лист 13</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Коллектор тёплого пола из нержавеющей стали 1" на 7 выходов: расходомеры на подаче, термостатические клапаны под сервопривод на обратке, автоматические воздухоотводчики, сливные краны, присоединение евроконус G¾"</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Гильза в плите пола для трубы Ecoflex Quattro</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr"/>
       <c r="D90" s="1" t="inlineStr"/>
       <c r="E90" s="1" t="inlineStr"/>
       <c r="F90" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G90" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H90" s="1" t="inlineStr"/>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>КШ-Б2 (с/у б3)</t>
+          <t>узлы 1, 2, лист 13</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Узел смесительный тёплого пола: термостатический смесительный клапан с выносным датчиком (подача 44,0 °С), насос циркуляционный с электронным управлением класса 25-40 (G=0,17 м³/ч, H=0,96 м), байпас, защитный термостат-ограничитель 55 °С</t>
+          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×2,9 на резьбу G1"</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по каталогу производителя трубы</t>
         </is>
       </c>
       <c r="D91" s="1" t="inlineStr"/>
       <c r="E91" s="1" t="inlineStr"/>
       <c r="F91" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G91" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H91" s="1" t="inlineStr"/>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>КШ-Б2 (с/у б3)</t>
+          <t>концы Т1, Т2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой полнопроходной G1" (ввод Ecoflex, подача и обратка)</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Лента сигнальная «Осторожно, теплотрасса»</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr"/>
       <c r="D92" s="1" t="inlineStr"/>
       <c r="E92" s="1" t="inlineStr"/>
       <c r="F92" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G92" s="1" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>ввод КШ-Б1</t>
+          <t>300 мм над трубой</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>Фильтр сетчатый G1" (ввод, подача)</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr"/>
-      <c r="E93" s="1" t="inlineStr"/>
-      <c r="F93" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G93" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H93" s="1" t="inlineStr"/>
-      <c r="I93" s="1" t="inlineStr">
-        <is>
-          <t>ФС</t>
-        </is>
-      </c>
+      <c r="A93" s="1" t="inlineStr"/>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>5. Вентиляция (листы 9–12)</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="n"/>
+      <c r="D93" s="1" t="n"/>
+      <c r="E93" s="1" t="n"/>
+      <c r="F93" s="1" t="n"/>
+      <c r="G93" s="1" t="n"/>
+      <c r="H93" s="1" t="n"/>
+      <c r="I93" s="1" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Клапан трёхходовой переключающий с электроприводом Ду 25, расход 1146 кг/ч; приоритет загрузки Б2 по датчику бойлера</t>
+          <t>Приточно-вытяжная установка с рекуперацией тепла и влаги (пластинчатый энтальпийный рекуператор), 750 м³/ч, свободный напор ≈180 Па при 750 м³/ч (по расчёту сети 159 Па при 700 м³/ч), водяной нагреватель (≈2,6 кВт, 70/50 °С) со смесительным узлом и автоматикой в комплекте, патрубки Ø250, ≈1500×1080×610 мм, ≈145 кг, 220 В, ≈0,8 кВт</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Turkov Zenit 750 Heco W (или аналог)</t>
         </is>
       </c>
       <c r="D94" s="1" t="inlineStr"/>
-      <c r="E94" s="1" t="inlineStr"/>
+      <c r="E94" s="1" t="inlineStr">
+        <is>
+          <t>Turkov</t>
+        </is>
+      </c>
       <c r="F94" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -3288,17 +3230,17 @@
       <c r="H94" s="1" t="inlineStr"/>
       <c r="I94" s="1" t="inlineStr">
         <is>
-          <t>УК1</t>
+          <t>П1, под потолком топочной (лист 9)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Клапан зональный двухходовой с электроприводом Ду 25 (линия ТО-Д, по таймеру СПА)</t>
+          <t>Кран шаровой G¾" (подключение нагревателя П1 к смесительному узлу, подача и обратка)</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -3314,22 +3256,22 @@
         </is>
       </c>
       <c r="G95" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H95" s="1" t="inlineStr"/>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>УК2</t>
+          <t>П1; фильтр — на отводе Н5 у РК</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Клапан балансировочный Ду 25 (линия ТО-Д)</t>
+          <t>Труба полипропиленовая канализационная Ø32 — дренаж конденсата П1 к трапу топочной (сифон с сухим затвором — раздел ВК)</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -3341,26 +3283,26 @@
       <c r="E96" s="1" t="inlineStr"/>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G96" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H96" s="1" t="inlineStr"/>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>ТО-Д</t>
+          <t>П1: опуск с +2,450 к трапу (листы 7, 9)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Теплообменник пластинчатый 20 кВт, 70/50 → 38/28 °С, расход греющей воды 860 кг/ч</t>
+          <t>Клапан воздушный круглый Ø250 с электроприводом 230 В с возвратной пружиной (нормально закрыт), на наружном воздухе П1; не ставится, если встроен в установку Turkov</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -3381,17 +3323,17 @@
       <c r="H97" s="1" t="inlineStr"/>
       <c r="I97" s="1" t="inlineStr">
         <is>
-          <t>ТО-Д; вторичный контур — СПА (ВК)</t>
+          <t>КВ-Н; защита нагревателя П1 от разморозки при отключении питания</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Бойлер косвенного нагрева 200 л, узкий Ø520 мм, змеевик 20 кВт (расход 1146 кг/ч)</t>
+          <t>Шумоглушитель круглый Ø250, L=600 мм</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -3407,223 +3349,191 @@
         </is>
       </c>
       <c r="G98" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H98" s="1" t="inlineStr"/>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>Б2; обвязка ГВС — раздел ВК</t>
+          <t>ШГ, на П и В у П1, между опуском и западной стеной топочной</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Сервопривод термоэлектрический 230 В, нормально закрытый, на термостатический клапан коллектора</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø100, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="inlineStr"/>
       <c r="D99" s="1" t="inlineStr"/>
       <c r="E99" s="1" t="inlineStr"/>
       <c r="F99" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G99" s="1" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="H99" s="1" t="inlineStr"/>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>управление — автоматика «Люкс»</t>
+          <t>П1 — 29 м; баня ВВ-б1, ВВ-б2 — 3 м</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 33/500, L=1100 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 1528 Вт</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø125, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="inlineStr"/>
       <c r="D100" s="1" t="inlineStr"/>
       <c r="E100" s="1" t="inlineStr"/>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G100" s="1" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H100" s="1" t="inlineStr"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>Р-б1 (б5)</t>
+          <t>П1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Радиатор стальной панельный 33/500, L=500 мм, нижнее подключение, тепловая мощность при 70/55 °С не менее 632 Вт</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø150, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr"/>
       <c r="D101" s="1" t="inlineStr"/>
       <c r="E101" s="1" t="inlineStr"/>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G101" s="1" t="n">
-        <v>1</v>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G101" s="1" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
       </c>
       <c r="H101" s="1" t="inlineStr"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>Р-б2 (б2)</t>
+          <t>ВЗ (кухонный зонт)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный с вентилятором 24 В пост. тока, L=2150 мм, тепловая мощность при 70/55 °С не менее 1108 Вт</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО «Бриз В», модель — по каталогу</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø160, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="inlineStr"/>
       <c r="D102" s="1" t="inlineStr"/>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E102" s="1" t="inlineStr"/>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G102" s="1" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H102" s="1" t="inlineStr"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>Кв-б1 (б6), Кв-б2 (б6)</t>
+          <t>П1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Конвектор внутрипольный из нержавеющей стали для влажных помещений, с вентилятором 24 В пост. тока, 260×140 мм, L=2200 мм, тепловая мощность при 70/55 °С не менее 2614 Вт</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО «Бриз В TURBO Нерж»</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø200, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr"/>
       <c r="D103" s="1" t="inlineStr"/>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>КЗТО</t>
-        </is>
-      </c>
+      <c r="E103" s="1" t="inlineStr"/>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G103" s="1" t="n">
-        <v>1</v>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G103" s="1" t="inlineStr">
+        <is>
+          <t>24,8</t>
+        </is>
       </c>
       <c r="H103" s="1" t="inlineStr"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>Кв-б3 (б7, у джакузи); в нише плиты, ≈2030 Вт/м при Δt50</t>
+          <t>П1 — 18 м; ВЗ (кухонный зонт) — 6,8 м</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Узел нижнего подключения радиатора запорный, присоединение евроконус G¾"</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод круглый из оцинкованной стали Ø250, толщина стали — по СП 60.13330</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr"/>
       <c r="D104" s="1" t="inlineStr"/>
       <c r="E104" s="1" t="inlineStr"/>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G104" s="1" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="H104" s="1" t="inlineStr"/>
       <c r="I104" s="1" t="inlineStr">
         <is>
-          <t>Р-б1, Р-б2</t>
+          <t>П1: магистрали, Н, выброс в Ш-2; В2 в Ш-2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Клапан запорный G½" для подключения конвектора</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 90° круглый оцинкованный Ø100</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr"/>
       <c r="D105" s="1" t="inlineStr"/>
       <c r="E105" s="1" t="inlineStr"/>
       <c r="F105" s="1" t="inlineStr">
@@ -3632,122 +3542,98 @@
         </is>
       </c>
       <c r="G105" s="1" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H105" s="1" t="inlineStr"/>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>Кв-б1…Кв-б3</t>
+          <t>в т. ч. баня ВВ-б1, ВВ-б2 — 2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — петли тёплого пола</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 90° круглый оцинкованный Ø125</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="inlineStr"/>
       <c r="D106" s="1" t="inlineStr"/>
       <c r="E106" s="1" t="inlineStr"/>
       <c r="F106" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G106" s="1" t="n">
-        <v>271</v>
+        <v>6</v>
       </c>
       <c r="H106" s="1" t="inlineStr"/>
-      <c r="I106" s="1" t="inlineStr">
-        <is>
-          <t>петли — 7 шт., лист 12</t>
-        </is>
-      </c>
+      <c r="I106" s="1" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 16×2,0 с антидиффузионным слоем (EVOH) — подводки к приборам</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 90° круглый оцинкованный Ø150</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="inlineStr"/>
       <c r="D107" s="1" t="inlineStr"/>
       <c r="E107" s="1" t="inlineStr"/>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>118</v>
+        <v>3</v>
       </c>
       <c r="H107" s="1" t="inlineStr"/>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>лист 12</t>
+          <t>ВЗ (кухонный зонт)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Труба PE-Xa 32×4,4 с антидиффузионным слоем (EVOH) — линии ТО-Д и Б2</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 90° круглый оцинкованный Ø160</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="inlineStr"/>
       <c r="D108" s="1" t="inlineStr"/>
       <c r="E108" s="1" t="inlineStr"/>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G108" s="1" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="H108" s="1" t="inlineStr"/>
-      <c r="I108" s="1" t="inlineStr">
-        <is>
-          <t>от ввода КШ-Б1</t>
-        </is>
-      </c>
+      <c r="I108" s="1" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Фитинг компрессионный (евроконус) для трубы PE-Xa 16×2,0 на G¾"</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 90° круглый оцинкованный Ø200</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr"/>
       <c r="D109" s="1" t="inlineStr"/>
       <c r="E109" s="1" t="inlineStr"/>
       <c r="F109" s="1" t="inlineStr">
@@ -3756,29 +3642,25 @@
         </is>
       </c>
       <c r="G109" s="1" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="H109" s="1" t="inlineStr"/>
       <c r="I109" s="1" t="inlineStr">
         <is>
-          <t>коллекторы, радиаторы</t>
+          <t>в т. ч. ВЗ (кухонный зонт) — 1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Фитинг компрессионный для трубы PE-Xa 16×2,0 на наружную резьбу G½"</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 90° круглый оцинкованный Ø250</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="inlineStr"/>
       <c r="D110" s="1" t="inlineStr"/>
       <c r="E110" s="1" t="inlineStr"/>
       <c r="F110" s="1" t="inlineStr">
@@ -3787,29 +3669,21 @@
         </is>
       </c>
       <c r="G110" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H110" s="1" t="inlineStr"/>
-      <c r="I110" s="1" t="inlineStr">
-        <is>
-          <t>конвекторы</t>
-        </is>
-      </c>
+      <c r="I110" s="1" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×4,4 на резьбу G1"</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Тройник круглый оцинкованный Ø125/Ø100</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="inlineStr"/>
       <c r="D111" s="1" t="inlineStr"/>
       <c r="E111" s="1" t="inlineStr"/>
       <c r="F111" s="1" t="inlineStr">
@@ -3818,22 +3692,18 @@
         </is>
       </c>
       <c r="G111" s="1" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H111" s="1" t="inlineStr"/>
-      <c r="I111" s="1" t="inlineStr">
-        <is>
-          <t>ТО-Д, Б2</t>
-        </is>
-      </c>
+      <c r="I111" s="1" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного каучука, толщина 13 мм, для трубы Ø32</t>
+          <t>Тройник круглый оцинкованный Ø160/Ø100</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr"/>
@@ -3841,26 +3711,22 @@
       <c r="E112" s="1" t="inlineStr"/>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G112" s="1" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="H112" s="1" t="inlineStr"/>
-      <c r="I112" s="1" t="inlineStr">
-        <is>
-          <t>ТО-Д, Б2</t>
-        </is>
-      </c>
+      <c r="I112" s="1" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Трубка теплоизоляционная из вспененного полиэтилена, толщина 6 мм, для трубы Ø16</t>
+          <t>Тройник круглый оцинкованный Ø160/Ø125</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr"/>
@@ -3868,26 +3734,22 @@
       <c r="E113" s="1" t="inlineStr"/>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G113" s="1" t="n">
-        <v>253</v>
+        <v>4</v>
       </c>
       <c r="H113" s="1" t="inlineStr"/>
-      <c r="I113" s="1" t="inlineStr">
-        <is>
-          <t>подводки вне своих петель</t>
-        </is>
-      </c>
+      <c r="I113" s="1" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Труба гофрированная защитная (гофра) для трубы Ø16</t>
+          <t>Тройник круглый оцинкованный Ø200/Ø125</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr"/>
@@ -3895,26 +3757,22 @@
       <c r="E114" s="1" t="inlineStr"/>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>253</v>
+        <v>2</v>
       </c>
       <c r="H114" s="1" t="inlineStr"/>
-      <c r="I114" s="1" t="inlineStr">
-        <is>
-          <t>подводки вне своих петель</t>
-        </is>
-      </c>
+      <c r="I114" s="1" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Фиксатор поворота трубы Ø16 на 90° (выход из пола у коллектора)</t>
+          <t>Тройник круглый оцинкованный Ø200/Ø160</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr"/>
@@ -3926,18 +3784,18 @@
         </is>
       </c>
       <c r="G115" s="1" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H115" s="1" t="inlineStr"/>
       <c r="I115" s="1" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Пленка (мат) с разметкой для укладки труб тёплого пола</t>
+          <t>Тройник круглый оцинкованный Ø200/Ø200</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr"/>
@@ -3945,26 +3803,22 @@
       <c r="E116" s="1" t="inlineStr"/>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G116" s="1" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H116" s="1" t="inlineStr"/>
-      <c r="I116" s="1" t="inlineStr">
-        <is>
-          <t>лист 12</t>
-        </is>
-      </c>
+      <c r="I116" s="1" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Лента демпферная 10×150 мм</t>
+          <t>Тройник круглый оцинкованный Ø250/Ø100</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr"/>
@@ -3972,26 +3826,22 @@
       <c r="E117" s="1" t="inlineStr"/>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G117" s="1" t="n">
-        <v>79</v>
+        <v>2</v>
       </c>
       <c r="H117" s="1" t="inlineStr"/>
-      <c r="I117" s="1" t="inlineStr">
-        <is>
-          <t>по периметру зон и по границам петель</t>
-        </is>
-      </c>
+      <c r="I117" s="1" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Скоба якорная для крепления трубы Ø16 к основанию, шаг 0,5 м</t>
+          <t>Тройник круглый оцинкованный Ø250/Ø200</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr"/>
@@ -4003,142 +3853,114 @@
         </is>
       </c>
       <c r="G118" s="1" t="n">
-        <v>600</v>
+        <v>2</v>
       </c>
       <c r="H118" s="1" t="inlineStr"/>
-      <c r="I118" s="1" t="inlineStr">
-        <is>
-          <t>лист 12</t>
-        </is>
-      </c>
+      <c r="I118" s="1" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="inlineStr"/>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>4. Теплотрасса дом – баня (листы 13, 14)</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="n"/>
-      <c r="D119" s="1" t="n"/>
-      <c r="E119" s="1" t="n"/>
-      <c r="F119" s="1" t="n"/>
-      <c r="G119" s="1" t="n"/>
-      <c r="H119" s="1" t="n"/>
-      <c r="I119" s="1" t="n"/>
+      <c r="A119" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Переход круглый оцинкованный Ø125/Ø100</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="inlineStr"/>
+      <c r="D119" s="1" t="inlineStr"/>
+      <c r="E119" s="1" t="inlineStr"/>
+      <c r="F119" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G119" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H119" s="1" t="inlineStr"/>
+      <c r="I119" s="1" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Труба предизолированная гибкая: две трубы PE-Xa 32×2,9 отопления и две санитарные трубы (по разделу ВК) в общей оболочке</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>Uponor Ecoflex Quattro, типоразмер — по каталогу</t>
-        </is>
-      </c>
+          <t>Переход круглый оцинкованный Ø160/Ø125</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr"/>
       <c r="D120" s="1" t="inlineStr"/>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>Uponor</t>
-        </is>
-      </c>
+      <c r="E120" s="1" t="inlineStr"/>
       <c r="F120" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G120" s="1" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H120" s="1" t="inlineStr"/>
-      <c r="I120" s="1" t="inlineStr">
-        <is>
-          <t>≈16,4 м по трассе с подъёмами + 10 %; лист 14</t>
-        </is>
-      </c>
+      <c r="I120" s="1" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Манжета концевая для трубы Ecoflex Quattro</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>по каталогу производителя трубы</t>
-        </is>
-      </c>
+          <t>Переход круглый оцинкованный Ø200/Ø100</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr"/>
       <c r="D121" s="1" t="inlineStr"/>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>Uponor</t>
-        </is>
-      </c>
+      <c r="E121" s="1" t="inlineStr"/>
       <c r="F121" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G121" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H121" s="1" t="inlineStr"/>
-      <c r="I121" s="1" t="inlineStr">
-        <is>
-          <t>вводы в дом и баню</t>
-        </is>
-      </c>
+      <c r="I121" s="1" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Гильза ввода с уплотнительным кольцом через фундамент (комплект ввода производителя)</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>по каталогу производителя трубы</t>
-        </is>
-      </c>
+          <t>Переход круглый оцинкованный Ø200/Ø150</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="inlineStr"/>
       <c r="D122" s="1" t="inlineStr"/>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>Uponor</t>
-        </is>
-      </c>
+      <c r="E122" s="1" t="inlineStr"/>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G122" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H122" s="1" t="inlineStr"/>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>узлы 1, 2, лист 13</t>
+          <t>ВЗ (кухонный зонт)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Гильза в плите пола для трубы Ecoflex Quattro</t>
+          <t>Переход круглый оцинкованный Ø200/Ø160</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr"/>
@@ -4150,29 +3972,21 @@
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H123" s="1" t="inlineStr"/>
-      <c r="I123" s="1" t="inlineStr">
-        <is>
-          <t>узлы 1, 2, лист 13</t>
-        </is>
-      </c>
+      <c r="I123" s="1" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Фитинг (пресс или компрессионный) для трубы PE-Xa 32×2,9 на резьбу G1"</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>по каталогу производителя трубы</t>
-        </is>
-      </c>
+          <t>Переход круглый оцинкованный Ø250/Ø160</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="inlineStr"/>
       <c r="D124" s="1" t="inlineStr"/>
       <c r="E124" s="1" t="inlineStr"/>
       <c r="F124" s="1" t="inlineStr">
@@ -4181,22 +3995,18 @@
         </is>
       </c>
       <c r="G124" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H124" s="1" t="inlineStr"/>
-      <c r="I124" s="1" t="inlineStr">
-        <is>
-          <t>концы Т1, Т2</t>
-        </is>
-      </c>
+      <c r="I124" s="1" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Лента сигнальная «Осторожно, теплотрасса»</t>
+          <t>Переход круглый оцинкованный Ø250/Ø200</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr"/>
@@ -4204,33 +4014,45 @@
       <c r="E125" s="1" t="inlineStr"/>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G125" s="1" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H125" s="1" t="inlineStr"/>
-      <c r="I125" s="1" t="inlineStr">
-        <is>
-          <t>300 мм над трубой</t>
-        </is>
-      </c>
+      <c r="I125" s="1" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="inlineStr"/>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>5. Вентиляция (листы 9–12)</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="n"/>
-      <c r="D126" s="1" t="n"/>
-      <c r="E126" s="1" t="n"/>
-      <c r="F126" s="1" t="n"/>
-      <c r="G126" s="1" t="n"/>
-      <c r="H126" s="1" t="n"/>
-      <c r="I126" s="1" t="n"/>
+      <c r="A126" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Регулятор расхода воздуха (ирисовый клапан) Ø100</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="inlineStr"/>
+      <c r="E126" s="1" t="inlineStr"/>
+      <c r="F126" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G126" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="H126" s="1" t="inlineStr"/>
+      <c r="I126" s="1" t="inlineStr">
+        <is>
+          <t>РР, на ответвлениях</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -4238,32 +4060,28 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Приточно-вытяжная установка с рекуперацией тепла и влаги (пластинчатый энтальпийный рекуператор), 750 м³/ч, свободный напор ≈180 Па при 750 м³/ч (по расчёту сети 159 Па при 700 м³/ч), водяной нагреватель (≈2,6 кВт, 70/50 °С) со смесительным узлом и автоматикой в комплекте, патрубки Ø250, ≈1500×1080×610 мм, ≈145 кг, 220 В, ≈0,8 кВт</t>
+          <t>Регулятор расхода воздуха (ирисовый клапан) Ø125</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>Turkov Zenit 750 Heco W (или аналог)</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr"/>
-      <c r="E127" s="1" t="inlineStr">
-        <is>
-          <t>Turkov</t>
-        </is>
-      </c>
+      <c r="E127" s="1" t="inlineStr"/>
       <c r="F127" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G127" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H127" s="1" t="inlineStr"/>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>П1, под потолком топочной (лист 9)</t>
+          <t>РР, на ответвлениях</t>
         </is>
       </c>
     </row>
@@ -4273,7 +4091,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Кран шаровой G¾" (подключение нагревателя П1 к смесительному узлу, подача и обратка)</t>
+          <t>Регулятор расхода воздуха (ирисовый клапан) Ø160</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
@@ -4289,12 +4107,12 @@
         </is>
       </c>
       <c r="G128" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H128" s="1" t="inlineStr"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>П1; фильтр — на отводе Н5 у РК</t>
+          <t>РР, на ответвлениях</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4122,7 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø32 — дренаж конденсата П1 к трапу топочной (сифон с сухим затвором — раздел ВК)</t>
+          <t>Диффузор щелевой (линейный) приточный в торце подшивки, L=600 мм, с камерой статического давления, присоединение Ø125, расход 70 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
@@ -4316,16 +4134,16 @@
       <c r="E129" s="1" t="inlineStr"/>
       <c r="F129" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G129" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H129" s="1" t="inlineStr"/>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>П1: опуск с +2,450 к трапу (листы 7, 9)</t>
+          <t>1.10 — 3 шт.</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4153,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Клапан воздушный круглый Ø250 с электроприводом 230 В с возвратной пружиной (нормально закрыт), на наружном воздухе П1; не ставится, если встроен в установку Turkov</t>
+          <t>Диффузор потолочный приточный с камерой статического давления, присоединение Ø100, расход 30/60 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
@@ -4351,12 +4169,12 @@
         </is>
       </c>
       <c r="G130" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H130" s="1" t="inlineStr"/>
       <c r="I130" s="1" t="inlineStr">
         <is>
-          <t>КВ-Н; защита нагревателя П1 от разморозки при отключении питания</t>
+          <t>1.11 — 2 шт., 2.2</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4184,7 @@
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Шумоглушитель круглый Ø250, L=600 мм</t>
+          <t>Решётка приточная настенная с регулирующим клапаном, на камере статического давления (КСД) с круглым патрубком, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
@@ -4382,12 +4200,12 @@
         </is>
       </c>
       <c r="G131" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H131" s="1" t="inlineStr"/>
       <c r="I131" s="1" t="inlineStr">
         <is>
-          <t>ШГ, на П и В у П1, между опуском и западной стеной топочной</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -4397,24 +4215,28 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø100, толщина стали — по СП 60.13330</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr"/>
+          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø100, расход 40/50/60 м³/ч; типоразмер — по расходу, по каталогу</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D132" s="1" t="inlineStr"/>
       <c r="E132" s="1" t="inlineStr"/>
       <c r="F132" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G132" s="1" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="H132" s="1" t="inlineStr"/>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>П1 — 29 м; баня ВВ-б1, ВВ-б2 — 3 м</t>
+          <t>1.4, 1.3, 2.6</t>
         </is>
       </c>
     </row>
@@ -4424,24 +4246,28 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø125, толщина стали — по СП 60.13330</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr"/>
+          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø125, расход 75/90 м³/ч; типоразмер — по расходу, по каталогу</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D133" s="1" t="inlineStr"/>
       <c r="E133" s="1" t="inlineStr"/>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G133" s="1" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="H133" s="1" t="inlineStr"/>
       <c r="I133" s="1" t="inlineStr">
         <is>
-          <t>П1</t>
+          <t>2.9, 2.8, 2.1</t>
         </is>
       </c>
     </row>
@@ -4451,26 +4277,28 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø150, толщина стали — по СП 60.13330</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr"/>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, на камере статического давления (КСД) с круглым патрубком, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D134" s="1" t="inlineStr"/>
       <c r="E134" s="1" t="inlineStr"/>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G134" s="1" t="inlineStr">
-        <is>
-          <t>2,7</t>
-        </is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G134" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="H134" s="1" t="inlineStr"/>
       <c r="I134" s="1" t="inlineStr">
         <is>
-          <t>ВЗ (кухонный зонт)</t>
+          <t>1.8</t>
         </is>
       </c>
     </row>
@@ -4480,24 +4308,28 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø160, толщина стали — по СП 60.13330</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr"/>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, на камере статического давления (КСД) с круглым патрубком, присоединение Ø125, расход 90 м³/ч; типоразмер — по расходу, по каталогу</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D135" s="1" t="inlineStr"/>
       <c r="E135" s="1" t="inlineStr"/>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G135" s="1" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H135" s="1" t="inlineStr"/>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>П1</t>
+          <t>1.10 (кухня)</t>
         </is>
       </c>
     </row>
@@ -4507,26 +4339,28 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø200, толщина стали — по СП 60.13330</t>
-        </is>
-      </c>
-      <c r="C136" s="1" t="inlineStr"/>
+          <t>Решётка вытяжная настенная с регулирующим клапаном, на камере статического давления (КСД) с круглым патрубком, присоединение Ø160, расход 120 м³/ч; типоразмер — по расходу, по каталогу</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D136" s="1" t="inlineStr"/>
       <c r="E136" s="1" t="inlineStr"/>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G136" s="1" t="inlineStr">
-        <is>
-          <t>24,8</t>
-        </is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G136" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="H136" s="1" t="inlineStr"/>
       <c r="I136" s="1" t="inlineStr">
         <is>
-          <t>П1 — 18 м; ВЗ (кухонный зонт) — 6,8 м</t>
+          <t>1.10 (верх 2-го света)</t>
         </is>
       </c>
     </row>
@@ -4536,24 +4370,28 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод круглый из оцинкованной стали Ø250, толщина стали — по СП 60.13330</t>
-        </is>
-      </c>
-      <c r="C137" s="1" t="inlineStr"/>
+          <t>Решётка наружная воздухозаборная 500×400, низ +2,600</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D137" s="1" t="inlineStr"/>
       <c r="E137" s="1" t="inlineStr"/>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G137" s="1" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="H137" s="1" t="inlineStr"/>
       <c r="I137" s="1" t="inlineStr">
         <is>
-          <t>П1: магистрали, Н, выброс в Ш-2; В2 в Ш-2</t>
+          <t>Н1, восточная стена топочной</t>
         </is>
       </c>
     </row>
@@ -4563,10 +4401,14 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø100</t>
-        </is>
-      </c>
-      <c r="C138" s="1" t="inlineStr"/>
+          <t>Оголовок (зонт) воздуховода Ø250 выше кровли</t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D138" s="1" t="inlineStr"/>
       <c r="E138" s="1" t="inlineStr"/>
       <c r="F138" s="1" t="inlineStr">
@@ -4575,12 +4417,12 @@
         </is>
       </c>
       <c r="G138" s="1" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H138" s="1" t="inlineStr"/>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>в т. ч. баня ВВ-б1, ВВ-б2 — 2</t>
+          <t>выброс П1, В2 (Ш-2)</t>
         </is>
       </c>
     </row>
@@ -4590,10 +4432,14 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø125</t>
-        </is>
-      </c>
-      <c r="C139" s="1" t="inlineStr"/>
+          <t>Оголовок (зонт) воздуховода Ø200 выше кровли</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D139" s="1" t="inlineStr"/>
       <c r="E139" s="1" t="inlineStr"/>
       <c r="F139" s="1" t="inlineStr">
@@ -4602,10 +4448,14 @@
         </is>
       </c>
       <c r="G139" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H139" s="1" t="inlineStr"/>
-      <c r="I139" s="1" t="inlineStr"/>
+      <c r="I139" s="1" t="inlineStr">
+        <is>
+          <t>ВЗ (кухонный зонт), шахта над мангалом 1.12</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -4613,10 +4463,14 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø150</t>
-        </is>
-      </c>
-      <c r="C140" s="1" t="inlineStr"/>
+          <t>Решётка вытяжная настенная под воздуховод Ø250 (вытяжка топочной, естественная)</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D140" s="1" t="inlineStr"/>
       <c r="E140" s="1" t="inlineStr"/>
       <c r="F140" s="1" t="inlineStr">
@@ -4625,12 +4479,12 @@
         </is>
       </c>
       <c r="G140" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H140" s="1" t="inlineStr"/>
       <c r="I140" s="1" t="inlineStr">
         <is>
-          <t>ВЗ (кухонный зонт)</t>
+          <t>В2, 188 м³/ч</t>
         </is>
       </c>
     </row>
@@ -4640,10 +4494,14 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø160</t>
-        </is>
-      </c>
-      <c r="C141" s="1" t="inlineStr"/>
+          <t>Решётка переточная в низу наружной двери топочной, живое сечение не менее 0,08 м²</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D141" s="1" t="inlineStr"/>
       <c r="E141" s="1" t="inlineStr"/>
       <c r="F141" s="1" t="inlineStr">
@@ -4652,10 +4510,14 @@
         </is>
       </c>
       <c r="G141" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H141" s="1" t="inlineStr"/>
-      <c r="I141" s="1" t="inlineStr"/>
+      <c r="I141" s="1" t="inlineStr">
+        <is>
+          <t>ПН, 282 м³/ч</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -4663,10 +4525,14 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø200</t>
-        </is>
-      </c>
-      <c r="C142" s="1" t="inlineStr"/>
+          <t>Решётка вентиляционная наружная 400×200</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D142" s="1" t="inlineStr"/>
       <c r="E142" s="1" t="inlineStr"/>
       <c r="F142" s="1" t="inlineStr">
@@ -4675,12 +4541,12 @@
         </is>
       </c>
       <c r="G142" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H142" s="1" t="inlineStr"/>
       <c r="I142" s="1" t="inlineStr">
         <is>
-          <t>в т. ч. ВЗ (кухонный зонт) — 1</t>
+          <t>гараж 1.5: приток внизу, вытяжка вверху</t>
         </is>
       </c>
     </row>
@@ -4690,7 +4556,7 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° круглый оцинкованный Ø250</t>
+          <t>Зонт кухонный над плитой 500–600 м³/ч, располагаемое давление не менее 200 Па при 600 м³/ч</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr"/>
@@ -4702,10 +4568,14 @@
         </is>
       </c>
       <c r="G143" s="1" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H143" s="1" t="inlineStr"/>
-      <c r="I143" s="1" t="inlineStr"/>
+      <c r="I143" s="1" t="inlineStr">
+        <is>
+          <t>ВЗ, поставка Заказчика</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -4713,10 +4583,14 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø125/Ø100</t>
-        </is>
-      </c>
-      <c r="C144" s="1" t="inlineStr"/>
+          <t>Клапан обратный Ø150</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D144" s="1" t="inlineStr"/>
       <c r="E144" s="1" t="inlineStr"/>
       <c r="F144" s="1" t="inlineStr">
@@ -4725,10 +4599,14 @@
         </is>
       </c>
       <c r="G144" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H144" s="1" t="inlineStr"/>
-      <c r="I144" s="1" t="inlineStr"/>
+      <c r="I144" s="1" t="inlineStr">
+        <is>
+          <t>ВЗ, на патрубке зонта</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -4736,10 +4614,14 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø160/Ø100</t>
-        </is>
-      </c>
-      <c r="C145" s="1" t="inlineStr"/>
+          <t>Гильза для прохода воздуховода Ø200 в изоляции через наружную стену (под отверстие Ø320)</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D145" s="1" t="inlineStr"/>
       <c r="E145" s="1" t="inlineStr"/>
       <c r="F145" s="1" t="inlineStr">
@@ -4748,10 +4630,14 @@
         </is>
       </c>
       <c r="G145" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H145" s="1" t="inlineStr"/>
-      <c r="I145" s="1" t="inlineStr"/>
+      <c r="I145" s="1" t="inlineStr">
+        <is>
+          <t>ВЗ, сквозь стену на +3,400</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -4759,22 +4645,30 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø160/Ø125</t>
-        </is>
-      </c>
-      <c r="C146" s="1" t="inlineStr"/>
+          <t>Клапан компенсации Ø200 с электроприводом, сблокирован с ВЗ, в наружной стене с решёткой</t>
+        </is>
+      </c>
+      <c r="C146" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D146" s="1" t="inlineStr"/>
       <c r="E146" s="1" t="inlineStr"/>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G146" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H146" s="1" t="inlineStr"/>
-      <c r="I146" s="1" t="inlineStr"/>
+      <c r="I146" s="1" t="inlineStr">
+        <is>
+          <t>КК</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -4782,22 +4676,30 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø200/Ø125</t>
-        </is>
-      </c>
-      <c r="C147" s="1" t="inlineStr"/>
+          <t>Теплоизоляция воздуховодов рулонная толщиной 25 мм с паробарьером (фольга), класс горючести — по СП 60</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D147" s="1" t="inlineStr"/>
       <c r="E147" s="1" t="inlineStr"/>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G147" s="1" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H147" s="1" t="inlineStr"/>
-      <c r="I147" s="1" t="inlineStr"/>
+      <c r="I147" s="1" t="inlineStr">
+        <is>
+          <t>Н и выброс П1 Ø250</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -4805,22 +4707,32 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø200/Ø160</t>
-        </is>
-      </c>
-      <c r="C148" s="1" t="inlineStr"/>
+          <t>Теплоизоляция воздуховода Ø200 из минеральной ваты, негорючая (НГ), толщина 50 мм, кашированная фольгой</t>
+        </is>
+      </c>
+      <c r="C148" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D148" s="1" t="inlineStr"/>
       <c r="E148" s="1" t="inlineStr"/>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G148" s="1" t="n">
-        <v>1</v>
+          <t>м</t>
+        </is>
+      </c>
+      <c r="G148" s="1" t="inlineStr">
+        <is>
+          <t>6,8</t>
+        </is>
       </c>
       <c r="H148" s="1" t="inlineStr"/>
-      <c r="I148" s="1" t="inlineStr"/>
+      <c r="I148" s="1" t="inlineStr">
+        <is>
+          <t>ВЗ: холодная шахта, рядом дымоход мангала — только НГ</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -4828,7 +4740,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø200/Ø200</t>
+          <t>Крепления воздуховодов: подвесы, хомуты с уплотнителем, шпильки, профиль</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr"/>
@@ -4836,14 +4748,18 @@
       <c r="E149" s="1" t="inlineStr"/>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G149" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H149" s="1" t="inlineStr"/>
-      <c r="I149" s="1" t="inlineStr"/>
+      <c r="I149" s="1" t="inlineStr">
+        <is>
+          <t>по месту</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -4851,10 +4767,14 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø250/Ø100</t>
-        </is>
-      </c>
-      <c r="C150" s="1" t="inlineStr"/>
+          <t>Вентилятор канальный малошумный Ø100, 2 скорости, датчик влажности и таймер, IPX4, с обратным клапаном</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D150" s="1" t="inlineStr"/>
       <c r="E150" s="1" t="inlineStr"/>
       <c r="F150" s="1" t="inlineStr">
@@ -4866,7 +4786,11 @@
         <v>2</v>
       </c>
       <c r="H150" s="1" t="inlineStr"/>
-      <c r="I150" s="1" t="inlineStr"/>
+      <c r="I150" s="1" t="inlineStr">
+        <is>
+          <t>ВВ-б1 (с/у б3) — 25/50 м³/ч; ВВ-б2 (помывочная б7) — 60/100 м³/ч; лист 12</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -4874,10 +4798,14 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Тройник круглый оцинкованный Ø250/Ø200</t>
-        </is>
-      </c>
-      <c r="C151" s="1" t="inlineStr"/>
+          <t>Решётка вытяжная потолочная под воздуховод Ø100</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D151" s="1" t="inlineStr"/>
       <c r="E151" s="1" t="inlineStr"/>
       <c r="F151" s="1" t="inlineStr">
@@ -4889,7 +4817,11 @@
         <v>2</v>
       </c>
       <c r="H151" s="1" t="inlineStr"/>
-      <c r="I151" s="1" t="inlineStr"/>
+      <c r="I151" s="1" t="inlineStr">
+        <is>
+          <t>ВВ-б1, ВВ-б2</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -4897,10 +4829,14 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø125/Ø100</t>
-        </is>
-      </c>
-      <c r="C152" s="1" t="inlineStr"/>
+          <t>Решётка наружная с гравитационными жалюзи Ø100</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D152" s="1" t="inlineStr"/>
       <c r="E152" s="1" t="inlineStr"/>
       <c r="F152" s="1" t="inlineStr">
@@ -4909,10 +4845,14 @@
         </is>
       </c>
       <c r="G152" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H152" s="1" t="inlineStr"/>
-      <c r="I152" s="1" t="inlineStr"/>
+      <c r="I152" s="1" t="inlineStr">
+        <is>
+          <t>ВВ-б1, ВВ-б2</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -4920,10 +4860,14 @@
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø160/Ø125</t>
-        </is>
-      </c>
-      <c r="C153" s="1" t="inlineStr"/>
+          <t>Гильза Ø110 для прохода воздуховода Ø100 через наружную стену</t>
+        </is>
+      </c>
+      <c r="C153" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D153" s="1" t="inlineStr"/>
       <c r="E153" s="1" t="inlineStr"/>
       <c r="F153" s="1" t="inlineStr">
@@ -4932,46 +4876,50 @@
         </is>
       </c>
       <c r="G153" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H153" s="1" t="inlineStr"/>
-      <c r="I153" s="1" t="inlineStr"/>
+      <c r="I153" s="1" t="inlineStr">
+        <is>
+          <t>ВВ-б1, ВВ-б2, ось +2,20</t>
+        </is>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
-        <v>147</v>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>Переход круглый оцинкованный Ø200/Ø100</t>
-        </is>
-      </c>
-      <c r="C154" s="1" t="inlineStr"/>
-      <c r="D154" s="1" t="inlineStr"/>
-      <c r="E154" s="1" t="inlineStr"/>
-      <c r="F154" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G154" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H154" s="1" t="inlineStr"/>
-      <c r="I154" s="1" t="inlineStr"/>
+      <c r="A154" s="1" t="inlineStr"/>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>6. Кондиционирование (листы 9–11, 14)</t>
+        </is>
+      </c>
+      <c r="C154" s="1" t="n"/>
+      <c r="D154" s="1" t="n"/>
+      <c r="E154" s="1" t="n"/>
+      <c r="F154" s="1" t="n"/>
+      <c r="G154" s="1" t="n"/>
+      <c r="H154" s="1" t="n"/>
+      <c r="I154" s="1" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø200/Ø150</t>
-        </is>
-      </c>
-      <c r="C155" s="1" t="inlineStr"/>
+          <t>Наружный блок мини-VRV, тепловой насос, Qх = 22,4 кВт, ночной малошумный режим</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="inlineStr">
+        <is>
+          <t>Daikin серии VRV-S, модель — по каталогу Daikin</t>
+        </is>
+      </c>
       <c r="D155" s="1" t="inlineStr"/>
-      <c r="E155" s="1" t="inlineStr"/>
+      <c r="E155" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -4983,68 +4931,96 @@
       <c r="H155" s="1" t="inlineStr"/>
       <c r="I155" s="1" t="inlineStr">
         <is>
-          <t>ВЗ (кухонный зонт)</t>
+          <t>НБ-1, площадка у восточной стены топочной</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø200/Ø160</t>
-        </is>
-      </c>
-      <c r="C156" s="1" t="inlineStr"/>
+          <t>Рама опорная наружного блока высотой 0,3–0,5 м</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D156" s="1" t="inlineStr"/>
       <c r="E156" s="1" t="inlineStr"/>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G156" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H156" s="1" t="inlineStr"/>
-      <c r="I156" s="1" t="inlineStr"/>
+      <c r="I156" s="1" t="inlineStr">
+        <is>
+          <t>НБ-1, лист 14</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø250/Ø160</t>
-        </is>
-      </c>
-      <c r="C157" s="1" t="inlineStr"/>
+          <t>Внутренний блок канальный тонкий, Qх = 5,6 кВт, ≈900 м³/ч</t>
+        </is>
+      </c>
+      <c r="C157" s="1" t="inlineStr">
+        <is>
+          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+        </is>
+      </c>
       <c r="D157" s="1" t="inlineStr"/>
-      <c r="E157" s="1" t="inlineStr"/>
+      <c r="E157" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G157" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H157" s="1" t="inlineStr"/>
-      <c r="I157" s="1" t="inlineStr"/>
+      <c r="I157" s="1" t="inlineStr">
+        <is>
+          <t>К-1 (1.10), К-2 (1.10)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Переход круглый оцинкованный Ø250/Ø200</t>
-        </is>
-      </c>
-      <c r="C158" s="1" t="inlineStr"/>
+          <t>Внутренний блок канальный тонкий, Qх = 3,6 кВт, ≈600 м³/ч</t>
+        </is>
+      </c>
+      <c r="C158" s="1" t="inlineStr">
+        <is>
+          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+        </is>
+      </c>
       <c r="D158" s="1" t="inlineStr"/>
-      <c r="E158" s="1" t="inlineStr"/>
+      <c r="E158" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -5054,55 +5030,67 @@
         <v>1</v>
       </c>
       <c r="H158" s="1" t="inlineStr"/>
-      <c r="I158" s="1" t="inlineStr"/>
+      <c r="I158" s="1" t="inlineStr">
+        <is>
+          <t>К-3 (1.11)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Регулятор расхода воздуха (ирисовый клапан) Ø100</t>
+          <t>Внутренний блок канальный тонкий, Qх = 2,8 кВт, ≈480 м³/ч</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr"/>
-      <c r="E159" s="1" t="inlineStr"/>
+      <c r="E159" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F159" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G159" s="1" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H159" s="1" t="inlineStr"/>
       <c r="I159" s="1" t="inlineStr">
         <is>
-          <t>РР, на ответвлениях</t>
+          <t>К-4 (2.3), К-5 (2.4), К-6 (2.5), К-7 (2.7)</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Регулятор расхода воздуха (ирисовый клапан) Ø125</t>
+          <t>Пульт управления внутренним блоком</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по каталогу Daikin</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr"/>
-      <c r="E160" s="1" t="inlineStr"/>
+      <c r="E160" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F160" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -5114,48 +5102,52 @@
       <c r="H160" s="1" t="inlineStr"/>
       <c r="I160" s="1" t="inlineStr">
         <is>
-          <t>РР, на ответвлениях</t>
+          <t>тип — по решению Заказчика</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Регулятор расхода воздуха (ирисовый клапан) Ø160</t>
+          <t>Разветвитель фреоновый REFNET</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по каталогу Daikin</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr"/>
-      <c r="E161" s="1" t="inlineStr"/>
+      <c r="E161" s="1" t="inlineStr">
+        <is>
+          <t>Daikin</t>
+        </is>
+      </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G161" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H161" s="1" t="inlineStr"/>
       <c r="I161" s="1" t="inlineStr">
         <is>
-          <t>РР, на ответвлениях</t>
+          <t>Р1…Р6</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Диффузор щелевой (линейный) приточный в торце подшивки, L=600 мм, с камерой статического давления, присоединение Ø125, расход 70 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Труба медная отожжённая для холодильной техники Ø6,35 мм</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -5167,26 +5159,26 @@
       <c r="E162" s="1" t="inlineStr"/>
       <c r="F162" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G162" s="1" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H162" s="1" t="inlineStr"/>
       <c r="I162" s="1" t="inlineStr">
         <is>
-          <t>1.10 — 3 шт.</t>
+          <t>жидкость</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Диффузор потолочный приточный с камерой статического давления, присоединение Ø100, расход 30/60 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Труба медная отожжённая для холодильной техники Ø9,52 мм</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -5198,26 +5190,26 @@
       <c r="E163" s="1" t="inlineStr"/>
       <c r="F163" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G163" s="1" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H163" s="1" t="inlineStr"/>
       <c r="I163" s="1" t="inlineStr">
         <is>
-          <t>1.11 — 2 шт., 2.2</t>
+          <t>жидкость</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Решётка приточная настенная с регулирующим клапаном, на камере статического давления (КСД) с круглым патрубком, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Труба медная отожжённая для холодильной техники Ø12,70 мм</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -5229,26 +5221,26 @@
       <c r="E164" s="1" t="inlineStr"/>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G164" s="1" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H164" s="1" t="inlineStr"/>
       <c r="I164" s="1" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>газ</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø100, расход 40/50/60 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Труба медная отожжённая для холодильной техники Ø15,88 мм</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
@@ -5260,26 +5252,26 @@
       <c r="E165" s="1" t="inlineStr"/>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G165" s="1" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="H165" s="1" t="inlineStr"/>
       <c r="I165" s="1" t="inlineStr">
         <is>
-          <t>1.4, 1.3, 2.6</t>
+          <t>газ</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Решётка (диффузор) вытяжная потолочная с камерой статического давления, присоединение Ø125, расход 75/90 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Труба медная отожжённая для холодильной техники Ø19,05 мм</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -5291,26 +5283,26 @@
       <c r="E166" s="1" t="inlineStr"/>
       <c r="F166" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G166" s="1" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H166" s="1" t="inlineStr"/>
       <c r="I166" s="1" t="inlineStr">
         <is>
-          <t>2.9, 2.8, 2.1</t>
+          <t>газ</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, на камере статического давления (КСД) с круглым патрубком, присоединение Ø100, расход 30 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø6,35, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
@@ -5322,26 +5314,22 @@
       <c r="E167" s="1" t="inlineStr"/>
       <c r="F167" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G167" s="1" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H167" s="1" t="inlineStr"/>
-      <c r="I167" s="1" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
+      <c r="I167" s="1" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, на камере статического давления (КСД) с круглым патрубком, присоединение Ø125, расход 90 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø9,52, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
@@ -5353,26 +5341,22 @@
       <c r="E168" s="1" t="inlineStr"/>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G168" s="1" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="H168" s="1" t="inlineStr"/>
-      <c r="I168" s="1" t="inlineStr">
-        <is>
-          <t>1.10 (кухня)</t>
-        </is>
-      </c>
+      <c r="I168" s="1" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная с регулирующим клапаном, на камере статического давления (КСД) с круглым патрубком, присоединение Ø160, расход 120 м³/ч; типоразмер — по расходу, по каталогу</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø12,70, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -5384,26 +5368,22 @@
       <c r="E169" s="1" t="inlineStr"/>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G169" s="1" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H169" s="1" t="inlineStr"/>
-      <c r="I169" s="1" t="inlineStr">
-        <is>
-          <t>1.10 (верх 2-го света)</t>
-        </is>
-      </c>
+      <c r="I169" s="1" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Решётка наружная воздухозаборная 500×400, низ +2,600</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø15,88, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -5415,26 +5395,22 @@
       <c r="E170" s="1" t="inlineStr"/>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G170" s="1" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H170" s="1" t="inlineStr"/>
-      <c r="I170" s="1" t="inlineStr">
-        <is>
-          <t>Н1, восточная стена топочной</t>
-        </is>
-      </c>
+      <c r="I170" s="1" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Оголовок (зонт) воздуховода Ø250 выше кровли</t>
+          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø19,05, толщина — по паспорту Daikin</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -5446,64 +5422,58 @@
       <c r="E171" s="1" t="inlineStr"/>
       <c r="F171" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G171" s="1" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H171" s="1" t="inlineStr"/>
-      <c r="I171" s="1" t="inlineStr">
-        <is>
-          <t>выброс П1, В2 (Ш-2)</t>
-        </is>
-      </c>
+      <c r="I171" s="1" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Оголовок (зонт) воздуховода Ø200 выше кровли</t>
+          <t>Хладагент для дозаправки (тип — по паспорту НБ-1)</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
         <is>
-          <t>или аналог</t>
+          <t>по паспорту НБ-1</t>
         </is>
       </c>
       <c r="D172" s="1" t="inlineStr"/>
       <c r="E172" s="1" t="inlineStr"/>
       <c r="F172" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G172" s="1" t="n">
-        <v>1</v>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="G172" s="1" t="inlineStr">
+        <is>
+          <t>2,15</t>
+        </is>
       </c>
       <c r="H172" s="1" t="inlineStr"/>
       <c r="I172" s="1" t="inlineStr">
         <is>
-          <t>ВЗ (кухонный зонт), шахта над мангалом 1.12</t>
+          <t>по расчёту, уточнить при пуске</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная настенная под воздуховод Ø250 (вытяжка топочной, естественная)</t>
-        </is>
-      </c>
-      <c r="C173" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Гильза стальная для прохода фреонопроводов и дренажа через наружную стену и перекрытие</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="inlineStr"/>
       <c r="D173" s="1" t="inlineStr"/>
       <c r="E173" s="1" t="inlineStr"/>
       <c r="F173" s="1" t="inlineStr">
@@ -5512,22 +5482,22 @@
         </is>
       </c>
       <c r="G173" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H173" s="1" t="inlineStr"/>
       <c r="I173" s="1" t="inlineStr">
         <is>
-          <t>В2, 188 м³/ч</t>
+          <t>стена топочной, Ш-1</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Решётка переточная в низу наружной двери топочной, живое сечение не менее 0,08 м²</t>
+          <t>Диффузор щелевой блока К в торце подшивки, L=1000 мм</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -5543,22 +5513,22 @@
         </is>
       </c>
       <c r="G174" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H174" s="1" t="inlineStr"/>
       <c r="I174" s="1" t="inlineStr">
         <is>
-          <t>ПН, 282 м³/ч</t>
+          <t>К-1, К-2</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Решётка вентиляционная наружная 400×200</t>
+          <t>Диффузор щелевой блока К в торце подшивки, L=1100 мм</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
@@ -5574,25 +5544,29 @@
         </is>
       </c>
       <c r="G175" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H175" s="1" t="inlineStr"/>
       <c r="I175" s="1" t="inlineStr">
         <is>
-          <t>гараж 1.5: приток внизу, вытяжка вверху</t>
+          <t>К-3</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Зонт кухонный над плитой 500–600 м³/ч, располагаемое давление не менее 200 Па при 600 м³/ч</t>
-        </is>
-      </c>
-      <c r="C176" s="1" t="inlineStr"/>
+          <t>Камера статического давления (КСД) щелевого диффузора блока К, переходная от фланца блока, с выравнивающей перфорированной решёткой, в теплоизоляции 10 мм</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D176" s="1" t="inlineStr"/>
       <c r="E176" s="1" t="inlineStr"/>
       <c r="F176" s="1" t="inlineStr">
@@ -5601,22 +5575,22 @@
         </is>
       </c>
       <c r="G176" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H176" s="1" t="inlineStr"/>
       <c r="I176" s="1" t="inlineStr">
         <is>
-          <t>ВЗ, поставка Заказчика</t>
+          <t>К-1 — L=1000, глуб. 240, К-2 — L=1000, глуб. 240, К-3 — L=1100, глуб. 350</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Клапан обратный Ø150</t>
+          <t>Решётка-люк рециркуляции потолочная съёмная 600×600 под блоком К (забор воздуха снизу)</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -5632,22 +5606,22 @@
         </is>
       </c>
       <c r="G177" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H177" s="1" t="inlineStr"/>
       <c r="I177" s="1" t="inlineStr">
         <is>
-          <t>ВЗ, на патрубке зонта</t>
+          <t>К-1…К-3, вместо люка 600×600</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Гильза для прохода воздуховода Ø200 в изоляции через наружную стену (под отверстие Ø320)</t>
+          <t>Решётка щелевая настенная 800×150 с регулированием (подача К и свежего воздуха П1)</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -5663,22 +5637,22 @@
         </is>
       </c>
       <c r="G178" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H178" s="1" t="inlineStr"/>
       <c r="I178" s="1" t="inlineStr">
         <is>
-          <t>ВЗ, сквозь стену на +3,400</t>
+          <t>ЩП, спальни 2.3–2.5, 2.7</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Клапан компенсации Ø200 с электроприводом, сблокирован с ВЗ, в наружной стене с решёткой</t>
+          <t>Камера статического давления (КСД) для решётки 800×150, подача, с выравнивающей перфорированной решёткой, в теплоизоляции 10 мм; присоединение — фланец блока (К-4…К-6) или 250×150 (К-7), боковой патрубок Ø100 свежего воздуха П1</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -5690,26 +5664,26 @@
       <c r="E179" s="1" t="inlineStr"/>
       <c r="F179" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G179" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H179" s="1" t="inlineStr"/>
       <c r="I179" s="1" t="inlineStr">
         <is>
-          <t>КК</t>
+          <t>КСД у ЩП</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Теплоизоляция воздуховодов рулонная толщиной 25 мм с паробарьером (фольга), класс горючести — по СП 60</t>
+          <t>Решётка щелевая настенная 800×150 с регулированием (возврат)</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -5721,26 +5695,26 @@
       <c r="E180" s="1" t="inlineStr"/>
       <c r="F180" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G180" s="1" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H180" s="1" t="inlineStr"/>
       <c r="I180" s="1" t="inlineStr">
         <is>
-          <t>Н и выброс П1 Ø250</t>
+          <t>ЩВ, спальни 2.3–2.5, 2.7</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Теплоизоляция воздуховода Ø200 из минеральной ваты, негорючая (НГ), толщина 50 мм, кашированная фольгой</t>
+          <t>Камера статического давления (КСД) для решётки 800×150, возврат, глубиной 220 мм, патрубок 250×150</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -5752,28 +5726,26 @@
       <c r="E181" s="1" t="inlineStr"/>
       <c r="F181" s="1" t="inlineStr">
         <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G181" s="1" t="inlineStr">
-        <is>
-          <t>6,8</t>
-        </is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G181" s="1" t="n">
+        <v>4</v>
       </c>
       <c r="H181" s="1" t="inlineStr"/>
       <c r="I181" s="1" t="inlineStr">
         <is>
-          <t>ВЗ: холодная шахта, рядом дымоход мангала — только НГ</t>
+          <t>КСД у ЩВ</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Крепления воздуховодов: подвесы, хомуты с уплотнителем, шпильки, профиль</t>
+          <t>Воздуховод прямоугольный из оцинкованной стали 250×150</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr"/>
@@ -5781,33 +5753,29 @@
       <c r="E182" s="1" t="inlineStr"/>
       <c r="F182" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G182" s="1" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H182" s="1" t="inlineStr"/>
       <c r="I182" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>блоки К-4…К-7</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Вентилятор канальный малошумный Ø100, 2 скорости, датчик влажности и таймер, IPX4, с обратным клапаном</t>
-        </is>
-      </c>
-      <c r="C183" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 90° прямоугольный оцинкованный 250×150</t>
+        </is>
+      </c>
+      <c r="C183" s="1" t="inlineStr"/>
       <c r="D183" s="1" t="inlineStr"/>
       <c r="E183" s="1" t="inlineStr"/>
       <c r="F183" s="1" t="inlineStr">
@@ -5816,29 +5784,25 @@
         </is>
       </c>
       <c r="G183" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H183" s="1" t="inlineStr"/>
       <c r="I183" s="1" t="inlineStr">
         <is>
-          <t>ВВ-б1 (с/у б3) — 25/50 м³/ч; ВВ-б2 (помывочная б7) — 60/100 м³/ч; лист 12</t>
+          <t>блоки К-4…К-7</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Решётка вытяжная потолочная под воздуховод Ø100</t>
-        </is>
-      </c>
-      <c r="C184" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 45° круглый оцинкованный Ø250</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="inlineStr"/>
       <c r="D184" s="1" t="inlineStr"/>
       <c r="E184" s="1" t="inlineStr"/>
       <c r="F184" s="1" t="inlineStr">
@@ -5847,29 +5811,25 @@
         </is>
       </c>
       <c r="G184" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H184" s="1" t="inlineStr"/>
       <c r="I184" s="1" t="inlineStr">
         <is>
-          <t>ВВ-б1, ВВ-б2</t>
+          <t>обходы пересечений, лист 11</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Решётка наружная с гравитационными жалюзи Ø100</t>
-        </is>
-      </c>
-      <c r="C185" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 45° круглый оцинкованный Ø200</t>
+        </is>
+      </c>
+      <c r="C185" s="1" t="inlineStr"/>
       <c r="D185" s="1" t="inlineStr"/>
       <c r="E185" s="1" t="inlineStr"/>
       <c r="F185" s="1" t="inlineStr">
@@ -5883,24 +5843,20 @@
       <c r="H185" s="1" t="inlineStr"/>
       <c r="I185" s="1" t="inlineStr">
         <is>
-          <t>ВВ-б1, ВВ-б2</t>
+          <t>обходы пересечений, лист 11</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Гильза Ø110 для прохода воздуховода Ø100 через наружную стену</t>
-        </is>
-      </c>
-      <c r="C186" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 45° круглый оцинкованный Ø160</t>
+        </is>
+      </c>
+      <c r="C186" s="1" t="inlineStr"/>
       <c r="D186" s="1" t="inlineStr"/>
       <c r="E186" s="1" t="inlineStr"/>
       <c r="F186" s="1" t="inlineStr">
@@ -5909,29 +5865,41 @@
         </is>
       </c>
       <c r="G186" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H186" s="1" t="inlineStr"/>
       <c r="I186" s="1" t="inlineStr">
         <is>
-          <t>ВВ-б1, ВВ-б2, ось +2,20</t>
+          <t>обходы пересечений, лист 11</t>
         </is>
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="inlineStr"/>
-      <c r="B187" s="3" t="inlineStr">
-        <is>
-          <t>6. Кондиционирование (листы 9–11, 14)</t>
-        </is>
-      </c>
-      <c r="C187" s="1" t="n"/>
-      <c r="D187" s="1" t="n"/>
-      <c r="E187" s="1" t="n"/>
-      <c r="F187" s="1" t="n"/>
-      <c r="G187" s="1" t="n"/>
-      <c r="H187" s="1" t="n"/>
-      <c r="I187" s="1" t="n"/>
+      <c r="A187" s="1" t="n">
+        <v>179</v>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Отвод 45° круглый оцинкованный Ø125</t>
+        </is>
+      </c>
+      <c r="C187" s="1" t="inlineStr"/>
+      <c r="D187" s="1" t="inlineStr"/>
+      <c r="E187" s="1" t="inlineStr"/>
+      <c r="F187" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G187" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="H187" s="1" t="inlineStr"/>
+      <c r="I187" s="1" t="inlineStr">
+        <is>
+          <t>обходы пересечений, лист 11</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -5939,32 +5907,24 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Наружный блок мини-VRV, тепловой насос, Qх = 22,4 кВт, ночной малошумный режим</t>
-        </is>
-      </c>
-      <c r="C188" s="1" t="inlineStr">
-        <is>
-          <t>Daikin серии VRV-S, модель — по каталогу Daikin</t>
-        </is>
-      </c>
+          <t>Отвод 45° круглый оцинкованный Ø100</t>
+        </is>
+      </c>
+      <c r="C188" s="1" t="inlineStr"/>
       <c r="D188" s="1" t="inlineStr"/>
-      <c r="E188" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E188" s="1" t="inlineStr"/>
       <c r="F188" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G188" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H188" s="1" t="inlineStr"/>
       <c r="I188" s="1" t="inlineStr">
         <is>
-          <t>НБ-1, площадка у восточной стены топочной</t>
+          <t>обходы пересечений, лист 11</t>
         </is>
       </c>
     </row>
@@ -5974,19 +5934,15 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Рама опорная наружного блока высотой 0,3–0,5 м</t>
-        </is>
-      </c>
-      <c r="C189" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод прямоугольный из оцинкованной стали 150×100</t>
+        </is>
+      </c>
+      <c r="C189" s="1" t="inlineStr"/>
       <c r="D189" s="1" t="inlineStr"/>
       <c r="E189" s="1" t="inlineStr"/>
       <c r="F189" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G189" s="1" t="n">
@@ -5995,7 +5951,7 @@
       <c r="H189" s="1" t="inlineStr"/>
       <c r="I189" s="1" t="inlineStr">
         <is>
-          <t>НБ-1, лист 14</t>
+          <t>В Ø125 под П, П-2</t>
         </is>
       </c>
     </row>
@@ -6005,20 +5961,12 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок канальный тонкий, Qх = 5,6 кВт, ≈900 м³/ч</t>
-        </is>
-      </c>
-      <c r="C190" s="1" t="inlineStr">
-        <is>
-          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
-        </is>
-      </c>
+          <t>Переход оцинкованный Ø125 / 150×100</t>
+        </is>
+      </c>
+      <c r="C190" s="1" t="inlineStr"/>
       <c r="D190" s="1" t="inlineStr"/>
-      <c r="E190" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E190" s="1" t="inlineStr"/>
       <c r="F190" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
@@ -6030,7 +5978,7 @@
       <c r="H190" s="1" t="inlineStr"/>
       <c r="I190" s="1" t="inlineStr">
         <is>
-          <t>К-1 (1.10), К-2 (1.10)</t>
+          <t>В Ø125 под П, П-2</t>
         </is>
       </c>
     </row>
@@ -6040,32 +5988,28 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок канальный тонкий, Qх = 3,6 кВт, ≈600 м³/ч</t>
+          <t>Теплоизоляция из вспененного каучука 10 мм, самоклеящаяся, для КСД и воздуховодов подачи блоков К</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D191" s="1" t="inlineStr"/>
-      <c r="E191" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E191" s="1" t="inlineStr"/>
       <c r="F191" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G191" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H191" s="1" t="inlineStr"/>
       <c r="I191" s="1" t="inlineStr">
         <is>
-          <t>К-3 (1.11)</t>
+          <t>КСД К-1…К-3 и ЩП, подача К-7</t>
         </is>
       </c>
     </row>
@@ -6075,32 +6019,28 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Внутренний блок канальный тонкий, Qх = 2,8 кВт, ≈480 м³/ч</t>
+          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
         <is>
-          <t>Daikin серии FXDQ, типоразмер — по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D192" s="1" t="inlineStr"/>
-      <c r="E192" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E192" s="1" t="inlineStr"/>
       <c r="F192" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G192" s="1" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="H192" s="1" t="inlineStr"/>
       <c r="I192" s="1" t="inlineStr">
         <is>
-          <t>К-4 (2.3), К-5 (2.4), К-6 (2.5), К-7 (2.7)</t>
+          <t>дренаж конденсата К-1…К-7</t>
         </is>
       </c>
     </row>
@@ -6110,32 +6050,28 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Пульт управления внутренним блоком</t>
+          <t>Отвод ПП Ø32 (45°/90°)</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t>по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr"/>
-      <c r="E193" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E193" s="1" t="inlineStr"/>
       <c r="F193" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G193" s="1" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H193" s="1" t="inlineStr"/>
       <c r="I193" s="1" t="inlineStr">
         <is>
-          <t>тип — по решению Заказчика</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
@@ -6145,34 +6081,26 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Разветвитель фреоновый REFNET</t>
+          <t>Тройник ПП Ø32</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t>по каталогу Daikin</t>
+          <t>или аналог</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr"/>
-      <c r="E194" s="1" t="inlineStr">
-        <is>
-          <t>Daikin</t>
-        </is>
-      </c>
+      <c r="E194" s="1" t="inlineStr"/>
       <c r="F194" s="1" t="inlineStr">
         <is>
           <t>шт.</t>
         </is>
       </c>
       <c r="G194" s="1" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H194" s="1" t="inlineStr"/>
-      <c r="I194" s="1" t="inlineStr">
-        <is>
-          <t>Р1…Р6</t>
-        </is>
-      </c>
+      <c r="I194" s="1" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -6180,991 +6108,30 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Труба медная отожжённая для холодильной техники Ø6,35 мм</t>
-        </is>
-      </c>
-      <c r="C195" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
+        </is>
+      </c>
+      <c r="C195" s="1" t="inlineStr"/>
       <c r="D195" s="1" t="inlineStr"/>
       <c r="E195" s="1" t="inlineStr"/>
       <c r="F195" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>компл.</t>
         </is>
       </c>
       <c r="G195" s="1" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H195" s="1" t="inlineStr"/>
       <c r="I195" s="1" t="inlineStr">
         <is>
-          <t>жидкость</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="1" t="n">
-        <v>188</v>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>Труба медная отожжённая для холодильной техники Ø9,52 мм</t>
-        </is>
-      </c>
-      <c r="C196" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D196" s="1" t="inlineStr"/>
-      <c r="E196" s="1" t="inlineStr"/>
-      <c r="F196" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G196" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="H196" s="1" t="inlineStr"/>
-      <c r="I196" s="1" t="inlineStr">
-        <is>
-          <t>жидкость</t>
+          <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
-        <v>189</v>
-      </c>
-      <c r="B197" s="2" t="inlineStr">
-        <is>
-          <t>Труба медная отожжённая для холодильной техники Ø12,70 мм</t>
-        </is>
-      </c>
-      <c r="C197" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D197" s="1" t="inlineStr"/>
-      <c r="E197" s="1" t="inlineStr"/>
-      <c r="F197" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G197" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="H197" s="1" t="inlineStr"/>
-      <c r="I197" s="1" t="inlineStr">
-        <is>
-          <t>газ</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="1" t="n">
-        <v>190</v>
-      </c>
-      <c r="B198" s="2" t="inlineStr">
-        <is>
-          <t>Труба медная отожжённая для холодильной техники Ø15,88 мм</t>
-        </is>
-      </c>
-      <c r="C198" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D198" s="1" t="inlineStr"/>
-      <c r="E198" s="1" t="inlineStr"/>
-      <c r="F198" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G198" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="H198" s="1" t="inlineStr"/>
-      <c r="I198" s="1" t="inlineStr">
-        <is>
-          <t>газ</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="1" t="n">
-        <v>191</v>
-      </c>
-      <c r="B199" s="2" t="inlineStr">
-        <is>
-          <t>Труба медная отожжённая для холодильной техники Ø19,05 мм</t>
-        </is>
-      </c>
-      <c r="C199" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D199" s="1" t="inlineStr"/>
-      <c r="E199" s="1" t="inlineStr"/>
-      <c r="F199" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G199" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="H199" s="1" t="inlineStr"/>
-      <c r="I199" s="1" t="inlineStr">
-        <is>
-          <t>газ</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="1" t="n">
-        <v>192</v>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø6,35, толщина — по паспорту Daikin</t>
-        </is>
-      </c>
-      <c r="C200" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D200" s="1" t="inlineStr"/>
-      <c r="E200" s="1" t="inlineStr"/>
-      <c r="F200" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G200" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="H200" s="1" t="inlineStr"/>
-      <c r="I200" s="1" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="1" t="n">
-        <v>193</v>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø9,52, толщина — по паспорту Daikin</t>
-        </is>
-      </c>
-      <c r="C201" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D201" s="1" t="inlineStr"/>
-      <c r="E201" s="1" t="inlineStr"/>
-      <c r="F201" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G201" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="H201" s="1" t="inlineStr"/>
-      <c r="I201" s="1" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="1" t="n">
-        <v>194</v>
-      </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø12,70, толщина — по паспорту Daikin</t>
-        </is>
-      </c>
-      <c r="C202" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D202" s="1" t="inlineStr"/>
-      <c r="E202" s="1" t="inlineStr"/>
-      <c r="F202" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G202" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="H202" s="1" t="inlineStr"/>
-      <c r="I202" s="1" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="1" t="n">
-        <v>195</v>
-      </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø15,88, толщина — по паспорту Daikin</t>
-        </is>
-      </c>
-      <c r="C203" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D203" s="1" t="inlineStr"/>
-      <c r="E203" s="1" t="inlineStr"/>
-      <c r="F203" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G203" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="H203" s="1" t="inlineStr"/>
-      <c r="I203" s="1" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="1" t="n">
-        <v>196</v>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>Трубка теплоизоляционная из вспененного каучука для медной трубы Ø19,05, толщина — по паспорту Daikin</t>
-        </is>
-      </c>
-      <c r="C204" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D204" s="1" t="inlineStr"/>
-      <c r="E204" s="1" t="inlineStr"/>
-      <c r="F204" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G204" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="H204" s="1" t="inlineStr"/>
-      <c r="I204" s="1" t="inlineStr"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="1" t="n">
-        <v>197</v>
-      </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>Хладагент для дозаправки (тип — по паспорту НБ-1)</t>
-        </is>
-      </c>
-      <c r="C205" s="1" t="inlineStr">
-        <is>
-          <t>по паспорту НБ-1</t>
-        </is>
-      </c>
-      <c r="D205" s="1" t="inlineStr"/>
-      <c r="E205" s="1" t="inlineStr"/>
-      <c r="F205" s="1" t="inlineStr">
-        <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="G205" s="1" t="inlineStr">
-        <is>
-          <t>2,15</t>
-        </is>
-      </c>
-      <c r="H205" s="1" t="inlineStr"/>
-      <c r="I205" s="1" t="inlineStr">
-        <is>
-          <t>по расчёту, уточнить при пуске</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" s="1" t="n">
-        <v>198</v>
-      </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>Гильза стальная для прохода фреонопроводов и дренажа через наружную стену и перекрытие</t>
-        </is>
-      </c>
-      <c r="C206" s="1" t="inlineStr"/>
-      <c r="D206" s="1" t="inlineStr"/>
-      <c r="E206" s="1" t="inlineStr"/>
-      <c r="F206" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G206" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H206" s="1" t="inlineStr"/>
-      <c r="I206" s="1" t="inlineStr">
-        <is>
-          <t>стена топочной, Ш-1</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" s="1" t="n">
-        <v>199</v>
-      </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>Диффузор щелевой блока К в торце подшивки, L=1000 мм</t>
-        </is>
-      </c>
-      <c r="C207" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D207" s="1" t="inlineStr"/>
-      <c r="E207" s="1" t="inlineStr"/>
-      <c r="F207" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G207" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H207" s="1" t="inlineStr"/>
-      <c r="I207" s="1" t="inlineStr">
-        <is>
-          <t>К-1, К-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>Диффузор щелевой блока К в торце подшивки, L=1100 мм</t>
-        </is>
-      </c>
-      <c r="C208" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D208" s="1" t="inlineStr"/>
-      <c r="E208" s="1" t="inlineStr"/>
-      <c r="F208" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G208" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H208" s="1" t="inlineStr"/>
-      <c r="I208" s="1" t="inlineStr">
-        <is>
-          <t>К-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="1" t="n">
-        <v>201</v>
-      </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>Камера статического давления (КСД) щелевого диффузора блока К, переходная от фланца блока, с выравнивающей перфорированной решёткой, в теплоизоляции 10 мм</t>
-        </is>
-      </c>
-      <c r="C209" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D209" s="1" t="inlineStr"/>
-      <c r="E209" s="1" t="inlineStr"/>
-      <c r="F209" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G209" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H209" s="1" t="inlineStr"/>
-      <c r="I209" s="1" t="inlineStr">
-        <is>
-          <t>К-1 — L=1000, глуб. 240, К-2 — L=1000, глуб. 240, К-3 — L=1100, глуб. 350</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="1" t="n">
-        <v>202</v>
-      </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t>Решётка-люк рециркуляции потолочная съёмная 600×600 под блоком К (забор воздуха снизу)</t>
-        </is>
-      </c>
-      <c r="C210" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D210" s="1" t="inlineStr"/>
-      <c r="E210" s="1" t="inlineStr"/>
-      <c r="F210" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G210" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H210" s="1" t="inlineStr"/>
-      <c r="I210" s="1" t="inlineStr">
-        <is>
-          <t>К-1…К-3, вместо люка 600×600</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="1" t="n">
-        <v>203</v>
-      </c>
-      <c r="B211" s="2" t="inlineStr">
-        <is>
-          <t>Решётка щелевая настенная 800×150 с регулированием (подача К и свежего воздуха П1)</t>
-        </is>
-      </c>
-      <c r="C211" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D211" s="1" t="inlineStr"/>
-      <c r="E211" s="1" t="inlineStr"/>
-      <c r="F211" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G211" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H211" s="1" t="inlineStr"/>
-      <c r="I211" s="1" t="inlineStr">
-        <is>
-          <t>ЩП, спальни 2.3–2.5, 2.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="1" t="n">
-        <v>204</v>
-      </c>
-      <c r="B212" s="2" t="inlineStr">
-        <is>
-          <t>Камера статического давления (КСД) для решётки 800×150, подача, с выравнивающей перфорированной решёткой, в теплоизоляции 10 мм; присоединение — фланец блока (К-4…К-6) или 250×150 (К-7), боковой патрубок Ø100 свежего воздуха П1</t>
-        </is>
-      </c>
-      <c r="C212" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D212" s="1" t="inlineStr"/>
-      <c r="E212" s="1" t="inlineStr"/>
-      <c r="F212" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G212" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H212" s="1" t="inlineStr"/>
-      <c r="I212" s="1" t="inlineStr">
-        <is>
-          <t>КСД у ЩП</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="1" t="n">
-        <v>205</v>
-      </c>
-      <c r="B213" s="2" t="inlineStr">
-        <is>
-          <t>Решётка щелевая настенная 800×150 с регулированием (возврат)</t>
-        </is>
-      </c>
-      <c r="C213" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D213" s="1" t="inlineStr"/>
-      <c r="E213" s="1" t="inlineStr"/>
-      <c r="F213" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G213" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H213" s="1" t="inlineStr"/>
-      <c r="I213" s="1" t="inlineStr">
-        <is>
-          <t>ЩВ, спальни 2.3–2.5, 2.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="1" t="n">
-        <v>206</v>
-      </c>
-      <c r="B214" s="2" t="inlineStr">
-        <is>
-          <t>Камера статического давления (КСД) для решётки 800×150, возврат, глубиной 220 мм, патрубок 250×150</t>
-        </is>
-      </c>
-      <c r="C214" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D214" s="1" t="inlineStr"/>
-      <c r="E214" s="1" t="inlineStr"/>
-      <c r="F214" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G214" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H214" s="1" t="inlineStr"/>
-      <c r="I214" s="1" t="inlineStr">
-        <is>
-          <t>КСД у ЩВ</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="1" t="n">
-        <v>207</v>
-      </c>
-      <c r="B215" s="2" t="inlineStr">
-        <is>
-          <t>Воздуховод прямоугольный из оцинкованной стали 250×150</t>
-        </is>
-      </c>
-      <c r="C215" s="1" t="inlineStr"/>
-      <c r="D215" s="1" t="inlineStr"/>
-      <c r="E215" s="1" t="inlineStr"/>
-      <c r="F215" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G215" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="H215" s="1" t="inlineStr"/>
-      <c r="I215" s="1" t="inlineStr">
-        <is>
-          <t>блоки К-4…К-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="1" t="n">
-        <v>208</v>
-      </c>
-      <c r="B216" s="2" t="inlineStr">
-        <is>
-          <t>Отвод 90° прямоугольный оцинкованный 250×150</t>
-        </is>
-      </c>
-      <c r="C216" s="1" t="inlineStr"/>
-      <c r="D216" s="1" t="inlineStr"/>
-      <c r="E216" s="1" t="inlineStr"/>
-      <c r="F216" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G216" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H216" s="1" t="inlineStr"/>
-      <c r="I216" s="1" t="inlineStr">
-        <is>
-          <t>блоки К-4…К-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="1" t="n">
-        <v>209</v>
-      </c>
-      <c r="B217" s="2" t="inlineStr">
-        <is>
-          <t>Отвод 45° круглый оцинкованный Ø250</t>
-        </is>
-      </c>
-      <c r="C217" s="1" t="inlineStr"/>
-      <c r="D217" s="1" t="inlineStr"/>
-      <c r="E217" s="1" t="inlineStr"/>
-      <c r="F217" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G217" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H217" s="1" t="inlineStr"/>
-      <c r="I217" s="1" t="inlineStr">
-        <is>
-          <t>обходы пересечений, лист 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="1" t="n">
-        <v>210</v>
-      </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t>Отвод 45° круглый оцинкованный Ø200</t>
-        </is>
-      </c>
-      <c r="C218" s="1" t="inlineStr"/>
-      <c r="D218" s="1" t="inlineStr"/>
-      <c r="E218" s="1" t="inlineStr"/>
-      <c r="F218" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G218" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H218" s="1" t="inlineStr"/>
-      <c r="I218" s="1" t="inlineStr">
-        <is>
-          <t>обходы пересечений, лист 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" s="1" t="n">
-        <v>211</v>
-      </c>
-      <c r="B219" s="2" t="inlineStr">
-        <is>
-          <t>Отвод 45° круглый оцинкованный Ø160</t>
-        </is>
-      </c>
-      <c r="C219" s="1" t="inlineStr"/>
-      <c r="D219" s="1" t="inlineStr"/>
-      <c r="E219" s="1" t="inlineStr"/>
-      <c r="F219" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G219" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H219" s="1" t="inlineStr"/>
-      <c r="I219" s="1" t="inlineStr">
-        <is>
-          <t>обходы пересечений, лист 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="1" t="n">
-        <v>212</v>
-      </c>
-      <c r="B220" s="2" t="inlineStr">
-        <is>
-          <t>Отвод 45° круглый оцинкованный Ø125</t>
-        </is>
-      </c>
-      <c r="C220" s="1" t="inlineStr"/>
-      <c r="D220" s="1" t="inlineStr"/>
-      <c r="E220" s="1" t="inlineStr"/>
-      <c r="F220" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G220" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="H220" s="1" t="inlineStr"/>
-      <c r="I220" s="1" t="inlineStr">
-        <is>
-          <t>обходы пересечений, лист 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" s="1" t="n">
-        <v>213</v>
-      </c>
-      <c r="B221" s="2" t="inlineStr">
-        <is>
-          <t>Отвод 45° круглый оцинкованный Ø100</t>
-        </is>
-      </c>
-      <c r="C221" s="1" t="inlineStr"/>
-      <c r="D221" s="1" t="inlineStr"/>
-      <c r="E221" s="1" t="inlineStr"/>
-      <c r="F221" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G221" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="H221" s="1" t="inlineStr"/>
-      <c r="I221" s="1" t="inlineStr">
-        <is>
-          <t>обходы пересечений, лист 11</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="1" t="n">
-        <v>214</v>
-      </c>
-      <c r="B222" s="2" t="inlineStr">
-        <is>
-          <t>Воздуховод прямоугольный из оцинкованной стали 150×100</t>
-        </is>
-      </c>
-      <c r="C222" s="1" t="inlineStr"/>
-      <c r="D222" s="1" t="inlineStr"/>
-      <c r="E222" s="1" t="inlineStr"/>
-      <c r="F222" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G222" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H222" s="1" t="inlineStr"/>
-      <c r="I222" s="1" t="inlineStr">
-        <is>
-          <t>В Ø125 под П, П-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="1" t="n">
-        <v>215</v>
-      </c>
-      <c r="B223" s="2" t="inlineStr">
-        <is>
-          <t>Переход оцинкованный Ø125 / 150×100</t>
-        </is>
-      </c>
-      <c r="C223" s="1" t="inlineStr"/>
-      <c r="D223" s="1" t="inlineStr"/>
-      <c r="E223" s="1" t="inlineStr"/>
-      <c r="F223" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G223" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H223" s="1" t="inlineStr"/>
-      <c r="I223" s="1" t="inlineStr">
-        <is>
-          <t>В Ø125 под П, П-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" s="1" t="n">
-        <v>216</v>
-      </c>
-      <c r="B224" s="2" t="inlineStr">
-        <is>
-          <t>Теплоизоляция из вспененного каучука 10 мм, самоклеящаяся, для КСД и воздуховодов подачи блоков К</t>
-        </is>
-      </c>
-      <c r="C224" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D224" s="1" t="inlineStr"/>
-      <c r="E224" s="1" t="inlineStr"/>
-      <c r="F224" s="1" t="inlineStr">
-        <is>
-          <t>м²</t>
-        </is>
-      </c>
-      <c r="G224" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="H224" s="1" t="inlineStr"/>
-      <c r="I224" s="1" t="inlineStr">
-        <is>
-          <t>КСД К-1…К-3 и ЩП, подача К-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" s="1" t="n">
-        <v>217</v>
-      </c>
-      <c r="B225" s="2" t="inlineStr">
-        <is>
-          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
-        </is>
-      </c>
-      <c r="C225" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D225" s="1" t="inlineStr"/>
-      <c r="E225" s="1" t="inlineStr"/>
-      <c r="F225" s="1" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="G225" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="H225" s="1" t="inlineStr"/>
-      <c r="I225" s="1" t="inlineStr">
-        <is>
-          <t>дренаж конденсата К-1…К-7</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" s="1" t="n">
-        <v>218</v>
-      </c>
-      <c r="B226" s="2" t="inlineStr">
-        <is>
-          <t>Отвод ПП Ø32 (45°/90°)</t>
-        </is>
-      </c>
-      <c r="C226" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D226" s="1" t="inlineStr"/>
-      <c r="E226" s="1" t="inlineStr"/>
-      <c r="F226" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G226" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="H226" s="1" t="inlineStr"/>
-      <c r="I226" s="1" t="inlineStr">
-        <is>
-          <t>по месту</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="1" t="n">
-        <v>219</v>
-      </c>
-      <c r="B227" s="2" t="inlineStr">
-        <is>
-          <t>Тройник ПП Ø32</t>
-        </is>
-      </c>
-      <c r="C227" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
-      <c r="D227" s="1" t="inlineStr"/>
-      <c r="E227" s="1" t="inlineStr"/>
-      <c r="F227" s="1" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="G227" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="H227" s="1" t="inlineStr"/>
-      <c r="I227" s="1" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="1" t="n">
-        <v>220</v>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
-        </is>
-      </c>
-      <c r="C228" s="1" t="inlineStr"/>
-      <c r="D228" s="1" t="inlineStr"/>
-      <c r="E228" s="1" t="inlineStr"/>
-      <c r="F228" s="1" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="G228" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H228" s="1" t="inlineStr"/>
-      <c r="I228" s="1" t="inlineStr">
-        <is>
-          <t>по месту</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr"/>
-      <c r="B230" t="inlineStr">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I197"/>
+  <dimension ref="A1:I200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Решётка щелевая настенная 800×150 с регулированием (подача К и свежего воздуха П1)</t>
+          <t>Решётка щелевая потолочная 800×150 с регулированием и поворотными жалюзи, в подшивке (подача К и свежего воздуха П1)</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -5637,12 +5637,12 @@
         </is>
       </c>
       <c r="G178" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H178" s="1" t="inlineStr"/>
       <c r="I178" s="1" t="inlineStr">
         <is>
-          <t>ЩП, спальни 2.3–2.5, 2.7</t>
+          <t>ЩП, спальни 2.3–2.5</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Камера статического давления (КСД) для решётки 800×150, подача, с выравнивающей перфорированной решёткой, в теплоизоляции 10 мм; присоединение — фланец блока (К-4…К-6) или 250×150 (К-7), боковой патрубок Ø100 свежего воздуха П1</t>
+          <t>Решётка щелевая потолочная 800×150 с регулированием, в подшивке (возврат)</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -5668,12 +5668,12 @@
         </is>
       </c>
       <c r="G179" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H179" s="1" t="inlineStr"/>
       <c r="I179" s="1" t="inlineStr">
         <is>
-          <t>КСД у ЩП</t>
+          <t>ЩВ, спальни 2.3–2.5</t>
         </is>
       </c>
     </row>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Решётка щелевая настенная 800×150 с регулированием (возврат)</t>
+          <t>Камера статического давления (КСД) для щелевой решётки 800×150 в подшивке, высотой 250 мм, с выравнивающей перфорированной решёткой, боковой патрубок 250×150; КСД подачи — в теплоизоляции 10 мм</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -5699,12 +5699,12 @@
         </is>
       </c>
       <c r="G180" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H180" s="1" t="inlineStr"/>
       <c r="I180" s="1" t="inlineStr">
         <is>
-          <t>ЩВ, спальни 2.3–2.5, 2.7</t>
+          <t>ЩП, ЩВ спален 2.3–2.5</t>
         </is>
       </c>
     </row>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Камера статического давления (КСД) для решётки 800×150, возврат, глубиной 220 мм, патрубок 250×150</t>
+          <t>Переход с фланца блока К на воздуховод 250×150, с боковым патрубком Ø100 свежего воздуха П1, в теплоизоляции 10 мм</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -5730,12 +5730,12 @@
         </is>
       </c>
       <c r="G181" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H181" s="1" t="inlineStr"/>
       <c r="I181" s="1" t="inlineStr">
         <is>
-          <t>КСД у ЩВ</t>
+          <t>К-4…К-6</t>
         </is>
       </c>
     </row>
@@ -5745,24 +5745,28 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод прямоугольный из оцинкованной стали 250×150</t>
-        </is>
-      </c>
-      <c r="C182" s="1" t="inlineStr"/>
+          <t>Решётка щелевая настенная 800×150 с регулированием (подача К-7)</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D182" s="1" t="inlineStr"/>
       <c r="E182" s="1" t="inlineStr"/>
       <c r="F182" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G182" s="1" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H182" s="1" t="inlineStr"/>
       <c r="I182" s="1" t="inlineStr">
         <is>
-          <t>блоки К-4…К-7</t>
+          <t>ЩП, спальня 2.7</t>
         </is>
       </c>
     </row>
@@ -5772,10 +5776,14 @@
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Отвод 90° прямоугольный оцинкованный 250×150</t>
-        </is>
-      </c>
-      <c r="C183" s="1" t="inlineStr"/>
+          <t>Решётка щелевая настенная 800×150 с регулированием (возврат К-7)</t>
+        </is>
+      </c>
+      <c r="C183" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D183" s="1" t="inlineStr"/>
       <c r="E183" s="1" t="inlineStr"/>
       <c r="F183" s="1" t="inlineStr">
@@ -5784,12 +5792,12 @@
         </is>
       </c>
       <c r="G183" s="1" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H183" s="1" t="inlineStr"/>
       <c r="I183" s="1" t="inlineStr">
         <is>
-          <t>блоки К-4…К-7</t>
+          <t>ЩВ, спальня 2.7</t>
         </is>
       </c>
     </row>
@@ -5799,10 +5807,14 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Отвод 45° круглый оцинкованный Ø250</t>
-        </is>
-      </c>
-      <c r="C184" s="1" t="inlineStr"/>
+          <t>Камера статического давления (КСД) для настенной решётки 800×150, глубиной 220 мм, патрубок 250×150; КСД подачи — в теплоизоляции 10 мм</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D184" s="1" t="inlineStr"/>
       <c r="E184" s="1" t="inlineStr"/>
       <c r="F184" s="1" t="inlineStr">
@@ -5811,12 +5823,12 @@
         </is>
       </c>
       <c r="G184" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H184" s="1" t="inlineStr"/>
       <c r="I184" s="1" t="inlineStr">
         <is>
-          <t>обходы пересечений, лист 11</t>
+          <t>ЩП, ЩВ спальни 2.7</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5838,7 @@
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Отвод 45° круглый оцинкованный Ø200</t>
+          <t>Воздуховод прямоугольный из оцинкованной стали 250×150</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr"/>
@@ -5834,16 +5846,16 @@
       <c r="E185" s="1" t="inlineStr"/>
       <c r="F185" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G185" s="1" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="H185" s="1" t="inlineStr"/>
       <c r="I185" s="1" t="inlineStr">
         <is>
-          <t>обходы пересечений, лист 11</t>
+          <t>блоки К-4…К-7</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5865,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Отвод 45° круглый оцинкованный Ø160</t>
+          <t>Отвод 90° прямоугольный оцинкованный 250×150</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr"/>
@@ -5865,12 +5877,12 @@
         </is>
       </c>
       <c r="G186" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H186" s="1" t="inlineStr"/>
       <c r="I186" s="1" t="inlineStr">
         <is>
-          <t>обходы пересечений, лист 11</t>
+          <t>блоки К-4…К-7</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5892,7 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Отвод 45° круглый оцинкованный Ø125</t>
+          <t>Отвод 45° круглый оцинкованный Ø250</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr"/>
@@ -5907,7 +5919,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Отвод 45° круглый оцинкованный Ø100</t>
+          <t>Отвод 45° круглый оцинкованный Ø200</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr"/>
@@ -5919,7 +5931,7 @@
         </is>
       </c>
       <c r="G188" s="1" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H188" s="1" t="inlineStr"/>
       <c r="I188" s="1" t="inlineStr">
@@ -5934,7 +5946,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Воздуховод прямоугольный из оцинкованной стали 150×100</t>
+          <t>Отвод 45° круглый оцинкованный Ø160</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr"/>
@@ -5942,16 +5954,16 @@
       <c r="E189" s="1" t="inlineStr"/>
       <c r="F189" s="1" t="inlineStr">
         <is>
-          <t>м</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G189" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H189" s="1" t="inlineStr"/>
       <c r="I189" s="1" t="inlineStr">
         <is>
-          <t>В Ø125 под П, П-2</t>
+          <t>обходы пересечений, лист 11</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5973,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Переход оцинкованный Ø125 / 150×100</t>
+          <t>Отвод 45° круглый оцинкованный Ø125</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr"/>
@@ -5973,12 +5985,12 @@
         </is>
       </c>
       <c r="G190" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H190" s="1" t="inlineStr"/>
       <c r="I190" s="1" t="inlineStr">
         <is>
-          <t>В Ø125 под П, П-2</t>
+          <t>обходы пересечений, лист 11</t>
         </is>
       </c>
     </row>
@@ -5988,28 +6000,24 @@
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Теплоизоляция из вспененного каучука 10 мм, самоклеящаяся, для КСД и воздуховодов подачи блоков К</t>
-        </is>
-      </c>
-      <c r="C191" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Отвод 45° круглый оцинкованный Ø100</t>
+        </is>
+      </c>
+      <c r="C191" s="1" t="inlineStr"/>
       <c r="D191" s="1" t="inlineStr"/>
       <c r="E191" s="1" t="inlineStr"/>
       <c r="F191" s="1" t="inlineStr">
         <is>
-          <t>м²</t>
+          <t>шт.</t>
         </is>
       </c>
       <c r="G191" s="1" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H191" s="1" t="inlineStr"/>
       <c r="I191" s="1" t="inlineStr">
         <is>
-          <t>КСД К-1…К-3 и ЩП, подача К-7</t>
+          <t>обходы пересечений, лист 11</t>
         </is>
       </c>
     </row>
@@ -6019,14 +6027,10 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
-        </is>
-      </c>
-      <c r="C192" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Воздуховод прямоугольный из оцинкованной стали 150×100</t>
+        </is>
+      </c>
+      <c r="C192" s="1" t="inlineStr"/>
       <c r="D192" s="1" t="inlineStr"/>
       <c r="E192" s="1" t="inlineStr"/>
       <c r="F192" s="1" t="inlineStr">
@@ -6035,12 +6039,12 @@
         </is>
       </c>
       <c r="G192" s="1" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="H192" s="1" t="inlineStr"/>
       <c r="I192" s="1" t="inlineStr">
         <is>
-          <t>дренаж конденсата К-1…К-7</t>
+          <t>В Ø125 под П, П-2</t>
         </is>
       </c>
     </row>
@@ -6050,14 +6054,10 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Отвод ПП Ø32 (45°/90°)</t>
-        </is>
-      </c>
-      <c r="C193" s="1" t="inlineStr">
-        <is>
-          <t>или аналог</t>
-        </is>
-      </c>
+          <t>Переход оцинкованный Ø125 / 150×100</t>
+        </is>
+      </c>
+      <c r="C193" s="1" t="inlineStr"/>
       <c r="D193" s="1" t="inlineStr"/>
       <c r="E193" s="1" t="inlineStr"/>
       <c r="F193" s="1" t="inlineStr">
@@ -6066,12 +6066,12 @@
         </is>
       </c>
       <c r="G193" s="1" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H193" s="1" t="inlineStr"/>
       <c r="I193" s="1" t="inlineStr">
         <is>
-          <t>по месту</t>
+          <t>В Ø125 под П, П-2</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Тройник ПП Ø32</t>
+          <t>Теплоизоляция из вспененного каучука 10 мм, самоклеящаяся, для КСД и воздуховодов подачи блоков К</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -6093,14 +6093,18 @@
       <c r="E194" s="1" t="inlineStr"/>
       <c r="F194" s="1" t="inlineStr">
         <is>
-          <t>шт.</t>
+          <t>м²</t>
         </is>
       </c>
       <c r="G194" s="1" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H194" s="1" t="inlineStr"/>
-      <c r="I194" s="1" t="inlineStr"/>
+      <c r="I194" s="1" t="inlineStr">
+        <is>
+          <t>КСД К-1…К-3 и ЩП, переходы, подача К-4…К-7</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -6108,30 +6112,119 @@
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
-        </is>
-      </c>
-      <c r="C195" s="1" t="inlineStr"/>
+          <t>Труба полипропиленовая канализационная Ø32, уклон не менее 0,01 к выпуску</t>
+        </is>
+      </c>
+      <c r="C195" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
       <c r="D195" s="1" t="inlineStr"/>
       <c r="E195" s="1" t="inlineStr"/>
       <c r="F195" s="1" t="inlineStr">
         <is>
-          <t>компл.</t>
+          <t>м</t>
         </is>
       </c>
       <c r="G195" s="1" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="H195" s="1" t="inlineStr"/>
       <c r="I195" s="1" t="inlineStr">
         <is>
+          <t>дренаж конденсата К-1…К-7</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Отвод ПП Ø32 (45°/90°)</t>
+        </is>
+      </c>
+      <c r="C196" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D196" s="1" t="inlineStr"/>
+      <c r="E196" s="1" t="inlineStr"/>
+      <c r="F196" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G196" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H196" s="1" t="inlineStr"/>
+      <c r="I196" s="1" t="inlineStr">
+        <is>
           <t>по месту</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr"/>
-      <c r="B197" t="inlineStr">
+      <c r="A197" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Тройник ПП Ø32</t>
+        </is>
+      </c>
+      <c r="C197" s="1" t="inlineStr">
+        <is>
+          <t>или аналог</t>
+        </is>
+      </c>
+      <c r="D197" s="1" t="inlineStr"/>
+      <c r="E197" s="1" t="inlineStr"/>
+      <c r="F197" s="1" t="inlineStr">
+        <is>
+          <t>шт.</t>
+        </is>
+      </c>
+      <c r="G197" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="H197" s="1" t="inlineStr"/>
+      <c r="I197" s="1" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Крепления фреонопроводов и дренажа (хомуты с уплотнителем, подвесы)</t>
+        </is>
+      </c>
+      <c r="C198" s="1" t="inlineStr"/>
+      <c r="D198" s="1" t="inlineStr"/>
+      <c r="E198" s="1" t="inlineStr"/>
+      <c r="F198" s="1" t="inlineStr">
+        <is>
+          <t>компл.</t>
+        </is>
+      </c>
+      <c r="G198" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" s="1" t="inlineStr"/>
+      <c r="I198" s="1" t="inlineStr">
+        <is>
+          <t>по месту</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
         <is>
           <t>Примечание — Допускается применение оборудования, изделий и материалов других изготовителей с техническими характеристиками не ниже указанных в настоящей спецификации.</t>
         </is>

--- a/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -3020,12 +3020,12 @@
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>≈16,4 м по трассе с подъёмами + 10 %; лист 14</t>
+          <t>≈18,1 м по трассе с подъёмами + 10 %; лист 14</t>
         </is>
       </c>
     </row>

--- a/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -3020,12 +3020,12 @@
         </is>
       </c>
       <c r="G87" s="1" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>≈18,1 м по трассе с подъёмами + 10 %; лист 14</t>
+          <t>≈16,4 м по трассе с подъёмами + 10 %; лист 14</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="G92" s="1" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H92" s="1" t="inlineStr"/>
       <c r="I92" s="1" t="inlineStr">

--- a/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -3025,7 +3025,7 @@
       <c r="H87" s="1" t="inlineStr"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>≈16,4 м по трассе с подъёмами + 10 %; лист 14</t>
+          <t>≈16,6 м по трассе с подъёмами + 10 %; лист 14</t>
         </is>
       </c>
     </row>

--- a/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
+++ b/ovk-dom-banya/release-rd/И05.09.26-ОВ.СО Спецификация оборудования, изделий и материалов.xlsx
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="G36" s="1" t="n">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr">
